--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Swimlane Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$K$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -129,11 +129,44 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +222,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -580,62 +614,58 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Total Active Jobs</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="25" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Automated AI Validations</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="5">
         <f>COUNTA('Job Directory'!A5:A24)</f>
         <v/>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="25" t="n"/>
       <c r="E5" s="5">
         <f>COUNTIF('Job Directory'!F5:F24, "Passed")</f>
         <v/>
       </c>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="F5" s="25" t="n"/>
+    </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Pending Manual Approval</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="25" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Total Revenue Pipeline</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="5">
         <f>COUNTIF('Job Directory'!G5:G24, "Pending")</f>
         <v/>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="25" t="n"/>
       <c r="E8" s="6">
         <f>SUM('Job Directory'!I5:I24)</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
+      <c r="F8" s="25" t="n"/>
+    </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -838,19 +868,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,11 +894,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tracking process flow across 6 standard Camunda BPMN swimlanes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Commercial, Residential &amp; Home Ventilation jobs across 6 BPMN swimlanes</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -881,40 +911,45 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
+          <t>Service Type</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
           <t>Job Category</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Current Swimlane</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>AI Check Status</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Approval Status</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Assigned Tech</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Est. Value ($)</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>BPMN Process ID</t>
         </is>
@@ -928,45 +963,50 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Canterbury Health Trust</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Commercial Inspection</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+          <t>Riccarton Business Park</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>3-Phase Power Distribution</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>5. Electrical Technician</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Mark Stevens</t>
         </is>
       </c>
-      <c r="I5" s="17" t="n">
-        <v>3450</v>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="J5" s="17" t="n">
+        <v>8200</v>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>PROC_COM_01</t>
         </is>
       </c>
     </row>
@@ -978,45 +1018,50 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Apex Retail Group</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
+          <t>Riccarton Business Park</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Switchboard Upgrade</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>2. Service Coordinator</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Sarah Jenkins</t>
         </is>
       </c>
-      <c r="I6" s="20" t="n">
-        <v>8200</v>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
+      <c r="J6" s="20" t="n">
+        <v>6400</v>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>PROC_COM_02</t>
         </is>
       </c>
     </row>
@@ -1028,45 +1073,50 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Riccarton Properties</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>HVAC Wiring &amp; Controls</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+          <t>Papanui Auto Workshop</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Motor Control Centre Repair</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>6. Accounts &amp; Billing</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Mark Stevens</t>
         </is>
       </c>
-      <c r="I7" s="17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="J7" s="17" t="n">
+        <v>11200</v>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>PROC_COM_01</t>
         </is>
       </c>
     </row>
@@ -1078,45 +1128,50 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Christchurch Tech Park</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Data &amp; Fiber Installation</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
+          <t>Papanui Auto Workshop</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Compliance Certification</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>4. AI Validation Layer</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="I8" s="20" t="n">
-        <v>4600</v>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_03</t>
+      <c r="J8" s="20" t="n">
+        <v>3100</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>PROC_COM_03</t>
         </is>
       </c>
     </row>
@@ -1128,45 +1183,50 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>High Street Cafe</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Emergency Lighting Maintenance</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+          <t>Addington Cold Stores</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Refrigeration Wiring</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>5. Electrical Technician</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Dave Wilson</t>
         </is>
       </c>
-      <c r="I9" s="17" t="n">
-        <v>850</v>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="J9" s="17" t="n">
+        <v>5400</v>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>PROC_COM_01</t>
         </is>
       </c>
     </row>
@@ -1178,45 +1238,50 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Southern Logistics</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Warehouse LED Retrofit</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
+          <t>Addington Cold Stores</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Emergency Lighting Maintenance</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>1. Client / Portal</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="I10" s="20" t="n">
-        <v>15400</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
+      <c r="J10" s="20" t="n">
+        <v>850</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>PROC_COM_02</t>
         </is>
       </c>
     </row>
@@ -1228,45 +1293,50 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Merivale Dental Clinic</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>UPS Backup Power Setup</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>3. Central Knowledge Repository</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+          <t>Aidan &amp; Grace Family Home</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Full House Rewire</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>5. Electrical Technician</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Mark Stevens</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>15400</v>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>PROC_RES_01</t>
         </is>
       </c>
     </row>
@@ -1278,45 +1348,50 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>University Student Housing</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>Compliance Certification</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>5. Electrical Technician</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
+          <t>Aidan &amp; Grace Family Home</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Switchboard Safety Upgrade</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>6. Accounts &amp; Billing</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>Dave Wilson</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>6100</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_03</t>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Mark Stevens</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>PROC_RES_02</t>
         </is>
       </c>
     </row>
@@ -1328,45 +1403,50 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Papanui Auto Workshop</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>3-Phase Power Distribution</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+          <t>Halswell Family Home</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>EV Charger Installation</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>2. Service Coordinator</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Sarah Jenkins</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
-        <v>7300</v>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
+      <c r="J13" s="17" t="n">
+        <v>3900</v>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>PROC_RES_01</t>
         </is>
       </c>
     </row>
@@ -1378,45 +1458,50 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Lyttelton Marine Services</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>Generator Control Automation</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>6. Accounts &amp; Billing</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
+          <t>Halswell Family Home</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Smart Lighting Setup</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>3. Central Knowledge Repository</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>Mark Stevens</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>9800</v>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>2750</v>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>PROC_RES_02</t>
         </is>
       </c>
     </row>
@@ -1428,45 +1513,50 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Sydenham Warehousing</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Solar Inverter Maintenance</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+          <t>Merivale Residence</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Solar Panel Wiring</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>4. AI Validation Layer</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="I15" s="17" t="n">
-        <v>3100</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_03</t>
+      <c r="J15" s="17" t="n">
+        <v>8900</v>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>PROC_RES_01</t>
         </is>
       </c>
     </row>
@@ -1478,45 +1568,50 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Fendalton Medical Centre</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Thermal Imaging Audit</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
+          <t>Merivale Residence</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Outdoor Security Lighting</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>5. Electrical Technician</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>Dave Wilson</t>
         </is>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="J16" s="20" t="n">
         <v>1850</v>
       </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>PROC_RES_02</t>
         </is>
       </c>
     </row>
@@ -1528,45 +1623,50 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Avonhead Shopping Centre</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Exterior Security Lighting</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>2. Service Coordinator</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
+          <t>Cashmere Residence</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Heat Pump Installation</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>5. Electrical Technician</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>4200</v>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Dave Wilson</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>PROC_VEN_01</t>
         </is>
       </c>
     </row>
@@ -1578,45 +1678,50 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Hornby Manufacturing</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>Motor Control Centre Repair</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>5. Electrical Technician</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
+          <t>Cashmere Residence</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Ventilation System Service</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>1. Client / Portal</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>Mark Stevens</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>11200</v>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>PROC_VEN_02</t>
         </is>
       </c>
     </row>
@@ -1628,45 +1733,50 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Addington Cold Stores</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Refrigeration Wiring</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>1. Client / Portal</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+          <t>Hornby Residence</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Whole-Home Ventilation System</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>2. Service Coordinator</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>5400</v>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>7300</v>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>PROC_VEN_01</t>
         </is>
       </c>
     </row>
@@ -1678,45 +1788,50 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>St Albans Bakery</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>Oven Control Panel Upgrade</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>3. Central Knowledge Repository</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
+          <t>Hornby Residence</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Bathroom Extraction Fan Upgrade</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>6. Accounts &amp; Billing</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="n">
-        <v>2750</v>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>Mark Stevens</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>950</v>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>PROC_VEN_02</t>
         </is>
       </c>
     </row>
@@ -1728,45 +1843,50 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Cashmere Secondary School</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>PA System Power Integration</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>2. Service Coordinator</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+          <t>Burnside Home</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Heat Recovery Ventilation Install</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>5. Electrical Technician</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>3900</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_03</t>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Dave Wilson</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>6100</v>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>PROC_VEN_01</t>
         </is>
       </c>
     </row>
@@ -1778,169 +1898,75 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Burnside Fitness Centre</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>Sauna Heater Rewiring</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>5. Electrical Technician</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
+          <t>Burnside Home</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Home Ventilation</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Ducted Ventilation Maintenance</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>4. AI Validation Layer</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>Dave Wilson</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="n">
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="n">
         <v>1600</v>
       </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>PROC_VEN_02</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>CDE-2026-019</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Linwood Community Hub</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>EV Charging Station Setup</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>4. AI Validation Layer</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="n">
-        <v>8900</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>CDE-2026-020</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>Halswell Library</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>BMS Sensor Calibrations</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>6. Accounts &amp; Billing</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>Mark Stevens</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>2150</v>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>PROC_ELEC_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Total Pipeline Value</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n"/>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="22">
-        <f>SUM(I5:I24)</f>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="22">
+        <f>SUM(J5:J22)</f>
         <v/>
       </c>
-      <c r="J25" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J24"/>
+  <autoFilter ref="A4:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1975,7 +2001,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A45C8B5C-F46F-0947-BFC8-F9C9F3B5CC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A65AB7-91F5-DC4F-8143-EBA45B9F2C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -139,9 +139,6 @@
     <t>CDE-2026-001</t>
   </si>
   <si>
-    <t>Riccarton Business Park</t>
-  </si>
-  <si>
     <t>Commercial</t>
   </si>
   <si>
@@ -473,6 +470,9 @@
   </si>
   <si>
     <t>Xero / MYOB API Integration</t>
+  </si>
+  <si>
+    <t>Riccarton Business Parks</t>
   </si>
 </sst>
 </file>
@@ -1284,634 +1284,634 @@
         <v>32</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>36</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="J5" s="13">
         <v>8200</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>45</v>
       </c>
       <c r="J6" s="16">
         <v>6400</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="J7" s="13">
         <v>11200</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>54</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="J8" s="16">
         <v>3100</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="I9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J9" s="13">
         <v>5400</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>63</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>64</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="16">
         <v>850</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="D11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="I11" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="J11" s="13">
         <v>15400</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>73</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="I12" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="J12" s="16">
         <v>2150</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="J13" s="13">
         <v>3900</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="E14" s="14" t="s">
         <v>80</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>81</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="I14" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J14" s="16">
         <v>2750</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>85</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="J15" s="13">
         <v>8900</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="I16" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J16" s="16">
         <v>1850</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>93</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="I17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J17" s="13">
         <v>4600</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J18" s="16">
         <v>1250</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="J19" s="13">
         <v>7300</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="I20" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="J20" s="16">
         <v>950</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="12" t="s">
         <v>108</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>109</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="I21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J21" s="13">
         <v>6100</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>111</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>112</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J22" s="16">
         <v>1600</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -1947,29 +1947,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -1977,16 +1977,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -1994,16 +1994,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="E6" s="15" t="s">
         <v>127</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -2011,16 +2011,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -2028,16 +2028,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="E8" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -2045,16 +2045,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.2">
@@ -2062,16 +2062,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="E10" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAF6DDE-EC7A-9E4D-AD97-65769184CE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66620D0-EDA7-F449-B179-B032529BC379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Job Directory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$K$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="103">
   <si>
     <t>Cassidy-Davies Electrical — Operations &amp; Workflow Dashboard</t>
   </si>
@@ -340,15 +340,6 @@
   </si>
   <si>
     <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>CDE-2026-018</t>
-  </si>
-  <si>
-    <t>Ducted Ventilation Maintenance</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
   </si>
   <si>
     <t>Total Pipeline Value</t>
@@ -518,18 +509,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,59 +835,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="E3" s="18" t="s">
+      <c r="C3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="15"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.2">
-      <c r="B4" s="16">
-        <f>COUNTA('Job Directory'!A5:A24)</f>
-        <v>19</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="E4" s="16">
-        <f>COUNTIF('Job Directory'!F5:F24, "Passed")</f>
+      <c r="B4" s="18">
+        <f>COUNTA('Job Directory'!A5:A23)</f>
+        <v>18</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="E4" s="18">
+        <f>COUNTIF('Job Directory'!F5:F23, "Passed")</f>
         <v>0</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="E6" s="18" t="s">
+      <c r="C6" s="17"/>
+      <c r="E6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.2">
-      <c r="B7" s="16">
-        <f>COUNTIF('Job Directory'!G5:G24, "Pending")</f>
+      <c r="B7" s="18">
+        <f>COUNTIF('Job Directory'!G5:G23, "Pending")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="E7" s="14">
-        <f>SUM('Job Directory'!I5:I24)</f>
+      <c r="C7" s="17"/>
+      <c r="E7" s="19">
+        <f>SUM('Job Directory'!I5:I23)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
@@ -919,7 +910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -984,7 +975,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>25</v>
@@ -1019,7 +1010,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>25</v>
@@ -1575,60 +1566,25 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="11">
-        <v>1600</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="13">
-        <f>SUM(J5:J22)</f>
-        <v>91900</v>
-      </c>
-      <c r="K23" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13">
+        <f>SUM(J5:J21)</f>
+        <v>90300</v>
+      </c>
+      <c r="K22" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K22" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:K21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66620D0-EDA7-F449-B179-B032529BC379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD46AE67-0B40-6A4E-92A4-C95A91415942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Job Directory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$I$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
   <si>
     <t>Cassidy-Davies Electrical — Operations &amp; Workflow Dashboard</t>
   </si>
@@ -54,24 +54,6 @@
     <t>Total Revenue Pipeline</t>
   </si>
   <si>
-    <t>1. Client / Portal</t>
-  </si>
-  <si>
-    <t>2. Service Coordinator</t>
-  </si>
-  <si>
-    <t>3. Central Knowledge Repository</t>
-  </si>
-  <si>
-    <t>4. AI Validation Layer</t>
-  </si>
-  <si>
-    <t>5. Electrical Technician</t>
-  </si>
-  <si>
-    <t>6. Accounts &amp; Billing</t>
-  </si>
-  <si>
     <t>Cassidy-Davies Electrical — Active Job Log</t>
   </si>
   <si>
@@ -93,9 +75,6 @@
     <t>Creation Date</t>
   </si>
   <si>
-    <t>Current Swimlane</t>
-  </si>
-  <si>
     <t>AI Check Status</t>
   </si>
   <si>
@@ -108,9 +87,6 @@
     <t>Est. Value ($)</t>
   </si>
   <si>
-    <t>BPMN Process ID</t>
-  </si>
-  <si>
     <t>CDE-2026-001</t>
   </si>
   <si>
@@ -132,9 +108,6 @@
     <t>Mark Stevens</t>
   </si>
   <si>
-    <t>PROC_COM_01</t>
-  </si>
-  <si>
     <t>CDE-2026-002</t>
   </si>
   <si>
@@ -150,9 +123,6 @@
     <t>Sarah Jenkins</t>
   </si>
   <si>
-    <t>PROC_COM_02</t>
-  </si>
-  <si>
     <t>CDE-2026-003</t>
   </si>
   <si>
@@ -180,9 +150,6 @@
     <t>Unassigned</t>
   </si>
   <si>
-    <t>PROC_COM_03</t>
-  </si>
-  <si>
     <t>CDE-2026-005</t>
   </si>
   <si>
@@ -222,9 +189,6 @@
     <t>2026-07-05</t>
   </si>
   <si>
-    <t>PROC_RES_01</t>
-  </si>
-  <si>
     <t>CDE-2026-008</t>
   </si>
   <si>
@@ -234,9 +198,6 @@
     <t>2026-07-19</t>
   </si>
   <si>
-    <t>PROC_RES_02</t>
-  </si>
-  <si>
     <t>CDE-2026-009</t>
   </si>
   <si>
@@ -294,9 +255,6 @@
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>PROC_VEN_01</t>
-  </si>
-  <si>
     <t>CDE-2026-014</t>
   </si>
   <si>
@@ -304,9 +262,6 @@
   </si>
   <si>
     <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>PROC_VEN_02</t>
   </si>
   <si>
     <t>CDE-2026-015</t>
@@ -861,9 +816,9 @@
         <v>18</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="E4" s="18">
-        <f>COUNTIF('Job Directory'!F5:F23, "Passed")</f>
-        <v>0</v>
+      <c r="E4" s="18" t="e">
+        <f>COUNTIF('Job Directory'!#REF!, "Passed")</f>
+        <v>#REF!</v>
       </c>
       <c r="F4" s="17"/>
     </row>
@@ -879,12 +834,12 @@
     </row>
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B7" s="18">
-        <f>COUNTIF('Job Directory'!G5:G23, "Pending")</f>
+        <f>COUNTIF('Job Directory'!F5:F23, "Pending")</f>
         <v>0</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="19">
-        <f>SUM('Job Directory'!I5:I23)</f>
+        <f>SUM('Job Directory'!H5:H23)</f>
         <v>0</v>
       </c>
       <c r="F7" s="17"/>
@@ -910,7 +865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -918,656 +873,546 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="6" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="I5" s="8">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="B6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="I6" s="11">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="8">
-        <v>8200</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="F7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="8">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="B8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="G8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="11">
-        <v>6400</v>
-      </c>
-      <c r="K6" s="9" t="s">
+      <c r="I8" s="11">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="8">
-        <v>11200</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="I9" s="8">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="B10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="F10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="11">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="8">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="11">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="8">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="11">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="11">
-        <v>3100</v>
-      </c>
-      <c r="K8" s="9" t="s">
+      <c r="G15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="8">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="8">
-        <v>5400</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="11">
-        <v>850</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="8">
-        <v>15400</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="11">
-        <v>2150</v>
-      </c>
-      <c r="K12" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="F16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="8">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="8">
-        <v>3900</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2750</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="I18" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="8">
-        <v>8900</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="C19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E19" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="8">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="11">
-        <v>1850</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="B20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="E20" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="F20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="11">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="C21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="8">
-        <v>4600</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+      <c r="F21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="8">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18" s="11">
-        <v>1250</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="8">
-        <v>7300</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="11">
-        <v>950</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="8">
-        <v>6100</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1576,15 +1421,13 @@
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="13">
-        <f>SUM(J5:J21)</f>
+      <c r="I22" s="13">
+        <f>SUM(I5:I21)</f>
         <v>90300</v>
       </c>
-      <c r="K22" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:I21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD46AE67-0B40-6A4E-92A4-C95A91415942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FADE0C7-5A79-594D-9DE7-60E0F05E64A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Job Directory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
   <si>
     <t>Cassidy-Davies Electrical — Operations &amp; Workflow Dashboard</t>
   </si>
@@ -174,19 +174,10 @@
     <t>2026-07-27</t>
   </si>
   <si>
-    <t>CDE-2026-007</t>
-  </si>
-  <si>
     <t>Aidan &amp; Grace Family Home</t>
   </si>
   <si>
     <t>Residential</t>
-  </si>
-  <si>
-    <t>Full House Rewire</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
   </si>
   <si>
     <t>CDE-2026-008</t>
@@ -812,8 +803,8 @@
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B4" s="18">
-        <f>COUNTA('Job Directory'!A5:A23)</f>
-        <v>18</v>
+        <f>COUNTA('Job Directory'!A5:A22)</f>
+        <v>17</v>
       </c>
       <c r="C4" s="17"/>
       <c r="E4" s="18" t="e">
@@ -834,12 +825,12 @@
     </row>
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B7" s="18">
-        <f>COUNTIF('Job Directory'!F5:F23, "Pending")</f>
+        <f>COUNTIF('Job Directory'!F5:F22, "Pending")</f>
         <v>0</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="19">
-        <f>SUM('Job Directory'!H5:H23)</f>
+        <f>SUM('Job Directory'!H5:H22)</f>
         <v>0</v>
       </c>
       <c r="F7" s="17"/>
@@ -865,7 +856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -922,7 +913,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -951,7 +942,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>17</v>
@@ -1092,342 +1083,313 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="8">
-        <v>15400</v>
+      <c r="I11" s="11">
+        <v>2150</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="8">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="C13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="11">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="8">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="8">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="8">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="11">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="I19" s="11">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="8">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="8">
-        <v>8900</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="10" t="s">
+      <c r="H20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="11">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" s="8">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="11">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="8">
-        <v>7300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="11">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="I20" s="8">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="8">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13">
-        <f>SUM(I5:I21)</f>
-        <v>90300</v>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="13">
+        <f>SUM(I5:I20)</f>
+        <v>74900</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:I20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FADE0C7-5A79-594D-9DE7-60E0F05E64A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA587DB-0ACA-9048-B86F-54853822FD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Job Directory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$H$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="83">
   <si>
     <t>Cassidy-Davies Electrical — Operations &amp; Workflow Dashboard</t>
   </si>
@@ -78,9 +78,6 @@
     <t>AI Check Status</t>
   </si>
   <si>
-    <t>Approval Status</t>
-  </si>
-  <si>
     <t>Assigned Tech</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
   </si>
   <si>
     <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>Passed</t>
   </si>
   <si>
     <t>Approved</t>
@@ -826,11 +820,11 @@
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B7" s="18">
         <f>COUNTIF('Job Directory'!F5:F22, "Pending")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="19">
-        <f>SUM('Job Directory'!H5:H22)</f>
+        <f>SUM('Job Directory'!G5:G22)</f>
         <v>0</v>
       </c>
       <c r="F7" s="17"/>
@@ -856,7 +850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -864,22 +858,22 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -904,477 +898,426 @@
       <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="8">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="B6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8">
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="H6" s="11">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="H7" s="8">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="11">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="C8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="E8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="11">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="8">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="11">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="8">
-        <v>11200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="H11" s="11">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="8">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="11">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="11">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="H14" s="8">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="H15" s="11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="8">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="8">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="8">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="11">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="11">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="8">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="11">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="8">
-        <v>8900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="11">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="H19" s="11">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="8">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="11">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="8">
-        <v>7300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="11">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="F20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="8">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="8">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1382,14 +1325,14 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13">
-        <f>SUM(I5:I20)</f>
+      <c r="H21" s="13">
+        <f>SUM(H5:H20)</f>
         <v>74900</v>
       </c>
     </row>
+    <row r="22" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A4:I20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:H20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA587DB-0ACA-9048-B86F-54853822FD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D110B8D4-753B-E144-A712-B57DEEE6ADF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>Creation Date</t>
   </si>
   <si>
-    <t>AI Check Status</t>
-  </si>
-  <si>
     <t>Assigned Tech</t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>Riccarton Business Parks</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -890,36 +890,36 @@
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="H5" s="8">
         <v>8200</v>
@@ -927,25 +927,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="H6" s="11">
         <v>6400</v>
@@ -953,25 +953,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="F7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="H7" s="8">
         <v>11200</v>
@@ -979,25 +979,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="H8" s="11">
         <v>3100</v>
@@ -1005,25 +1005,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="H9" s="8">
         <v>5400</v>
@@ -1031,25 +1031,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="F10" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="11">
         <v>850</v>
@@ -1057,25 +1057,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="F11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="H11" s="11">
         <v>2150</v>
@@ -1083,25 +1083,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="H12" s="8">
         <v>3900</v>
@@ -1109,25 +1109,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="11">
         <v>2750</v>
@@ -1135,25 +1135,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="F14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="H14" s="8">
         <v>8900</v>
@@ -1161,25 +1161,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15" s="11">
         <v>1850</v>
@@ -1187,25 +1187,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="8">
         <v>4600</v>
@@ -1213,25 +1213,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17" s="11">
         <v>1250</v>
@@ -1239,25 +1239,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="F18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="H18" s="8">
         <v>7300</v>
@@ -1265,25 +1265,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="F19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="H19" s="11">
         <v>950</v>
@@ -1291,25 +1291,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>80</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20" s="8">
         <v>6100</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixkwan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D110B8D4-753B-E144-A712-B57DEEE6ADF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86D82AD-8D60-3F49-A3DC-9CED32EB2782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Job Directory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Job Directory'!$A$4:$H$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t>Cassidy-Davies Electrical — Operations &amp; Workflow Dashboard</t>
   </si>
@@ -190,15 +190,6 @@
   </si>
   <si>
     <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>CDE-2026-010</t>
-  </si>
-  <si>
-    <t>Smart Lighting Setup</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
   </si>
   <si>
     <t>CDE-2026-011</t>
@@ -797,8 +788,8 @@
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B4" s="18">
-        <f>COUNTA('Job Directory'!A5:A22)</f>
-        <v>17</v>
+        <f>COUNTA('Job Directory'!A5:A21)</f>
+        <v>16</v>
       </c>
       <c r="C4" s="17"/>
       <c r="E4" s="18" t="e">
@@ -819,12 +810,12 @@
     </row>
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="B7" s="18">
-        <f>COUNTIF('Job Directory'!F5:F22, "Pending")</f>
+        <f>COUNTIF('Job Directory'!F5:F21, "Pending")</f>
         <v>5</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="19">
-        <f>SUM('Job Directory'!G5:G22)</f>
+        <f>SUM('Job Directory'!G5:G21)</f>
         <v>0</v>
       </c>
       <c r="F7" s="17"/>
@@ -850,7 +841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -890,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>12</v>
@@ -904,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>15</v>
@@ -930,7 +921,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>15</v>
@@ -1108,231 +1099,205 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="8">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="C14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="11">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="8">
-        <v>8900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="H17" s="8">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="D18" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="11">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="11">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="8">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="11">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="8">
-        <v>7300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="11">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="H19" s="8">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="8">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13">
-        <f>SUM(H5:H20)</f>
-        <v>74900</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13">
+        <f>SUM(H5:H19)</f>
+        <v>72150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A4:H20" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:H19" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -11458,30 +11458,74 @@
       <c r="C41" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="53"/>
+      <c r="D41" s="52">
+        <v>128258.5</v>
+      </c>
+      <c r="E41" s="52">
+        <v>36398.39</v>
+      </c>
+      <c r="F41" s="52">
+        <v>91860.11</v>
+      </c>
+      <c r="G41" s="53">
+        <v>0.7162106994858041</v>
+      </c>
+      <c r="H41" s="52">
+        <v>94098.32</v>
+      </c>
+      <c r="I41" s="52">
+        <v>34659.62</v>
+      </c>
+      <c r="J41" s="52">
+        <v>69042.09000000001</v>
+      </c>
+      <c r="K41" s="52">
+        <v>28340.06</v>
+      </c>
+      <c r="L41" s="52">
+        <v>40702.03000000001</v>
+      </c>
+      <c r="M41" s="53">
+        <v>0.5895248825752524</v>
+      </c>
       <c r="N41" s="53"/>
-      <c r="O41" s="52"/>
-      <c r="P41" s="52"/>
-      <c r="Q41" s="52"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="54"/>
-      <c r="V41" s="53"/>
+      <c r="O41" s="52">
+        <v>25056.23</v>
+      </c>
+      <c r="P41" s="52">
+        <v>6319.56</v>
+      </c>
+      <c r="Q41" s="52">
+        <v>18736.67</v>
+      </c>
+      <c r="R41" s="53">
+        <v>0.7477848822428593</v>
+      </c>
+      <c r="S41" s="54">
+        <v>501.83</v>
+      </c>
+      <c r="T41" s="54">
+        <v>123.75</v>
+      </c>
+      <c r="U41" s="54">
+        <v>378.08</v>
+      </c>
+      <c r="V41" s="53">
+        <v>0.7534025466791543</v>
+      </c>
       <c r="W41" s="53"/>
-      <c r="X41" s="55"/>
-      <c r="Y41" s="55"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="56"/>
+      <c r="X41" s="55">
+        <v>14.050666666666666</v>
+      </c>
+      <c r="Y41" s="55">
+        <v>68.07122423898531</v>
+      </c>
+      <c r="Z41" s="53">
+        <v>0.0478</v>
+      </c>
+      <c r="AA41" s="56">
+        <v>0.2663</v>
+      </c>
       <c r="AB41" s="57"/>
       <c r="AD41" s="35"/>
       <c r="AE41" s="35"/>
@@ -11823,30 +11867,74 @@
       <c r="C48" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="53"/>
+      <c r="D48" s="52">
+        <v>65693.36</v>
+      </c>
+      <c r="E48" s="52">
+        <v>25322.07</v>
+      </c>
+      <c r="F48" s="52">
+        <v>40371.29</v>
+      </c>
+      <c r="G48" s="53">
+        <v>0.6145414087512041</v>
+      </c>
+      <c r="H48" s="52">
+        <v>50582.37</v>
+      </c>
+      <c r="I48" s="52">
+        <v>25131.9</v>
+      </c>
+      <c r="J48" s="52">
+        <v>39438.990000000005</v>
+      </c>
+      <c r="K48" s="52">
+        <v>20456.64</v>
+      </c>
+      <c r="L48" s="52">
+        <v>18982.350000000006</v>
+      </c>
+      <c r="M48" s="53">
+        <v>0.4813092323104624</v>
+      </c>
       <c r="N48" s="53"/>
-      <c r="O48" s="52"/>
-      <c r="P48" s="52"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="54"/>
-      <c r="T48" s="54"/>
-      <c r="U48" s="54"/>
-      <c r="V48" s="53"/>
+      <c r="O48" s="52">
+        <v>11143.38</v>
+      </c>
+      <c r="P48" s="52">
+        <v>4675.26</v>
+      </c>
+      <c r="Q48" s="52">
+        <v>6468.119999999999</v>
+      </c>
+      <c r="R48" s="53">
+        <v>0.5804450714235716</v>
+      </c>
+      <c r="S48" s="54">
+        <v>223.22</v>
+      </c>
+      <c r="T48" s="54">
+        <v>102.25</v>
+      </c>
+      <c r="U48" s="54">
+        <v>120.97</v>
+      </c>
+      <c r="V48" s="53">
+        <v>0.5419317265478004</v>
+      </c>
       <c r="W48" s="53"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="56"/>
+      <c r="X48" s="55">
+        <v>1.8598533007334963</v>
+      </c>
+      <c r="Y48" s="55">
+        <v>67.69550512136009</v>
+      </c>
+      <c r="Z48" s="53">
+        <v>0.0075</v>
+      </c>
+      <c r="AA48" s="56">
+        <v>0.23</v>
+      </c>
       <c r="AB48" s="57"/>
       <c r="AD48" s="35"/>
       <c r="AE48" s="35"/>
@@ -12186,30 +12274,74 @@
       <c r="C55" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="53"/>
+      <c r="D55" s="52">
+        <v>154527.79</v>
+      </c>
+      <c r="E55" s="52">
+        <v>98562.5</v>
+      </c>
+      <c r="F55" s="52">
+        <v>55965.29000000001</v>
+      </c>
+      <c r="G55" s="53">
+        <v>0.36216974306045535</v>
+      </c>
+      <c r="H55" s="52">
+        <v>108880.28</v>
+      </c>
+      <c r="I55" s="52">
+        <v>90918.83</v>
+      </c>
+      <c r="J55" s="52">
+        <v>74953.01000000001</v>
+      </c>
+      <c r="K55" s="52">
+        <v>71302.07</v>
+      </c>
+      <c r="L55" s="52">
+        <v>3650.9400000000023</v>
+      </c>
+      <c r="M55" s="53">
+        <v>0.04870971826214854</v>
+      </c>
       <c r="N55" s="53"/>
-      <c r="O55" s="52"/>
-      <c r="P55" s="52"/>
-      <c r="Q55" s="52"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="54"/>
-      <c r="T55" s="54"/>
-      <c r="U55" s="54"/>
-      <c r="V55" s="53"/>
+      <c r="O55" s="52">
+        <v>33927.27</v>
+      </c>
+      <c r="P55" s="52">
+        <v>19616.76</v>
+      </c>
+      <c r="Q55" s="52">
+        <v>14310.509999999998</v>
+      </c>
+      <c r="R55" s="53">
+        <v>0.4217996319774624</v>
+      </c>
+      <c r="S55" s="54">
+        <v>679.42</v>
+      </c>
+      <c r="T55" s="54">
+        <v>413</v>
+      </c>
+      <c r="U55" s="54">
+        <v>266.41999999999996</v>
+      </c>
+      <c r="V55" s="53">
+        <v>0.39212858025963315</v>
+      </c>
       <c r="W55" s="53"/>
-      <c r="X55" s="55"/>
-      <c r="Y55" s="55"/>
-      <c r="Z55" s="53"/>
-      <c r="AA55" s="56"/>
+      <c r="X55" s="55">
+        <v>18.50767554479419</v>
+      </c>
+      <c r="Y55" s="55">
+        <v>67.18600078134293</v>
+      </c>
+      <c r="Z55" s="53">
+        <v>0.0776</v>
+      </c>
+      <c r="AA55" s="56">
+        <v>0.2954</v>
+      </c>
       <c r="AB55" s="57"/>
       <c r="AD55" s="35"/>
       <c r="AE55" s="35"/>
@@ -12549,30 +12681,74 @@
       <c r="C62" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="53"/>
+      <c r="D62" s="52">
+        <v>20420.56</v>
+      </c>
+      <c r="E62" s="52">
+        <v>16358.37</v>
+      </c>
+      <c r="F62" s="52">
+        <v>4062.1900000000005</v>
+      </c>
+      <c r="G62" s="53">
+        <v>0.19892647410257114</v>
+      </c>
+      <c r="H62" s="52">
+        <v>15859.68</v>
+      </c>
+      <c r="I62" s="52">
+        <v>13601.05</v>
+      </c>
+      <c r="J62" s="52">
+        <v>12689.1</v>
+      </c>
+      <c r="K62" s="52">
+        <v>11685.13</v>
+      </c>
+      <c r="L62" s="52">
+        <v>1003.9700000000012</v>
+      </c>
+      <c r="M62" s="53">
+        <v>0.07912066261594605</v>
+      </c>
       <c r="N62" s="53"/>
-      <c r="O62" s="52"/>
-      <c r="P62" s="52"/>
-      <c r="Q62" s="52"/>
-      <c r="R62" s="53"/>
-      <c r="S62" s="54"/>
-      <c r="T62" s="54"/>
-      <c r="U62" s="54"/>
-      <c r="V62" s="53"/>
+      <c r="O62" s="52">
+        <v>3170.58</v>
+      </c>
+      <c r="P62" s="52">
+        <v>1915.92</v>
+      </c>
+      <c r="Q62" s="52">
+        <v>1254.6599999999999</v>
+      </c>
+      <c r="R62" s="53">
+        <v>0.39571939518952365</v>
+      </c>
+      <c r="S62" s="54">
+        <v>63.5</v>
+      </c>
+      <c r="T62" s="54">
+        <v>47.5</v>
+      </c>
+      <c r="U62" s="54">
+        <v>16</v>
+      </c>
+      <c r="V62" s="53">
+        <v>0.25196850393700787</v>
+      </c>
       <c r="W62" s="53"/>
-      <c r="X62" s="55"/>
-      <c r="Y62" s="55"/>
-      <c r="Z62" s="53"/>
-      <c r="AA62" s="56"/>
+      <c r="X62" s="55">
+        <v>58.04884210526316</v>
+      </c>
+      <c r="Y62" s="55">
+        <v>71.82495570677168</v>
+      </c>
+      <c r="Z62" s="53">
+        <v>0.1686</v>
+      </c>
+      <c r="AA62" s="56">
+        <v>0.2233</v>
+      </c>
       <c r="AB62" s="57"/>
       <c r="AD62" s="35"/>
       <c r="AE62" s="35"/>
@@ -13213,30 +13389,74 @@
       <c r="C76" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
-      <c r="J76" s="52"/>
-      <c r="K76" s="52"/>
-      <c r="L76" s="52"/>
-      <c r="M76" s="53"/>
+      <c r="D76" s="52">
+        <v>77166.16</v>
+      </c>
+      <c r="E76" s="52">
+        <v>0</v>
+      </c>
+      <c r="F76" s="52">
+        <v>77166.16</v>
+      </c>
+      <c r="G76" s="53">
+        <v>1</v>
+      </c>
+      <c r="H76" s="52">
+        <v>54302.66</v>
+      </c>
+      <c r="I76" s="52">
+        <v>22353.17</v>
+      </c>
+      <c r="J76" s="52">
+        <v>31383.390000000003</v>
+      </c>
+      <c r="K76" s="52">
+        <v>22353.17</v>
+      </c>
+      <c r="L76" s="52">
+        <v>9030.220000000005</v>
+      </c>
+      <c r="M76" s="53">
+        <v>0.28773883254804544</v>
+      </c>
       <c r="N76" s="53"/>
-      <c r="O76" s="52"/>
-      <c r="P76" s="52"/>
-      <c r="Q76" s="52"/>
-      <c r="R76" s="53"/>
-      <c r="S76" s="54"/>
-      <c r="T76" s="54"/>
-      <c r="U76" s="54"/>
-      <c r="V76" s="53"/>
+      <c r="O76" s="52">
+        <v>22919.27</v>
+      </c>
+      <c r="P76" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="52">
+        <v>22919.27</v>
+      </c>
+      <c r="R76" s="53">
+        <v>1</v>
+      </c>
+      <c r="S76" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="T76" s="54">
+        <v>0</v>
+      </c>
+      <c r="U76" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="V76" s="53">
+        <v>1</v>
+      </c>
       <c r="W76" s="53"/>
-      <c r="X76" s="55"/>
-      <c r="Y76" s="55"/>
-      <c r="Z76" s="53"/>
-      <c r="AA76" s="56"/>
+      <c r="X76" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="55">
+        <v>48.58165977967362</v>
+      </c>
+      <c r="Z76" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="56">
+        <v>0.2963</v>
+      </c>
       <c r="AB76" s="57"/>
       <c r="AD76" s="35"/>
       <c r="AE76" s="35"/>
@@ -13935,30 +14155,74 @@
       <c r="C90" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="53"/>
+      <c r="D90" s="67">
+        <v>37083.03</v>
+      </c>
+      <c r="E90" s="67">
+        <v>33023.07</v>
+      </c>
+      <c r="F90" s="52">
+        <v>4059.959999999999</v>
+      </c>
+      <c r="G90" s="53">
+        <v>0.10948296296176444</v>
+      </c>
+      <c r="H90" s="52">
+        <v>27002.93</v>
+      </c>
+      <c r="I90" s="52">
+        <v>25996.77</v>
+      </c>
+      <c r="J90" s="52">
+        <v>15440.32</v>
+      </c>
+      <c r="K90" s="52">
+        <v>15990.78</v>
+      </c>
+      <c r="L90" s="52">
+        <v>-550.460000000001</v>
+      </c>
+      <c r="M90" s="53">
+        <v>-0.0356508155271394</v>
+      </c>
       <c r="N90" s="53"/>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="53"/>
-      <c r="S90" s="68"/>
-      <c r="T90" s="68"/>
-      <c r="U90" s="54"/>
-      <c r="V90" s="53"/>
+      <c r="O90" s="52">
+        <v>11562.61</v>
+      </c>
+      <c r="P90" s="52">
+        <v>10005.99</v>
+      </c>
+      <c r="Q90" s="52">
+        <v>1556.6200000000008</v>
+      </c>
+      <c r="R90" s="53">
+        <v>0.13462531383485224</v>
+      </c>
+      <c r="S90" s="68">
+        <v>231.75</v>
+      </c>
+      <c r="T90" s="68">
+        <v>204.75</v>
+      </c>
+      <c r="U90" s="54">
+        <v>27</v>
+      </c>
+      <c r="V90" s="53">
+        <v>0.11650485436893204</v>
+      </c>
       <c r="W90" s="53"/>
-      <c r="X90" s="55"/>
-      <c r="Y90" s="55"/>
-      <c r="Z90" s="53"/>
-      <c r="AA90" s="56"/>
+      <c r="X90" s="55">
+        <v>34.316483516483515</v>
+      </c>
+      <c r="Y90" s="55">
+        <v>43.49557070636461</v>
+      </c>
+      <c r="Z90" s="53">
+        <v>0.21280000000000002</v>
+      </c>
+      <c r="AA90" s="56">
+        <v>0.2718</v>
+      </c>
       <c r="AB90" s="57"/>
       <c r="AD90" s="35"/>
       <c r="AE90" s="35"/>
@@ -14617,30 +14881,74 @@
       <c r="C104" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D104" s="52"/>
-      <c r="E104" s="69"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="52"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="53"/>
+      <c r="D104" s="52">
+        <v>32473.02</v>
+      </c>
+      <c r="E104" s="69">
+        <v>33188.03</v>
+      </c>
+      <c r="F104" s="52">
+        <v>-715.0099999999984</v>
+      </c>
+      <c r="G104" s="53">
+        <v>-0.022018586506582952</v>
+      </c>
+      <c r="H104" s="52">
+        <v>23075.07</v>
+      </c>
+      <c r="I104" s="52">
+        <v>31131.57</v>
+      </c>
+      <c r="J104" s="52">
+        <v>12691.21</v>
+      </c>
+      <c r="K104" s="52">
+        <v>15390.63</v>
+      </c>
+      <c r="L104" s="52">
+        <v>-2699.42</v>
+      </c>
+      <c r="M104" s="53">
+        <v>-0.21269997108234756</v>
+      </c>
       <c r="N104" s="53"/>
-      <c r="O104" s="52"/>
-      <c r="P104" s="52"/>
-      <c r="Q104" s="52"/>
-      <c r="R104" s="53"/>
-      <c r="S104" s="54"/>
-      <c r="T104" s="54"/>
-      <c r="U104" s="54"/>
-      <c r="V104" s="53"/>
+      <c r="O104" s="52">
+        <v>10383.86</v>
+      </c>
+      <c r="P104" s="52">
+        <v>15740.94</v>
+      </c>
+      <c r="Q104" s="52">
+        <v>-5357.08</v>
+      </c>
+      <c r="R104" s="53">
+        <v>-0.5159044902377343</v>
+      </c>
+      <c r="S104" s="54">
+        <v>208.2</v>
+      </c>
+      <c r="T104" s="54">
+        <v>317.25</v>
+      </c>
+      <c r="U104" s="54">
+        <v>-109.05000000000001</v>
+      </c>
+      <c r="V104" s="53">
+        <v>-0.5237752161383286</v>
+      </c>
       <c r="W104" s="53"/>
-      <c r="X104" s="55"/>
-      <c r="Y104" s="55"/>
-      <c r="Z104" s="53"/>
-      <c r="AA104" s="56"/>
+      <c r="X104" s="55">
+        <v>6.482143420015761</v>
+      </c>
+      <c r="Y104" s="55">
+        <v>45.139084580403456</v>
+      </c>
+      <c r="Z104" s="53">
+        <v>0.062</v>
+      </c>
+      <c r="AA104" s="56">
+        <v>0.2894</v>
+      </c>
       <c r="AB104" s="57"/>
       <c r="AD104" s="35"/>
       <c r="AE104" s="35"/>
@@ -14982,30 +15290,74 @@
       <c r="C111" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="52"/>
-      <c r="I111" s="52"/>
-      <c r="J111" s="52"/>
-      <c r="K111" s="52"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="53"/>
+      <c r="D111" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="E111" s="52">
+        <v>0</v>
+      </c>
+      <c r="F111" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="G111" s="53">
+        <v>1</v>
+      </c>
+      <c r="H111" s="52">
+        <v>37601.88</v>
+      </c>
+      <c r="I111" s="52">
+        <v>38195.76</v>
+      </c>
+      <c r="J111" s="52">
+        <v>21415.85</v>
+      </c>
+      <c r="K111" s="52">
+        <v>19158.27</v>
+      </c>
+      <c r="L111" s="52">
+        <v>2257.579999999998</v>
+      </c>
+      <c r="M111" s="53">
+        <v>0.10541631548596009</v>
+      </c>
       <c r="N111" s="53"/>
-      <c r="O111" s="52"/>
-      <c r="P111" s="52"/>
-      <c r="Q111" s="52"/>
-      <c r="R111" s="53"/>
-      <c r="S111" s="54"/>
-      <c r="T111" s="54"/>
-      <c r="U111" s="54"/>
-      <c r="V111" s="53"/>
+      <c r="O111" s="52">
+        <v>16186.03</v>
+      </c>
+      <c r="P111" s="52">
+        <v>19037.49</v>
+      </c>
+      <c r="Q111" s="52">
+        <v>-2851.460000000001</v>
+      </c>
+      <c r="R111" s="53">
+        <v>-0.1761679670678975</v>
+      </c>
+      <c r="S111" s="54">
+        <v>324.19</v>
+      </c>
+      <c r="T111" s="54">
+        <v>412.5</v>
+      </c>
+      <c r="U111" s="54">
+        <v>-88.31</v>
+      </c>
+      <c r="V111" s="53">
+        <v>-0.2724019864894044</v>
+      </c>
       <c r="W111" s="53"/>
-      <c r="X111" s="55"/>
-      <c r="Y111" s="55"/>
-      <c r="Z111" s="53"/>
-      <c r="AA111" s="56"/>
+      <c r="X111" s="55">
+        <v>-6.6456484848484845</v>
+      </c>
+      <c r="Y111" s="55">
+        <v>65.70431400737223</v>
+      </c>
+      <c r="Z111" s="53">
+        <v>-0.07730000000000001</v>
+      </c>
+      <c r="AA111" s="56">
+        <v>0.3616</v>
+      </c>
       <c r="AB111" s="57"/>
       <c r="AD111" s="35"/>
       <c r="AE111" s="35"/>
@@ -15670,32 +16022,74 @@
       <c r="C125" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D125" s="52"/>
-      <c r="E125" s="52"/>
+      <c r="D125" s="52">
+        <v>99768.39</v>
+      </c>
+      <c r="E125" s="52">
+        <v>15366.74</v>
+      </c>
       <c r="F125" s="52">
-        <v>0</v>
-      </c>
-      <c r="G125" s="53"/>
-      <c r="H125" s="52"/>
-      <c r="I125" s="52"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="52"/>
-      <c r="M125" s="53"/>
+        <v>84401.65</v>
+      </c>
+      <c r="G125" s="53">
+        <v>0.8459758647002321</v>
+      </c>
+      <c r="H125" s="52">
+        <v>81719.58</v>
+      </c>
+      <c r="I125" s="52">
+        <v>18551.86</v>
+      </c>
+      <c r="J125" s="52">
+        <v>67238.96</v>
+      </c>
+      <c r="K125" s="52">
+        <v>14369.1</v>
+      </c>
+      <c r="L125" s="52">
+        <v>52869.86000000001</v>
+      </c>
+      <c r="M125" s="53">
+        <v>0.7862980034194461</v>
+      </c>
       <c r="N125" s="53"/>
-      <c r="O125" s="52"/>
-      <c r="P125" s="52"/>
-      <c r="Q125" s="52"/>
-      <c r="R125" s="53"/>
-      <c r="S125" s="54"/>
-      <c r="T125" s="54"/>
-      <c r="U125" s="54"/>
-      <c r="V125" s="53"/>
+      <c r="O125" s="52">
+        <v>14480.62</v>
+      </c>
+      <c r="P125" s="52">
+        <v>4182.76</v>
+      </c>
+      <c r="Q125" s="52">
+        <v>10297.86</v>
+      </c>
+      <c r="R125" s="53">
+        <v>0.7111477271000828</v>
+      </c>
+      <c r="S125" s="54">
+        <v>290.15</v>
+      </c>
+      <c r="T125" s="54">
+        <v>91.75</v>
+      </c>
+      <c r="U125" s="54">
+        <v>198.39999999999998</v>
+      </c>
+      <c r="V125" s="53">
+        <v>0.6837842495261072</v>
+      </c>
       <c r="W125" s="53"/>
-      <c r="X125" s="55"/>
-      <c r="Y125" s="55"/>
-      <c r="Z125" s="53"/>
-      <c r="AA125" s="56"/>
+      <c r="X125" s="55">
+        <v>-34.715204359673024</v>
+      </c>
+      <c r="Y125" s="55">
+        <v>62.2051177714286</v>
+      </c>
+      <c r="Z125" s="53">
+        <v>-0.2073</v>
+      </c>
+      <c r="AA125" s="56">
+        <v>0.1809</v>
+      </c>
       <c r="AB125" s="57"/>
       <c r="AD125" s="35"/>
       <c r="AE125" s="35"/>
@@ -16357,30 +16751,74 @@
       <c r="C139" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D139" s="52"/>
-      <c r="E139" s="52"/>
-      <c r="F139" s="52"/>
-      <c r="G139" s="53"/>
-      <c r="H139" s="52"/>
-      <c r="I139" s="52"/>
-      <c r="J139" s="52"/>
-      <c r="K139" s="52"/>
-      <c r="L139" s="52"/>
-      <c r="M139" s="53"/>
+      <c r="D139" s="52">
+        <v>30749.24</v>
+      </c>
+      <c r="E139" s="52">
+        <v>30749.24</v>
+      </c>
+      <c r="F139" s="52">
+        <v>0</v>
+      </c>
+      <c r="G139" s="53">
+        <v>0</v>
+      </c>
+      <c r="H139" s="52">
+        <v>22587.89</v>
+      </c>
+      <c r="I139" s="52">
+        <v>25550.31</v>
+      </c>
+      <c r="J139" s="52">
+        <v>12565.06</v>
+      </c>
+      <c r="K139" s="52">
+        <v>11750.840000000002</v>
+      </c>
+      <c r="L139" s="52">
+        <v>814.2199999999975</v>
+      </c>
+      <c r="M139" s="53">
+        <v>0.06480032725669416</v>
+      </c>
       <c r="N139" s="53"/>
-      <c r="O139" s="52"/>
-      <c r="P139" s="52"/>
-      <c r="Q139" s="52"/>
-      <c r="R139" s="53"/>
-      <c r="S139" s="54"/>
-      <c r="T139" s="54"/>
-      <c r="U139" s="54"/>
-      <c r="V139" s="53"/>
+      <c r="O139" s="52">
+        <v>10022.83</v>
+      </c>
+      <c r="P139" s="52">
+        <v>13799.47</v>
+      </c>
+      <c r="Q139" s="52">
+        <v>-3776.6399999999994</v>
+      </c>
+      <c r="R139" s="53">
+        <v>-0.37680375702271707</v>
+      </c>
+      <c r="S139" s="54">
+        <v>200.82</v>
+      </c>
+      <c r="T139" s="54">
+        <v>278.25</v>
+      </c>
+      <c r="U139" s="54">
+        <v>-77.43</v>
+      </c>
+      <c r="V139" s="53">
+        <v>-0.3855691664176875</v>
+      </c>
       <c r="W139" s="53"/>
-      <c r="X139" s="55"/>
-      <c r="Y139" s="55"/>
-      <c r="Z139" s="53"/>
-      <c r="AA139" s="56"/>
+      <c r="X139" s="55">
+        <v>18.68438454627134</v>
+      </c>
+      <c r="Y139" s="55">
+        <v>40.64013272149188</v>
+      </c>
+      <c r="Z139" s="53">
+        <v>0.1691</v>
+      </c>
+      <c r="AA139" s="56">
+        <v>0.2654</v>
+      </c>
       <c r="AB139" s="57"/>
       <c r="AD139" s="35"/>
       <c r="AE139" s="35"/>
@@ -18014,32 +18452,74 @@
       <c r="C174" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D174" s="52"/>
-      <c r="E174" s="52"/>
-      <c r="F174" s="52"/>
-      <c r="G174" s="53"/>
-      <c r="H174" s="52"/>
-      <c r="I174" s="52"/>
-      <c r="J174" s="52"/>
+      <c r="D174" s="52">
+        <v>146237.11</v>
+      </c>
+      <c r="E174" s="52">
+        <v>94266.45</v>
+      </c>
+      <c r="F174" s="52">
+        <v>51970.65999999999</v>
+      </c>
+      <c r="G174" s="53">
+        <v>0.355386262761894</v>
+      </c>
+      <c r="H174" s="52">
+        <v>114651.87</v>
+      </c>
+      <c r="I174" s="52">
+        <v>95876.35</v>
+      </c>
+      <c r="J174" s="52">
+        <v>82888.07999999999</v>
+      </c>
       <c r="K174" s="52">
-        <v>0</v>
-      </c>
-      <c r="L174" s="52"/>
-      <c r="M174" s="53"/>
+        <v>74503.91</v>
+      </c>
+      <c r="L174" s="52">
+        <v>8384.169999999984</v>
+      </c>
+      <c r="M174" s="53">
+        <v>0.10115049112007402</v>
+      </c>
       <c r="N174" s="53"/>
-      <c r="O174" s="52"/>
-      <c r="P174" s="52"/>
-      <c r="Q174" s="52"/>
-      <c r="R174" s="53"/>
-      <c r="S174" s="54"/>
-      <c r="T174" s="54"/>
-      <c r="U174" s="54"/>
-      <c r="V174" s="53"/>
+      <c r="O174" s="52">
+        <v>31763.79</v>
+      </c>
+      <c r="P174" s="52">
+        <v>21372.44</v>
+      </c>
+      <c r="Q174" s="52">
+        <v>10391.350000000002</v>
+      </c>
+      <c r="R174" s="53">
+        <v>0.32714452525973764</v>
+      </c>
+      <c r="S174" s="54">
+        <v>659.73</v>
+      </c>
+      <c r="T174" s="54">
+        <v>430</v>
+      </c>
+      <c r="U174" s="54">
+        <v>229.73000000000002</v>
+      </c>
+      <c r="V174" s="53">
+        <v>0.34821821048004487</v>
+      </c>
       <c r="W174" s="53"/>
-      <c r="X174" s="55"/>
-      <c r="Y174" s="55"/>
-      <c r="Z174" s="53"/>
-      <c r="AA174" s="56"/>
+      <c r="X174" s="55">
+        <v>-3.7439534883720933</v>
+      </c>
+      <c r="Y174" s="55">
+        <v>47.87601261940491</v>
+      </c>
+      <c r="Z174" s="53">
+        <v>-0.0171</v>
+      </c>
+      <c r="AA174" s="56">
+        <v>0.216</v>
+      </c>
       <c r="AB174" s="57"/>
       <c r="AD174" s="35"/>
       <c r="AE174" s="35"/>
@@ -20269,34 +20749,74 @@
       <c r="C222" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D222" s="52"/>
-      <c r="E222" s="52"/>
-      <c r="F222" s="52"/>
-      <c r="G222" s="53"/>
-      <c r="H222" s="52"/>
-      <c r="I222" s="52"/>
+      <c r="D222" s="52">
+        <v>389318.35</v>
+      </c>
+      <c r="E222" s="52">
+        <v>271388.15</v>
+      </c>
+      <c r="F222" s="52">
+        <v>117930.19999999995</v>
+      </c>
+      <c r="G222" s="53">
+        <v>0.3029145685015874</v>
+      </c>
+      <c r="H222" s="52">
+        <v>289549.48</v>
+      </c>
+      <c r="I222" s="52">
+        <v>228314.4</v>
+      </c>
       <c r="J222" s="52">
-        <v>0</v>
+        <v>174279.97999999998</v>
       </c>
       <c r="K222" s="52">
-        <v>0</v>
-      </c>
-      <c r="L222" s="52"/>
-      <c r="M222" s="53"/>
+        <v>175133.49</v>
+      </c>
+      <c r="L222" s="52">
+        <v>-853.5100000000093</v>
+      </c>
+      <c r="M222" s="53">
+        <v>-0.004897349655422324</v>
+      </c>
       <c r="N222" s="53"/>
-      <c r="O222" s="52"/>
-      <c r="P222" s="52"/>
-      <c r="Q222" s="52"/>
-      <c r="R222" s="53"/>
-      <c r="S222" s="54"/>
-      <c r="T222" s="54"/>
-      <c r="U222" s="54"/>
-      <c r="V222" s="53"/>
+      <c r="O222" s="52">
+        <v>115269.5</v>
+      </c>
+      <c r="P222" s="52">
+        <v>53180.91</v>
+      </c>
+      <c r="Q222" s="52">
+        <v>62088.59</v>
+      </c>
+      <c r="R222" s="53">
+        <v>0.5386384950051835</v>
+      </c>
+      <c r="S222" s="54">
+        <v>2312.68</v>
+      </c>
+      <c r="T222" s="54">
+        <v>1120.5</v>
+      </c>
+      <c r="U222" s="54">
+        <v>1192.1799999999998</v>
+      </c>
+      <c r="V222" s="53">
+        <v>0.5154971721120085</v>
+      </c>
       <c r="W222" s="53"/>
-      <c r="X222" s="55"/>
-      <c r="Y222" s="55"/>
-      <c r="Z222" s="53"/>
-      <c r="AA222" s="56"/>
+      <c r="X222" s="55">
+        <v>38.441543953592145</v>
+      </c>
+      <c r="Y222" s="55">
+        <v>43.1399392286741</v>
+      </c>
+      <c r="Z222" s="53">
+        <v>0.15869999999999998</v>
+      </c>
+      <c r="AA222" s="56">
+        <v>0.2563</v>
+      </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
         <v>93</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21671,10 +21671,10 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="52">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="D4" s="52">
-        <v>10272.17</v>
+        <v>48113.58</v>
       </c>
       <c r="E4" s="52">
         <f>C4-D4</f>
@@ -21743,10 +21743,10 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C6" s="52">
-        <v>0</v>
+        <v>3912</v>
       </c>
       <c r="D6" s="52">
-        <v>3968.93</v>
+        <v>6513.389999999999</v>
       </c>
       <c r="E6" s="52">
         <f>C6-D6</f>
@@ -21820,10 +21820,10 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C8" s="52">
-        <v>6999.08</v>
+        <v>0</v>
       </c>
       <c r="D8" s="52">
-        <v>4771.92</v>
+        <v>0</v>
       </c>
       <c r="E8" s="52">
         <f>C8-D8</f>
@@ -21890,10 +21890,10 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C10" s="52">
-        <v>53231</v>
+        <v>0</v>
       </c>
       <c r="D10" s="52">
-        <v>33984.22</v>
+        <v>5315.239999999991</v>
       </c>
       <c r="E10" s="52">
         <f>C10-D10</f>
@@ -21961,10 +21961,10 @@
         <v>115</v>
       </c>
       <c r="C12" s="52">
-        <v>20350</v>
+        <v>0</v>
       </c>
       <c r="D12" s="52">
-        <v>13205.66</v>
+        <v>1154.6499999999942</v>
       </c>
       <c r="E12" s="52">
         <f>C12-D12</f>
@@ -22035,10 +22035,10 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C14" s="52">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="D14" s="52">
-        <v>6684.89</v>
+        <v>2138.1600000000035</v>
       </c>
       <c r="E14" s="52">
         <f>C14-D14</f>
@@ -22108,10 +22108,10 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C16" s="52">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="D16" s="52">
-        <v>4840</v>
+        <v>5565.0300000000025</v>
       </c>
       <c r="E16" s="52">
         <f>C16-D16</f>
@@ -22180,10 +22180,10 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C18" s="52">
-        <v>37161.1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="52">
-        <v>21086</v>
+        <v>10982.64</v>
       </c>
       <c r="E18" s="52">
         <f>C18-D18</f>
@@ -22260,7 +22260,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="52">
-        <v>0</v>
+        <v>1407.8799999999992</v>
       </c>
       <c r="E20" s="52">
         <f>C20-D20</f>
@@ -22325,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="52">
-        <v>0</v>
+        <v>4584.16</v>
       </c>
       <c r="E22" s="52">
         <f>C22-D22</f>
@@ -22395,7 +22395,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="52">
-        <v>0</v>
+        <v>22353.17</v>
       </c>
       <c r="E24" s="52">
         <f>C24-D24</f>
@@ -22459,8 +22459,12 @@
         <f>'Main Sheet'!B26</f>
         <v>5 Sanscrit Place</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
+      <c r="C26" s="52">
+        <v>0</v>
+      </c>
+      <c r="D26" s="52">
+        <v>-192.5</v>
+      </c>
       <c r="E26" s="52">
         <f>C26-D26</f>
         <v>0</v>
@@ -22528,10 +22532,10 @@
         <v>Melhuish House</v>
       </c>
       <c r="C28" s="52">
-        <v>6681.34</v>
+        <v>0</v>
       </c>
       <c r="D28" s="52">
-        <v>4367.65</v>
+        <v>4476.1500000000015</v>
       </c>
       <c r="E28" s="52">
         <f>C28-D28</f>
@@ -22597,8 +22601,12 @@
         <f>'Main Sheet'!B30</f>
         <v>6 Tiroroa Lane</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
+      <c r="C30" s="52">
+        <v>0</v>
+      </c>
+      <c r="D30" s="52">
+        <v>0</v>
+      </c>
       <c r="E30" s="52">
         <f>C30-D30</f>
         <v>0</v>
@@ -22664,10 +22672,10 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C32" s="52">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="D32" s="52">
-        <v>1922.47</v>
+        <v>-1171.8899999999994</v>
       </c>
       <c r="E32" s="52">
         <f>C32-D32</f>
@@ -22737,8 +22745,12 @@
         <f>'Main Sheet'!B34</f>
         <v>Inline Architecture</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
+      <c r="C34" s="52">
+        <v>-35454.43</v>
+      </c>
+      <c r="D34" s="52">
+        <v>16334.04</v>
+      </c>
       <c r="E34" s="52">
         <f>C34-D34</f>
         <v>0</v>
@@ -22806,10 +22818,10 @@
         <v>Percival Bach</v>
       </c>
       <c r="C36" s="52">
-        <v>21632.1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="52">
-        <v>10930</v>
+        <v>0</v>
       </c>
       <c r="E36" s="52">
         <f>C36-D36</f>
@@ -22879,8 +22891,12 @@
         <f>'Main Sheet'!B38</f>
         <v>St Albans Street</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
+      <c r="C38" s="52">
+        <v>0</v>
+      </c>
+      <c r="D38" s="52">
+        <v>6365.780000000001</v>
+      </c>
       <c r="E38" s="52">
         <f>C38-D38</f>
         <v>0</v>
@@ -22945,8 +22961,12 @@
         <f>'Main Sheet'!B40</f>
         <v>4 Perry St</v>
       </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
+      <c r="C40" s="52">
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <v>0</v>
+      </c>
       <c r="E40" s="52">
         <f>C40-D40</f>
         <v>0</v>
@@ -23014,10 +23034,10 @@
         <v>Ryans House</v>
       </c>
       <c r="C42" s="52">
-        <v>6708.7</v>
+        <v>3554.300000000003</v>
       </c>
       <c r="D42" s="52">
-        <v>6814.9</v>
+        <v>584.890000000003</v>
       </c>
       <c r="E42" s="52">
         <f>C42-D42</f>
@@ -23084,10 +23104,10 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C44" s="52">
-        <v>6377.31</v>
+        <v>9034.53</v>
       </c>
       <c r="D44" s="52">
-        <v>4386</v>
+        <v>6362.08</v>
       </c>
       <c r="E44" s="52">
         <f>C44-D44</f>
@@ -23152,10 +23172,10 @@
         <v>Dixon House</v>
       </c>
       <c r="C46" s="99">
-        <v>5089.31</v>
+        <v>0</v>
       </c>
       <c r="D46" s="99">
-        <v>4437.9</v>
+        <v>15.4900000000016</v>
       </c>
       <c r="E46" s="99">
         <f>C46-D46</f>
@@ -23223,7 +23243,7 @@
         <v>13424.5</v>
       </c>
       <c r="D48" s="99">
-        <v>7562.1</v>
+        <v>2862.0099999999993</v>
       </c>
       <c r="E48" s="99">
         <f>C48-D48</f>
@@ -23289,8 +23309,12 @@
         <f>'Main Sheet'!B50</f>
         <v>Daves Twizel Shack</v>
       </c>
-      <c r="C50" s="99"/>
-      <c r="D50" s="99"/>
+      <c r="C50" s="99">
+        <v>0</v>
+      </c>
+      <c r="D50" s="99">
+        <v>0</v>
+      </c>
       <c r="E50" s="99">
         <f>C50-D50</f>
         <v>0</v>
@@ -23359,10 +23383,10 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C52" s="99">
-        <v>4702.15</v>
+        <v>0</v>
       </c>
       <c r="D52" s="99">
-        <v>2018.57</v>
+        <v>20350.28</v>
       </c>
       <c r="E52" s="99">
         <f>C52-D52</f>
@@ -23434,7 +23458,7 @@
         <v>5491.7</v>
       </c>
       <c r="D54" s="99">
-        <v>2946.15</v>
+        <v>756.6300000000001</v>
       </c>
       <c r="E54" s="99">
         <f>C54-D54</f>
@@ -23506,7 +23530,7 @@
         <v>12937.1</v>
       </c>
       <c r="D56" s="99">
-        <v>3877.27</v>
+        <v>4850.19</v>
       </c>
       <c r="E56" s="99">
         <f>C56-D56</f>
@@ -23574,8 +23598,12 @@
         <f>'Main Sheet'!B58</f>
         <v>St Barnabas Church</v>
       </c>
-      <c r="C58" s="99"/>
-      <c r="D58" s="99"/>
+      <c r="C58" s="99">
+        <v>0</v>
+      </c>
+      <c r="D58" s="99">
+        <v>7180.07</v>
+      </c>
       <c r="E58" s="99">
         <f>C58-D58</f>
         <v>0</v>
@@ -23768,8 +23796,12 @@
         <f>'Main Sheet'!B64</f>
         <v>Westcoast Vaults</v>
       </c>
-      <c r="C64" s="99"/>
-      <c r="D64" s="99"/>
+      <c r="C64" s="99">
+        <v>0</v>
+      </c>
+      <c r="D64" s="99">
+        <v>1749.8</v>
+      </c>
       <c r="E64" s="99">
         <f>C64-D64</f>
         <v>0</v>
@@ -23834,10 +23866,10 @@
         <v>Roydvale</v>
       </c>
       <c r="C66" s="99">
-        <v>30500</v>
+        <v>0</v>
       </c>
       <c r="D66" s="99">
-        <v>19018</v>
+        <v>3855.079999999987</v>
       </c>
       <c r="E66" s="99">
         <f>C66-D66</f>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9721,30 +9721,74 @@
       <c r="C7" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53"/>
+      <c r="D7" s="52">
+        <v>233882.27</v>
+      </c>
+      <c r="E7" s="52">
+        <v>205915.9</v>
+      </c>
+      <c r="F7" s="52">
+        <v>27966.369999999995</v>
+      </c>
+      <c r="G7" s="53">
+        <v>0.1195745620221661</v>
+      </c>
+      <c r="H7" s="52">
+        <v>199128.99</v>
+      </c>
+      <c r="I7" s="52">
+        <v>165210.04</v>
+      </c>
+      <c r="J7" s="52">
+        <v>172860.11</v>
+      </c>
+      <c r="K7" s="52">
+        <v>137410.69</v>
+      </c>
+      <c r="L7" s="52">
+        <v>35449.419999999984</v>
+      </c>
+      <c r="M7" s="53">
+        <v>0.20507576907130273</v>
+      </c>
       <c r="N7" s="53"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="53"/>
+      <c r="O7" s="52">
+        <v>26268.88</v>
+      </c>
+      <c r="P7" s="52">
+        <v>27799.35</v>
+      </c>
+      <c r="Q7" s="52">
+        <v>-1530.4699999999975</v>
+      </c>
+      <c r="R7" s="53">
+        <v>-0.05826171500269511</v>
+      </c>
+      <c r="S7" s="54">
+        <v>530.95</v>
+      </c>
+      <c r="T7" s="54">
+        <v>556.5</v>
+      </c>
+      <c r="U7" s="54">
+        <v>-25.549999999999955</v>
+      </c>
+      <c r="V7" s="53">
+        <v>-0.04812129202373096</v>
+      </c>
       <c r="W7" s="53"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="56"/>
+      <c r="X7" s="55">
+        <v>73.14619946091645</v>
+      </c>
+      <c r="Y7" s="55">
+        <v>65.45490166985587</v>
+      </c>
+      <c r="Z7" s="53">
+        <v>0.1977</v>
+      </c>
+      <c r="AA7" s="56">
+        <v>0.1486</v>
+      </c>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
         <v>96</v>
@@ -21674,7 +21718,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="52">
-        <v>48113.58</v>
+        <v>51687.05</v>
       </c>
       <c r="E4" s="52">
         <f>C4-D4</f>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9737,54 +9737,54 @@
         <v>199128.99</v>
       </c>
       <c r="I7" s="52">
-        <v>165210.04</v>
+        <v>164808.35</v>
       </c>
       <c r="J7" s="52">
         <v>172860.11</v>
       </c>
       <c r="K7" s="52">
-        <v>137410.69</v>
+        <v>137510.76</v>
       </c>
       <c r="L7" s="52">
-        <v>35449.419999999984</v>
+        <v>35349.34999999998</v>
       </c>
       <c r="M7" s="53">
-        <v>0.20507576907130273</v>
+        <v>0.20449686165304407</v>
       </c>
       <c r="N7" s="53"/>
       <c r="O7" s="52">
         <v>26268.88</v>
       </c>
       <c r="P7" s="52">
-        <v>27799.35</v>
+        <v>27297.59</v>
       </c>
       <c r="Q7" s="52">
-        <v>-1530.4699999999975</v>
+        <v>-1028.7099999999991</v>
       </c>
       <c r="R7" s="53">
-        <v>-0.05826171500269511</v>
+        <v>-0.03916078645149695</v>
       </c>
       <c r="S7" s="54">
         <v>530.95</v>
       </c>
       <c r="T7" s="54">
-        <v>556.5</v>
+        <v>548</v>
       </c>
       <c r="U7" s="54">
-        <v>-25.549999999999955</v>
+        <v>-17.049999999999955</v>
       </c>
       <c r="V7" s="53">
-        <v>-0.04812129202373096</v>
+        <v>-0.032112251624446655</v>
       </c>
       <c r="W7" s="53"/>
       <c r="X7" s="55">
-        <v>73.14619946091645</v>
+        <v>75.01377737226278</v>
       </c>
       <c r="Y7" s="55">
         <v>65.45490166985587</v>
       </c>
       <c r="Z7" s="53">
-        <v>0.1977</v>
+        <v>0.1996</v>
       </c>
       <c r="AA7" s="56">
         <v>0.1486</v>
@@ -10128,30 +10128,74 @@
       <c r="C14" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="53"/>
+      <c r="D14" s="52">
+        <v>129074.86</v>
+      </c>
+      <c r="E14" s="62">
+        <v>55068.11</v>
+      </c>
+      <c r="F14" s="52">
+        <v>74006.75</v>
+      </c>
+      <c r="G14" s="53">
+        <v>0.5733630081024299</v>
+      </c>
+      <c r="H14" s="52">
+        <v>101420.72</v>
+      </c>
+      <c r="I14" s="52">
+        <v>55851.96</v>
+      </c>
+      <c r="J14" s="52">
+        <v>83645.65</v>
+      </c>
+      <c r="K14" s="52">
+        <v>51392.88</v>
+      </c>
+      <c r="L14" s="52">
+        <v>32252.769999999997</v>
+      </c>
+      <c r="M14" s="53">
+        <v>0.3855881327959075</v>
+      </c>
       <c r="N14" s="53"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="53"/>
+      <c r="O14" s="52">
+        <v>17775.07</v>
+      </c>
+      <c r="P14" s="52">
+        <v>4459.08</v>
+      </c>
+      <c r="Q14" s="52">
+        <v>13315.99</v>
+      </c>
+      <c r="R14" s="53">
+        <v>0.7491385406639749</v>
+      </c>
+      <c r="S14" s="54">
+        <v>356.07</v>
+      </c>
+      <c r="T14" s="54">
+        <v>90.75</v>
+      </c>
+      <c r="U14" s="54">
+        <v>265.32</v>
+      </c>
+      <c r="V14" s="53">
+        <v>0.7451343836886005</v>
+      </c>
       <c r="W14" s="53"/>
-      <c r="X14" s="55"/>
-      <c r="Y14" s="55"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="56"/>
+      <c r="X14" s="55">
+        <v>-8.637465564738292</v>
+      </c>
+      <c r="Y14" s="55">
+        <v>77.66490997775718</v>
+      </c>
+      <c r="Z14" s="53">
+        <v>-0.014199999999999999</v>
+      </c>
+      <c r="AA14" s="56">
+        <v>0.2142</v>
+      </c>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
         <v>96</v>
@@ -10447,30 +10491,74 @@
       <c r="C21" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="53"/>
+      <c r="D21" s="52">
+        <v>27500.32</v>
+      </c>
+      <c r="E21" s="52">
+        <v>6999.08</v>
+      </c>
+      <c r="F21" s="52">
+        <v>20501.239999999998</v>
+      </c>
+      <c r="G21" s="53">
+        <v>0.74549096155972</v>
+      </c>
+      <c r="H21" s="52">
+        <v>19565.83</v>
+      </c>
+      <c r="I21" s="52">
+        <v>7621.92</v>
+      </c>
+      <c r="J21" s="52">
+        <v>13767.340000000002</v>
+      </c>
+      <c r="K21" s="52">
+        <v>5911.24</v>
+      </c>
+      <c r="L21" s="52">
+        <v>7856.100000000002</v>
+      </c>
+      <c r="M21" s="53">
+        <v>0.5706331070490016</v>
+      </c>
       <c r="N21" s="53"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="53"/>
+      <c r="O21" s="52">
+        <v>5798.49</v>
+      </c>
+      <c r="P21" s="52">
+        <v>1710.68</v>
+      </c>
+      <c r="Q21" s="52">
+        <v>4087.8099999999995</v>
+      </c>
+      <c r="R21" s="53">
+        <v>0.7049783650571096</v>
+      </c>
+      <c r="S21" s="54">
+        <v>125.39</v>
+      </c>
+      <c r="T21" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U21" s="54">
+        <v>90.64</v>
+      </c>
+      <c r="V21" s="53">
+        <v>0.7228646622537682</v>
+      </c>
       <c r="W21" s="53"/>
-      <c r="X21" s="55"/>
-      <c r="Y21" s="55"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="56"/>
+      <c r="X21" s="55">
+        <v>-17.923453237410072</v>
+      </c>
+      <c r="Y21" s="55">
+        <v>63.27846478985563</v>
+      </c>
+      <c r="Z21" s="53">
+        <v>-0.08900000000000001</v>
+      </c>
+      <c r="AA21" s="56">
+        <v>0.2885</v>
+      </c>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
         <v>96</v>
@@ -10812,30 +10900,74 @@
       <c r="C28" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="53"/>
+      <c r="D28" s="55">
+        <v>150850.82</v>
+      </c>
+      <c r="E28" s="55">
+        <v>111983.72</v>
+      </c>
+      <c r="F28" s="52">
+        <v>38867.100000000006</v>
+      </c>
+      <c r="G28" s="53">
+        <v>0.25765256032416667</v>
+      </c>
+      <c r="H28" s="52">
+        <v>102178.42</v>
+      </c>
+      <c r="I28" s="52">
+        <v>84545.62</v>
+      </c>
+      <c r="J28" s="52">
+        <v>62464.86</v>
+      </c>
+      <c r="K28" s="52">
+        <v>58627.5</v>
+      </c>
+      <c r="L28" s="52">
+        <v>3837.3600000000006</v>
+      </c>
+      <c r="M28" s="53">
+        <v>0.06143229969618119</v>
+      </c>
       <c r="N28" s="53"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="53"/>
+      <c r="O28" s="52">
+        <v>39713.56</v>
+      </c>
+      <c r="P28" s="52">
+        <v>25918.12</v>
+      </c>
+      <c r="Q28" s="52">
+        <v>13795.439999999999</v>
+      </c>
+      <c r="R28" s="53">
+        <v>0.34737354193378783</v>
+      </c>
+      <c r="S28" s="54">
+        <v>795.22</v>
+      </c>
+      <c r="T28" s="54">
+        <v>531.25</v>
+      </c>
+      <c r="U28" s="54">
+        <v>263.97</v>
+      </c>
+      <c r="V28" s="53">
+        <v>0.33194587661276126</v>
+      </c>
       <c r="W28" s="53"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="56"/>
+      <c r="X28" s="55">
+        <v>51.648188235294114</v>
+      </c>
+      <c r="Y28" s="55">
+        <v>61.20621468124544</v>
+      </c>
+      <c r="Z28" s="53">
+        <v>0.245</v>
+      </c>
+      <c r="AA28" s="56">
+        <v>0.3227</v>
+      </c>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
         <v>96</v>
@@ -11175,30 +11307,74 @@
       <c r="C35" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="53"/>
+      <c r="D35" s="52">
+        <v>396422.03</v>
+      </c>
+      <c r="E35" s="52">
+        <v>176161.65</v>
+      </c>
+      <c r="F35" s="52">
+        <v>220260.38000000003</v>
+      </c>
+      <c r="G35" s="53">
+        <v>0.5556209376153994</v>
+      </c>
+      <c r="H35" s="52">
+        <v>327431.12</v>
+      </c>
+      <c r="I35" s="65">
+        <v>150094.16</v>
+      </c>
+      <c r="J35" s="52">
+        <v>271519.78</v>
+      </c>
+      <c r="K35" s="52">
+        <v>132259.14</v>
+      </c>
+      <c r="L35" s="52">
+        <v>139260.64</v>
+      </c>
+      <c r="M35" s="53">
+        <v>0.5128931674885712</v>
+      </c>
       <c r="N35" s="53"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="53"/>
+      <c r="O35" s="52">
+        <v>55911.34</v>
+      </c>
+      <c r="P35" s="52">
+        <v>17835.02</v>
+      </c>
+      <c r="Q35" s="52">
+        <v>38076.31999999999</v>
+      </c>
+      <c r="R35" s="53">
+        <v>0.6810124743924935</v>
+      </c>
+      <c r="S35" s="54">
+        <v>1120.27</v>
+      </c>
+      <c r="T35" s="54">
+        <v>416.25</v>
+      </c>
+      <c r="U35" s="54">
+        <v>704.02</v>
+      </c>
+      <c r="V35" s="53">
+        <v>0.6284377873191285</v>
+      </c>
       <c r="W35" s="53"/>
-      <c r="X35" s="55"/>
-      <c r="Y35" s="55"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="56"/>
+      <c r="X35" s="55">
+        <v>62.6246006006006</v>
+      </c>
+      <c r="Y35" s="55">
+        <v>61.5841822414239</v>
+      </c>
+      <c r="Z35" s="53">
+        <v>0.14800000000000002</v>
+      </c>
+      <c r="AA35" s="56">
+        <v>0.174</v>
+      </c>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
         <v>96</v>
@@ -11582,30 +11758,74 @@
       <c r="C42" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="53"/>
+      <c r="D42" s="52">
+        <v>128258.5</v>
+      </c>
+      <c r="E42" s="52">
+        <v>36398.39</v>
+      </c>
+      <c r="F42" s="52">
+        <v>91860.11</v>
+      </c>
+      <c r="G42" s="53">
+        <v>0.7162106994858041</v>
+      </c>
+      <c r="H42" s="52">
+        <v>94098.32</v>
+      </c>
+      <c r="I42" s="52">
+        <v>34659.62</v>
+      </c>
+      <c r="J42" s="52">
+        <v>69042.09000000001</v>
+      </c>
+      <c r="K42" s="52">
+        <v>28340.06</v>
+      </c>
+      <c r="L42" s="52">
+        <v>40702.03000000001</v>
+      </c>
+      <c r="M42" s="53">
+        <v>0.5895248825752524</v>
+      </c>
       <c r="N42" s="53"/>
-      <c r="O42" s="52"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="54"/>
-      <c r="T42" s="54"/>
-      <c r="U42" s="54"/>
-      <c r="V42" s="53"/>
+      <c r="O42" s="52">
+        <v>25056.23</v>
+      </c>
+      <c r="P42" s="52">
+        <v>6319.56</v>
+      </c>
+      <c r="Q42" s="52">
+        <v>18736.67</v>
+      </c>
+      <c r="R42" s="53">
+        <v>0.7477848822428593</v>
+      </c>
+      <c r="S42" s="54">
+        <v>501.83</v>
+      </c>
+      <c r="T42" s="54">
+        <v>123.75</v>
+      </c>
+      <c r="U42" s="54">
+        <v>378.08</v>
+      </c>
+      <c r="V42" s="53">
+        <v>0.7534025466791543</v>
+      </c>
       <c r="W42" s="53"/>
-      <c r="X42" s="55"/>
-      <c r="Y42" s="55"/>
-      <c r="Z42" s="53"/>
-      <c r="AA42" s="56"/>
+      <c r="X42" s="55">
+        <v>14.050666666666666</v>
+      </c>
+      <c r="Y42" s="55">
+        <v>68.07122423898531</v>
+      </c>
+      <c r="Z42" s="53">
+        <v>0.0478</v>
+      </c>
+      <c r="AA42" s="56">
+        <v>0.2663</v>
+      </c>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
         <v>96</v>
@@ -11991,30 +12211,74 @@
       <c r="C49" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="53"/>
+      <c r="D49" s="52">
+        <v>65693.36</v>
+      </c>
+      <c r="E49" s="52">
+        <v>25322.07</v>
+      </c>
+      <c r="F49" s="52">
+        <v>40371.29</v>
+      </c>
+      <c r="G49" s="53">
+        <v>0.6145414087512041</v>
+      </c>
+      <c r="H49" s="52">
+        <v>50582.37</v>
+      </c>
+      <c r="I49" s="52">
+        <v>25131.9</v>
+      </c>
+      <c r="J49" s="52">
+        <v>39438.990000000005</v>
+      </c>
+      <c r="K49" s="52">
+        <v>20456.64</v>
+      </c>
+      <c r="L49" s="52">
+        <v>18982.350000000006</v>
+      </c>
+      <c r="M49" s="53">
+        <v>0.4813092323104624</v>
+      </c>
       <c r="N49" s="53"/>
-      <c r="O49" s="52"/>
-      <c r="P49" s="52"/>
-      <c r="Q49" s="52"/>
-      <c r="R49" s="53"/>
-      <c r="S49" s="54"/>
-      <c r="T49" s="54"/>
-      <c r="U49" s="54"/>
-      <c r="V49" s="53"/>
+      <c r="O49" s="52">
+        <v>11143.38</v>
+      </c>
+      <c r="P49" s="52">
+        <v>4675.26</v>
+      </c>
+      <c r="Q49" s="52">
+        <v>6468.119999999999</v>
+      </c>
+      <c r="R49" s="53">
+        <v>0.5804450714235716</v>
+      </c>
+      <c r="S49" s="54">
+        <v>223.22</v>
+      </c>
+      <c r="T49" s="54">
+        <v>102.25</v>
+      </c>
+      <c r="U49" s="54">
+        <v>120.97</v>
+      </c>
+      <c r="V49" s="53">
+        <v>0.5419317265478004</v>
+      </c>
       <c r="W49" s="53"/>
-      <c r="X49" s="55"/>
-      <c r="Y49" s="55"/>
-      <c r="Z49" s="53"/>
-      <c r="AA49" s="56"/>
+      <c r="X49" s="55">
+        <v>1.8598533007334963</v>
+      </c>
+      <c r="Y49" s="55">
+        <v>67.69550512136009</v>
+      </c>
+      <c r="Z49" s="53">
+        <v>0.0075</v>
+      </c>
+      <c r="AA49" s="56">
+        <v>0.23</v>
+      </c>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
         <v>96</v>
@@ -12398,30 +12662,74 @@
       <c r="C56" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
-      <c r="K56" s="52"/>
-      <c r="L56" s="52"/>
-      <c r="M56" s="53"/>
+      <c r="D56" s="52">
+        <v>154527.79</v>
+      </c>
+      <c r="E56" s="52">
+        <v>98562.5</v>
+      </c>
+      <c r="F56" s="52">
+        <v>55965.29000000001</v>
+      </c>
+      <c r="G56" s="53">
+        <v>0.36216974306045535</v>
+      </c>
+      <c r="H56" s="52">
+        <v>108880.28</v>
+      </c>
+      <c r="I56" s="52">
+        <v>90918.83</v>
+      </c>
+      <c r="J56" s="52">
+        <v>74953.01000000001</v>
+      </c>
+      <c r="K56" s="52">
+        <v>71302.07</v>
+      </c>
+      <c r="L56" s="52">
+        <v>3650.9400000000023</v>
+      </c>
+      <c r="M56" s="53">
+        <v>0.04870971826214854</v>
+      </c>
       <c r="N56" s="53"/>
-      <c r="O56" s="52"/>
-      <c r="P56" s="52"/>
-      <c r="Q56" s="52"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="54"/>
-      <c r="T56" s="54"/>
-      <c r="U56" s="54"/>
-      <c r="V56" s="53"/>
+      <c r="O56" s="52">
+        <v>33927.27</v>
+      </c>
+      <c r="P56" s="52">
+        <v>19616.76</v>
+      </c>
+      <c r="Q56" s="52">
+        <v>14310.509999999998</v>
+      </c>
+      <c r="R56" s="53">
+        <v>0.4217996319774624</v>
+      </c>
+      <c r="S56" s="54">
+        <v>679.42</v>
+      </c>
+      <c r="T56" s="54">
+        <v>413</v>
+      </c>
+      <c r="U56" s="54">
+        <v>266.41999999999996</v>
+      </c>
+      <c r="V56" s="53">
+        <v>0.39212858025963315</v>
+      </c>
       <c r="W56" s="53"/>
-      <c r="X56" s="55"/>
-      <c r="Y56" s="55"/>
-      <c r="Z56" s="53"/>
-      <c r="AA56" s="56"/>
+      <c r="X56" s="55">
+        <v>18.50767554479419</v>
+      </c>
+      <c r="Y56" s="55">
+        <v>67.18600078134293</v>
+      </c>
+      <c r="Z56" s="53">
+        <v>0.0776</v>
+      </c>
+      <c r="AA56" s="56">
+        <v>0.2954</v>
+      </c>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
         <v>96</v>
@@ -12805,30 +13113,74 @@
       <c r="C63" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="52"/>
-      <c r="J63" s="52"/>
-      <c r="K63" s="52"/>
-      <c r="L63" s="52"/>
-      <c r="M63" s="53"/>
+      <c r="D63" s="52">
+        <v>20420.56</v>
+      </c>
+      <c r="E63" s="52">
+        <v>16358.37</v>
+      </c>
+      <c r="F63" s="52">
+        <v>4062.1900000000005</v>
+      </c>
+      <c r="G63" s="53">
+        <v>0.19892647410257114</v>
+      </c>
+      <c r="H63" s="52">
+        <v>15859.68</v>
+      </c>
+      <c r="I63" s="52">
+        <v>13601.05</v>
+      </c>
+      <c r="J63" s="52">
+        <v>12689.1</v>
+      </c>
+      <c r="K63" s="52">
+        <v>11685.13</v>
+      </c>
+      <c r="L63" s="52">
+        <v>1003.9700000000012</v>
+      </c>
+      <c r="M63" s="53">
+        <v>0.07912066261594605</v>
+      </c>
       <c r="N63" s="53"/>
-      <c r="O63" s="52"/>
-      <c r="P63" s="52"/>
-      <c r="Q63" s="52"/>
-      <c r="R63" s="53"/>
-      <c r="S63" s="54"/>
-      <c r="T63" s="54"/>
-      <c r="U63" s="54"/>
-      <c r="V63" s="53"/>
+      <c r="O63" s="52">
+        <v>3170.58</v>
+      </c>
+      <c r="P63" s="52">
+        <v>1915.92</v>
+      </c>
+      <c r="Q63" s="52">
+        <v>1254.6599999999999</v>
+      </c>
+      <c r="R63" s="53">
+        <v>0.39571939518952365</v>
+      </c>
+      <c r="S63" s="54">
+        <v>63.5</v>
+      </c>
+      <c r="T63" s="54">
+        <v>47.5</v>
+      </c>
+      <c r="U63" s="54">
+        <v>16</v>
+      </c>
+      <c r="V63" s="53">
+        <v>0.25196850393700787</v>
+      </c>
       <c r="W63" s="53"/>
-      <c r="X63" s="55"/>
-      <c r="Y63" s="55"/>
-      <c r="Z63" s="53"/>
-      <c r="AA63" s="56"/>
+      <c r="X63" s="55">
+        <v>58.04884210526316</v>
+      </c>
+      <c r="Y63" s="55">
+        <v>71.82495570677168</v>
+      </c>
+      <c r="Z63" s="53">
+        <v>0.1686</v>
+      </c>
+      <c r="AA63" s="56">
+        <v>0.2233</v>
+      </c>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
         <v>96</v>
@@ -13160,30 +13512,74 @@
       <c r="C70" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="52"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="52"/>
-      <c r="I70" s="52"/>
-      <c r="J70" s="52"/>
-      <c r="K70" s="52"/>
-      <c r="L70" s="52"/>
-      <c r="M70" s="53"/>
+      <c r="D70" s="52">
+        <v>46303.5</v>
+      </c>
+      <c r="E70" s="52">
+        <v>6131.46</v>
+      </c>
+      <c r="F70" s="52">
+        <v>40172.04</v>
+      </c>
+      <c r="G70" s="53">
+        <v>0.8675810683857592</v>
+      </c>
+      <c r="H70" s="52">
+        <v>34612.41</v>
+      </c>
+      <c r="I70" s="52">
+        <v>9981.43</v>
+      </c>
+      <c r="J70" s="52">
+        <v>26584.530000000002</v>
+      </c>
+      <c r="K70" s="52">
+        <v>9832.65</v>
+      </c>
+      <c r="L70" s="52">
+        <v>16751.880000000005</v>
+      </c>
+      <c r="M70" s="53">
+        <v>0.6301363988755868</v>
+      </c>
       <c r="N70" s="53"/>
-      <c r="O70" s="52"/>
-      <c r="P70" s="52"/>
-      <c r="Q70" s="52"/>
-      <c r="R70" s="53"/>
-      <c r="S70" s="54"/>
-      <c r="T70" s="54"/>
-      <c r="U70" s="54"/>
-      <c r="V70" s="53"/>
+      <c r="O70" s="52">
+        <v>8027.88</v>
+      </c>
+      <c r="P70" s="52">
+        <v>148.78</v>
+      </c>
+      <c r="Q70" s="52">
+        <v>7879.1</v>
+      </c>
+      <c r="R70" s="53">
+        <v>0.9814670872011042</v>
+      </c>
+      <c r="S70" s="54">
+        <v>160.82</v>
+      </c>
+      <c r="T70" s="54">
+        <v>2.75</v>
+      </c>
+      <c r="U70" s="54">
+        <v>158.07</v>
+      </c>
+      <c r="V70" s="53">
+        <v>0.9829001367989056</v>
+      </c>
       <c r="W70" s="53"/>
-      <c r="X70" s="55"/>
-      <c r="Y70" s="55"/>
-      <c r="Z70" s="53"/>
-      <c r="AA70" s="56"/>
+      <c r="X70" s="55">
+        <v>-1399.989090909091</v>
+      </c>
+      <c r="Y70" s="55">
+        <v>72.69676349334662</v>
+      </c>
+      <c r="Z70" s="53">
+        <v>-0.6279</v>
+      </c>
+      <c r="AA70" s="56">
+        <v>0.2525</v>
+      </c>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
         <v>96</v>
@@ -13513,30 +13909,74 @@
       <c r="C77" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="53"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="52"/>
-      <c r="K77" s="52"/>
-      <c r="L77" s="52"/>
-      <c r="M77" s="53"/>
+      <c r="D77" s="52">
+        <v>77166.16</v>
+      </c>
+      <c r="E77" s="52">
+        <v>0</v>
+      </c>
+      <c r="F77" s="52">
+        <v>77166.16</v>
+      </c>
+      <c r="G77" s="53">
+        <v>1</v>
+      </c>
+      <c r="H77" s="52">
+        <v>54302.66</v>
+      </c>
+      <c r="I77" s="52">
+        <v>22353.17</v>
+      </c>
+      <c r="J77" s="52">
+        <v>31383.390000000003</v>
+      </c>
+      <c r="K77" s="52">
+        <v>22353.17</v>
+      </c>
+      <c r="L77" s="52">
+        <v>9030.220000000005</v>
+      </c>
+      <c r="M77" s="53">
+        <v>0.28773883254804544</v>
+      </c>
       <c r="N77" s="53"/>
-      <c r="O77" s="52"/>
-      <c r="P77" s="52"/>
-      <c r="Q77" s="52"/>
-      <c r="R77" s="53"/>
-      <c r="S77" s="54"/>
-      <c r="T77" s="54"/>
-      <c r="U77" s="54"/>
-      <c r="V77" s="53"/>
+      <c r="O77" s="52">
+        <v>22919.27</v>
+      </c>
+      <c r="P77" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="52">
+        <v>22919.27</v>
+      </c>
+      <c r="R77" s="53">
+        <v>1</v>
+      </c>
+      <c r="S77" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="T77" s="54">
+        <v>0</v>
+      </c>
+      <c r="U77" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="V77" s="53">
+        <v>1</v>
+      </c>
       <c r="W77" s="53"/>
-      <c r="X77" s="55"/>
-      <c r="Y77" s="55"/>
-      <c r="Z77" s="53"/>
-      <c r="AA77" s="56"/>
+      <c r="X77" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="55">
+        <v>48.58165977967362</v>
+      </c>
+      <c r="Z77" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="56">
+        <v>0.2963</v>
+      </c>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
         <v>96</v>
@@ -13872,30 +14312,74 @@
       <c r="C84" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="53"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
-      <c r="J84" s="52"/>
-      <c r="K84" s="52"/>
-      <c r="L84" s="52"/>
-      <c r="M84" s="53"/>
+      <c r="D84" s="52">
+        <v>25467.84</v>
+      </c>
+      <c r="E84" s="52">
+        <v>19598.41</v>
+      </c>
+      <c r="F84" s="52">
+        <v>5869.43</v>
+      </c>
+      <c r="G84" s="53">
+        <v>0.2304643817457625</v>
+      </c>
+      <c r="H84" s="52">
+        <v>16606.83</v>
+      </c>
+      <c r="I84" s="52">
+        <v>12729.14</v>
+      </c>
+      <c r="J84" s="52">
+        <v>9659.990000000002</v>
+      </c>
+      <c r="K84" s="52">
+        <v>5354.119999999999</v>
+      </c>
+      <c r="L84" s="52">
+        <v>4305.870000000003</v>
+      </c>
+      <c r="M84" s="53">
+        <v>0.44574269745620876</v>
+      </c>
       <c r="N84" s="53"/>
-      <c r="O84" s="52"/>
-      <c r="P84" s="52"/>
-      <c r="Q84" s="52"/>
-      <c r="R84" s="53"/>
-      <c r="S84" s="54"/>
-      <c r="T84" s="54"/>
-      <c r="U84" s="54"/>
-      <c r="V84" s="53"/>
+      <c r="O84" s="52">
+        <v>6946.84</v>
+      </c>
+      <c r="P84" s="52">
+        <v>7375.02</v>
+      </c>
+      <c r="Q84" s="52">
+        <v>-428.1800000000003</v>
+      </c>
+      <c r="R84" s="53">
+        <v>-0.061636657818518965</v>
+      </c>
+      <c r="S84" s="54">
+        <v>139.07</v>
+      </c>
+      <c r="T84" s="54">
+        <v>143.25</v>
+      </c>
+      <c r="U84" s="54">
+        <v>-4.180000000000007</v>
+      </c>
+      <c r="V84" s="53">
+        <v>-0.030056805925073756</v>
+      </c>
       <c r="W84" s="53"/>
-      <c r="X84" s="55"/>
-      <c r="Y84" s="55"/>
-      <c r="Z84" s="53"/>
-      <c r="AA84" s="56"/>
+      <c r="X84" s="55">
+        <v>47.95301919720768</v>
+      </c>
+      <c r="Y84" s="55">
+        <v>63.7162162306752</v>
+      </c>
+      <c r="Z84" s="53">
+        <v>0.3505</v>
+      </c>
+      <c r="AA84" s="56">
+        <v>0.3479</v>
+      </c>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
         <v>96</v>
@@ -14279,30 +14763,74 @@
       <c r="C91" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="52"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="52"/>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="53"/>
+      <c r="D91" s="67">
+        <v>37083.03</v>
+      </c>
+      <c r="E91" s="67">
+        <v>33023.07</v>
+      </c>
+      <c r="F91" s="52">
+        <v>4059.959999999999</v>
+      </c>
+      <c r="G91" s="53">
+        <v>0.10948296296176444</v>
+      </c>
+      <c r="H91" s="52">
+        <v>27002.93</v>
+      </c>
+      <c r="I91" s="52">
+        <v>25996.77</v>
+      </c>
+      <c r="J91" s="52">
+        <v>15440.32</v>
+      </c>
+      <c r="K91" s="52">
+        <v>15990.78</v>
+      </c>
+      <c r="L91" s="52">
+        <v>-550.460000000001</v>
+      </c>
+      <c r="M91" s="53">
+        <v>-0.0356508155271394</v>
+      </c>
       <c r="N91" s="53"/>
-      <c r="O91" s="52"/>
-      <c r="P91" s="52"/>
-      <c r="Q91" s="52"/>
-      <c r="R91" s="53"/>
-      <c r="S91" s="68"/>
-      <c r="T91" s="68"/>
-      <c r="U91" s="54"/>
-      <c r="V91" s="53"/>
+      <c r="O91" s="52">
+        <v>11562.61</v>
+      </c>
+      <c r="P91" s="52">
+        <v>10005.99</v>
+      </c>
+      <c r="Q91" s="52">
+        <v>1556.6200000000008</v>
+      </c>
+      <c r="R91" s="53">
+        <v>0.13462531383485224</v>
+      </c>
+      <c r="S91" s="68">
+        <v>231.75</v>
+      </c>
+      <c r="T91" s="68">
+        <v>204.75</v>
+      </c>
+      <c r="U91" s="54">
+        <v>27</v>
+      </c>
+      <c r="V91" s="53">
+        <v>0.11650485436893204</v>
+      </c>
       <c r="W91" s="53"/>
-      <c r="X91" s="55"/>
-      <c r="Y91" s="55"/>
-      <c r="Z91" s="53"/>
-      <c r="AA91" s="56"/>
+      <c r="X91" s="55">
+        <v>34.316483516483515</v>
+      </c>
+      <c r="Y91" s="55">
+        <v>43.49557070636461</v>
+      </c>
+      <c r="Z91" s="53">
+        <v>0.21280000000000002</v>
+      </c>
+      <c r="AA91" s="56">
+        <v>0.2718</v>
+      </c>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
         <v>96</v>
@@ -14598,30 +15126,74 @@
       <c r="C98" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="53"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
-      <c r="M98" s="53"/>
+      <c r="D98" s="52">
+        <v>26186.14</v>
+      </c>
+      <c r="E98" s="52">
+        <v>5762.27</v>
+      </c>
+      <c r="F98" s="52">
+        <v>20423.87</v>
+      </c>
+      <c r="G98" s="53">
+        <v>0.7799496222047235</v>
+      </c>
+      <c r="H98" s="52">
+        <v>19428.98</v>
+      </c>
+      <c r="I98" s="52">
+        <v>7925.81</v>
+      </c>
+      <c r="J98" s="52">
+        <v>12051.32</v>
+      </c>
+      <c r="K98" s="52">
+        <v>7679.910000000001</v>
+      </c>
+      <c r="L98" s="52">
+        <v>4371.409999999999</v>
+      </c>
+      <c r="M98" s="53">
+        <v>0.36273287905391266</v>
+      </c>
       <c r="N98" s="53"/>
-      <c r="O98" s="52"/>
-      <c r="P98" s="52"/>
-      <c r="Q98" s="52"/>
-      <c r="R98" s="53"/>
-      <c r="S98" s="54"/>
-      <c r="T98" s="54"/>
-      <c r="U98" s="54"/>
-      <c r="V98" s="53"/>
+      <c r="O98" s="52">
+        <v>7377.66</v>
+      </c>
+      <c r="P98" s="52">
+        <v>245.9</v>
+      </c>
+      <c r="Q98" s="52">
+        <v>7131.76</v>
+      </c>
+      <c r="R98" s="53">
+        <v>0.9666696486419813</v>
+      </c>
+      <c r="S98" s="54">
+        <v>147.9</v>
+      </c>
+      <c r="T98" s="54">
+        <v>5</v>
+      </c>
+      <c r="U98" s="54">
+        <v>142.9</v>
+      </c>
+      <c r="V98" s="53">
+        <v>0.9661933739012847</v>
+      </c>
       <c r="W98" s="53"/>
-      <c r="X98" s="55"/>
-      <c r="Y98" s="55"/>
-      <c r="Z98" s="53"/>
-      <c r="AA98" s="56"/>
+      <c r="X98" s="55">
+        <v>-432.70799999999997</v>
+      </c>
+      <c r="Y98" s="55">
+        <v>45.687352144692355</v>
+      </c>
+      <c r="Z98" s="53">
+        <v>-0.37549999999999994</v>
+      </c>
+      <c r="AA98" s="56">
+        <v>0.258</v>
+      </c>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
         <v>96</v>
@@ -15005,30 +15577,74 @@
       <c r="C105" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D105" s="52"/>
-      <c r="E105" s="69"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="52"/>
-      <c r="I105" s="52"/>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52"/>
-      <c r="L105" s="52"/>
-      <c r="M105" s="53"/>
+      <c r="D105" s="52">
+        <v>32473.02</v>
+      </c>
+      <c r="E105" s="69">
+        <v>33188.03</v>
+      </c>
+      <c r="F105" s="52">
+        <v>-715.0099999999984</v>
+      </c>
+      <c r="G105" s="53">
+        <v>-0.022018586506582952</v>
+      </c>
+      <c r="H105" s="52">
+        <v>23075.07</v>
+      </c>
+      <c r="I105" s="52">
+        <v>31131.57</v>
+      </c>
+      <c r="J105" s="52">
+        <v>12691.21</v>
+      </c>
+      <c r="K105" s="52">
+        <v>15390.63</v>
+      </c>
+      <c r="L105" s="52">
+        <v>-2699.42</v>
+      </c>
+      <c r="M105" s="53">
+        <v>-0.21269997108234756</v>
+      </c>
       <c r="N105" s="53"/>
-      <c r="O105" s="52"/>
-      <c r="P105" s="52"/>
-      <c r="Q105" s="52"/>
-      <c r="R105" s="53"/>
-      <c r="S105" s="54"/>
-      <c r="T105" s="54"/>
-      <c r="U105" s="54"/>
-      <c r="V105" s="53"/>
+      <c r="O105" s="52">
+        <v>10383.86</v>
+      </c>
+      <c r="P105" s="52">
+        <v>15740.94</v>
+      </c>
+      <c r="Q105" s="52">
+        <v>-5357.08</v>
+      </c>
+      <c r="R105" s="53">
+        <v>-0.5159044902377343</v>
+      </c>
+      <c r="S105" s="54">
+        <v>208.2</v>
+      </c>
+      <c r="T105" s="54">
+        <v>317.25</v>
+      </c>
+      <c r="U105" s="54">
+        <v>-109.05000000000001</v>
+      </c>
+      <c r="V105" s="53">
+        <v>-0.5237752161383286</v>
+      </c>
       <c r="W105" s="53"/>
-      <c r="X105" s="55"/>
-      <c r="Y105" s="55"/>
-      <c r="Z105" s="53"/>
-      <c r="AA105" s="56"/>
+      <c r="X105" s="55">
+        <v>6.482143420015761</v>
+      </c>
+      <c r="Y105" s="55">
+        <v>45.139084580403456</v>
+      </c>
+      <c r="Z105" s="53">
+        <v>0.062</v>
+      </c>
+      <c r="AA105" s="56">
+        <v>0.2894</v>
+      </c>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
         <v>96</v>
@@ -15414,30 +16030,74 @@
       <c r="C112" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D112" s="52"/>
-      <c r="E112" s="52"/>
-      <c r="F112" s="52"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="52"/>
-      <c r="I112" s="52"/>
-      <c r="J112" s="52"/>
-      <c r="K112" s="52"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="53"/>
+      <c r="D112" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="E112" s="52">
+        <v>0</v>
+      </c>
+      <c r="F112" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="G112" s="53">
+        <v>1</v>
+      </c>
+      <c r="H112" s="52">
+        <v>37601.88</v>
+      </c>
+      <c r="I112" s="52">
+        <v>38195.76</v>
+      </c>
+      <c r="J112" s="52">
+        <v>21415.85</v>
+      </c>
+      <c r="K112" s="52">
+        <v>19158.27</v>
+      </c>
+      <c r="L112" s="52">
+        <v>2257.579999999998</v>
+      </c>
+      <c r="M112" s="53">
+        <v>0.10541631548596009</v>
+      </c>
       <c r="N112" s="53"/>
-      <c r="O112" s="52"/>
-      <c r="P112" s="52"/>
-      <c r="Q112" s="52"/>
-      <c r="R112" s="53"/>
-      <c r="S112" s="54"/>
-      <c r="T112" s="54"/>
-      <c r="U112" s="54"/>
-      <c r="V112" s="53"/>
+      <c r="O112" s="52">
+        <v>16186.03</v>
+      </c>
+      <c r="P112" s="52">
+        <v>19037.49</v>
+      </c>
+      <c r="Q112" s="52">
+        <v>-2851.460000000001</v>
+      </c>
+      <c r="R112" s="53">
+        <v>-0.1761679670678975</v>
+      </c>
+      <c r="S112" s="54">
+        <v>324.19</v>
+      </c>
+      <c r="T112" s="54">
+        <v>412.5</v>
+      </c>
+      <c r="U112" s="54">
+        <v>-88.31</v>
+      </c>
+      <c r="V112" s="53">
+        <v>-0.2724019864894044</v>
+      </c>
       <c r="W112" s="53"/>
-      <c r="X112" s="55"/>
-      <c r="Y112" s="55"/>
-      <c r="Z112" s="53"/>
-      <c r="AA112" s="56"/>
+      <c r="X112" s="55">
+        <v>-6.6456484848484845</v>
+      </c>
+      <c r="Y112" s="55">
+        <v>65.70431400737223</v>
+      </c>
+      <c r="Z112" s="53">
+        <v>-0.07730000000000001</v>
+      </c>
+      <c r="AA112" s="56">
+        <v>0.3616</v>
+      </c>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
         <v>96</v>
@@ -15747,32 +16407,74 @@
       <c r="C119" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D119" s="52"/>
-      <c r="E119" s="52"/>
+      <c r="D119" s="52">
+        <v>21404.82</v>
+      </c>
+      <c r="E119" s="52">
+        <v>0</v>
+      </c>
       <c r="F119" s="52">
-        <v>0</v>
-      </c>
-      <c r="G119" s="53"/>
-      <c r="H119" s="52"/>
-      <c r="I119" s="52"/>
-      <c r="J119" s="52"/>
-      <c r="K119" s="52"/>
-      <c r="L119" s="52"/>
-      <c r="M119" s="53"/>
+        <v>21404.82</v>
+      </c>
+      <c r="G119" s="53">
+        <v>1</v>
+      </c>
+      <c r="H119" s="52">
+        <v>17514.09</v>
+      </c>
+      <c r="I119" s="52">
+        <v>0</v>
+      </c>
+      <c r="J119" s="52">
+        <v>13318.880000000001</v>
+      </c>
+      <c r="K119" s="52">
+        <v>0</v>
+      </c>
+      <c r="L119" s="52">
+        <v>13318.880000000001</v>
+      </c>
+      <c r="M119" s="53">
+        <v>1</v>
+      </c>
       <c r="N119" s="53"/>
-      <c r="O119" s="52"/>
-      <c r="P119" s="52"/>
-      <c r="Q119" s="52"/>
-      <c r="R119" s="53"/>
-      <c r="S119" s="54"/>
-      <c r="T119" s="54"/>
-      <c r="U119" s="54"/>
-      <c r="V119" s="53"/>
+      <c r="O119" s="52">
+        <v>4195.21</v>
+      </c>
+      <c r="P119" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="52">
+        <v>4195.21</v>
+      </c>
+      <c r="R119" s="53">
+        <v>1</v>
+      </c>
+      <c r="S119" s="54">
+        <v>84.05</v>
+      </c>
+      <c r="T119" s="54">
+        <v>0</v>
+      </c>
+      <c r="U119" s="54">
+        <v>84.05</v>
+      </c>
+      <c r="V119" s="53">
+        <v>1</v>
+      </c>
       <c r="W119" s="53"/>
-      <c r="X119" s="55"/>
-      <c r="Y119" s="55"/>
-      <c r="Z119" s="53"/>
-      <c r="AA119" s="56"/>
+      <c r="X119" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="55">
+        <v>46.29062162403328</v>
+      </c>
+      <c r="Z119" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="56">
+        <v>0.1818</v>
+      </c>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
         <v>96</v>
@@ -16146,32 +16848,74 @@
       <c r="C126" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D126" s="52"/>
-      <c r="E126" s="52"/>
+      <c r="D126" s="52">
+        <v>99768.39</v>
+      </c>
+      <c r="E126" s="52">
+        <v>15366.74</v>
+      </c>
       <c r="F126" s="52">
-        <v>0</v>
-      </c>
-      <c r="G126" s="53"/>
-      <c r="H126" s="52"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="53"/>
+        <v>84401.65</v>
+      </c>
+      <c r="G126" s="53">
+        <v>0.8459758647002321</v>
+      </c>
+      <c r="H126" s="52">
+        <v>81719.58</v>
+      </c>
+      <c r="I126" s="52">
+        <v>18551.86</v>
+      </c>
+      <c r="J126" s="52">
+        <v>67238.96</v>
+      </c>
+      <c r="K126" s="52">
+        <v>14369.1</v>
+      </c>
+      <c r="L126" s="52">
+        <v>52869.86000000001</v>
+      </c>
+      <c r="M126" s="53">
+        <v>0.7862980034194461</v>
+      </c>
       <c r="N126" s="53"/>
-      <c r="O126" s="52"/>
-      <c r="P126" s="52"/>
-      <c r="Q126" s="52"/>
-      <c r="R126" s="53"/>
-      <c r="S126" s="54"/>
-      <c r="T126" s="54"/>
-      <c r="U126" s="54"/>
-      <c r="V126" s="53"/>
+      <c r="O126" s="52">
+        <v>14480.62</v>
+      </c>
+      <c r="P126" s="52">
+        <v>4182.76</v>
+      </c>
+      <c r="Q126" s="52">
+        <v>10297.86</v>
+      </c>
+      <c r="R126" s="53">
+        <v>0.7111477271000828</v>
+      </c>
+      <c r="S126" s="54">
+        <v>290.15</v>
+      </c>
+      <c r="T126" s="54">
+        <v>91.75</v>
+      </c>
+      <c r="U126" s="54">
+        <v>198.39999999999998</v>
+      </c>
+      <c r="V126" s="53">
+        <v>0.6837842495261072</v>
+      </c>
       <c r="W126" s="53"/>
-      <c r="X126" s="55"/>
-      <c r="Y126" s="55"/>
-      <c r="Z126" s="53"/>
-      <c r="AA126" s="56"/>
+      <c r="X126" s="55">
+        <v>-34.715204359673024</v>
+      </c>
+      <c r="Y126" s="55">
+        <v>62.2051177714286</v>
+      </c>
+      <c r="Z126" s="53">
+        <v>-0.2073</v>
+      </c>
+      <c r="AA126" s="56">
+        <v>0.1809</v>
+      </c>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
         <v>96</v>
@@ -16468,30 +17212,74 @@
       <c r="C133" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D133" s="52"/>
-      <c r="E133" s="52"/>
-      <c r="F133" s="52"/>
-      <c r="G133" s="53"/>
-      <c r="H133" s="52"/>
-      <c r="I133" s="52"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
-      <c r="L133" s="52"/>
-      <c r="M133" s="53"/>
+      <c r="D133" s="52">
+        <v>31802.41</v>
+      </c>
+      <c r="E133" s="52">
+        <v>14370.83</v>
+      </c>
+      <c r="F133" s="52">
+        <v>17431.58</v>
+      </c>
+      <c r="G133" s="53">
+        <v>0.5481213530672676</v>
+      </c>
+      <c r="H133" s="52">
+        <v>23448.14</v>
+      </c>
+      <c r="I133" s="52">
+        <v>11238.62</v>
+      </c>
+      <c r="J133" s="52">
+        <v>15632.029999999999</v>
+      </c>
+      <c r="K133" s="52">
+        <v>11154.51</v>
+      </c>
+      <c r="L133" s="52">
+        <v>4477.519999999999</v>
+      </c>
+      <c r="M133" s="53">
+        <v>0.2864324083308437</v>
+      </c>
       <c r="N133" s="53"/>
-      <c r="O133" s="52"/>
-      <c r="P133" s="52"/>
-      <c r="Q133" s="52"/>
-      <c r="R133" s="53"/>
-      <c r="S133" s="54"/>
-      <c r="T133" s="54"/>
-      <c r="U133" s="54"/>
-      <c r="V133" s="53"/>
+      <c r="O133" s="52">
+        <v>7816.11</v>
+      </c>
+      <c r="P133" s="52">
+        <v>84.11</v>
+      </c>
+      <c r="Q133" s="52">
+        <v>7732</v>
+      </c>
+      <c r="R133" s="53">
+        <v>0.989238892492557</v>
+      </c>
+      <c r="S133" s="54">
+        <v>156.69</v>
+      </c>
+      <c r="T133" s="54">
+        <v>2</v>
+      </c>
+      <c r="U133" s="54">
+        <v>154.69</v>
+      </c>
+      <c r="V133" s="53">
+        <v>0.9872359435828706</v>
+      </c>
       <c r="W133" s="53"/>
-      <c r="X133" s="55"/>
-      <c r="Y133" s="55"/>
-      <c r="Z133" s="53"/>
-      <c r="AA133" s="56"/>
+      <c r="X133" s="55">
+        <v>1566.105</v>
+      </c>
+      <c r="Y133" s="55">
+        <v>53.31719360265494</v>
+      </c>
+      <c r="Z133" s="53">
+        <v>0.218</v>
+      </c>
+      <c r="AA133" s="56">
+        <v>0.2627</v>
+      </c>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
         <v>96</v>
@@ -16875,30 +17663,74 @@
       <c r="C140" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D140" s="52"/>
-      <c r="E140" s="52"/>
-      <c r="F140" s="52"/>
-      <c r="G140" s="53"/>
-      <c r="H140" s="52"/>
-      <c r="I140" s="52"/>
-      <c r="J140" s="52"/>
-      <c r="K140" s="52"/>
-      <c r="L140" s="52"/>
-      <c r="M140" s="53"/>
+      <c r="D140" s="52">
+        <v>30749.24</v>
+      </c>
+      <c r="E140" s="52">
+        <v>30749.24</v>
+      </c>
+      <c r="F140" s="52">
+        <v>0</v>
+      </c>
+      <c r="G140" s="53">
+        <v>0</v>
+      </c>
+      <c r="H140" s="52">
+        <v>22587.89</v>
+      </c>
+      <c r="I140" s="52">
+        <v>25550.31</v>
+      </c>
+      <c r="J140" s="52">
+        <v>12565.06</v>
+      </c>
+      <c r="K140" s="52">
+        <v>11750.840000000002</v>
+      </c>
+      <c r="L140" s="52">
+        <v>814.2199999999975</v>
+      </c>
+      <c r="M140" s="53">
+        <v>0.06480032725669416</v>
+      </c>
       <c r="N140" s="53"/>
-      <c r="O140" s="52"/>
-      <c r="P140" s="52"/>
-      <c r="Q140" s="52"/>
-      <c r="R140" s="53"/>
-      <c r="S140" s="54"/>
-      <c r="T140" s="54"/>
-      <c r="U140" s="54"/>
-      <c r="V140" s="53"/>
+      <c r="O140" s="52">
+        <v>10022.83</v>
+      </c>
+      <c r="P140" s="52">
+        <v>13799.47</v>
+      </c>
+      <c r="Q140" s="52">
+        <v>-3776.6399999999994</v>
+      </c>
+      <c r="R140" s="53">
+        <v>-0.37680375702271707</v>
+      </c>
+      <c r="S140" s="54">
+        <v>200.82</v>
+      </c>
+      <c r="T140" s="54">
+        <v>278.25</v>
+      </c>
+      <c r="U140" s="54">
+        <v>-77.43</v>
+      </c>
+      <c r="V140" s="53">
+        <v>-0.3855691664176875</v>
+      </c>
       <c r="W140" s="53"/>
-      <c r="X140" s="55"/>
-      <c r="Y140" s="55"/>
-      <c r="Z140" s="53"/>
-      <c r="AA140" s="56"/>
+      <c r="X140" s="55">
+        <v>18.68438454627134</v>
+      </c>
+      <c r="Y140" s="55">
+        <v>40.64013272149188</v>
+      </c>
+      <c r="Z140" s="53">
+        <v>0.1691</v>
+      </c>
+      <c r="AA140" s="56">
+        <v>0.2654</v>
+      </c>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
         <v>96</v>
@@ -17196,30 +18028,74 @@
       <c r="C147" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D147" s="52"/>
-      <c r="E147" s="52"/>
-      <c r="F147" s="52"/>
-      <c r="G147" s="53"/>
-      <c r="H147" s="52"/>
-      <c r="I147" s="52"/>
-      <c r="J147" s="52"/>
-      <c r="K147" s="52"/>
-      <c r="L147" s="52"/>
-      <c r="M147" s="53"/>
+      <c r="D147" s="52">
+        <v>268228.26</v>
+      </c>
+      <c r="E147" s="52">
+        <v>9034.53</v>
+      </c>
+      <c r="F147" s="52">
+        <v>259193.73</v>
+      </c>
+      <c r="G147" s="53">
+        <v>0.9663177548853353</v>
+      </c>
+      <c r="H147" s="52">
+        <v>238611.58</v>
+      </c>
+      <c r="I147" s="52">
+        <v>6362.08</v>
+      </c>
+      <c r="J147" s="52">
+        <v>214154.25</v>
+      </c>
+      <c r="K147" s="52">
+        <v>3465.35</v>
+      </c>
+      <c r="L147" s="52">
+        <v>210688.9</v>
+      </c>
+      <c r="M147" s="53">
+        <v>0.9838184392791645</v>
+      </c>
       <c r="N147" s="53"/>
-      <c r="O147" s="52"/>
-      <c r="P147" s="52"/>
-      <c r="Q147" s="52"/>
-      <c r="R147" s="53"/>
-      <c r="S147" s="54"/>
-      <c r="T147" s="54"/>
-      <c r="U147" s="54"/>
-      <c r="V147" s="53"/>
+      <c r="O147" s="52">
+        <v>24457.33</v>
+      </c>
+      <c r="P147" s="52">
+        <v>2896.73</v>
+      </c>
+      <c r="Q147" s="52">
+        <v>21560.600000000002</v>
+      </c>
+      <c r="R147" s="53">
+        <v>0.8815598432044708</v>
+      </c>
+      <c r="S147" s="54">
+        <v>497.55</v>
+      </c>
+      <c r="T147" s="54">
+        <v>58.25</v>
+      </c>
+      <c r="U147" s="54">
+        <v>439.3</v>
+      </c>
+      <c r="V147" s="53">
+        <v>0.8829263390614008</v>
+      </c>
       <c r="W147" s="53"/>
-      <c r="X147" s="55"/>
-      <c r="Y147" s="55"/>
-      <c r="Z147" s="53"/>
-      <c r="AA147" s="56"/>
+      <c r="X147" s="55">
+        <v>45.878969957081544</v>
+      </c>
+      <c r="Y147" s="55">
+        <v>59.525035875791396</v>
+      </c>
+      <c r="Z147" s="53">
+        <v>0.2958</v>
+      </c>
+      <c r="AA147" s="56">
+        <v>0.1104</v>
+      </c>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
         <v>96</v>
@@ -17549,30 +18425,74 @@
       <c r="C154" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D154" s="52"/>
-      <c r="E154" s="52"/>
-      <c r="F154" s="52"/>
-      <c r="G154" s="53"/>
-      <c r="H154" s="52"/>
-      <c r="I154" s="52"/>
-      <c r="J154" s="52"/>
-      <c r="K154" s="52"/>
-      <c r="L154" s="52"/>
-      <c r="M154" s="53"/>
+      <c r="D154" s="52">
+        <v>32773.41</v>
+      </c>
+      <c r="E154" s="52">
+        <v>32773.41</v>
+      </c>
+      <c r="F154" s="52">
+        <v>0</v>
+      </c>
+      <c r="G154" s="53">
+        <v>0</v>
+      </c>
+      <c r="H154" s="52">
+        <v>22750.99</v>
+      </c>
+      <c r="I154" s="52">
+        <v>22254.11</v>
+      </c>
+      <c r="J154" s="52">
+        <v>12243.410000000002</v>
+      </c>
+      <c r="K154" s="52">
+        <v>9324.41</v>
+      </c>
+      <c r="L154" s="52">
+        <v>2919.000000000002</v>
+      </c>
+      <c r="M154" s="53">
+        <v>0.23841397127107575</v>
+      </c>
       <c r="N154" s="53"/>
-      <c r="O154" s="52"/>
-      <c r="P154" s="52"/>
-      <c r="Q154" s="52"/>
-      <c r="R154" s="53"/>
-      <c r="S154" s="54"/>
-      <c r="T154" s="54"/>
-      <c r="U154" s="54"/>
-      <c r="V154" s="53"/>
+      <c r="O154" s="52">
+        <v>10507.58</v>
+      </c>
+      <c r="P154" s="52">
+        <v>12929.7</v>
+      </c>
+      <c r="Q154" s="52">
+        <v>-2422.120000000001</v>
+      </c>
+      <c r="R154" s="53">
+        <v>-0.23051168775303169</v>
+      </c>
+      <c r="S154" s="54">
+        <v>210.6</v>
+      </c>
+      <c r="T154" s="54">
+        <v>260.75</v>
+      </c>
+      <c r="U154" s="54">
+        <v>-50.150000000000006</v>
+      </c>
+      <c r="V154" s="53">
+        <v>-0.2381291547958215</v>
+      </c>
       <c r="W154" s="53"/>
-      <c r="X154" s="55"/>
-      <c r="Y154" s="55"/>
-      <c r="Z154" s="53"/>
-      <c r="AA154" s="56"/>
+      <c r="X154" s="55">
+        <v>40.342473633748796</v>
+      </c>
+      <c r="Y154" s="55">
+        <v>47.58984852136751</v>
+      </c>
+      <c r="Z154" s="53">
+        <v>0.321</v>
+      </c>
+      <c r="AA154" s="56">
+        <v>0.3058</v>
+      </c>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
         <v>96</v>
@@ -17904,34 +18824,74 @@
       <c r="C161" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D161" s="52"/>
-      <c r="E161" s="52"/>
-      <c r="F161" s="52"/>
-      <c r="G161" s="53"/>
-      <c r="H161" s="52"/>
-      <c r="I161" s="52"/>
+      <c r="D161" s="52">
+        <v>17899.33</v>
+      </c>
+      <c r="E161" s="52">
+        <v>13424.5</v>
+      </c>
+      <c r="F161" s="52">
+        <v>4474.830000000002</v>
+      </c>
+      <c r="G161" s="53">
+        <v>0.24999986032996774</v>
+      </c>
+      <c r="H161" s="52">
+        <v>13919.4</v>
+      </c>
+      <c r="I161" s="52">
+        <v>10424.13</v>
+      </c>
       <c r="J161" s="52">
-        <v>0</v>
+        <v>8410.93</v>
       </c>
       <c r="K161" s="52">
-        <v>0</v>
-      </c>
-      <c r="L161" s="52"/>
-      <c r="M161" s="53"/>
+        <v>7300.139999999999</v>
+      </c>
+      <c r="L161" s="52">
+        <v>1110.7900000000009</v>
+      </c>
+      <c r="M161" s="53">
+        <v>0.13206506295974416</v>
+      </c>
       <c r="N161" s="53"/>
-      <c r="O161" s="52"/>
-      <c r="P161" s="52"/>
-      <c r="Q161" s="52"/>
-      <c r="R161" s="53"/>
-      <c r="S161" s="54"/>
-      <c r="T161" s="54"/>
-      <c r="U161" s="54"/>
-      <c r="V161" s="53"/>
+      <c r="O161" s="52">
+        <v>5508.47</v>
+      </c>
+      <c r="P161" s="52">
+        <v>3123.99</v>
+      </c>
+      <c r="Q161" s="52">
+        <v>2384.4800000000005</v>
+      </c>
+      <c r="R161" s="53">
+        <v>0.43287519038861977</v>
+      </c>
+      <c r="S161" s="54">
+        <v>110.44</v>
+      </c>
+      <c r="T161" s="54">
+        <v>60.75</v>
+      </c>
+      <c r="U161" s="54">
+        <v>49.69</v>
+      </c>
+      <c r="V161" s="53">
+        <v>0.44992756247736326</v>
+      </c>
       <c r="W161" s="53"/>
-      <c r="X161" s="55"/>
-      <c r="Y161" s="55"/>
-      <c r="Z161" s="53"/>
-      <c r="AA161" s="56"/>
+      <c r="X161" s="55">
+        <v>49.388806584362136</v>
+      </c>
+      <c r="Y161" s="55">
+        <v>36.03704967040926</v>
+      </c>
+      <c r="Z161" s="53">
+        <v>0.2235</v>
+      </c>
+      <c r="AA161" s="56">
+        <v>0.2224</v>
+      </c>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
         <v>96</v>
@@ -18941,30 +19901,74 @@
       <c r="C182" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D182" s="52"/>
-      <c r="E182" s="52"/>
-      <c r="F182" s="52"/>
-      <c r="G182" s="53"/>
-      <c r="H182" s="52"/>
-      <c r="I182" s="52"/>
-      <c r="J182" s="52"/>
-      <c r="K182" s="52"/>
-      <c r="L182" s="52"/>
-      <c r="M182" s="53"/>
+      <c r="D182" s="52">
+        <v>16897.53</v>
+      </c>
+      <c r="E182" s="52">
+        <v>5491.7</v>
+      </c>
+      <c r="F182" s="52">
+        <v>11405.829999999998</v>
+      </c>
+      <c r="G182" s="53">
+        <v>0.6749998372543206</v>
+      </c>
+      <c r="H182" s="52">
+        <v>9226.27</v>
+      </c>
+      <c r="I182" s="52">
+        <v>3702.78</v>
+      </c>
+      <c r="J182" s="52">
+        <v>2977.1100000000006</v>
+      </c>
+      <c r="K182" s="52">
+        <v>2335.9700000000003</v>
+      </c>
+      <c r="L182" s="52">
+        <v>641.1400000000003</v>
+      </c>
+      <c r="M182" s="53">
+        <v>0.2153565034546927</v>
+      </c>
       <c r="N182" s="53"/>
-      <c r="O182" s="52"/>
-      <c r="P182" s="52"/>
-      <c r="Q182" s="52"/>
-      <c r="R182" s="53"/>
-      <c r="S182" s="54"/>
-      <c r="T182" s="54"/>
-      <c r="U182" s="54"/>
-      <c r="V182" s="53"/>
+      <c r="O182" s="52">
+        <v>6249.16</v>
+      </c>
+      <c r="P182" s="52">
+        <v>1366.81</v>
+      </c>
+      <c r="Q182" s="52">
+        <v>4882.35</v>
+      </c>
+      <c r="R182" s="53">
+        <v>0.7812810041669601</v>
+      </c>
+      <c r="S182" s="54">
+        <v>125.17</v>
+      </c>
+      <c r="T182" s="54">
+        <v>23.75</v>
+      </c>
+      <c r="U182" s="54">
+        <v>101.42</v>
+      </c>
+      <c r="V182" s="53">
+        <v>0.8102580490532876</v>
+      </c>
       <c r="W182" s="53"/>
-      <c r="X182" s="55"/>
-      <c r="Y182" s="55"/>
-      <c r="Z182" s="53"/>
-      <c r="AA182" s="56"/>
+      <c r="X182" s="55">
+        <v>75.32294736842105</v>
+      </c>
+      <c r="Y182" s="55">
+        <v>61.286703843093385</v>
+      </c>
+      <c r="Z182" s="53">
+        <v>0.3257</v>
+      </c>
+      <c r="AA182" s="56">
+        <v>0.454</v>
+      </c>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
         <v>96</v>
@@ -21718,7 +22722,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="52">
-        <v>51687.05</v>
+        <v>51285.36</v>
       </c>
       <c r="E4" s="52">
         <f>C4-D4</f>
@@ -21790,7 +22794,7 @@
         <v>3912</v>
       </c>
       <c r="D6" s="52">
-        <v>6513.389999999999</v>
+        <v>7555.1500000000015</v>
       </c>
       <c r="E6" s="52">
         <f>C6-D6</f>
@@ -21937,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="52">
-        <v>5315.239999999991</v>
+        <v>8827.48999999999</v>
       </c>
       <c r="E10" s="52">
         <f>C10-D10</f>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9737,54 +9737,54 @@
         <v>199128.99</v>
       </c>
       <c r="I7" s="52">
-        <v>164808.35</v>
+        <v>165210.04</v>
       </c>
       <c r="J7" s="52">
         <v>172860.11</v>
       </c>
       <c r="K7" s="52">
-        <v>137510.76</v>
+        <v>137410.69</v>
       </c>
       <c r="L7" s="52">
-        <v>35349.34999999998</v>
+        <v>35449.419999999984</v>
       </c>
       <c r="M7" s="53">
-        <v>0.20449686165304407</v>
+        <v>0.20507576907130273</v>
       </c>
       <c r="N7" s="53"/>
       <c r="O7" s="52">
         <v>26268.88</v>
       </c>
       <c r="P7" s="52">
-        <v>27297.59</v>
+        <v>27799.35</v>
       </c>
       <c r="Q7" s="52">
-        <v>-1028.7099999999991</v>
+        <v>-1530.4699999999975</v>
       </c>
       <c r="R7" s="53">
-        <v>-0.03916078645149695</v>
+        <v>-0.05826171500269511</v>
       </c>
       <c r="S7" s="54">
         <v>530.95</v>
       </c>
       <c r="T7" s="54">
-        <v>548</v>
+        <v>556.5</v>
       </c>
       <c r="U7" s="54">
-        <v>-17.049999999999955</v>
+        <v>-25.549999999999955</v>
       </c>
       <c r="V7" s="53">
-        <v>-0.032112251624446655</v>
+        <v>-0.04812129202373096</v>
       </c>
       <c r="W7" s="53"/>
       <c r="X7" s="55">
-        <v>75.01377737226278</v>
+        <v>73.14619946091645</v>
       </c>
       <c r="Y7" s="55">
         <v>65.45490166985587</v>
       </c>
       <c r="Z7" s="53">
-        <v>0.1996</v>
+        <v>0.1977</v>
       </c>
       <c r="AA7" s="56">
         <v>0.1486</v>
@@ -19536,32 +19536,74 @@
       <c r="C175" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D175" s="52"/>
-      <c r="E175" s="52"/>
-      <c r="F175" s="52"/>
-      <c r="G175" s="53"/>
-      <c r="H175" s="52"/>
-      <c r="I175" s="52"/>
-      <c r="J175" s="52"/>
+      <c r="D175" s="52">
+        <v>146237.11</v>
+      </c>
+      <c r="E175" s="52">
+        <v>94266.45</v>
+      </c>
+      <c r="F175" s="52">
+        <v>51970.65999999999</v>
+      </c>
+      <c r="G175" s="53">
+        <v>0.355386262761894</v>
+      </c>
+      <c r="H175" s="52">
+        <v>114651.87</v>
+      </c>
+      <c r="I175" s="52">
+        <v>95876.35</v>
+      </c>
+      <c r="J175" s="52">
+        <v>82888.07999999999</v>
+      </c>
       <c r="K175" s="52">
-        <v>0</v>
-      </c>
-      <c r="L175" s="52"/>
-      <c r="M175" s="53"/>
+        <v>74503.91</v>
+      </c>
+      <c r="L175" s="52">
+        <v>8384.169999999984</v>
+      </c>
+      <c r="M175" s="53">
+        <v>0.10115049112007402</v>
+      </c>
       <c r="N175" s="53"/>
-      <c r="O175" s="52"/>
-      <c r="P175" s="52"/>
-      <c r="Q175" s="52"/>
-      <c r="R175" s="53"/>
-      <c r="S175" s="54"/>
-      <c r="T175" s="54"/>
-      <c r="U175" s="54"/>
-      <c r="V175" s="53"/>
+      <c r="O175" s="52">
+        <v>31763.79</v>
+      </c>
+      <c r="P175" s="52">
+        <v>21372.44</v>
+      </c>
+      <c r="Q175" s="52">
+        <v>10391.350000000002</v>
+      </c>
+      <c r="R175" s="53">
+        <v>0.32714452525973764</v>
+      </c>
+      <c r="S175" s="54">
+        <v>659.73</v>
+      </c>
+      <c r="T175" s="54">
+        <v>430</v>
+      </c>
+      <c r="U175" s="54">
+        <v>229.73000000000002</v>
+      </c>
+      <c r="V175" s="53">
+        <v>0.34821821048004487</v>
+      </c>
       <c r="W175" s="53"/>
-      <c r="X175" s="55"/>
-      <c r="Y175" s="55"/>
-      <c r="Z175" s="53"/>
-      <c r="AA175" s="56"/>
+      <c r="X175" s="55">
+        <v>-3.7439534883720933</v>
+      </c>
+      <c r="Y175" s="55">
+        <v>47.87601261940491</v>
+      </c>
+      <c r="Z175" s="53">
+        <v>-0.0171</v>
+      </c>
+      <c r="AA175" s="56">
+        <v>0.216</v>
+      </c>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
         <v>96</v>
@@ -20637,32 +20679,74 @@
       <c r="C196" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D196" s="52"/>
-      <c r="E196" s="52"/>
-      <c r="F196" s="52"/>
-      <c r="G196" s="53"/>
-      <c r="H196" s="52"/>
-      <c r="I196" s="52"/>
-      <c r="J196" s="52"/>
+      <c r="D196" s="52">
+        <v>23770.95</v>
+      </c>
+      <c r="E196" s="52">
+        <v>0</v>
+      </c>
+      <c r="F196" s="52">
+        <v>23770.95</v>
+      </c>
+      <c r="G196" s="53">
+        <v>1</v>
+      </c>
+      <c r="H196" s="52">
+        <v>14310.96</v>
+      </c>
+      <c r="I196" s="52">
+        <v>7180.07</v>
+      </c>
+      <c r="J196" s="52">
+        <v>7389.339999999999</v>
+      </c>
       <c r="K196" s="52">
-        <v>0</v>
-      </c>
-      <c r="L196" s="52"/>
-      <c r="M196" s="53"/>
+        <v>6849.16</v>
+      </c>
+      <c r="L196" s="52">
+        <v>540.1799999999994</v>
+      </c>
+      <c r="M196" s="53">
+        <v>0.07310260456278903</v>
+      </c>
       <c r="N196" s="53"/>
-      <c r="O196" s="52"/>
-      <c r="P196" s="52"/>
-      <c r="Q196" s="52"/>
-      <c r="R196" s="53"/>
-      <c r="S196" s="54"/>
-      <c r="T196" s="54"/>
-      <c r="U196" s="54"/>
-      <c r="V196" s="53"/>
+      <c r="O196" s="52">
+        <v>6921.62</v>
+      </c>
+      <c r="P196" s="52">
+        <v>330.91</v>
+      </c>
+      <c r="Q196" s="52">
+        <v>6590.71</v>
+      </c>
+      <c r="R196" s="53">
+        <v>0.9521918279246766</v>
+      </c>
+      <c r="S196" s="54">
+        <v>140.15</v>
+      </c>
+      <c r="T196" s="54">
+        <v>5.75</v>
+      </c>
+      <c r="U196" s="54">
+        <v>134.4</v>
+      </c>
+      <c r="V196" s="53">
+        <v>0.9589725294327506</v>
+      </c>
       <c r="W196" s="53"/>
-      <c r="X196" s="55"/>
-      <c r="Y196" s="55"/>
-      <c r="Z196" s="53"/>
-      <c r="AA196" s="56"/>
+      <c r="X196" s="55">
+        <v>-1248.7078260869564</v>
+      </c>
+      <c r="Y196" s="55">
+        <v>67.49902570438813</v>
+      </c>
+      <c r="Z196" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="56">
+        <v>0.398</v>
+      </c>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
         <v>96</v>
@@ -21566,30 +21650,74 @@
       <c r="C217" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D217" s="52"/>
-      <c r="E217" s="52"/>
-      <c r="F217" s="52"/>
-      <c r="G217" s="53"/>
-      <c r="H217" s="52"/>
-      <c r="I217" s="52"/>
-      <c r="J217" s="52"/>
-      <c r="K217" s="52"/>
-      <c r="L217" s="52"/>
-      <c r="M217" s="53"/>
+      <c r="D217" s="52">
+        <v>137109.56</v>
+      </c>
+      <c r="E217" s="52">
+        <v>0</v>
+      </c>
+      <c r="F217" s="52">
+        <v>137109.56</v>
+      </c>
+      <c r="G217" s="53">
+        <v>1</v>
+      </c>
+      <c r="H217" s="52">
+        <v>117394.57</v>
+      </c>
+      <c r="I217" s="52">
+        <v>1749.8</v>
+      </c>
+      <c r="J217" s="52">
+        <v>99479.62000000001</v>
+      </c>
+      <c r="K217" s="52">
+        <v>1749.8</v>
+      </c>
+      <c r="L217" s="52">
+        <v>97729.82</v>
+      </c>
+      <c r="M217" s="53">
+        <v>0.9824104675912513</v>
+      </c>
       <c r="N217" s="53"/>
-      <c r="O217" s="52"/>
-      <c r="P217" s="52"/>
-      <c r="Q217" s="52"/>
-      <c r="R217" s="53"/>
-      <c r="S217" s="54"/>
-      <c r="T217" s="54"/>
-      <c r="U217" s="54"/>
-      <c r="V217" s="53"/>
+      <c r="O217" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="P217" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q217" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="R217" s="53">
+        <v>1</v>
+      </c>
+      <c r="S217" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="T217" s="54">
+        <v>0</v>
+      </c>
+      <c r="U217" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="V217" s="53">
+        <v>1</v>
+      </c>
       <c r="W217" s="53"/>
-      <c r="X217" s="55"/>
-      <c r="Y217" s="55"/>
-      <c r="Z217" s="53"/>
-      <c r="AA217" s="56"/>
+      <c r="X217" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y217" s="55">
+        <v>54.93783457863793</v>
+      </c>
+      <c r="Z217" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="56">
+        <v>0.1438</v>
+      </c>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
         <v>96</v>
@@ -21919,34 +22047,74 @@
       <c r="C224" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D224" s="52"/>
-      <c r="E224" s="52"/>
-      <c r="F224" s="52"/>
-      <c r="G224" s="53"/>
-      <c r="H224" s="52"/>
-      <c r="I224" s="52"/>
+      <c r="D224" s="52">
+        <v>389318.35</v>
+      </c>
+      <c r="E224" s="52">
+        <v>271388.15</v>
+      </c>
+      <c r="F224" s="52">
+        <v>117930.19999999995</v>
+      </c>
+      <c r="G224" s="53">
+        <v>0.3029145685015874</v>
+      </c>
+      <c r="H224" s="52">
+        <v>289549.48</v>
+      </c>
+      <c r="I224" s="52">
+        <v>227043.56</v>
+      </c>
       <c r="J224" s="52">
-        <v>0</v>
+        <v>174279.97999999998</v>
       </c>
       <c r="K224" s="52">
-        <v>0</v>
-      </c>
-      <c r="L224" s="52"/>
-      <c r="M224" s="53"/>
+        <v>173862.65</v>
+      </c>
+      <c r="L224" s="52">
+        <v>417.3299999999872</v>
+      </c>
+      <c r="M224" s="53">
+        <v>0.0023945951795495226</v>
+      </c>
       <c r="N224" s="53"/>
-      <c r="O224" s="52"/>
-      <c r="P224" s="52"/>
-      <c r="Q224" s="52"/>
-      <c r="R224" s="53"/>
-      <c r="S224" s="54"/>
-      <c r="T224" s="54"/>
-      <c r="U224" s="54"/>
-      <c r="V224" s="53"/>
+      <c r="O224" s="52">
+        <v>115269.5</v>
+      </c>
+      <c r="P224" s="52">
+        <v>53180.91</v>
+      </c>
+      <c r="Q224" s="52">
+        <v>62088.59</v>
+      </c>
+      <c r="R224" s="53">
+        <v>0.5386384950051835</v>
+      </c>
+      <c r="S224" s="54">
+        <v>2312.68</v>
+      </c>
+      <c r="T224" s="54">
+        <v>1120.5</v>
+      </c>
+      <c r="U224" s="54">
+        <v>1192.1799999999998</v>
+      </c>
+      <c r="V224" s="53">
+        <v>0.5154971721120085</v>
+      </c>
       <c r="W224" s="53"/>
-      <c r="X224" s="55"/>
-      <c r="Y224" s="55"/>
-      <c r="Z224" s="53"/>
-      <c r="AA224" s="56"/>
+      <c r="X224" s="55">
+        <v>39.57571619812583</v>
+      </c>
+      <c r="Y224" s="55">
+        <v>43.1399392286741</v>
+      </c>
+      <c r="Z224" s="53">
+        <v>0.1634</v>
+      </c>
+      <c r="AA224" s="56">
+        <v>0.2563</v>
+      </c>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
         <v>96</v>
@@ -22722,7 +22890,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="52">
-        <v>51285.36</v>
+        <v>51687.05</v>
       </c>
       <c r="E4" s="52">
         <f>C4-D4</f>
@@ -24917,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="99">
-        <v>3855.079999999987</v>
+        <v>2584.2399999999907</v>
       </c>
       <c r="E66" s="99">
         <f>C66-D66</f>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -10144,19 +10144,19 @@
         <v>101420.72</v>
       </c>
       <c r="I14" s="52">
-        <v>55851.96</v>
+        <v>54087.96</v>
       </c>
       <c r="J14" s="52">
         <v>83645.65</v>
       </c>
       <c r="K14" s="52">
-        <v>51392.88</v>
+        <v>49628.88</v>
       </c>
       <c r="L14" s="52">
-        <v>32252.769999999997</v>
+        <v>34016.77</v>
       </c>
       <c r="M14" s="53">
-        <v>0.3855881327959075</v>
+        <v>0.4066770955811808</v>
       </c>
       <c r="N14" s="53"/>
       <c r="O14" s="52">
@@ -10185,13 +10185,13 @@
       </c>
       <c r="W14" s="53"/>
       <c r="X14" s="55">
-        <v>-8.637465564738292</v>
+        <v>10.800550964187327</v>
       </c>
       <c r="Y14" s="55">
         <v>77.66490997775718</v>
       </c>
       <c r="Z14" s="53">
-        <v>-0.014199999999999999</v>
+        <v>0.0178</v>
       </c>
       <c r="AA14" s="56">
         <v>0.2142</v>
@@ -22962,7 +22962,7 @@
         <v>3912</v>
       </c>
       <c r="D6" s="52">
-        <v>7555.1500000000015</v>
+        <v>5791.1500000000015</v>
       </c>
       <c r="E6" s="52">
         <f>C6-D6</f>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -20346,32 +20346,74 @@
       <c r="C189" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D189" s="52"/>
-      <c r="E189" s="52"/>
-      <c r="F189" s="52"/>
-      <c r="G189" s="53"/>
-      <c r="H189" s="52"/>
-      <c r="I189" s="52"/>
-      <c r="J189" s="52"/>
+      <c r="D189" s="52">
+        <v>20992.12</v>
+      </c>
+      <c r="E189" s="52">
+        <v>14169.68</v>
+      </c>
+      <c r="F189" s="52">
+        <v>6822.439999999999</v>
+      </c>
+      <c r="G189" s="53">
+        <v>0.32500004763692275</v>
+      </c>
+      <c r="H189" s="52">
+        <v>16299.09</v>
+      </c>
+      <c r="I189" s="52">
+        <v>9755.47</v>
+      </c>
+      <c r="J189" s="52">
+        <v>9784.33</v>
+      </c>
       <c r="K189" s="52">
-        <v>0</v>
-      </c>
-      <c r="L189" s="52"/>
-      <c r="M189" s="53"/>
+        <v>8193.84</v>
+      </c>
+      <c r="L189" s="52">
+        <v>1590.4899999999998</v>
+      </c>
+      <c r="M189" s="53">
+        <v>0.16255481979859632</v>
+      </c>
       <c r="N189" s="53"/>
-      <c r="O189" s="52"/>
-      <c r="P189" s="52"/>
-      <c r="Q189" s="52"/>
-      <c r="R189" s="53"/>
-      <c r="S189" s="54"/>
-      <c r="T189" s="54"/>
-      <c r="U189" s="54"/>
-      <c r="V189" s="53"/>
+      <c r="O189" s="52">
+        <v>6514.76</v>
+      </c>
+      <c r="P189" s="52">
+        <v>1561.63</v>
+      </c>
+      <c r="Q189" s="52">
+        <v>4953.13</v>
+      </c>
+      <c r="R189" s="53">
+        <v>0.7602935488030257</v>
+      </c>
+      <c r="S189" s="54">
+        <v>130.62</v>
+      </c>
+      <c r="T189" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U189" s="54">
+        <v>95.87</v>
+      </c>
+      <c r="V189" s="53">
+        <v>0.7339611085591793</v>
+      </c>
       <c r="W189" s="53"/>
-      <c r="X189" s="55"/>
-      <c r="Y189" s="55"/>
-      <c r="Z189" s="53"/>
-      <c r="AA189" s="56"/>
+      <c r="X189" s="55">
+        <v>127.02762589928058</v>
+      </c>
+      <c r="Y189" s="55">
+        <v>35.92887828502527</v>
+      </c>
+      <c r="Z189" s="53">
+        <v>0.3115</v>
+      </c>
+      <c r="AA189" s="56">
+        <v>0.2236</v>
+      </c>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
         <v>96</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -17207,7 +17207,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -22817,7 +22817,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22831,7 +22831,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -22853,7 +22853,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>99</v>
       </c>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -22919,7 +22919,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <f>'Main Sheet'!A4</f>
         <v>7658</v>
@@ -22935,15 +22935,13 @@
         <v>51687.05</v>
       </c>
       <c r="E4" s="52">
-        <f>C4-D4</f>
-        <v>9727.83</v>
+        <v>-51687.05</v>
       </c>
       <c r="F4" s="52">
         <v>0</v>
       </c>
       <c r="G4" s="53">
-        <f>(E4+F4)/C4</f>
-        <v>0.4863915</v>
+        <v>0</v>
       </c>
       <c r="H4" s="53">
         <v>0.2149</v>
@@ -22955,26 +22953,22 @@
         <v>90</v>
       </c>
       <c r="K4" s="52">
-        <f>(I4*40)+J4</f>
         <v>90</v>
       </c>
       <c r="L4" s="53">
-        <f>((E4-K4)+F4)/C4</f>
-        <v>0.4818915</v>
+        <v>0</v>
       </c>
       <c r="M4" s="52">
-        <f>SUM(E4:F4)-K4</f>
-        <v>9637.83</v>
+        <v>-51777.05</v>
       </c>
       <c r="N4" s="54">
         <v>20</v>
       </c>
       <c r="O4" s="58">
-        <f>SUM(M4/(N4+I4))</f>
-        <v>481.8915</v>
-      </c>
-    </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-2588.8525</v>
+      </c>
+    </row>
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -22991,7 +22985,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <f>'Main Sheet'!A6</f>
         <v>8142</v>
@@ -23007,15 +23001,13 @@
         <v>5791.1500000000015</v>
       </c>
       <c r="E6" s="52">
-        <f>C6-D6</f>
-        <v>-3968.93</v>
+        <v>-1879.1500000000015</v>
       </c>
       <c r="F6" s="52">
         <v>0</v>
       </c>
-      <c r="G6" s="53" t="e">
-        <f>(E6+F6)/C6</f>
-        <v>#DIV/0!</v>
+      <c r="G6" s="53">
+        <v>-0.4803553169734155</v>
       </c>
       <c r="H6" s="53">
         <f>'Deliverables Sheet'!AA11</f>
@@ -23028,30 +23020,26 @@
         <v>272.6</v>
       </c>
       <c r="K6" s="52">
-        <f>(I6*40)+J6</f>
         <v>912.6</v>
       </c>
-      <c r="L6" s="53" t="e">
-        <f>((E6-K6)+F6)/C6</f>
-        <v>#DIV/0!</v>
+      <c r="L6" s="53">
+        <v>-0.7136375255623726</v>
       </c>
       <c r="M6" s="52">
-        <f>SUM(E6:F6)-K6</f>
-        <v>-4881.53</v>
+        <v>-2791.7500000000014</v>
       </c>
       <c r="N6" s="54">
         <f>'Deliverables Sheet'!AE11</f>
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <f>SUM(M6/(N6+I6))</f>
-        <v>133.740547945205</v>
+        <v>76.48630136986306</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23068,7 +23056,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <f>'Main Sheet'!A8</f>
         <v>8824</v>
@@ -23084,13 +23072,11 @@
         <v>0</v>
       </c>
       <c r="E8" s="52">
-        <f>C8-D8</f>
-        <v>2227.16</v>
+        <v>0</v>
       </c>
       <c r="F8" s="52"/>
       <c r="G8" s="53">
-        <f>(E8+F8)/C8</f>
-        <v>0.318207535847569</v>
+        <v>0</v>
       </c>
       <c r="H8" s="53">
         <f>'Deliverables Sheet'!AA18</f>
@@ -23101,27 +23087,23 @@
       </c>
       <c r="J8" s="52"/>
       <c r="K8" s="52">
-        <f>(I8*40)+J8</f>
         <v>640</v>
       </c>
       <c r="L8" s="53">
-        <f>((E8-K8)+F8)/C8</f>
-        <v>0.22676694651297</v>
+        <v>0</v>
       </c>
       <c r="M8" s="52">
-        <f>SUM(E8:F8)-K8</f>
-        <v>1587.16</v>
+        <v>-640</v>
       </c>
       <c r="N8" s="54">
         <f>'Deliverables Sheet'!AE18</f>
         <v>-34.75</v>
       </c>
       <c r="O8" s="58">
-        <f>SUM(M8/(N8+I8))</f>
-        <v>-84.6485333333333</v>
-      </c>
-    </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>34.13333333333333</v>
+      </c>
+    </row>
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23138,7 +23120,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <f>'Main Sheet'!A10</f>
         <v>8127</v>
@@ -23154,15 +23136,13 @@
         <v>8827.48999999999</v>
       </c>
       <c r="E10" s="52">
-        <f>C10-D10</f>
-        <v>19246.78</v>
+        <v>-8827.48999999999</v>
       </c>
       <c r="F10" s="52">
         <v>0</v>
       </c>
       <c r="G10" s="53">
-        <f>(E10+F10)/C10</f>
-        <v>0.361570889143544</v>
+        <v>0</v>
       </c>
       <c r="H10" s="53">
         <f>'Deliverables Sheet'!AA25</f>
@@ -23175,26 +23155,23 @@
         <v>3000</v>
       </c>
       <c r="K10" s="52">
-        <v>1000</v>
+        <v>4920</v>
       </c>
       <c r="L10" s="53">
-        <f>((E10-K10)+F10)/C10</f>
-        <v>0.342784843418309</v>
+        <v>0</v>
       </c>
       <c r="M10" s="52">
-        <f>SUM(E10:F10)-K10</f>
-        <v>18246.78</v>
+        <v>-13747.48999999999</v>
       </c>
       <c r="N10" s="54">
         <f>'Deliverables Sheet'!AE25</f>
         <v>-388.25</v>
       </c>
       <c r="O10" s="58">
-        <f>SUM(M10/(N10+I10))</f>
-        <v>-53.6275679647318</v>
-      </c>
-    </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>40.40408523144744</v>
+      </c>
+    </row>
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23211,7 +23188,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23225,13 +23202,11 @@
         <v>1154.6499999999942</v>
       </c>
       <c r="E12" s="52">
-        <f>C12-D12</f>
-        <v>7144.34</v>
+        <v>-1154.6499999999942</v>
       </c>
       <c r="F12" s="52"/>
       <c r="G12" s="53">
-        <f>(E12+F12)/C12</f>
-        <v>0.351073218673219</v>
+        <v>0</v>
       </c>
       <c r="H12" s="53">
         <f>'Deliverables Sheet'!AA32</f>
@@ -23244,29 +23219,25 @@
         <v>2000</v>
       </c>
       <c r="K12" s="52">
-        <f>(I12*40)+J12</f>
         <v>2640</v>
       </c>
       <c r="L12" s="53">
-        <f>((E12-K12)+F12)/C12</f>
-        <v>0.221343488943489</v>
+        <v>0</v>
       </c>
       <c r="M12" s="52">
-        <f>SUM(E12:F12)-K12</f>
-        <v>4504.34</v>
+        <v>-3794.649999999994</v>
       </c>
       <c r="N12" s="54">
         <v>53</v>
       </c>
       <c r="O12" s="58">
-        <f>SUM(M12/(N12+I12))</f>
-        <v>65.2802898550725</v>
+        <v>-54.9949275362318</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23283,7 +23254,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <f>'Main Sheet'!A14</f>
         <v>8886</v>
@@ -23299,15 +23270,13 @@
         <v>2138.1600000000035</v>
       </c>
       <c r="E14" s="52">
-        <f>C14-D14</f>
-        <v>3415.11</v>
+        <v>-2138.1600000000035</v>
       </c>
       <c r="F14" s="52">
         <v>0</v>
       </c>
       <c r="G14" s="53">
-        <f>(E14+F14)/C14</f>
-        <v>0.338129702970297</v>
+        <v>0</v>
       </c>
       <c r="H14" s="53">
         <f>'Deliverables Sheet'!AA39</f>
@@ -23320,26 +23289,23 @@
         <v>3000</v>
       </c>
       <c r="K14" s="52">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L14" s="53">
-        <f>((E14-K14)+F14)/C14</f>
-        <v>0.338129702970297</v>
+        <v>0</v>
       </c>
       <c r="M14" s="52">
-        <f>SUM(E14:F14)-K14</f>
-        <v>3415.11</v>
+        <v>-5138.1600000000035</v>
       </c>
       <c r="N14" s="54">
         <f>'Deliverables Sheet'!AE39</f>
         <v>-112</v>
       </c>
       <c r="O14" s="58">
-        <f>SUM(M14/(N14+I14))</f>
-        <v>-30.4920535714286</v>
-      </c>
-    </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>45.876428571428605</v>
+      </c>
+    </row>
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23356,7 +23322,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <f>'Main Sheet'!A16</f>
         <v>8887</v>
@@ -23372,13 +23338,11 @@
         <v>5565.0300000000025</v>
       </c>
       <c r="E16" s="52">
-        <f>C16-D16</f>
-        <v>5660</v>
+        <v>-5565.0300000000025</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="53">
-        <f>(E16+F16)/C16</f>
-        <v>0.539047619047619</v>
+        <v>0</v>
       </c>
       <c r="H16" s="53">
         <f>'Deliverables Sheet'!AA46</f>
@@ -23391,27 +23355,23 @@
         <v>3000</v>
       </c>
       <c r="K16" s="52">
-        <f>(I16*40)+J16</f>
         <v>3000</v>
       </c>
       <c r="L16" s="53">
-        <f>((E16-K16)+F16)/C16</f>
-        <v>0.253333333333333</v>
+        <v>0</v>
       </c>
       <c r="M16" s="52">
-        <f>SUM(E16:F16)-K16</f>
-        <v>2660</v>
+        <v>-8565.030000000002</v>
       </c>
       <c r="N16" s="54">
         <f>'Deliverables Sheet'!AE46</f>
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
-        <f>SUM(M16/(N16+I16))</f>
-        <v>-30.6628242074928</v>
-      </c>
-    </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>98.73233429394816</v>
+      </c>
+    </row>
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23428,7 +23388,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <f>'Main Sheet'!A18</f>
         <v>8670</v>
@@ -23444,15 +23404,13 @@
         <v>10982.64</v>
       </c>
       <c r="E18" s="52">
-        <f>C18-D18</f>
-        <v>16075.1</v>
+        <v>-10982.64</v>
       </c>
       <c r="F18" s="52">
         <v>0</v>
       </c>
       <c r="G18" s="53">
-        <f>(E18+F18)/C18</f>
-        <v>0.432578691158227</v>
+        <v>0</v>
       </c>
       <c r="H18" s="53">
         <f>'Deliverables Sheet'!AA53</f>
@@ -23465,30 +23423,26 @@
         <v>5000</v>
       </c>
       <c r="K18" s="52">
-        <f>(I18*40)+J18</f>
         <v>8200</v>
       </c>
       <c r="L18" s="53">
-        <f>((E18-K18)+F18)/C18</f>
-        <v>0.21191783881532</v>
+        <v>0</v>
       </c>
       <c r="M18" s="52">
-        <f>SUM(E18:F18)-K18</f>
-        <v>7875.1</v>
+        <v>-19182.64</v>
       </c>
       <c r="N18" s="54">
         <f>'Deliverables Sheet'!AE53</f>
         <v>-269</v>
       </c>
       <c r="O18" s="58">
-        <f>SUM(M18/(N18+I18))</f>
-        <v>-41.6671957671958</v>
+        <v>101.49544973544974</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23505,7 +23459,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <f>'Main Sheet'!A20</f>
         <v>8907</v>
@@ -23521,13 +23475,11 @@
         <v>1407.8799999999992</v>
       </c>
       <c r="E20" s="52">
-        <f>C20-D20</f>
-        <v>0</v>
+        <v>-1407.8799999999992</v>
       </c>
       <c r="F20" s="52"/>
-      <c r="G20" s="53" t="e">
-        <f>(E20+F20)/C20</f>
-        <v>#DIV/0!</v>
+      <c r="G20" s="53">
+        <v>0</v>
       </c>
       <c r="H20" s="53">
         <f>'Deliverables Sheet'!AA60</f>
@@ -23536,24 +23488,20 @@
       <c r="I20" s="54"/>
       <c r="J20" s="52"/>
       <c r="K20" s="52">
-        <f>(I20*40)+J20</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="53" t="e">
-        <f>((E20-K20)+F20)/C20</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="53">
+        <v>0</v>
       </c>
       <c r="M20" s="52">
-        <f>SUM(E20:F20)-K20</f>
-        <v>0</v>
+        <v>-1407.8799999999992</v>
       </c>
       <c r="N20" s="54"/>
-      <c r="O20" s="58" t="e">
-        <f>SUM(M20/(N20+I20))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O20" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23570,7 +23518,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <f>'Main Sheet'!A22</f>
         <v>9065</v>
@@ -23586,15 +23534,13 @@
         <v>4584.16</v>
       </c>
       <c r="E22" s="52">
-        <f>C22-D22</f>
-        <v>0</v>
+        <v>-4584.16</v>
       </c>
       <c r="F22" s="52">
         <v>0</v>
       </c>
-      <c r="G22" s="53" t="e">
-        <f>(E22+F22)/C22</f>
-        <v>#DIV/0!</v>
+      <c r="G22" s="53">
+        <v>0</v>
       </c>
       <c r="H22" s="53">
         <f>'Deliverables Sheet'!AA67</f>
@@ -23603,27 +23549,23 @@
       <c r="I22" s="54"/>
       <c r="J22" s="52"/>
       <c r="K22" s="52">
-        <f>(I22*40)+J22</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="53" t="e">
-        <f>((E22-K22)+F22)/C22</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="53">
+        <v>0</v>
       </c>
       <c r="M22" s="52">
-        <f>SUM(E22:F22)-K22</f>
-        <v>0</v>
+        <v>-4584.16</v>
       </c>
       <c r="N22" s="54">
         <f>'Deliverables Sheet'!AE67</f>
         <v>0</v>
       </c>
-      <c r="O22" s="58" t="e">
-        <f>SUM(M22/(N22+I22))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O22" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23640,7 +23582,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <f>'Main Sheet'!A24</f>
         <v>9259</v>
@@ -23656,13 +23598,11 @@
         <v>22353.17</v>
       </c>
       <c r="E24" s="52">
-        <f>C24-D24</f>
-        <v>0</v>
+        <v>-22353.17</v>
       </c>
       <c r="F24" s="52"/>
-      <c r="G24" s="53" t="e">
-        <f>(E24+F24)/C24</f>
-        <v>#DIV/0!</v>
+      <c r="G24" s="53">
+        <v>0</v>
       </c>
       <c r="H24" s="53" t="e">
         <f>'Deliverables Sheet'!AA74</f>
@@ -23671,27 +23611,23 @@
       <c r="I24" s="54"/>
       <c r="J24" s="52"/>
       <c r="K24" s="52">
-        <f>(I24*40)+J24</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="53" t="e">
-        <f>((E24-K24)+F24)/C24</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L24" s="53">
+        <v>0</v>
       </c>
       <c r="M24" s="52">
-        <f>SUM(E24:F24)-K24</f>
-        <v>0</v>
+        <v>-22353.17</v>
       </c>
       <c r="N24" s="54">
         <f>'Deliverables Sheet'!AE74</f>
         <v>0</v>
       </c>
-      <c r="O24" s="58" t="e">
-        <f>SUM(M24/(N24+I24))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O24" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23708,7 +23644,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <f>'Main Sheet'!A26</f>
         <v>8352</v>
@@ -23724,15 +23660,13 @@
         <v>-192.5</v>
       </c>
       <c r="E26" s="52">
-        <f>C26-D26</f>
-        <v>0</v>
+        <v>192.5</v>
       </c>
       <c r="F26" s="52">
         <v>0</v>
       </c>
-      <c r="G26" s="53" t="e">
-        <f>(E26+F26)/C26</f>
-        <v>#DIV/0!</v>
+      <c r="G26" s="53">
+        <v>0</v>
       </c>
       <c r="H26" s="53">
         <f>'Deliverables Sheet'!AA81</f>
@@ -23743,27 +23677,23 @@
         <v>0</v>
       </c>
       <c r="K26" s="52">
-        <f>(I26*40)+J26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="53" t="e">
-        <f>((E26-K26)+F26)/C26</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L26" s="53">
+        <v>0</v>
       </c>
       <c r="M26" s="52">
-        <f>SUM(E26:F26)-K26</f>
-        <v>0</v>
+        <v>192.5</v>
       </c>
       <c r="N26" s="54">
         <f>'Deliverables Sheet'!AE81</f>
         <v>-143.25</v>
       </c>
       <c r="O26" s="58">
-        <f>SUM(M26/(N26+I26))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-1.343804537521815</v>
+      </c>
+    </row>
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23780,7 +23710,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <f>'Main Sheet'!A28</f>
         <v>8234</v>
@@ -23796,15 +23726,13 @@
         <v>4476.1500000000015</v>
       </c>
       <c r="E28" s="52">
-        <f>C28-D28</f>
-        <v>2313.69</v>
+        <v>-4476.1500000000015</v>
       </c>
       <c r="F28" s="52">
         <v>0</v>
       </c>
       <c r="G28" s="53">
-        <f>(E28+F28)/C28</f>
-        <v>0.346291312820482</v>
+        <v>0</v>
       </c>
       <c r="H28" s="53">
         <f>'Deliverables Sheet'!AA88</f>
@@ -23813,27 +23741,23 @@
       <c r="I28" s="54"/>
       <c r="J28" s="52"/>
       <c r="K28" s="52">
-        <f>(I28*40)+J28</f>
         <v>0</v>
       </c>
       <c r="L28" s="53">
-        <f>((E28-K28)+F28)/C28</f>
-        <v>0.346291312820482</v>
+        <v>0</v>
       </c>
       <c r="M28" s="52">
-        <f>SUM(E28:F28)-K28</f>
-        <v>2313.69</v>
+        <v>-4476.1500000000015</v>
       </c>
       <c r="N28" s="54">
         <f>'Deliverables Sheet'!AE88</f>
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
-        <f>SUM(M28/(N28+I28))</f>
-        <v>-15.580404040404</v>
-      </c>
-    </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>30.14242424242425</v>
+      </c>
+    </row>
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23850,7 +23774,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <f>'Main Sheet'!A30</f>
         <v>8214</v>
@@ -23866,15 +23790,13 @@
         <v>0</v>
       </c>
       <c r="E30" s="52">
-        <f>C30-D30</f>
         <v>0</v>
       </c>
       <c r="F30" s="52">
         <v>0</v>
       </c>
-      <c r="G30" s="53" t="e">
-        <f>(E30+F30)/C30</f>
-        <v>#DIV/0!</v>
+      <c r="G30" s="53">
+        <v>0</v>
       </c>
       <c r="H30" s="53">
         <f>'Deliverables Sheet'!AA95</f>
@@ -23883,15 +23805,12 @@
       <c r="I30" s="54"/>
       <c r="J30" s="52"/>
       <c r="K30" s="52">
-        <f>(I30*40)+J30</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="53" t="e">
-        <f>((E30-K30)+F30)/C30</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L30" s="53">
+        <v>0</v>
       </c>
       <c r="M30" s="52">
-        <f>SUM(E30:F30)-K30</f>
         <v>0</v>
       </c>
       <c r="N30" s="54">
@@ -23899,11 +23818,10 @@
         <v>-5</v>
       </c>
       <c r="O30" s="58">
-        <f>SUM(M30/(N30+I30))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23920,7 +23838,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <f>'Main Sheet'!A32</f>
         <v>6792</v>
@@ -23936,15 +23854,13 @@
         <v>-1171.8899999999994</v>
       </c>
       <c r="E32" s="52">
-        <f>C32-D32</f>
-        <v>4327.53</v>
+        <v>1171.8899999999994</v>
       </c>
       <c r="F32" s="52">
         <v>0</v>
       </c>
       <c r="G32" s="53">
-        <f>(E32+F32)/C32</f>
-        <v>0.6924048</v>
+        <v>0</v>
       </c>
       <c r="H32" s="53">
         <f>'Deliverables Sheet'!AA102</f>
@@ -23957,27 +23873,23 @@
         <v>0</v>
       </c>
       <c r="K32" s="52">
-        <f>(I32*40)+J32</f>
         <v>2560</v>
       </c>
       <c r="L32" s="53">
-        <f>((E32-K32)+F32)/C32</f>
-        <v>0.2828048</v>
+        <v>0</v>
       </c>
       <c r="M32" s="52">
-        <f>SUM(E32:F32)-K32</f>
-        <v>1767.53</v>
+        <v>-1388.1100000000006</v>
       </c>
       <c r="N32" s="54">
         <f>'Deliverables Sheet'!AE102</f>
         <v>-317.25</v>
       </c>
       <c r="O32" s="58">
-        <f>SUM(M32/(N32+I32))</f>
-        <v>-6.97938795656466</v>
-      </c>
-    </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>5.481184600197436</v>
+      </c>
+    </row>
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23994,7 +23906,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <f>'Main Sheet'!A34</f>
         <v>8840</v>
@@ -24010,15 +23922,13 @@
         <v>16334.04</v>
       </c>
       <c r="E34" s="52">
-        <f>C34-D34</f>
-        <v>0</v>
+        <v>-51788.47</v>
       </c>
       <c r="F34" s="52">
         <v>0</v>
       </c>
-      <c r="G34" s="53" t="e">
-        <f>(E34+F34)/C34</f>
-        <v>#DIV/0!</v>
+      <c r="G34" s="53">
+        <v>1.4607051925528065</v>
       </c>
       <c r="H34" s="53">
         <f>'Deliverables Sheet'!AA109</f>
@@ -24029,27 +23939,23 @@
         <v>0</v>
       </c>
       <c r="K34" s="52">
-        <f>(I34*40)+J34</f>
-        <v>0</v>
-      </c>
-      <c r="L34" s="53" t="e">
-        <f>((E34-K34)+F34)/C34</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="53">
+        <v>1.4607051925528065</v>
       </c>
       <c r="M34" s="52">
-        <f>SUM(E34:F34)-K34</f>
-        <v>0</v>
+        <v>-51788.47</v>
       </c>
       <c r="N34" s="54">
         <f>'Deliverables Sheet'!AE109</f>
         <v>-204.75</v>
       </c>
       <c r="O34" s="58">
-        <f>SUM(M34/(N34+I34))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>252.9351404151404</v>
+      </c>
+    </row>
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -24066,7 +23972,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <f>'Main Sheet'!A36</f>
         <v>8769</v>
@@ -24082,15 +23988,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="52">
-        <f>C36-D36</f>
-        <v>10702.1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="52">
         <v>0</v>
       </c>
       <c r="G36" s="53">
-        <f>(E36+F36)/C36</f>
-        <v>0.494732365327453</v>
+        <v>0</v>
       </c>
       <c r="H36" s="53" t="e">
         <f>'Deliverables Sheet'!AA116</f>
@@ -24103,27 +24007,23 @@
         <v>0</v>
       </c>
       <c r="K36" s="52">
-        <f>(I36*40)+J36</f>
         <v>3200</v>
       </c>
       <c r="L36" s="53">
-        <f>((E36-K36)+F36)/C36</f>
-        <v>0.346804055084805</v>
+        <v>0</v>
       </c>
       <c r="M36" s="52">
-        <f>SUM(E36:F36)-K36</f>
-        <v>7502.1</v>
+        <v>-3200</v>
       </c>
       <c r="N36" s="54">
         <f>'Deliverables Sheet'!AE116</f>
         <v>0</v>
       </c>
       <c r="O36" s="58">
-        <f>SUM(M36/(N36+I36))</f>
-        <v>93.77625</v>
-      </c>
-    </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24140,7 +24040,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <f>'Main Sheet'!A38</f>
         <v>7901</v>
@@ -24156,15 +24056,13 @@
         <v>6365.780000000001</v>
       </c>
       <c r="E38" s="52">
-        <f>C38-D38</f>
-        <v>0</v>
+        <v>-6365.780000000001</v>
       </c>
       <c r="F38" s="52">
         <v>0</v>
       </c>
-      <c r="G38" s="53" t="e">
-        <f>(E38+F38)/C38</f>
-        <v>#DIV/0!</v>
+      <c r="G38" s="53">
+        <v>0</v>
       </c>
       <c r="H38" s="53">
         <f>'Deliverables Sheet'!AA123</f>
@@ -24173,27 +24071,23 @@
       <c r="I38" s="54"/>
       <c r="J38" s="52"/>
       <c r="K38" s="52">
-        <f>(I38*40)+J38</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="53" t="e">
-        <f>((E38-K38)+F38)/C38</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L38" s="53">
+        <v>0</v>
       </c>
       <c r="M38" s="52">
-        <f>SUM(E38:F38)-K38</f>
-        <v>0</v>
+        <v>-6365.780000000001</v>
       </c>
       <c r="N38" s="54">
         <f>'Deliverables Sheet'!AE123</f>
         <v>0</v>
       </c>
-      <c r="O38" s="58" t="e">
-        <f>SUM(M38/(N38+I38))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O38" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24210,7 +24104,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <f>'Main Sheet'!A40</f>
         <v>8923</v>
@@ -24226,15 +24120,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="52">
-        <f>C40-D40</f>
         <v>0</v>
       </c>
       <c r="F40" s="52">
         <v>0</v>
       </c>
-      <c r="G40" s="53" t="e">
-        <f>(E40+F40)/C40</f>
-        <v>#DIV/0!</v>
+      <c r="G40" s="53">
+        <v>0</v>
       </c>
       <c r="H40" s="53">
         <f>'Deliverables Sheet'!AA130</f>
@@ -24245,15 +24137,12 @@
         <v>0</v>
       </c>
       <c r="K40" s="52">
-        <f>(I40*40)+J40</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="53" t="e">
-        <f>((E40-K40)+F40)/C40</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L40" s="53">
+        <v>0</v>
       </c>
       <c r="M40" s="52">
-        <f>SUM(E40:F40)-K40</f>
         <v>0</v>
       </c>
       <c r="N40" s="54">
@@ -24261,11 +24150,10 @@
         <v>-2</v>
       </c>
       <c r="O40" s="58">
-        <f>SUM(M40/(N40+I40))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24282,7 +24170,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <f>'Main Sheet'!A42</f>
         <v>7864</v>
@@ -24298,13 +24186,11 @@
         <v>584.890000000003</v>
       </c>
       <c r="E42" s="52">
-        <f>C42-D42</f>
-        <v>-106.2</v>
+        <v>2969.41</v>
       </c>
       <c r="F42" s="52"/>
       <c r="G42" s="53">
-        <f>(E42+F42)/C42</f>
-        <v>-0.0158301906479646</v>
+        <v>0.8354415778071624</v>
       </c>
       <c r="H42" s="53">
         <f>'Deliverables Sheet'!AA137</f>
@@ -24315,27 +24201,23 @@
       </c>
       <c r="J42" s="52"/>
       <c r="K42" s="52">
-        <f>(I42*40)+J42</f>
         <v>0</v>
       </c>
       <c r="L42" s="53">
-        <f>((E42-K42)+F42)/C42</f>
-        <v>-0.0158301906479646</v>
+        <v>0.8354415778071624</v>
       </c>
       <c r="M42" s="52">
-        <f>SUM(E42:F42)-K42</f>
-        <v>-106.2</v>
+        <v>2969.41</v>
       </c>
       <c r="N42" s="54">
         <f>'Deliverables Sheet'!AE137</f>
         <v>-266.75</v>
       </c>
       <c r="O42" s="58">
-        <f>SUM(M42/(N42+I42))</f>
-        <v>0.398125585754451</v>
-      </c>
-    </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-11.131808809746953</v>
+      </c>
+    </row>
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24352,7 +24234,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <f>'Main Sheet'!A44</f>
         <v>7912</v>
@@ -24368,13 +24250,11 @@
         <v>6362.08</v>
       </c>
       <c r="E44" s="52">
-        <f>C44-D44</f>
-        <v>1991.31</v>
+        <v>2672.4500000000007</v>
       </c>
       <c r="F44" s="52"/>
       <c r="G44" s="53">
-        <f>(E44+F44)/C44</f>
-        <v>0.312249208522089</v>
+        <v>0.29580398758983595</v>
       </c>
       <c r="H44" s="53" t="e">
         <f>'Deliverables Sheet'!AA144</f>
@@ -24383,27 +24263,23 @@
       <c r="I44" s="54"/>
       <c r="J44" s="52"/>
       <c r="K44" s="52">
-        <f>(I44*40)+J44</f>
         <v>0</v>
       </c>
       <c r="L44" s="53">
-        <f>((E44-K44)+F44)/C44</f>
-        <v>0.312249208522089</v>
+        <v>0.29580398758983595</v>
       </c>
       <c r="M44" s="52">
-        <f>SUM(E44:F44)-K44</f>
-        <v>1991.31</v>
+        <v>2672.4500000000007</v>
       </c>
       <c r="N44" s="54">
         <f>'Deliverables Sheet'!AE144</f>
         <v>0</v>
       </c>
-      <c r="O44" s="58" t="e">
-        <f>SUM(M44/(N44+I44))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O44" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24420,7 +24296,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <f>'Main Sheet'!A46</f>
         <v>8360</v>
@@ -24436,13 +24312,11 @@
         <v>15.4900000000016</v>
       </c>
       <c r="E46" s="99">
-        <f>C46-D46</f>
-        <v>651.410000000001</v>
+        <v>-15.4900000000016</v>
       </c>
       <c r="F46" s="99"/>
       <c r="G46" s="100">
-        <f>(E46+F46)/C46</f>
-        <v>0.127995740090504</v>
+        <v>0</v>
       </c>
       <c r="H46" s="100">
         <f>'Deliverables Sheet'!AA151</f>
@@ -24451,27 +24325,23 @@
       <c r="I46" s="98"/>
       <c r="J46" s="99"/>
       <c r="K46" s="99">
-        <f>(I46*40)+J46</f>
         <v>0</v>
       </c>
       <c r="L46" s="100">
-        <f>((E46-K46)+F46)/C46</f>
-        <v>0.127995740090504</v>
+        <v>0</v>
       </c>
       <c r="M46" s="99">
-        <f>SUM(E46:F46)-K46</f>
-        <v>651.410000000001</v>
+        <v>-15.4900000000016</v>
       </c>
       <c r="N46" s="98">
         <f>'Deliverables Sheet'!AE151</f>
         <v>-260.75</v>
       </c>
       <c r="O46" s="60">
-        <f>SUM(M46/(N46+I46))</f>
-        <v>-2.49821668264622</v>
-      </c>
-    </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.05940556088207709</v>
+      </c>
+    </row>
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24488,7 +24358,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <f>'Main Sheet'!A48</f>
         <v>8337</v>
@@ -24504,13 +24374,11 @@
         <v>2862.0099999999993</v>
       </c>
       <c r="E48" s="99">
-        <f>C48-D48</f>
-        <v>5862.4</v>
+        <v>10562.490000000002</v>
       </c>
       <c r="F48" s="99"/>
       <c r="G48" s="100">
-        <f>(E48+F48)/C48</f>
-        <v>0.436694104063466</v>
+        <v>0.7868069574285822</v>
       </c>
       <c r="H48" s="100">
         <f>'Deliverables Sheet'!AA158</f>
@@ -24521,27 +24389,23 @@
         <v>2530</v>
       </c>
       <c r="K48" s="99">
-        <f>(I48*40)+J48</f>
         <v>2530</v>
       </c>
       <c r="L48" s="100">
-        <f>((E48-K48)+F48)/C48</f>
-        <v>0.248232708853216</v>
+        <v>0.5983455622183322</v>
       </c>
       <c r="M48" s="99">
-        <f>SUM(E48:F48)-K48</f>
-        <v>3332.4</v>
+        <v>8032.490000000002</v>
       </c>
       <c r="N48" s="98">
         <f>'Deliverables Sheet'!AE158</f>
         <v>-44.75</v>
       </c>
       <c r="O48" s="60">
-        <f>SUM(M48/(N48+I48))</f>
-        <v>-74.4670391061452</v>
-      </c>
-    </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-179.4969832402235</v>
+      </c>
+    </row>
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24558,7 +24422,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <f>'Main Sheet'!A50</f>
         <v>9240</v>
@@ -24574,13 +24438,11 @@
         <v>0</v>
       </c>
       <c r="E50" s="99">
-        <f>C50-D50</f>
         <v>0</v>
       </c>
       <c r="F50" s="99"/>
-      <c r="G50" s="100" t="e">
-        <f>(E50+F50)/C50</f>
-        <v>#DIV/0!</v>
+      <c r="G50" s="100">
+        <v>0</v>
       </c>
       <c r="H50" s="100" t="e">
         <f>'Deliverables Sheet'!AA165</f>
@@ -24591,30 +24453,26 @@
       </c>
       <c r="J50" s="99"/>
       <c r="K50" s="99">
-        <f>(I50*40)+J50</f>
-        <v>0</v>
-      </c>
-      <c r="L50" s="100" t="e">
-        <f>((E50-K50)+F50)/C50</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L50" s="100">
+        <v>0</v>
       </c>
       <c r="M50" s="99">
-        <f>SUM(E50:F50)-K50</f>
         <v>0</v>
       </c>
       <c r="N50" s="98">
         <f>'Deliverables Sheet'!AE165</f>
         <v>0</v>
       </c>
-      <c r="O50" s="60" t="e">
-        <f>SUM(M50/(N50+I50))</f>
-        <v>#DIV/0!</v>
+      <c r="O50" s="60">
+        <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24631,7 +24489,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <f>'Main Sheet'!A52</f>
         <v>7428</v>
@@ -24647,13 +24505,11 @@
         <v>20350.28</v>
       </c>
       <c r="E52" s="99">
-        <f>C52-D52</f>
-        <v>2683.58</v>
+        <v>-20350.28</v>
       </c>
       <c r="F52" s="99"/>
       <c r="G52" s="100">
-        <f>(E52+F52)/C52</f>
-        <v>0.570713397063046</v>
+        <v>0</v>
       </c>
       <c r="H52" s="100">
         <f>'Deliverables Sheet'!AA172</f>
@@ -24666,27 +24522,23 @@
         <v>0</v>
       </c>
       <c r="K52" s="99">
-        <f>(I52*40)+J52</f>
         <v>1280</v>
       </c>
       <c r="L52" s="100">
-        <f>((E52-K52)+F52)/C52</f>
-        <v>0.298497495826377</v>
+        <v>0</v>
       </c>
       <c r="M52" s="99">
-        <f>SUM(E52:F52)-K52</f>
-        <v>1403.58</v>
+        <v>-21630.28</v>
       </c>
       <c r="N52" s="98">
         <f>'Deliverables Sheet'!AE172</f>
         <v>-304.75</v>
       </c>
       <c r="O52" s="60">
-        <f>SUM(M52/(N52+I52))</f>
-        <v>-5.14603116406966</v>
-      </c>
-    </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>79.30441796516956</v>
+      </c>
+    </row>
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24703,7 +24555,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <f>'Main Sheet'!A54</f>
         <v>9351</v>
@@ -24719,13 +24571,11 @@
         <v>756.6300000000001</v>
       </c>
       <c r="E54" s="99">
-        <f>C54-D54</f>
-        <v>2545.55</v>
+        <v>4735.07</v>
       </c>
       <c r="F54" s="99"/>
       <c r="G54" s="100">
-        <f>(E54+F54)/C54</f>
-        <v>0.46352677677222</v>
+        <v>0.8622229910592348</v>
       </c>
       <c r="H54" s="100">
         <f>'Deliverables Sheet'!AA179</f>
@@ -24738,27 +24588,23 @@
         <v>0</v>
       </c>
       <c r="K54" s="99">
-        <f>(I54*40)+J54</f>
         <v>640</v>
       </c>
       <c r="L54" s="100">
-        <f>((E54-K54)+F54)/C54</f>
-        <v>0.34698727170093</v>
+        <v>0.7456834859879454</v>
       </c>
       <c r="M54" s="99">
-        <f>SUM(E54:F54)-K54</f>
-        <v>1905.55</v>
+        <v>4095.0699999999997</v>
       </c>
       <c r="N54" s="98">
         <f>'Deliverables Sheet'!AE179</f>
         <v>-11.25</v>
       </c>
       <c r="O54" s="60">
-        <f>SUM(M54/(N54+I54))</f>
-        <v>401.168421052632</v>
-      </c>
-    </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>862.1199999999999</v>
+      </c>
+    </row>
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24775,7 +24621,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <f>'Main Sheet'!A56</f>
         <v>7429</v>
@@ -24791,13 +24637,11 @@
         <v>4850.19</v>
       </c>
       <c r="E56" s="99">
-        <f>C56-D56</f>
-        <v>9059.83</v>
+        <v>8086.910000000001</v>
       </c>
       <c r="F56" s="99"/>
       <c r="G56" s="100">
-        <f>(E56+F56)/C56</f>
-        <v>0.700298366712787</v>
+        <v>0.6250944956752287</v>
       </c>
       <c r="H56" s="100">
         <f>'Deliverables Sheet'!AA186</f>
@@ -24810,27 +24654,23 @@
         <v>5000</v>
       </c>
       <c r="K56" s="99">
-        <f>(I56*40)+J56</f>
         <v>5400</v>
       </c>
       <c r="L56" s="100">
-        <f>((E56-K56)+F56)/C56</f>
-        <v>0.282894157114036</v>
+        <v>0.20769028607647777</v>
       </c>
       <c r="M56" s="99">
-        <f>SUM(E56:F56)-K56</f>
-        <v>3659.83</v>
+        <v>2686.9100000000008</v>
       </c>
       <c r="N56" s="98">
         <f>'Deliverables Sheet'!AE186</f>
         <v>-32.25</v>
       </c>
       <c r="O56" s="60">
-        <f>SUM(M56/(N56+I56))</f>
-        <v>-164.486741573034</v>
-      </c>
-    </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-120.76000000000003</v>
+      </c>
+    </row>
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24847,7 +24687,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <f>'Main Sheet'!A58</f>
         <v>9508</v>
@@ -24863,13 +24703,11 @@
         <v>7180.07</v>
       </c>
       <c r="E58" s="99">
-        <f>C58-D58</f>
-        <v>0</v>
+        <v>-7180.07</v>
       </c>
       <c r="F58" s="99"/>
-      <c r="G58" s="100" t="e">
-        <f>(E58+F58)/C58</f>
-        <v>#DIV/0!</v>
+      <c r="G58" s="100">
+        <v>0</v>
       </c>
       <c r="H58" s="100" t="e">
         <f>'Deliverables Sheet'!AA193</f>
@@ -24878,27 +24716,23 @@
       <c r="I58" s="98"/>
       <c r="J58" s="99"/>
       <c r="K58" s="99">
-        <f>(I58*40)+J58</f>
-        <v>0</v>
-      </c>
-      <c r="L58" s="100" t="e">
-        <f>((E58-K58)+F58)/C58</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="L58" s="100">
+        <v>0</v>
       </c>
       <c r="M58" s="99">
-        <f>SUM(E58:F58)-K58</f>
-        <v>0</v>
+        <v>-7180.07</v>
       </c>
       <c r="N58" s="98">
         <f>'Deliverables Sheet'!AE193</f>
         <v>0</v>
       </c>
-      <c r="O58" s="60" t="e">
-        <f>SUM(M58/(N58+I58))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O58" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24915,7 +24749,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59">
         <f>'Main Sheet'!A60</f>
         <v>0</v>
@@ -24962,7 +24796,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24979,7 +24813,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59">
         <f>'Main Sheet'!A62</f>
         <v>0</v>
@@ -25028,7 +24862,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -25045,7 +24879,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <f>'Main Sheet'!A64</f>
         <v>8946</v>
@@ -25061,13 +24895,11 @@
         <v>1749.8</v>
       </c>
       <c r="E64" s="99">
-        <f>C64-D64</f>
-        <v>0</v>
+        <v>-1749.8</v>
       </c>
       <c r="F64" s="99"/>
-      <c r="G64" s="100" t="e">
-        <f>(E64+F64)/C64</f>
-        <v>#DIV/0!</v>
+      <c r="G64" s="100">
+        <v>0</v>
       </c>
       <c r="H64" s="100">
         <f>'Deliverables Sheet'!AA214</f>
@@ -25078,27 +24910,23 @@
         <v>1750</v>
       </c>
       <c r="K64" s="99">
-        <f>(I64*40)+J64</f>
         <v>1750</v>
       </c>
-      <c r="L64" s="100" t="e">
-        <f>((E64-K64)+F64)/C64</f>
-        <v>#DIV/0!</v>
+      <c r="L64" s="100">
+        <v>0</v>
       </c>
       <c r="M64" s="99">
-        <f>SUM(E64:F64)-K64</f>
-        <v>-1750</v>
+        <v>-3499.8</v>
       </c>
       <c r="N64" s="98">
         <f>'Deliverables Sheet'!AE214</f>
         <v>0</v>
       </c>
-      <c r="O64" s="60" t="e">
-        <f>SUM(M64/(N64+I64))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="O64" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -25115,7 +24943,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -25130,13 +24958,11 @@
         <v>2584.2399999999907</v>
       </c>
       <c r="E66" s="99">
-        <f>C66-D66</f>
-        <v>11482</v>
+        <v>-2584.2399999999907</v>
       </c>
       <c r="F66" s="99"/>
       <c r="G66" s="100">
-        <f>(E66+F66)/C66</f>
-        <v>0.376459016393443</v>
+        <v>0</v>
       </c>
       <c r="H66" s="100">
         <f>'Deliverables Sheet'!AA221</f>
@@ -25149,27 +24975,23 @@
         <v>0</v>
       </c>
       <c r="K66" s="99">
-        <f>(I66*40)+J66</f>
         <v>3200</v>
       </c>
       <c r="L66" s="100">
-        <f>((E66-K66)+F66)/C66</f>
-        <v>0.271540983606557</v>
+        <v>0</v>
       </c>
       <c r="M66" s="99">
-        <f>SUM(E66:F66)-K66</f>
-        <v>8282</v>
+        <v>-5784.239999999991</v>
       </c>
       <c r="N66" s="98">
         <f>'Deliverables Sheet'!AE221</f>
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
-        <f>SUM(M66/(N66+I66))</f>
-        <v>-8.86486486486487</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>6.191319240032102</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -25186,7 +25008,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -25203,7 +25025,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>119</v>
       </c>
@@ -25211,30 +25033,25 @@
         <v>120</v>
       </c>
       <c r="C69" s="104">
-        <f>SUM(C4,C6,C8,C10,C12,C14,C16,C18,C20,C22,C24)</f>
-        <v>158341.18</v>
+        <v>3912</v>
       </c>
       <c r="D69" s="104">
-        <f>SUM(D4,D6,D8,D10,D12,D14,D16,D18,D20,D22,D24)</f>
-        <v>98813.79</v>
+        <v>114491.38</v>
       </c>
       <c r="E69" s="105">
-        <f>SUM(E4,E6,E8,E10,E12,E14,E16,E18,E20,E22,E24)</f>
-        <v>59527.39</v>
+        <v>-110579.38</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>121</v>
       </c>
       <c r="G69" s="107">
-        <f>SUM(E69/C69)</f>
-        <v>0.375943832173033</v>
+        <v>-28.266712678936607</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>122</v>
       </c>
       <c r="I69" s="109">
-        <f>(E69-(K4+K6+K8+K10+K12+K14+K16+K18+K20+K22+K24))/C69</f>
-        <v>0.271848359346571</v>
+        <v>-34.24897239263804</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -25243,36 +25060,31 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>123</v>
       </c>
       <c r="C70" s="99">
-        <f>SUM(C26,C28,C30,C32,C34,C36,C38,C40,C42,C44,C46)</f>
-        <v>52738.76</v>
+        <v>-22865.6</v>
       </c>
       <c r="D70" s="99">
-        <f>SUM(D26,D28,D30,D32,D34,D36,D38,D40,D42,D44,D46)</f>
-        <v>32858.92</v>
+        <v>32774.04000000001</v>
       </c>
       <c r="E70" s="110">
-        <f>SUM(E26,E28,E30,E32,E34,E36,E38,E40,E42,E44,E46)</f>
-        <v>19879.84</v>
+        <v>-55639.640000000014</v>
       </c>
       <c r="F70" s="111" t="s">
         <v>121</v>
       </c>
       <c r="G70" s="112">
-        <f>SUM(E70/C70)</f>
-        <v>0.376949325315954</v>
+        <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
         <v>122</v>
       </c>
       <c r="I70" s="114">
-        <f>(E70-(K26+K28+K30+K32+K34+K36+K38+K40+K42+K44+K46))/C70</f>
-        <v>0.267731740374632</v>
+        <v>2.685240710936954</v>
       </c>
       <c r="J70" s="36"/>
       <c r="K70" s="36"/>
@@ -25633,7 +25445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25644,7 +25456,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25665,7 +25477,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>124</v>
@@ -25727,7 +25539,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>140</v>
       </c>
@@ -25785,7 +25597,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <f>'Main Sheet'!A4</f>
         <v>7658</v>
@@ -25824,7 +25636,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25843,7 +25655,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <f>'Main Sheet'!A6</f>
         <v>8142</v>
@@ -25882,7 +25694,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25901,7 +25713,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <f>'Main Sheet'!A8</f>
         <v>8824</v>
@@ -25940,7 +25752,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25959,7 +25771,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <f>'Main Sheet'!A10</f>
         <v>8127</v>
@@ -26000,7 +25812,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -26019,7 +25831,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -26060,7 +25872,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -26079,7 +25891,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <f>'Main Sheet'!A14</f>
         <v>8886</v>
@@ -26122,7 +25934,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -26141,7 +25953,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <f>'Main Sheet'!A16</f>
         <v>8887</v>
@@ -26179,7 +25991,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -26198,7 +26010,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <f>'Main Sheet'!A18</f>
         <v>8670</v>
@@ -26236,7 +26048,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -26255,7 +26067,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <f>'Main Sheet'!A20</f>
         <v>8907</v>
@@ -26291,7 +26103,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26310,7 +26122,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <f>'Main Sheet'!A22</f>
         <v>9065</v>
@@ -26350,7 +26162,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26369,7 +26181,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <f>'Main Sheet'!A24</f>
         <v>9259</v>
@@ -26401,7 +26213,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26420,7 +26232,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <f>'Main Sheet'!A26</f>
         <v>8352</v>
@@ -26456,7 +26268,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26475,7 +26287,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <f>'Main Sheet'!A28</f>
         <v>8234</v>
@@ -26512,7 +26324,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26531,7 +26343,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <f>'Main Sheet'!A30</f>
         <v>8214</v>
@@ -26572,7 +26384,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26591,7 +26403,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <f>'Main Sheet'!A32</f>
         <v>6792</v>
@@ -26625,7 +26437,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26644,7 +26456,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <f>'Main Sheet'!A34</f>
         <v>8840</v>
@@ -26680,7 +26492,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26699,7 +26511,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <f>'Main Sheet'!A36</f>
         <v>8769</v>
@@ -26737,7 +26549,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26756,7 +26568,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <f>'Main Sheet'!A38</f>
         <v>7901</v>
@@ -26797,7 +26609,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26816,7 +26628,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <f>'Main Sheet'!A40</f>
         <v>8923</v>
@@ -26856,7 +26668,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26875,7 +26687,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <f>'Main Sheet'!A42</f>
         <v>7864</v>
@@ -26910,7 +26722,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26929,7 +26741,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <f>'Main Sheet'!A44</f>
         <v>7912</v>
@@ -26974,7 +26786,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26993,7 +26805,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <f>'Main Sheet'!A46</f>
         <v>8360</v>
@@ -27027,7 +26839,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27046,7 +26858,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <f>'Main Sheet'!A48</f>
         <v>8337</v>
@@ -27084,7 +26896,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -27103,7 +26915,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <f>'Main Sheet'!A50</f>
         <v>9240</v>
@@ -27141,7 +26953,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -27160,7 +26972,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <f>'Main Sheet'!A52</f>
         <v>7428</v>
@@ -27201,7 +27013,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -27220,7 +27032,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <f>'Main Sheet'!A54</f>
         <v>9351</v>
@@ -27261,7 +27073,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -27280,7 +27092,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <f>'Main Sheet'!A56</f>
         <v>7429</v>
@@ -27319,7 +27131,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -27338,7 +27150,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <f>'Main Sheet'!A58</f>
         <v>9508</v>
@@ -27378,7 +27190,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27397,7 +27209,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19">
         <f>'Main Sheet'!A60</f>
         <v>0</v>
@@ -27431,7 +27243,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27450,7 +27262,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19">
         <f>'Main Sheet'!A62</f>
         <v>0</v>
@@ -27484,7 +27296,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27503,7 +27315,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <f>'Main Sheet'!A64</f>
         <v>8946</v>
@@ -27541,7 +27353,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27560,7 +27372,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <f>'Main Sheet'!A66</f>
         <v>8308</v>
@@ -27604,7 +27416,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27623,7 +27435,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27642,7 +27454,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27661,7 +27473,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>144</v>
@@ -27727,7 +27539,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>145</v>
@@ -27793,7 +27605,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>146</v>
@@ -27859,7 +27671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>147</v>
@@ -27916,7 +27728,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>148</v>
@@ -27973,7 +27785,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27992,7 +27804,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>149</v>
@@ -28039,7 +27851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>151</v>
@@ -28084,7 +27896,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28103,7 +27915,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>152</v>
@@ -28126,7 +27938,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>154</v>
@@ -28149,7 +27961,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>155</v>
@@ -28172,7 +27984,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>156</v>
@@ -28195,7 +28007,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>157</v>
@@ -28218,7 +28030,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>158</v>
@@ -28241,7 +28053,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>159</v>
@@ -28264,7 +28076,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>160</v>
@@ -28287,7 +28099,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>161</v>
@@ -28310,7 +28122,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>162</v>
@@ -28333,7 +28145,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>163</v>
@@ -28356,7 +28168,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>164</v>
@@ -28379,7 +28191,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -28400,7 +28212,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -28421,7 +28233,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -28442,7 +28254,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -28463,7 +28275,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -28484,7 +28296,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -28505,7 +28317,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28526,7 +28338,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>165</v>
@@ -28549,7 +28361,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>166</v>
@@ -28572,7 +28384,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>167</v>
@@ -28595,7 +28407,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>168</v>
@@ -28618,7 +28430,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>169</v>
@@ -28641,7 +28453,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>170</v>
@@ -28664,7 +28476,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>171</v>
@@ -28687,7 +28499,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28706,7 +28518,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28725,7 +28537,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28744,7 +28556,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28763,7 +28575,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>172</v>
@@ -28838,11 +28650,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>173</v>
       </c>
@@ -28874,7 +28685,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>174</v>
       </c>
@@ -28907,7 +28718,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>175</v>
       </c>
@@ -28940,7 +28751,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>176</v>
       </c>
@@ -28973,7 +28784,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>177</v>
       </c>
@@ -29006,7 +28817,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>178</v>
       </c>
@@ -29039,7 +28850,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>179</v>
       </c>
@@ -29072,7 +28883,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>180</v>
       </c>
@@ -29105,7 +28916,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29136,7 +28947,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29167,7 +28978,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>181</v>
       </c>
@@ -29200,7 +29011,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>182</v>
       </c>
@@ -29233,7 +29044,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>183</v>
       </c>
@@ -29266,7 +29077,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>184</v>
       </c>
@@ -29299,7 +29110,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>185</v>
       </c>
@@ -29332,7 +29143,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>186</v>
       </c>
@@ -29365,7 +29176,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>187</v>
       </c>
@@ -29398,7 +29209,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>188</v>
       </c>
@@ -29431,7 +29242,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>189</v>
       </c>
@@ -29464,7 +29275,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>190</v>
       </c>
@@ -29497,7 +29308,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>191</v>
       </c>
@@ -29530,7 +29341,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>192</v>
       </c>
@@ -29563,7 +29374,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>193</v>
       </c>
@@ -29596,7 +29407,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>194</v>
       </c>
@@ -29629,7 +29440,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>195</v>
       </c>
@@ -29662,7 +29473,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>196</v>
       </c>
@@ -29695,7 +29506,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>197</v>
       </c>
@@ -29727,7 +29538,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>198</v>
       </c>
@@ -29759,7 +29570,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>199</v>
       </c>
@@ -29791,7 +29602,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>200</v>
       </c>
@@ -29823,7 +29634,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>201</v>
       </c>
@@ -29855,7 +29666,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29885,7 +29696,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29915,7 +29726,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>202</v>
       </c>
@@ -29947,7 +29758,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>203</v>
       </c>
@@ -29979,7 +29790,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>204</v>
       </c>
@@ -30011,7 +29822,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>205</v>
       </c>
@@ -30043,7 +29854,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>206</v>
       </c>
@@ -30075,7 +29886,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30105,7 +29916,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>207</v>
       </c>
@@ -30137,7 +29948,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>208</v>
       </c>
@@ -30169,7 +29980,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>209</v>
       </c>
@@ -30201,7 +30012,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>210</v>
       </c>
@@ -30233,7 +30044,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -30263,7 +30074,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -30293,7 +30104,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -30323,7 +30134,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -30353,7 +30164,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>211</v>
       </c>
@@ -30385,7 +30196,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>212</v>
       </c>
@@ -30417,7 +30228,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -30447,7 +30258,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -30477,7 +30288,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -30507,7 +30318,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30537,7 +30348,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30567,7 +30378,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30662,11 +30473,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>213</v>
       </c>
@@ -30698,7 +30508,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30729,7 +30539,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30760,7 +30570,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30791,7 +30601,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30822,7 +30632,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30853,7 +30663,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30884,7 +30694,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30915,7 +30725,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30946,7 +30756,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30977,7 +30787,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31008,7 +30818,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31039,7 +30849,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31070,7 +30880,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31101,7 +30911,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31132,7 +30942,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31163,7 +30973,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31194,7 +31004,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31225,7 +31035,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31256,7 +31066,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -31287,7 +31097,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -31317,7 +31127,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -31347,7 +31157,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -31377,7 +31187,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -31407,7 +31217,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -31437,7 +31247,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -31467,7 +31277,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -31497,7 +31307,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31527,7 +31337,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31557,7 +31367,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31587,7 +31397,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31617,7 +31427,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31647,7 +31457,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31677,7 +31487,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31707,7 +31517,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31737,7 +31547,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31767,7 +31577,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>211</v>
       </c>
@@ -31799,7 +31609,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>212</v>
       </c>
@@ -31831,7 +31641,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31861,7 +31671,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31891,7 +31701,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31921,7 +31731,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31951,7 +31761,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31981,7 +31791,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53724,19 +53534,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53750,7 +53560,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>220</v>
       </c>
@@ -53762,7 +53572,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>221</v>
       </c>
@@ -53773,7 +53583,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>222</v>
       </c>
@@ -53784,7 +53594,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>223</v>
       </c>
@@ -53795,13 +53605,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -17207,7 +17207,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -22817,7 +22817,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22831,7 +22831,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -22853,7 +22853,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>99</v>
       </c>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -22919,7 +22919,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <f>'Main Sheet'!A4</f>
         <v>7658</v>
@@ -22968,7 +22968,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -22985,7 +22985,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <f>'Main Sheet'!A6</f>
         <v>8142</v>
@@ -23039,7 +23039,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23056,7 +23056,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <f>'Main Sheet'!A8</f>
         <v>8824</v>
@@ -23103,7 +23103,7 @@
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23120,7 +23120,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <f>'Main Sheet'!A10</f>
         <v>8127</v>
@@ -23171,7 +23171,7 @@
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23188,7 +23188,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23237,7 +23237,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23254,7 +23254,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <f>'Main Sheet'!A14</f>
         <v>8886</v>
@@ -23305,7 +23305,7 @@
         <v>45.876428571428605</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23322,7 +23322,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <f>'Main Sheet'!A16</f>
         <v>8887</v>
@@ -23371,7 +23371,7 @@
         <v>98.73233429394816</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23388,7 +23388,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <f>'Main Sheet'!A18</f>
         <v>8670</v>
@@ -23442,7 +23442,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23459,7 +23459,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <f>'Main Sheet'!A20</f>
         <v>8907</v>
@@ -23501,7 +23501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23518,7 +23518,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <f>'Main Sheet'!A22</f>
         <v>9065</v>
@@ -23565,7 +23565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23582,7 +23582,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <f>'Main Sheet'!A24</f>
         <v>9259</v>
@@ -23627,7 +23627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23644,7 +23644,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <f>'Main Sheet'!A26</f>
         <v>8352</v>
@@ -23693,7 +23693,7 @@
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23710,7 +23710,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <f>'Main Sheet'!A28</f>
         <v>8234</v>
@@ -23757,7 +23757,7 @@
         <v>30.14242424242425</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23774,7 +23774,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <f>'Main Sheet'!A30</f>
         <v>8214</v>
@@ -23821,7 +23821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23838,7 +23838,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <f>'Main Sheet'!A32</f>
         <v>6792</v>
@@ -23889,7 +23889,7 @@
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23906,7 +23906,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <f>'Main Sheet'!A34</f>
         <v>8840</v>
@@ -23955,7 +23955,7 @@
         <v>252.9351404151404</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -23972,7 +23972,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <f>'Main Sheet'!A36</f>
         <v>8769</v>
@@ -24023,7 +24023,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24040,7 +24040,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <f>'Main Sheet'!A38</f>
         <v>7901</v>
@@ -24087,7 +24087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24104,7 +24104,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <f>'Main Sheet'!A40</f>
         <v>8923</v>
@@ -24153,7 +24153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24170,7 +24170,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <f>'Main Sheet'!A42</f>
         <v>7864</v>
@@ -24217,7 +24217,7 @@
         <v>-11.131808809746953</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24234,7 +24234,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <f>'Main Sheet'!A44</f>
         <v>7912</v>
@@ -24279,7 +24279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24296,7 +24296,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <f>'Main Sheet'!A46</f>
         <v>8360</v>
@@ -24341,7 +24341,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24358,7 +24358,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <f>'Main Sheet'!A48</f>
         <v>8337</v>
@@ -24405,7 +24405,7 @@
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24422,7 +24422,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <f>'Main Sheet'!A50</f>
         <v>9240</v>
@@ -24472,7 +24472,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24489,7 +24489,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <f>'Main Sheet'!A52</f>
         <v>7428</v>
@@ -24538,7 +24538,7 @@
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24555,7 +24555,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <f>'Main Sheet'!A54</f>
         <v>9351</v>
@@ -24604,7 +24604,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24621,7 +24621,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <f>'Main Sheet'!A56</f>
         <v>7429</v>
@@ -24670,7 +24670,7 @@
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24687,7 +24687,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <f>'Main Sheet'!A58</f>
         <v>9508</v>
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24749,7 +24749,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59">
         <f>'Main Sheet'!A60</f>
         <v>0</v>
@@ -24796,7 +24796,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24813,7 +24813,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59">
         <f>'Main Sheet'!A62</f>
         <v>0</v>
@@ -24862,7 +24862,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24879,7 +24879,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <f>'Main Sheet'!A64</f>
         <v>8946</v>
@@ -24926,7 +24926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24943,7 +24943,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -25008,7 +25008,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -25025,7 +25025,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>119</v>
       </c>
@@ -25060,7 +25060,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>123</v>
@@ -25445,7 +25445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25456,7 +25456,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25477,7 +25477,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>124</v>
@@ -25539,7 +25539,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>140</v>
       </c>
@@ -25597,7 +25597,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <f>'Main Sheet'!A4</f>
         <v>7658</v>
@@ -25607,16 +25607,13 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="54">
-        <f t="array" ref="C4:C4">LOOKUP(2,1/('Deliverables Sheet'!S4:S9&lt;&gt;0),'Deliverables Sheet'!S4:S9)</f>
         <v>530.95</v>
       </c>
       <c r="D4" s="54">
-        <f t="array" ref="D4:D4">LOOKUP(2,1/('Deliverables Sheet'!T4:T9&lt;&gt;0),'Deliverables Sheet'!T4:T9)</f>
-        <v>418</v>
+        <v>556.5</v>
       </c>
       <c r="E4" s="54">
-        <f t="array" ref="E4:E4">LOOKUP(2,1/('Deliverables Sheet'!U4:U9&lt;&gt;0),'Deliverables Sheet'!U4:U9)</f>
-        <v>112.95</v>
+        <v>-25.549999999999955</v>
       </c>
       <c r="F4" s="54"/>
       <c r="G4" s="54"/>
@@ -25636,7 +25633,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25655,7 +25652,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <f>'Main Sheet'!A6</f>
         <v>8142</v>
@@ -25665,16 +25662,13 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C6" s="54">
-        <f t="array" ref="C6:C6">LOOKUP(2,1/('Deliverables Sheet'!S11:S16&lt;&gt;0),'Deliverables Sheet'!S11:S16)</f>
-        <v>311.89</v>
+        <v>356.07</v>
       </c>
       <c r="D6" s="54">
-        <f t="array" ref="D6:D6">LOOKUP(2,1/('Deliverables Sheet'!T11:T16&lt;&gt;0),'Deliverables Sheet'!T11:T16)</f>
-        <v>52.5</v>
+        <v>90.75</v>
       </c>
       <c r="E6" s="54">
-        <f t="array" ref="E6:E6">LOOKUP(2,1/('Deliverables Sheet'!U11:U16&lt;&gt;0),'Deliverables Sheet'!U11:U16)</f>
-        <v>259.39</v>
+        <v>265.32</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -25694,7 +25688,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25713,7 +25707,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <f>'Main Sheet'!A8</f>
         <v>8824</v>
@@ -25723,15 +25717,12 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C8" s="54">
-        <f t="array" ref="C8:C8">LOOKUP(2,1/('Deliverables Sheet'!S18:S23&lt;&gt;0),'Deliverables Sheet'!S18:S23)</f>
         <v>125.39</v>
       </c>
       <c r="D8" s="54">
-        <f t="array" ref="D8:D8">LOOKUP(2,1/('Deliverables Sheet'!T18:T23&lt;&gt;0),'Deliverables Sheet'!T18:T23)</f>
         <v>34.75</v>
       </c>
       <c r="E8" s="54">
-        <f t="array" ref="E8:E8">LOOKUP(2,1/('Deliverables Sheet'!U18:U23&lt;&gt;0),'Deliverables Sheet'!U18:U23)</f>
         <v>90.64</v>
       </c>
       <c r="F8" s="54"/>
@@ -25752,7 +25743,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25771,7 +25762,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <f>'Main Sheet'!A10</f>
         <v>8127</v>
@@ -25781,16 +25772,13 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C10" s="54">
-        <f t="array" ref="C10:C10">LOOKUP(2,1/('Deliverables Sheet'!S25:S30&lt;&gt;0),'Deliverables Sheet'!S25:S30)</f>
         <v>795.22</v>
       </c>
       <c r="D10" s="54">
-        <f t="array" ref="D10:D10">LOOKUP(2,1/('Deliverables Sheet'!T25:T30&lt;&gt;0),'Deliverables Sheet'!T25:T30)</f>
-        <v>388.25</v>
+        <v>531.25</v>
       </c>
       <c r="E10" s="54">
-        <f t="array" ref="E10:E10">LOOKUP(2,1/('Deliverables Sheet'!U25:U30&lt;&gt;0),'Deliverables Sheet'!U25:U30)</f>
-        <v>406.97</v>
+        <v>263.97</v>
       </c>
       <c r="F10" s="54"/>
       <c r="G10" s="54"/>
@@ -25812,7 +25800,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25831,7 +25819,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25839,16 +25827,13 @@
         <v>115</v>
       </c>
       <c r="C12" s="54">
-        <f>'Deliverables Sheet'!S32</f>
         <v>1120.27</v>
       </c>
       <c r="D12" s="54">
-        <f>'Deliverables Sheet'!T32</f>
-        <v>387.5</v>
+        <v>416.25</v>
       </c>
       <c r="E12" s="54">
-        <f t="array" ref="E12:E12">LOOKUP(2,1/('Deliverables Sheet'!U32:U37&lt;&gt;0),'Deliverables Sheet'!U32:U37)</f>
-        <v>732.77</v>
+        <v>704.02</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="54"/>
@@ -25872,7 +25857,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25891,7 +25876,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <f>'Main Sheet'!A14</f>
         <v>8886</v>
@@ -25901,16 +25886,13 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C14" s="54">
-        <f>'Deliverables Sheet'!S39</f>
-        <v>501</v>
+        <v>501.83</v>
       </c>
       <c r="D14" s="54">
-        <f>'Deliverables Sheet'!T39</f>
-        <v>112</v>
+        <v>123.75</v>
       </c>
       <c r="E14" s="54">
-        <f t="array" ref="E14:E14">LOOKUP(2,1/('Deliverables Sheet'!U39:U44&lt;&gt;0),'Deliverables Sheet'!U39:U44)</f>
-        <v>389</v>
+        <v>378.08</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -25934,7 +25916,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25953,7 +25935,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <f>'Main Sheet'!A16</f>
         <v>8887</v>
@@ -25963,16 +25945,13 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C16" s="54">
-        <f t="array" ref="C16:C16">LOOKUP(2,1/('Deliverables Sheet'!S46:S51&lt;&gt;0),'Deliverables Sheet'!S46:S51)</f>
-        <v>212.3</v>
+        <v>223.22</v>
       </c>
       <c r="D16" s="54">
-        <f t="array" ref="D16:D16">LOOKUP(2,1/('Deliverables Sheet'!T46:T51&lt;&gt;0),'Deliverables Sheet'!T46:T51)</f>
-        <v>86.75</v>
+        <v>102.25</v>
       </c>
       <c r="E16" s="54">
-        <f t="array" ref="E16:E16">LOOKUP(2,1/('Deliverables Sheet'!U46:U51&lt;&gt;0),'Deliverables Sheet'!U46:U51)</f>
-        <v>125.55</v>
+        <v>120.97</v>
       </c>
       <c r="F16" s="54"/>
       <c r="G16" s="54"/>
@@ -25991,7 +25970,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -26010,7 +25989,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <f>'Main Sheet'!A18</f>
         <v>8670</v>
@@ -26020,16 +25999,13 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C18" s="54">
-        <f t="array" ref="C18:C18">LOOKUP(2,1/('Deliverables Sheet'!S53:S58&lt;&gt;0),'Deliverables Sheet'!S53:S58)</f>
-        <v>668.92</v>
+        <v>679.42</v>
       </c>
       <c r="D18" s="54">
-        <f t="array" ref="D18:D18">LOOKUP(2,1/('Deliverables Sheet'!T53:T58&lt;&gt;0),'Deliverables Sheet'!T53:T58)</f>
-        <v>269</v>
+        <v>413</v>
       </c>
       <c r="E18" s="54">
-        <f t="array" ref="E18:E18">LOOKUP(2,1/('Deliverables Sheet'!U53:U58&lt;&gt;0),'Deliverables Sheet'!U53:U58)</f>
-        <v>399.92</v>
+        <v>266.41999999999996</v>
       </c>
       <c r="F18" s="54"/>
       <c r="G18" s="54"/>
@@ -26048,7 +26024,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -26067,7 +26043,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <f>'Main Sheet'!A20</f>
         <v>8907</v>
@@ -26077,16 +26053,13 @@
         <v>35 Mania</v>
       </c>
       <c r="C20" s="54">
-        <f t="array" ref="C20:C20">LOOKUP(2,1/('Deliverables Sheet'!S60:S65&lt;&gt;0),'Deliverables Sheet'!S60:S65)</f>
         <v>63.5</v>
       </c>
       <c r="D20" s="54">
-        <f t="array" ref="D20:D20">LOOKUP(2,1/('Deliverables Sheet'!T60:T65&lt;&gt;0),'Deliverables Sheet'!T60:T65)</f>
-        <v>26.75</v>
+        <v>47.5</v>
       </c>
       <c r="E20" s="54">
-        <f t="array" ref="E20:E20">LOOKUP(2,1/('Deliverables Sheet'!U60:U65&lt;&gt;0),'Deliverables Sheet'!U60:U65)</f>
-        <v>36.75</v>
+        <v>16</v>
       </c>
       <c r="F20" s="54"/>
       <c r="G20" s="54"/>
@@ -26103,7 +26076,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26122,7 +26095,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <f>'Main Sheet'!A22</f>
         <v>9065</v>
@@ -26132,16 +26105,13 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C22" s="54">
-        <f t="array" ref="C22:C22">LOOKUP(2,1/('Deliverables Sheet'!S67:S72&lt;&gt;0),'Deliverables Sheet'!S67:S72)</f>
         <v>160.82</v>
       </c>
-      <c r="D22" s="54" t="e">
-        <f t="array" ref="D22:D22">LOOKUP(2,1/('Deliverables Sheet'!T67:T72&lt;&gt;0),'Deliverables Sheet'!T67:T72)</f>
-        <v>#N/A</v>
+      <c r="D22" s="54">
+        <v>2.75</v>
       </c>
       <c r="E22" s="54">
-        <f t="array" ref="E22:E22">LOOKUP(2,1/('Deliverables Sheet'!U67:U72&lt;&gt;0),'Deliverables Sheet'!U67:U72)</f>
-        <v>160.82</v>
+        <v>158.07</v>
       </c>
       <c r="F22" s="54"/>
       <c r="G22" s="54"/>
@@ -26162,7 +26132,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26181,7 +26151,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <f>'Main Sheet'!A24</f>
         <v>9259</v>
@@ -26190,11 +26160,14 @@
         <f>'Main Sheet'!B24</f>
         <v>Andrew Reeve Stage 2</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54" t="e">
-        <f t="array" ref="E24:E24">LOOKUP(2,1/('Deliverables Sheet'!U69:U74&lt;&gt;0),'Deliverables Sheet'!U69:U74)</f>
-        <v>#N/A</v>
+      <c r="C24" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="D24" s="54">
+        <v>0</v>
+      </c>
+      <c r="E24" s="54">
+        <v>470.62</v>
       </c>
       <c r="F24" s="54"/>
       <c r="G24" s="54"/>
@@ -26213,7 +26186,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26232,7 +26205,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <f>'Main Sheet'!A26</f>
         <v>8352</v>
@@ -26242,16 +26215,13 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C26" s="54">
-        <f t="array" ref="C26:C26">LOOKUP(2,1/('Deliverables Sheet'!S81:S86&lt;&gt;0),'Deliverables Sheet'!S81:S86)</f>
         <v>139.07</v>
       </c>
       <c r="D26" s="54">
-        <f t="array" ref="D26:D26">LOOKUP(2,1/('Deliverables Sheet'!T81:T86&lt;&gt;0),'Deliverables Sheet'!T81:T86)</f>
         <v>143.25</v>
       </c>
       <c r="E26" s="54">
-        <f t="array" ref="E26:E26">LOOKUP(2,1/('Deliverables Sheet'!U81:U86&lt;&gt;0),'Deliverables Sheet'!U81:U86)</f>
-        <v>-4.18000000000001</v>
+        <v>-4.180000000000007</v>
       </c>
       <c r="F26" s="54"/>
       <c r="G26" s="54"/>
@@ -26268,7 +26238,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26287,7 +26257,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <f>'Main Sheet'!A28</f>
         <v>8234</v>
@@ -26297,16 +26267,13 @@
         <v>Melhuish House</v>
       </c>
       <c r="C28" s="54">
-        <f t="array" ref="C28:C28">LOOKUP(2,1/('Deliverables Sheet'!S88:S93&lt;&gt;0),'Deliverables Sheet'!S88:S93)</f>
         <v>231.75</v>
       </c>
       <c r="D28" s="54">
-        <f t="array" ref="D28:D28">LOOKUP(2,1/('Deliverables Sheet'!T88:T93&lt;&gt;0),'Deliverables Sheet'!T88:T93)</f>
-        <v>148.5</v>
+        <v>204.75</v>
       </c>
       <c r="E28" s="54">
-        <f t="array" ref="E28:E28">LOOKUP(2,1/('Deliverables Sheet'!U88:U93&lt;&gt;0),'Deliverables Sheet'!U88:U93)</f>
-        <v>83.25</v>
+        <v>27</v>
       </c>
       <c r="F28" s="54"/>
       <c r="G28" s="54"/>
@@ -26324,7 +26291,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26343,7 +26310,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <f>'Main Sheet'!A30</f>
         <v>8214</v>
@@ -26353,15 +26320,12 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C30" s="54">
-        <f t="array" ref="C30:C30">LOOKUP(2,1/('Deliverables Sheet'!S95:S100&lt;&gt;0),'Deliverables Sheet'!S95:S100)</f>
         <v>147.9</v>
       </c>
       <c r="D30" s="54">
-        <f t="array" ref="D30:D30">LOOKUP(2,1/('Deliverables Sheet'!T95:T100&lt;&gt;0),'Deliverables Sheet'!T95:T100)</f>
         <v>5</v>
       </c>
       <c r="E30" s="54">
-        <f t="array" ref="E30:E30">LOOKUP(2,1/('Deliverables Sheet'!U95:U100&lt;&gt;0),'Deliverables Sheet'!U95:U100)</f>
         <v>142.9</v>
       </c>
       <c r="F30" s="54"/>
@@ -26384,7 +26348,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26403,7 +26367,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <f>'Main Sheet'!A32</f>
         <v>6792</v>
@@ -26413,16 +26377,13 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C32" s="54">
-        <f t="array" ref="C32:C32">LOOKUP(2,1/('Deliverables Sheet'!S102:S107&lt;&gt;0),'Deliverables Sheet'!S102:S107)</f>
         <v>208.2</v>
       </c>
       <c r="D32" s="54">
-        <f t="array" ref="D32:D32">LOOKUP(2,1/('Deliverables Sheet'!T102:T107&lt;&gt;0),'Deliverables Sheet'!T102:T107)</f>
         <v>317.25</v>
       </c>
       <c r="E32" s="54">
-        <f t="array" ref="E32:E32">LOOKUP(2,1/('Deliverables Sheet'!U102:U107&lt;&gt;0),'Deliverables Sheet'!U102:U107)</f>
-        <v>-109.05</v>
+        <v>-109.05000000000001</v>
       </c>
       <c r="F32" s="54"/>
       <c r="G32" s="54"/>
@@ -26437,7 +26398,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26456,7 +26417,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <f>'Main Sheet'!A34</f>
         <v>8840</v>
@@ -26466,16 +26427,13 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C34" s="54">
-        <f t="array" ref="C34:C34">LOOKUP(2,1/('Deliverables Sheet'!S109:S114&lt;&gt;0),'Deliverables Sheet'!S109:S114)</f>
-        <v>316.34</v>
+        <v>324.19</v>
       </c>
       <c r="D34" s="54">
-        <f t="array" ref="D34:D34">LOOKUP(2,1/('Deliverables Sheet'!T109:T114&lt;&gt;0),'Deliverables Sheet'!T109:T114)</f>
-        <v>204.75</v>
+        <v>412.5</v>
       </c>
       <c r="E34" s="54">
-        <f t="array" ref="E34:E34">LOOKUP(2,1/('Deliverables Sheet'!U109:U114&lt;&gt;0),'Deliverables Sheet'!U109:U114)</f>
-        <v>111.59</v>
+        <v>-88.31</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
@@ -26492,7 +26450,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26511,7 +26469,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <f>'Main Sheet'!A36</f>
         <v>8769</v>
@@ -26520,17 +26478,14 @@
         <f>'Main Sheet'!B36</f>
         <v>Percival Bach</v>
       </c>
-      <c r="C36" s="54" t="e">
-        <f t="array" ref="C36:C36">LOOKUP(2,1/('Deliverables Sheet'!S116:S121&lt;&gt;0),'Deliverables Sheet'!S116:S121)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D36" s="54" t="e">
-        <f t="array" ref="D36:D36">LOOKUP(2,1/('Deliverables Sheet'!T116:T121&lt;&gt;0),'Deliverables Sheet'!T116:T121)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E36" s="54" t="e">
-        <f t="array" ref="E36:E36">LOOKUP(2,1/('Deliverables Sheet'!U116:U121&lt;&gt;0),'Deliverables Sheet'!U116:U121)</f>
-        <v>#N/A</v>
+      <c r="C36" s="54">
+        <v>84.05</v>
+      </c>
+      <c r="D36" s="54">
+        <v>0</v>
+      </c>
+      <c r="E36" s="54">
+        <v>84.05</v>
       </c>
       <c r="F36" s="54"/>
       <c r="G36" s="54"/>
@@ -26549,7 +26504,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26568,7 +26523,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <f>'Main Sheet'!A38</f>
         <v>7901</v>
@@ -26578,16 +26533,13 @@
         <v>St Albans Street</v>
       </c>
       <c r="C38" s="54">
-        <f t="array" ref="C38:C38">LOOKUP(2,1/('Deliverables Sheet'!S123:S128&lt;&gt;0),'Deliverables Sheet'!S123:S128)</f>
-        <v>273.37</v>
-      </c>
-      <c r="D38" s="54" t="e">
-        <f t="array" ref="D38:D38">LOOKUP(2,1/('Deliverables Sheet'!T123:T128&lt;&gt;0),'Deliverables Sheet'!T123:T128)</f>
-        <v>#N/A</v>
+        <v>290.15</v>
+      </c>
+      <c r="D38" s="54">
+        <v>91.75</v>
       </c>
       <c r="E38" s="54">
-        <f t="array" ref="E38:E38">LOOKUP(2,1/('Deliverables Sheet'!U123:U128&lt;&gt;0),'Deliverables Sheet'!U123:U128)</f>
-        <v>273.37</v>
+        <v>198.39999999999998</v>
       </c>
       <c r="F38" s="54"/>
       <c r="G38" s="54"/>
@@ -26609,7 +26561,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26628,7 +26580,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <f>'Main Sheet'!A40</f>
         <v>8923</v>
@@ -26638,16 +26590,13 @@
         <v>4 Perry St</v>
       </c>
       <c r="C40" s="54">
-        <f t="array" ref="C40:C40">LOOKUP(2,1/('Deliverables Sheet'!S130:S135&lt;&gt;0),'Deliverables Sheet'!S130:S135)</f>
-        <v>157</v>
+        <v>156.69</v>
       </c>
       <c r="D40" s="54">
-        <f t="array" ref="D40:D40">LOOKUP(2,1/('Deliverables Sheet'!T130:T135&lt;&gt;0),'Deliverables Sheet'!T130:T135)</f>
         <v>2</v>
       </c>
       <c r="E40" s="54">
-        <f t="array" ref="E40:E40">LOOKUP(2,1/('Deliverables Sheet'!U130:U135&lt;&gt;0),'Deliverables Sheet'!U130:U135)</f>
-        <v>155</v>
+        <v>154.69</v>
       </c>
       <c r="F40" s="54">
         <v>60</v>
@@ -26668,7 +26617,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26687,7 +26636,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <f>'Main Sheet'!A42</f>
         <v>7864</v>
@@ -26697,16 +26646,13 @@
         <v>Ryans House</v>
       </c>
       <c r="C42" s="54">
-        <f t="array" ref="C42:C42">LOOKUP(2,1/('Deliverables Sheet'!S137:S142&lt;&gt;0),'Deliverables Sheet'!S137:S142)</f>
-        <v>193.82</v>
+        <v>200.82</v>
       </c>
       <c r="D42" s="54">
-        <f t="array" ref="D42:D42">LOOKUP(2,1/('Deliverables Sheet'!T137:T142&lt;&gt;0),'Deliverables Sheet'!T137:T142)</f>
-        <v>266.75</v>
+        <v>278.25</v>
       </c>
       <c r="E42" s="54">
-        <f t="array" ref="E42:E42">LOOKUP(2,1/('Deliverables Sheet'!U137:U142&lt;&gt;0),'Deliverables Sheet'!U137:U142)</f>
-        <v>-72.93</v>
+        <v>-77.43</v>
       </c>
       <c r="F42" s="54"/>
       <c r="G42" s="54"/>
@@ -26722,7 +26668,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26741,7 +26687,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <f>'Main Sheet'!A44</f>
         <v>7912</v>
@@ -26750,17 +26696,14 @@
         <f>'Main Sheet'!B44</f>
         <v>71A Fendalton Road </v>
       </c>
-      <c r="C44" s="54" t="e">
-        <f t="array" ref="C44:C44">LOOKUP(2,1/('Deliverables Sheet'!S144:S149&lt;&gt;0),'Deliverables Sheet'!S144:S149)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D44" s="54" t="e">
-        <f t="array" ref="D44:D44">LOOKUP(2,1/('Deliverables Sheet'!T144:T149&lt;&gt;0),'Deliverables Sheet'!T144:T149)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E44" s="54" t="e">
-        <f t="array" ref="E44:E44">LOOKUP(2,1/('Deliverables Sheet'!U144:U149&lt;&gt;0),'Deliverables Sheet'!U144:U149)</f>
-        <v>#N/A</v>
+      <c r="C44" s="54">
+        <v>497.55</v>
+      </c>
+      <c r="D44" s="54">
+        <v>58.25</v>
+      </c>
+      <c r="E44" s="54">
+        <v>439.3</v>
       </c>
       <c r="F44" s="54">
         <v>80</v>
@@ -26786,7 +26729,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26805,7 +26748,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <f>'Main Sheet'!A46</f>
         <v>8360</v>
@@ -26815,16 +26758,13 @@
         <v>Dixon House</v>
       </c>
       <c r="C46" s="54">
-        <f t="array" ref="C46:C46">LOOKUP(2,1/('Deliverables Sheet'!S151:S156&lt;&gt;0),'Deliverables Sheet'!S151:S156)</f>
         <v>210.6</v>
       </c>
       <c r="D46" s="54">
-        <f t="array" ref="D46:D46">LOOKUP(2,1/('Deliverables Sheet'!T151:T156&lt;&gt;0),'Deliverables Sheet'!T151:T156)</f>
         <v>260.75</v>
       </c>
       <c r="E46" s="54">
-        <f t="array" ref="E46:E46">LOOKUP(2,1/('Deliverables Sheet'!U151:U156&lt;&gt;0),'Deliverables Sheet'!U151:U156)</f>
-        <v>-50.15</v>
+        <v>-50.150000000000006</v>
       </c>
       <c r="F46" s="98"/>
       <c r="G46" s="98"/>
@@ -26839,7 +26779,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26858,7 +26798,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <f>'Main Sheet'!A48</f>
         <v>8337</v>
@@ -26868,16 +26808,13 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C48" s="54">
-        <f t="array" ref="C48:C48">LOOKUP(2,1/('Deliverables Sheet'!S158:S163&lt;&gt;0),'Deliverables Sheet'!S158:S163)</f>
         <v>110.44</v>
       </c>
       <c r="D48" s="54">
-        <f t="array" ref="D48:D48">LOOKUP(2,1/('Deliverables Sheet'!T158:T163&lt;&gt;0),'Deliverables Sheet'!T158:T163)</f>
-        <v>44.75</v>
+        <v>60.75</v>
       </c>
       <c r="E48" s="54">
-        <f t="array" ref="E48:E48">LOOKUP(2,1/('Deliverables Sheet'!U158:U163&lt;&gt;0),'Deliverables Sheet'!U158:U163)</f>
-        <v>65.69</v>
+        <v>49.69</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
@@ -26896,7 +26833,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26915,7 +26852,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <f>'Main Sheet'!A50</f>
         <v>9240</v>
@@ -26924,17 +26861,14 @@
         <f>'Main Sheet'!B50</f>
         <v>Daves Twizel Shack</v>
       </c>
-      <c r="C50" s="54" t="e">
-        <f t="array" ref="C50:C50">LOOKUP(2,1/('Deliverables Sheet'!S165:S170&lt;&gt;0),'Deliverables Sheet'!S165:S170)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D50" s="54" t="e">
-        <f t="array" ref="D50:D50">LOOKUP(2,1/('Deliverables Sheet'!T165:T170&lt;&gt;0),'Deliverables Sheet'!T165:T170)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E50" s="54" t="e">
-        <f t="array" ref="E50:E50">LOOKUP(2,1/('Deliverables Sheet'!U165:U170&lt;&gt;0),'Deliverables Sheet'!U165:U170)</f>
-        <v>#N/A</v>
+      <c r="C50" s="54">
+        <v>0</v>
+      </c>
+      <c r="D50" s="54">
+        <v>0</v>
+      </c>
+      <c r="E50" s="54">
+        <v>0</v>
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="54"/>
@@ -26953,7 +26887,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26972,7 +26906,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <f>'Main Sheet'!A52</f>
         <v>7428</v>
@@ -26982,16 +26916,13 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C52" s="54">
-        <f t="array" ref="C52:C52">LOOKUP(2,1/('Deliverables Sheet'!S172:S177&lt;&gt;0),'Deliverables Sheet'!S172:S177)</f>
         <v>659.73</v>
       </c>
       <c r="D52" s="54">
-        <f t="array" ref="D52:D52">LOOKUP(2,1/('Deliverables Sheet'!T172:T177&lt;&gt;0),'Deliverables Sheet'!T172:T177)</f>
-        <v>304.75</v>
+        <v>430</v>
       </c>
       <c r="E52" s="54">
-        <f t="array" ref="E52:E52">LOOKUP(2,1/('Deliverables Sheet'!U172:U177&lt;&gt;0),'Deliverables Sheet'!U172:U177)</f>
-        <v>354.98</v>
+        <v>229.73000000000002</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="54"/>
@@ -27013,7 +26944,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -27032,7 +26963,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <f>'Main Sheet'!A54</f>
         <v>9351</v>
@@ -27042,16 +26973,13 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C54" s="54">
-        <f t="array" ref="C54:C54">LOOKUP(2,1/('Deliverables Sheet'!S179:S184&lt;&gt;0),'Deliverables Sheet'!S179:S184)</f>
         <v>125.17</v>
       </c>
       <c r="D54" s="54">
-        <f t="array" ref="D54:D54">LOOKUP(2,1/('Deliverables Sheet'!T179:T184&lt;&gt;0),'Deliverables Sheet'!T179:T184)</f>
-        <v>11.25</v>
+        <v>23.75</v>
       </c>
       <c r="E54" s="54">
-        <f t="array" ref="E54:E54">LOOKUP(2,1/('Deliverables Sheet'!U179:U184&lt;&gt;0),'Deliverables Sheet'!U179:U184)</f>
-        <v>113.92</v>
+        <v>101.42</v>
       </c>
       <c r="F54" s="54"/>
       <c r="G54" s="54"/>
@@ -27073,7 +27001,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -27092,7 +27020,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <f>'Main Sheet'!A56</f>
         <v>7429</v>
@@ -27102,16 +27030,13 @@
         <v>Taggart House</v>
       </c>
       <c r="C56" s="54">
-        <f t="array" ref="C56:C56">LOOKUP(2,1/('Deliverables Sheet'!S186:S191&lt;&gt;0),'Deliverables Sheet'!S186:S191)</f>
         <v>130.62</v>
       </c>
       <c r="D56" s="54">
-        <f t="array" ref="D56:D56">LOOKUP(2,1/('Deliverables Sheet'!T186:T191&lt;&gt;0),'Deliverables Sheet'!T186:T191)</f>
-        <v>32.25</v>
+        <v>34.75</v>
       </c>
       <c r="E56" s="54">
-        <f t="array" ref="E56:E56">LOOKUP(2,1/('Deliverables Sheet'!U186:U191&lt;&gt;0),'Deliverables Sheet'!U186:U191)</f>
-        <v>98.37</v>
+        <v>95.87</v>
       </c>
       <c r="F56" s="54"/>
       <c r="G56" s="54"/>
@@ -27131,7 +27056,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -27150,7 +27075,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <f>'Main Sheet'!A58</f>
         <v>9508</v>
@@ -27159,17 +27084,14 @@
         <f>'Main Sheet'!B58</f>
         <v>St Barnabas Church</v>
       </c>
-      <c r="C58" s="54" t="e">
-        <f t="array" ref="C58:C58">LOOKUP(2,1/('Deliverables Sheet'!S193:S198&lt;&gt;0),'Deliverables Sheet'!S193:S198)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D58" s="54" t="e">
-        <f t="array" ref="D58:D58">LOOKUP(2,1/('Deliverables Sheet'!T193:T198&lt;&gt;0),'Deliverables Sheet'!T193:T198)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E58" s="54" t="e">
-        <f t="array" ref="E58:E58">LOOKUP(2,1/('Deliverables Sheet'!U193:U198&lt;&gt;0),'Deliverables Sheet'!U193:U198)</f>
-        <v>#N/A</v>
+      <c r="C58" s="54">
+        <v>140.15</v>
+      </c>
+      <c r="D58" s="54">
+        <v>5.75</v>
+      </c>
+      <c r="E58" s="54">
+        <v>134.4</v>
       </c>
       <c r="F58" s="54"/>
       <c r="G58" s="54"/>
@@ -27190,7 +27112,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27209,7 +27131,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19">
         <f>'Main Sheet'!A60</f>
         <v>0</v>
@@ -27243,7 +27165,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27262,7 +27184,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19">
         <f>'Main Sheet'!A62</f>
         <v>0</v>
@@ -27296,7 +27218,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27315,7 +27237,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <f>'Main Sheet'!A64</f>
         <v>8946</v>
@@ -27325,15 +27247,12 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C64" s="54">
-        <f t="array" ref="C64:C64">LOOKUP(2,1/('Deliverables Sheet'!S214:S219&lt;&gt;0),'Deliverables Sheet'!S214:S219)</f>
         <v>358.86</v>
       </c>
-      <c r="D64" s="54" t="e">
-        <f t="array" ref="D64:D64">LOOKUP(2,1/('Deliverables Sheet'!T214:T219&lt;&gt;0),'Deliverables Sheet'!T214:T219)</f>
-        <v>#N/A</v>
+      <c r="D64" s="54">
+        <v>0</v>
       </c>
       <c r="E64" s="54">
-        <f t="array" ref="E64:E64">LOOKUP(2,1/('Deliverables Sheet'!U214:U219&lt;&gt;0),'Deliverables Sheet'!U214:U219)</f>
         <v>358.86</v>
       </c>
       <c r="F64" s="54"/>
@@ -27353,7 +27272,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27372,7 +27291,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <f>'Main Sheet'!A66</f>
         <v>8308</v>
@@ -27382,16 +27301,13 @@
         <v>Roydvale</v>
       </c>
       <c r="C66" s="54">
-        <f t="array" ref="C66:C66">LOOKUP(2,1/('Deliverables Sheet'!S221:S226&lt;&gt;0),'Deliverables Sheet'!S221:S226)</f>
         <v>2312.68</v>
       </c>
       <c r="D66" s="54">
-        <f t="array" ref="D66:D66">LOOKUP(2,1/('Deliverables Sheet'!T221:T226&lt;&gt;0),'Deliverables Sheet'!T221:T226)</f>
-        <v>1014.25</v>
+        <v>1120.5</v>
       </c>
       <c r="E66" s="54">
-        <f t="array" ref="E66:E66">LOOKUP(2,1/('Deliverables Sheet'!U221:U226&lt;&gt;0),'Deliverables Sheet'!U221:U226)</f>
-        <v>1298.43</v>
+        <v>1192.1799999999998</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>
@@ -27416,7 +27332,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27435,7 +27351,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27454,7 +27370,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27473,7 +27389,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>144</v>
@@ -27539,7 +27455,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>145</v>
@@ -27605,7 +27521,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>146</v>
@@ -27671,7 +27587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>147</v>
@@ -27728,7 +27644,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>148</v>
@@ -27785,7 +27701,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27804,7 +27720,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>149</v>
@@ -27851,7 +27767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>151</v>
@@ -27896,7 +27812,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27915,7 +27831,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>152</v>
@@ -27938,7 +27854,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>154</v>
@@ -27961,7 +27877,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>155</v>
@@ -27984,7 +27900,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>156</v>
@@ -28007,7 +27923,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>157</v>
@@ -28030,7 +27946,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>158</v>
@@ -28053,7 +27969,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>159</v>
@@ -28076,7 +27992,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>160</v>
@@ -28099,7 +28015,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>161</v>
@@ -28122,7 +28038,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>162</v>
@@ -28145,7 +28061,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>163</v>
@@ -28168,7 +28084,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>164</v>
@@ -28191,7 +28107,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -28212,7 +28128,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -28233,7 +28149,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -28254,7 +28170,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -28275,7 +28191,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -28296,7 +28212,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -28317,7 +28233,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28338,7 +28254,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>165</v>
@@ -28361,7 +28277,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>166</v>
@@ -28384,7 +28300,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>167</v>
@@ -28407,7 +28323,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>168</v>
@@ -28430,7 +28346,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>169</v>
@@ -28453,7 +28369,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>170</v>
@@ -28476,7 +28392,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>171</v>
@@ -28499,7 +28415,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28518,7 +28434,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28537,7 +28453,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28556,7 +28472,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28575,7 +28491,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>172</v>
@@ -28650,10 +28566,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>173</v>
       </c>
@@ -28685,7 +28602,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>174</v>
       </c>
@@ -28718,7 +28635,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>175</v>
       </c>
@@ -28751,7 +28668,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>176</v>
       </c>
@@ -28784,7 +28701,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>177</v>
       </c>
@@ -28817,7 +28734,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>178</v>
       </c>
@@ -28850,7 +28767,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>179</v>
       </c>
@@ -28883,7 +28800,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>180</v>
       </c>
@@ -28916,7 +28833,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28947,7 +28864,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28978,7 +28895,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>181</v>
       </c>
@@ -29011,7 +28928,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>182</v>
       </c>
@@ -29044,7 +28961,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>183</v>
       </c>
@@ -29077,7 +28994,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>184</v>
       </c>
@@ -29110,7 +29027,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>185</v>
       </c>
@@ -29143,7 +29060,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>186</v>
       </c>
@@ -29176,7 +29093,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>187</v>
       </c>
@@ -29209,7 +29126,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>188</v>
       </c>
@@ -29242,7 +29159,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>189</v>
       </c>
@@ -29275,7 +29192,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>190</v>
       </c>
@@ -29308,7 +29225,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>191</v>
       </c>
@@ -29341,7 +29258,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>192</v>
       </c>
@@ -29374,7 +29291,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>193</v>
       </c>
@@ -29407,7 +29324,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>194</v>
       </c>
@@ -29440,7 +29357,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>195</v>
       </c>
@@ -29473,7 +29390,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>196</v>
       </c>
@@ -29506,7 +29423,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>197</v>
       </c>
@@ -29538,7 +29455,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>198</v>
       </c>
@@ -29570,7 +29487,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>199</v>
       </c>
@@ -29602,7 +29519,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>200</v>
       </c>
@@ -29634,7 +29551,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>201</v>
       </c>
@@ -29666,7 +29583,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29696,7 +29613,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29726,7 +29643,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>202</v>
       </c>
@@ -29758,7 +29675,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>203</v>
       </c>
@@ -29790,7 +29707,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>204</v>
       </c>
@@ -29822,7 +29739,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>205</v>
       </c>
@@ -29854,7 +29771,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>206</v>
       </c>
@@ -29886,7 +29803,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29916,7 +29833,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>207</v>
       </c>
@@ -29948,7 +29865,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>208</v>
       </c>
@@ -29980,7 +29897,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>209</v>
       </c>
@@ -30012,7 +29929,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>210</v>
       </c>
@@ -30044,7 +29961,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -30074,7 +29991,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -30104,7 +30021,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -30134,7 +30051,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -30164,7 +30081,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>211</v>
       </c>
@@ -30196,7 +30113,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>212</v>
       </c>
@@ -30228,7 +30145,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -30258,7 +30175,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -30288,7 +30205,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -30318,7 +30235,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30348,7 +30265,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30378,7 +30295,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30473,10 +30390,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>213</v>
       </c>
@@ -30508,7 +30426,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30539,7 +30457,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30570,7 +30488,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30601,7 +30519,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30632,7 +30550,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30663,7 +30581,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30694,7 +30612,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30725,7 +30643,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30756,7 +30674,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30787,7 +30705,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30818,7 +30736,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30849,7 +30767,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30880,7 +30798,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30911,7 +30829,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30942,7 +30860,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30973,7 +30891,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31004,7 +30922,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31035,7 +30953,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31066,7 +30984,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -31097,7 +31015,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -31127,7 +31045,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -31157,7 +31075,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -31187,7 +31105,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -31217,7 +31135,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -31247,7 +31165,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -31277,7 +31195,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -31307,7 +31225,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31337,7 +31255,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31367,7 +31285,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31397,7 +31315,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31427,7 +31345,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31457,7 +31375,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31487,7 +31405,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31517,7 +31435,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31547,7 +31465,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31577,7 +31495,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>211</v>
       </c>
@@ -31609,7 +31527,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>212</v>
       </c>
@@ -31641,7 +31559,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31671,7 +31589,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31701,7 +31619,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31731,7 +31649,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31761,7 +31679,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31791,7 +31709,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53534,19 +53452,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53560,7 +53478,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>220</v>
       </c>
@@ -53572,7 +53490,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>221</v>
       </c>
@@ -53583,7 +53501,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>222</v>
       </c>
@@ -53594,7 +53512,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>223</v>
       </c>
@@ -53605,13 +53523,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>[object Object]</t>
   </si>
   <si>
     <t>Job Number</t>
@@ -9521,7 +9524,7 @@
         <v>9131.01000000001</v>
       </c>
       <c r="G4" s="53">
-        <v>0.0424605496540267</v>
+        <v>0.042460549654026694</v>
       </c>
       <c r="H4" s="52">
         <v>181293.63</v>
@@ -9539,7 +9542,7 @@
         <v>62072.19</v>
       </c>
       <c r="M4" s="53">
-        <v>0.400401806808268</v>
+        <v>0.4004018068082677</v>
       </c>
       <c r="N4" s="53">
         <v>0.9</v>
@@ -9551,10 +9554,10 @@
         <v>20570.43</v>
       </c>
       <c r="Q4" s="52">
-        <v>5698.45</v>
+        <v>5698.450000000001</v>
       </c>
       <c r="R4" s="53">
-        <v>0.21692778679563</v>
+        <v>0.21692778679563043</v>
       </c>
       <c r="S4" s="54">
         <v>530.95</v>
@@ -9563,23 +9566,23 @@
         <v>418</v>
       </c>
       <c r="U4" s="54">
-        <v>112.95</v>
+        <v>112.95000000000005</v>
       </c>
       <c r="V4" s="53">
         <v>0.212731895658725</v>
       </c>
       <c r="W4" s="53"/>
       <c r="X4" s="55">
-        <v>221.035669856459</v>
+        <v>221.03566985645935</v>
       </c>
       <c r="Y4" s="55">
-        <v>63.5714850739241</v>
+        <v>63.57148507392409</v>
       </c>
       <c r="Z4" s="53">
-        <v>0.448692451627096</v>
+        <v>0.4486924516270963</v>
       </c>
       <c r="AA4" s="56">
-        <v>0.156957754008184</v>
+        <v>0.1569577540081836</v>
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
@@ -9928,7 +9931,7 @@
         <v>43867.36</v>
       </c>
       <c r="G11" s="53">
-        <v>0.461647632947944</v>
+        <v>0.4616476329479443</v>
       </c>
       <c r="H11" s="52">
         <v>72292.47</v>
@@ -9937,16 +9940,16 @@
         <v>48296.81</v>
       </c>
       <c r="J11" s="52">
-        <v>56719.74</v>
+        <v>56719.740000000005</v>
       </c>
       <c r="K11" s="52">
         <v>45701.86</v>
       </c>
       <c r="L11" s="52">
-        <v>11017.88</v>
+        <v>11017.880000000005</v>
       </c>
       <c r="M11" s="53">
-        <v>0.194251243041664</v>
+        <v>0.19425124304166422</v>
       </c>
       <c r="N11" s="53"/>
       <c r="O11" s="52">
@@ -9956,10 +9959,10 @@
         <v>2594.95</v>
       </c>
       <c r="Q11" s="52">
-        <v>12977.78</v>
+        <v>12977.779999999999</v>
       </c>
       <c r="R11" s="53">
-        <v>0.833365761815687</v>
+        <v>0.8333657618156868</v>
       </c>
       <c r="S11" s="54">
         <v>311.89</v>
@@ -9971,22 +9974,22 @@
         <v>259.39</v>
       </c>
       <c r="V11" s="53">
-        <v>0.831671422616948</v>
+        <v>0.8316714226169483</v>
       </c>
       <c r="W11" s="53">
         <v>0.3</v>
       </c>
       <c r="X11" s="55">
-        <v>54.4628571428571</v>
+        <v>54.462857142857146</v>
       </c>
       <c r="Y11" s="55">
-        <v>72.8814646189362</v>
+        <v>72.88146461893615</v>
       </c>
       <c r="Z11" s="53">
-        <v>0.055893616617839</v>
+        <v>0.05589361661783901</v>
       </c>
       <c r="AA11" s="56">
-        <v>0.239214585617637</v>
+        <v>0.23921458561763742</v>
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
@@ -10332,7 +10335,7 @@
         <v>6999.08</v>
       </c>
       <c r="F18" s="52">
-        <v>20501.24</v>
+        <v>20501.239999999998</v>
       </c>
       <c r="G18" s="53">
         <v>0.74549096155972</v>
@@ -10344,16 +10347,16 @@
         <v>7621.92</v>
       </c>
       <c r="J18" s="52">
-        <v>13767.34</v>
+        <v>13767.340000000002</v>
       </c>
       <c r="K18" s="52">
         <v>5911.24</v>
       </c>
       <c r="L18" s="52">
-        <v>7856.1</v>
+        <v>7856.100000000002</v>
       </c>
       <c r="M18" s="53">
-        <v>0.570633107049002</v>
+        <v>0.5706331070490016</v>
       </c>
       <c r="N18" s="53"/>
       <c r="O18" s="52">
@@ -10363,10 +10366,10 @@
         <v>1710.68</v>
       </c>
       <c r="Q18" s="52">
-        <v>4087.81</v>
+        <v>4087.8099999999995</v>
       </c>
       <c r="R18" s="53">
-        <v>0.70497836505711</v>
+        <v>0.7049783650571096</v>
       </c>
       <c r="S18" s="54">
         <v>125.39</v>
@@ -10378,22 +10381,22 @@
         <v>90.64</v>
       </c>
       <c r="V18" s="53">
-        <v>0.722864662253768</v>
+        <v>0.7228646622537682</v>
       </c>
       <c r="W18" s="53">
         <v>0.25</v>
       </c>
       <c r="X18" s="55">
-        <v>-17.9234532374101</v>
+        <v>-17.92345323741007</v>
       </c>
       <c r="Y18" s="55">
-        <v>63.2784911077438</v>
+        <v>63.278491107743825</v>
       </c>
       <c r="Z18" s="53">
-        <v>-0.0889888385330643</v>
+        <v>-0.08898883853306433</v>
       </c>
       <c r="AA18" s="56">
-        <v>0.288523551725943</v>
+        <v>0.28852355172594346</v>
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
@@ -10695,10 +10698,10 @@
         <v>111983.72</v>
       </c>
       <c r="F25" s="52">
-        <v>38867.1</v>
+        <v>38867.100000000006</v>
       </c>
       <c r="G25" s="53">
-        <v>0.257652560324167</v>
+        <v>0.25765256032416667</v>
       </c>
       <c r="H25" s="52">
         <v>102178.42</v>
@@ -10710,13 +10713,13 @@
         <v>62464.86</v>
       </c>
       <c r="K25" s="52">
-        <v>56964.81</v>
+        <v>56964.810000000005</v>
       </c>
       <c r="L25" s="52">
-        <v>5500.05</v>
+        <v>5500.049999999996</v>
       </c>
       <c r="M25" s="53">
-        <v>0.0880503054037101</v>
+        <v>0.08805030540371012</v>
       </c>
       <c r="N25" s="53">
         <v>0.9</v>
@@ -10728,10 +10731,10 @@
         <v>18753.32</v>
       </c>
       <c r="Q25" s="52">
-        <v>20960.24</v>
+        <v>20960.239999999998</v>
       </c>
       <c r="R25" s="53">
-        <v>0.527785471763297</v>
+        <v>0.5277854717632969</v>
       </c>
       <c r="S25" s="54">
         <v>795.22</v>
@@ -10743,22 +10746,22 @@
         <v>406.97</v>
       </c>
       <c r="V25" s="53">
-        <v>0.511770327708056</v>
+        <v>0.5117703277080556</v>
       </c>
       <c r="W25" s="53">
         <v>0.6</v>
       </c>
       <c r="X25" s="55">
-        <v>93.4078300064391</v>
+        <v>93.40783000643914</v>
       </c>
       <c r="Y25" s="55">
-        <v>61.2062070873469</v>
+        <v>61.206207087346904</v>
       </c>
       <c r="Z25" s="53">
-        <v>0.32384698418663</v>
+        <v>0.32384698418662994</v>
       </c>
       <c r="AA25" s="56">
-        <v>0.32265253844825</v>
+        <v>0.32265253844824976</v>
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
@@ -11104,10 +11107,10 @@
         <v>176161.65</v>
       </c>
       <c r="F32" s="52">
-        <v>212860.38</v>
+        <v>212860.38000000003</v>
       </c>
       <c r="G32" s="53">
-        <v>0.547167932880305</v>
+        <v>0.5471679328803051</v>
       </c>
       <c r="H32" s="52">
         <v>320431.12</v>
@@ -11119,13 +11122,13 @@
         <v>264519.78</v>
       </c>
       <c r="K32" s="52">
-        <v>132316.71</v>
+        <v>132316.71000000002</v>
       </c>
       <c r="L32" s="52">
         <v>132203.07</v>
       </c>
       <c r="M32" s="53">
-        <v>0.499785195647751</v>
+        <v>0.49978519564775076</v>
       </c>
       <c r="N32" s="64"/>
       <c r="O32" s="52">
@@ -11135,10 +11138,10 @@
         <v>16622.8</v>
       </c>
       <c r="Q32" s="52">
-        <v>39288.54</v>
+        <v>39288.53999999999</v>
       </c>
       <c r="R32" s="53">
-        <v>0.702693585952331</v>
+        <v>0.7026935859523309</v>
       </c>
       <c r="S32" s="54">
         <v>1120.27</v>
@@ -11150,22 +11153,22 @@
         <v>732.77</v>
       </c>
       <c r="V32" s="53">
-        <v>0.65410124345024</v>
+        <v>0.6541012434502397</v>
       </c>
       <c r="W32" s="53">
         <v>0.4</v>
       </c>
       <c r="X32" s="55">
-        <v>70.2506838709677</v>
+        <v>70.25068387096768</v>
       </c>
       <c r="Y32" s="55">
-        <v>61.2271238183652</v>
+        <v>61.22712381836522</v>
       </c>
       <c r="Z32" s="53">
-        <v>0.154529320087544</v>
+        <v>0.15452932008754444</v>
       </c>
       <c r="AA32" s="56">
-        <v>0.176316261575212</v>
+        <v>0.17631626157521216</v>
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
@@ -11514,7 +11517,7 @@
         <v>91860.11</v>
       </c>
       <c r="G39" s="53">
-        <v>0.716210699485804</v>
+        <v>0.7162106994858041</v>
       </c>
       <c r="H39" s="52">
         <v>94098.32</v>
@@ -11523,13 +11526,13 @@
         <v>32521.46</v>
       </c>
       <c r="J39" s="52">
-        <v>69042.09</v>
+        <v>69042.09000000001</v>
       </c>
       <c r="K39" s="52">
         <v>26847.46</v>
       </c>
       <c r="L39" s="52">
-        <v>42194.63</v>
+        <v>42194.63000000001</v>
       </c>
       <c r="M39" s="53">
         <v>0.611143579228265</v>
@@ -11545,7 +11548,7 @@
         <v>19382.23</v>
       </c>
       <c r="R39" s="53">
-        <v>0.773549332840575</v>
+        <v>0.7735493328405749</v>
       </c>
       <c r="S39" s="54">
         <v>501</v>
@@ -11557,22 +11560,22 @@
         <v>389</v>
       </c>
       <c r="V39" s="53">
-        <v>0.776447105788423</v>
+        <v>0.7764471057884231</v>
       </c>
       <c r="W39" s="53">
         <v>0.4</v>
       </c>
       <c r="X39" s="55">
-        <v>34.6154464285714</v>
+        <v>34.61544642857143</v>
       </c>
       <c r="Y39" s="55">
-        <v>68.183992015968</v>
+        <v>68.18399201596804</v>
       </c>
       <c r="Z39" s="53">
-        <v>0.106513777120362</v>
+        <v>0.10651377712036166</v>
       </c>
       <c r="AA39" s="56">
-        <v>0.266338527271097</v>
+        <v>0.26633852727109697</v>
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
@@ -11965,7 +11968,7 @@
         <v>38983.14</v>
       </c>
       <c r="G46" s="53">
-        <v>0.606220553513471</v>
+        <v>0.6062205535134711</v>
       </c>
       <c r="H46" s="52">
         <v>49749.48</v>
@@ -11980,10 +11983,10 @@
         <v>15639.05</v>
       </c>
       <c r="L46" s="52">
-        <v>23512.35</v>
+        <v>23512.350000000002</v>
       </c>
       <c r="M46" s="53">
-        <v>0.600549405640667</v>
+        <v>0.6005494056406668</v>
       </c>
       <c r="N46" s="53">
         <v>0</v>
@@ -11998,7 +12001,7 @@
         <v>6670.26</v>
       </c>
       <c r="R46" s="53">
-        <v>0.629383812917057</v>
+        <v>0.6293838129170567</v>
       </c>
       <c r="S46" s="54">
         <v>212.3</v>
@@ -12007,25 +12010,25 @@
         <v>86.75</v>
       </c>
       <c r="U46" s="54">
-        <v>125.55</v>
+        <v>125.55000000000001</v>
       </c>
       <c r="V46" s="53">
-        <v>0.591380122468205</v>
+        <v>0.5913801224682054</v>
       </c>
       <c r="W46" s="53">
         <v>0.4</v>
       </c>
       <c r="X46" s="55">
-        <v>66.3423631123919</v>
+        <v>66.34236311239194</v>
       </c>
       <c r="Y46" s="55">
-        <v>68.5620819594913</v>
+        <v>68.56208195949127</v>
       </c>
       <c r="Z46" s="53">
-        <v>0.22727999725141</v>
+        <v>0.22727999725140957</v>
       </c>
       <c r="AA46" s="56">
-        <v>0.226353821097855</v>
+        <v>0.22635382109785498</v>
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
@@ -12418,7 +12421,7 @@
         <v>51589.66</v>
       </c>
       <c r="G53" s="53">
-        <v>0.343582536541599</v>
+        <v>0.34358253654159887</v>
       </c>
       <c r="H53" s="52">
         <v>105626.39</v>
@@ -12433,10 +12436,10 @@
         <v>66399.88</v>
       </c>
       <c r="L53" s="52">
-        <v>5824.28999999999</v>
+        <v>5824.289999999994</v>
       </c>
       <c r="M53" s="53">
-        <v>0.0806418405362082</v>
+        <v>0.08064184053620822</v>
       </c>
       <c r="N53" s="53"/>
       <c r="O53" s="52">
@@ -12446,10 +12449,10 @@
         <v>13536.31</v>
       </c>
       <c r="Q53" s="52">
-        <v>19865.91</v>
+        <v>19865.910000000003</v>
       </c>
       <c r="R53" s="53">
-        <v>0.594748193383554</v>
+        <v>0.5947481933835537</v>
       </c>
       <c r="S53" s="54">
         <v>668.92</v>
@@ -12458,25 +12461,25 @@
         <v>269</v>
       </c>
       <c r="U53" s="54">
-        <v>399.92</v>
+        <v>399.91999999999996</v>
       </c>
       <c r="V53" s="53">
-        <v>0.597859235783053</v>
+        <v>0.5978592357830532</v>
       </c>
       <c r="W53" s="53">
         <v>0.3</v>
       </c>
       <c r="X53" s="55">
-        <v>69.2427881040892</v>
+        <v>69.24278810408921</v>
       </c>
       <c r="Y53" s="55">
-        <v>66.5636697960892</v>
+        <v>66.56366979608923</v>
       </c>
       <c r="Z53" s="53">
-        <v>0.188979682942295</v>
+        <v>0.18897968294229547</v>
       </c>
       <c r="AA53" s="56">
-        <v>0.296537658865514</v>
+        <v>0.29653765886551353</v>
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
@@ -12866,10 +12869,10 @@
         <v>16358.37</v>
       </c>
       <c r="F60" s="52">
-        <v>4062.19</v>
+        <v>4062.1900000000005</v>
       </c>
       <c r="G60" s="53">
-        <v>0.198926474102571</v>
+        <v>0.19892647410257114</v>
       </c>
       <c r="H60" s="52">
         <v>15859.68</v>
@@ -12884,10 +12887,10 @@
         <v>11159.14</v>
       </c>
       <c r="L60" s="52">
-        <v>1529.96</v>
+        <v>1529.960000000001</v>
       </c>
       <c r="M60" s="53">
-        <v>0.120572775058909</v>
+        <v>0.1205727750589089</v>
       </c>
       <c r="N60" s="53"/>
       <c r="O60" s="52">
@@ -12900,7 +12903,7 @@
         <v>2136.55</v>
       </c>
       <c r="R60" s="53">
-        <v>0.673867241955731</v>
+        <v>0.6738672419557306</v>
       </c>
       <c r="S60" s="54">
         <v>63.5</v>
@@ -12912,22 +12915,22 @@
         <v>36.75</v>
       </c>
       <c r="V60" s="53">
-        <v>0.578740157480315</v>
+        <v>0.5787401574803149</v>
       </c>
       <c r="W60" s="53">
         <v>0.4</v>
       </c>
       <c r="X60" s="55">
-        <v>155.708411214953</v>
+        <v>155.70841121495334</v>
       </c>
       <c r="Y60" s="55">
         <v>71.8248818897638</v>
       </c>
       <c r="Z60" s="53">
-        <v>0.254621945829566</v>
+        <v>0.2546219458295662</v>
       </c>
       <c r="AA60" s="56">
-        <v>0.223347449825078</v>
+        <v>0.2233474498250783</v>
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
@@ -13320,7 +13323,7 @@
         <v>40172.04</v>
       </c>
       <c r="G67" s="53">
-        <v>0.867581068385759</v>
+        <v>0.8675810683857592</v>
       </c>
       <c r="H67" s="52">
         <v>34612.41</v>
@@ -13329,16 +13332,16 @@
         <v>5397.27</v>
       </c>
       <c r="J67" s="52">
-        <v>26584.53</v>
+        <v>26584.530000000002</v>
       </c>
       <c r="K67" s="52">
         <v>5397.27</v>
       </c>
       <c r="L67" s="52">
-        <v>21187.26</v>
+        <v>21187.260000000002</v>
       </c>
       <c r="M67" s="53">
-        <v>0.796977038901948</v>
+        <v>0.7969770389019478</v>
       </c>
       <c r="N67" s="53"/>
       <c r="O67" s="52">
@@ -13368,13 +13371,13 @@
       <c r="W67" s="53"/>
       <c r="X67" s="55"/>
       <c r="Y67" s="55">
-        <v>72.6967416987937</v>
+        <v>72.69674169879366</v>
       </c>
       <c r="Z67" s="53">
-        <v>0.11974146451253</v>
+        <v>0.11974146451253039</v>
       </c>
       <c r="AA67" s="56">
-        <v>0.252488256827238</v>
+        <v>0.25248825682723763</v>
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
@@ -13709,28 +13712,46 @@
       </c>
       <c r="D74" s="52"/>
       <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
+      <c r="F74" s="52" t="s">
+        <v>99</v>
+      </c>
       <c r="G74" s="53"/>
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="52"/>
+      <c r="J74" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="K74" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L74" s="52" t="s">
+        <v>99</v>
+      </c>
       <c r="M74" s="53"/>
       <c r="N74" s="53"/>
       <c r="O74" s="52"/>
       <c r="P74" s="52"/>
-      <c r="Q74" s="52"/>
+      <c r="Q74" s="52" t="s">
+        <v>99</v>
+      </c>
       <c r="R74" s="53"/>
-      <c r="S74" s="54"/>
+      <c r="S74" s="54">
+        <v>470.3</v>
+      </c>
       <c r="T74" s="54"/>
-      <c r="U74" s="54"/>
-      <c r="V74" s="53"/>
+      <c r="U74" s="54">
+        <v>470.3</v>
+      </c>
+      <c r="V74" s="53">
+        <v>1</v>
+      </c>
       <c r="W74" s="53">
         <v>0</v>
       </c>
       <c r="X74" s="55"/>
-      <c r="Y74" s="55"/>
+      <c r="Y74" s="55" t="s">
+        <v>99</v>
+      </c>
       <c r="Z74" s="53"/>
       <c r="AA74" s="56"/>
       <c r="AB74" s="57"/>
@@ -14112,7 +14133,7 @@
         <v>5869.43</v>
       </c>
       <c r="G81" s="53">
-        <v>0.230464381745763</v>
+        <v>0.2304643817457625</v>
       </c>
       <c r="H81" s="52">
         <v>16606.83</v>
@@ -14121,16 +14142,16 @@
         <v>12921.64</v>
       </c>
       <c r="J81" s="52">
-        <v>9659.99</v>
+        <v>9659.990000000002</v>
       </c>
       <c r="K81" s="52">
         <v>5569.48</v>
       </c>
       <c r="L81" s="52">
-        <v>4090.51</v>
+        <v>4090.510000000002</v>
       </c>
       <c r="M81" s="53">
-        <v>0.423448678518301</v>
+        <v>0.42344867851830087</v>
       </c>
       <c r="N81" s="53">
         <v>0</v>
@@ -14142,10 +14163,10 @@
         <v>7352.16</v>
       </c>
       <c r="Q81" s="52">
-        <v>-405.32</v>
+        <v>-405.3199999999997</v>
       </c>
       <c r="R81" s="53">
-        <v>-0.05834595298006</v>
+        <v>-0.058345952980059956</v>
       </c>
       <c r="S81" s="54">
         <v>139.07</v>
@@ -14154,23 +14175,23 @@
         <v>143.25</v>
       </c>
       <c r="U81" s="54">
-        <v>-4.18000000000001</v>
+        <v>-4.180000000000007</v>
       </c>
       <c r="V81" s="53">
-        <v>-0.0300568059250738</v>
+        <v>-0.030056805925073756</v>
       </c>
       <c r="W81" s="53"/>
       <c r="X81" s="55">
-        <v>46.6092146596859</v>
+        <v>46.60921465968587</v>
       </c>
       <c r="Y81" s="55">
-        <v>63.7161860933343</v>
+        <v>63.71618609333429</v>
       </c>
       <c r="Z81" s="53">
-        <v>0.340679167340616</v>
+        <v>0.34067916734061593</v>
       </c>
       <c r="AA81" s="56">
-        <v>0.347929388593615</v>
+        <v>0.3479293885936145</v>
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
@@ -14516,10 +14537,10 @@
         <v>33023.07</v>
       </c>
       <c r="F88" s="52">
-        <v>4059.96</v>
+        <v>4059.959999999999</v>
       </c>
       <c r="G88" s="53">
-        <v>0.109482962961764</v>
+        <v>0.10948296296176444</v>
       </c>
       <c r="H88" s="52">
         <v>27002.93</v>
@@ -14531,13 +14552,13 @@
         <v>15440.32</v>
       </c>
       <c r="K88" s="52">
-        <v>14143.19</v>
+        <v>14143.189999999999</v>
       </c>
       <c r="L88" s="52">
-        <v>1297.13</v>
+        <v>1297.130000000001</v>
       </c>
       <c r="M88" s="53">
-        <v>0.0840092692379433</v>
+        <v>0.08400926923794333</v>
       </c>
       <c r="N88" s="53">
         <v>0</v>
@@ -14552,7 +14573,7 @@
         <v>4185.18</v>
       </c>
       <c r="R88" s="53">
-        <v>0.361958070020523</v>
+        <v>0.36195807002052305</v>
       </c>
       <c r="S88" s="68">
         <v>231.75</v>
@@ -14564,20 +14585,20 @@
         <v>83.25</v>
       </c>
       <c r="V88" s="53">
-        <v>0.359223300970874</v>
+        <v>0.3592233009708738</v>
       </c>
       <c r="W88" s="53"/>
       <c r="X88" s="55">
-        <v>77.4575757575758</v>
+        <v>77.45757575757577</v>
       </c>
       <c r="Y88" s="55">
-        <v>43.4955771305286</v>
+        <v>43.49557713052858</v>
       </c>
       <c r="Z88" s="53">
         <v>0.34831558664897</v>
       </c>
       <c r="AA88" s="56">
-        <v>0.271825144816915</v>
+        <v>0.2718251448169149</v>
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
@@ -14970,7 +14991,7 @@
         <v>20423.87</v>
       </c>
       <c r="G95" s="53">
-        <v>0.779949622204724</v>
+        <v>0.7799496222047235</v>
       </c>
       <c r="H95" s="52">
         <v>19428.98</v>
@@ -14982,13 +15003,13 @@
         <v>12051.32</v>
       </c>
       <c r="K95" s="52">
-        <v>7679.91</v>
+        <v>7679.910000000001</v>
       </c>
       <c r="L95" s="52">
-        <v>4371.41</v>
+        <v>4371.409999999999</v>
       </c>
       <c r="M95" s="53">
-        <v>0.362732879053913</v>
+        <v>0.36273287905391266</v>
       </c>
       <c r="N95" s="53">
         <v>0</v>
@@ -15003,7 +15024,7 @@
         <v>7131.76</v>
       </c>
       <c r="R95" s="53">
-        <v>0.966669648641981</v>
+        <v>0.9666696486419813</v>
       </c>
       <c r="S95" s="54">
         <v>147.9</v>
@@ -15015,20 +15036,20 @@
         <v>142.9</v>
       </c>
       <c r="V95" s="53">
-        <v>0.966193373901285</v>
+        <v>0.9661933739012847</v>
       </c>
       <c r="W95" s="53"/>
       <c r="X95" s="55">
-        <v>-432.708</v>
+        <v>-432.7080000000001</v>
       </c>
       <c r="Y95" s="55">
-        <v>45.6873563218391</v>
+        <v>45.687356321839076</v>
       </c>
       <c r="Z95" s="53">
-        <v>-0.375466612984119</v>
+        <v>-0.37546661298411915</v>
       </c>
       <c r="AA95" s="56">
-        <v>0.258043377145314</v>
+        <v>0.2580433771453143</v>
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
@@ -15330,10 +15351,10 @@
         <v>33188.03</v>
       </c>
       <c r="F102" s="52">
-        <v>-0.0100000000020373</v>
+        <v>-0.010000000002037268</v>
       </c>
       <c r="G102" s="53">
-        <v>-3.01313546335011e-7</v>
+        <v>-3.0131354633501094e-7</v>
       </c>
       <c r="H102" s="52">
         <v>23790.07</v>
@@ -15345,13 +15366,13 @@
         <v>13406.21</v>
       </c>
       <c r="K102" s="52">
-        <v>16562.52</v>
+        <v>16562.519999999997</v>
       </c>
       <c r="L102" s="52">
-        <v>-3156.31</v>
+        <v>-3156.3099999999977</v>
       </c>
       <c r="M102" s="53">
-        <v>-0.235436413423331</v>
+        <v>-0.23543641342333127</v>
       </c>
       <c r="N102" s="53">
         <v>0</v>
@@ -15366,7 +15387,7 @@
         <v>-5357.08</v>
       </c>
       <c r="R102" s="53">
-        <v>-0.515904490237734</v>
+        <v>-0.5159044902377343</v>
       </c>
       <c r="S102" s="54">
         <v>208.2</v>
@@ -15375,23 +15396,23 @@
         <v>317.25</v>
       </c>
       <c r="U102" s="54">
-        <v>-109.05</v>
+        <v>-109.05000000000001</v>
       </c>
       <c r="V102" s="53">
-        <v>-0.523775216138329</v>
+        <v>-0.5237752161383286</v>
       </c>
       <c r="W102" s="53"/>
       <c r="X102" s="55">
-        <v>2.78824271079591</v>
+        <v>2.788242710795907</v>
       </c>
       <c r="Y102" s="55">
-        <v>45.1390489913545</v>
+        <v>45.13904899135446</v>
       </c>
       <c r="Z102" s="53">
-        <v>0.0266532843317305</v>
+        <v>0.026653284331730493</v>
       </c>
       <c r="AA102" s="56">
-        <v>0.283172964220222</v>
+        <v>0.2831729642202216</v>
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
@@ -15781,10 +15802,10 @@
         <v>35454.43</v>
       </c>
       <c r="F109" s="52">
-        <v>21102.12</v>
+        <v>21102.120000000003</v>
       </c>
       <c r="G109" s="53">
-        <v>0.373115403962936</v>
+        <v>0.37311540396293624</v>
       </c>
       <c r="H109" s="52">
         <v>35959.67</v>
@@ -15793,16 +15814,16 @@
         <v>21861.72</v>
       </c>
       <c r="J109" s="52">
-        <v>20162.34</v>
+        <v>20162.339999999997</v>
       </c>
       <c r="K109" s="52">
         <v>12155.27</v>
       </c>
       <c r="L109" s="52">
-        <v>8007.07</v>
+        <v>8007.069999999996</v>
       </c>
       <c r="M109" s="53">
-        <v>0.397129995823897</v>
+        <v>0.3971299958238973</v>
       </c>
       <c r="N109" s="53">
         <v>0</v>
@@ -15814,10 +15835,10 @@
         <v>9706.45</v>
       </c>
       <c r="Q109" s="52">
-        <v>6090.88</v>
+        <v>6090.879999999999</v>
       </c>
       <c r="R109" s="53">
-        <v>0.385563889594001</v>
+        <v>0.38556388959400095</v>
       </c>
       <c r="S109" s="54">
         <v>316.34</v>
@@ -15826,25 +15847,25 @@
         <v>204.75</v>
       </c>
       <c r="U109" s="54">
-        <v>111.59</v>
+        <v>111.58999999999997</v>
       </c>
       <c r="V109" s="53">
-        <v>0.35275336663084</v>
+        <v>0.35275336663084017</v>
       </c>
       <c r="W109" s="53">
         <v>0</v>
       </c>
       <c r="X109" s="55">
-        <v>66.386862026862</v>
+        <v>66.38686202686202</v>
       </c>
       <c r="Y109" s="55">
-        <v>65.1099449958905</v>
+        <v>65.10994499589052</v>
       </c>
       <c r="Z109" s="53">
-        <v>0.383385376665201</v>
+        <v>0.3833853766652009</v>
       </c>
       <c r="AA109" s="56">
-        <v>0.364182044343228</v>
+        <v>0.3641820443432282</v>
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
@@ -16228,51 +16249,73 @@
         <v>90</v>
       </c>
       <c r="D116" s="52">
-        <v>0</v>
+        <v>21404.82</v>
       </c>
       <c r="E116" s="52">
         <v>0</v>
       </c>
       <c r="F116" s="52">
-        <v>0</v>
-      </c>
-      <c r="G116" s="53"/>
+        <v>21404.82</v>
+      </c>
+      <c r="G116" s="53">
+        <v>1</v>
+      </c>
       <c r="H116" s="52">
-        <v>0</v>
+        <v>17424.66</v>
       </c>
       <c r="I116" s="52">
         <v>0</v>
       </c>
-      <c r="J116" s="52"/>
-      <c r="K116" s="52"/>
-      <c r="L116" s="52"/>
-      <c r="M116" s="53"/>
+      <c r="J116" s="52">
+        <v>13229.5</v>
+      </c>
+      <c r="K116" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L116" s="52">
+        <v>13229.5</v>
+      </c>
+      <c r="M116" s="53">
+        <v>1</v>
+      </c>
       <c r="N116" s="53">
         <v>0</v>
       </c>
       <c r="O116" s="52">
-        <v>0</v>
+        <v>4195.16</v>
       </c>
       <c r="P116" s="52">
         <v>0</v>
       </c>
-      <c r="Q116" s="52"/>
-      <c r="R116" s="53"/>
+      <c r="Q116" s="52">
+        <v>4195.16</v>
+      </c>
+      <c r="R116" s="53">
+        <v>1</v>
+      </c>
       <c r="S116" s="54">
-        <v>0</v>
+        <v>84.03</v>
       </c>
       <c r="T116" s="54">
         <v>0</v>
       </c>
-      <c r="U116" s="54"/>
-      <c r="V116" s="53"/>
+      <c r="U116" s="54">
+        <v>84.03</v>
+      </c>
+      <c r="V116" s="53">
+        <v>1</v>
+      </c>
       <c r="W116" s="53">
         <v>0</v>
       </c>
       <c r="X116" s="55"/>
-      <c r="Y116" s="55"/>
+      <c r="Y116" s="55">
+        <v>47.36594073545162</v>
+      </c>
       <c r="Z116" s="53"/>
-      <c r="AA116" s="56"/>
+      <c r="AA116" s="56">
+        <v>0.18594690354789248</v>
+      </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
         <v>91</v>
@@ -16611,9 +16654,11 @@
         <v>15366.74</v>
       </c>
       <c r="F123" s="52">
-        <v>0</v>
-      </c>
-      <c r="G123" s="53"/>
+        <v>81206.28</v>
+      </c>
+      <c r="G123" s="53">
+        <v>0.8408795748543433</v>
+      </c>
       <c r="H123" s="52">
         <v>79663.84</v>
       </c>
@@ -16627,10 +16672,10 @@
         <v>12186.08</v>
       </c>
       <c r="L123" s="52">
-        <v>53835.87</v>
+        <v>53835.869999999995</v>
       </c>
       <c r="M123" s="53">
-        <v>0.815423809808708</v>
+        <v>0.8154238098087075</v>
       </c>
       <c r="N123" s="53"/>
       <c r="O123" s="52">
@@ -16660,13 +16705,13 @@
       <c r="W123" s="53"/>
       <c r="X123" s="55"/>
       <c r="Y123" s="55">
-        <v>61.8545560961335</v>
+        <v>61.85455609613347</v>
       </c>
       <c r="Z123" s="53">
-        <v>0.206983394005495</v>
+        <v>0.20698339400549498</v>
       </c>
       <c r="AA123" s="56">
-        <v>0.1750921737769</v>
+        <v>0.17509217377689967</v>
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
@@ -17057,7 +17102,7 @@
         <v>17431.58</v>
       </c>
       <c r="G130" s="53">
-        <v>0.548121353067268</v>
+        <v>0.5481213530672676</v>
       </c>
       <c r="H130" s="52">
         <v>23448.14</v>
@@ -17066,16 +17111,16 @@
         <v>11238.62</v>
       </c>
       <c r="J130" s="52">
-        <v>15632.03</v>
+        <v>15632.029999999999</v>
       </c>
       <c r="K130" s="52">
         <v>11154.51</v>
       </c>
       <c r="L130" s="52">
-        <v>4477.52</v>
+        <v>4477.519999999999</v>
       </c>
       <c r="M130" s="53">
-        <v>0.286432408330844</v>
+        <v>0.2864324083308437</v>
       </c>
       <c r="N130" s="53"/>
       <c r="O130" s="52">
@@ -17100,22 +17145,22 @@
         <v>155</v>
       </c>
       <c r="V130" s="53">
-        <v>0.987261146496815</v>
+        <v>0.9872611464968153</v>
       </c>
       <c r="W130" s="53">
         <v>0</v>
       </c>
       <c r="X130" s="55">
-        <v>1566.105</v>
+        <v>1566.1049999999998</v>
       </c>
       <c r="Y130" s="55">
-        <v>53.2119108280255</v>
+        <v>53.21191082802548</v>
       </c>
       <c r="Z130" s="53">
-        <v>0.217956095785699</v>
+        <v>0.2179560957856992</v>
       </c>
       <c r="AA130" s="56">
-        <v>0.262692984588275</v>
+        <v>0.26269298458827495</v>
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
@@ -17416,10 +17461,10 @@
         <v>27194.94</v>
       </c>
       <c r="F137" s="52">
-        <v>1431.31</v>
+        <v>1431.3100000000013</v>
       </c>
       <c r="G137" s="53">
-        <v>0.0499999126675691</v>
+        <v>0.049999912667569146</v>
       </c>
       <c r="H137" s="52">
         <v>21262.27</v>
@@ -17428,16 +17473,16 @@
         <v>24965.42</v>
       </c>
       <c r="J137" s="52">
-        <v>11588.8</v>
+        <v>11588.800000000001</v>
       </c>
       <c r="K137" s="52">
-        <v>11702.32</v>
+        <v>11702.319999999998</v>
       </c>
       <c r="L137" s="52">
-        <v>-113.519999999997</v>
+        <v>-113.5199999999968</v>
       </c>
       <c r="M137" s="53">
-        <v>-0.0097956647797871</v>
+        <v>-0.009795664779787104</v>
       </c>
       <c r="N137" s="53">
         <v>0</v>
@@ -17449,10 +17494,10 @@
         <v>13263.1</v>
       </c>
       <c r="Q137" s="52">
-        <v>-3589.63</v>
+        <v>-3589.630000000001</v>
       </c>
       <c r="R137" s="53">
-        <v>-0.3710798710287</v>
+        <v>-0.37107987102870027</v>
       </c>
       <c r="S137" s="54">
         <v>193.82</v>
@@ -17464,20 +17509,20 @@
         <v>-72.93</v>
       </c>
       <c r="V137" s="53">
-        <v>-0.37627695800227</v>
+        <v>-0.3762769580022702</v>
       </c>
       <c r="W137" s="53"/>
       <c r="X137" s="55">
-        <v>8.35808809746954</v>
+        <v>8.358088097469542</v>
       </c>
       <c r="Y137" s="55">
-        <v>37.9939118769993</v>
+        <v>37.99391187699927</v>
       </c>
       <c r="Z137" s="53">
-        <v>0.0819828982891671</v>
+        <v>0.08198289828916705</v>
       </c>
       <c r="AA137" s="56">
-        <v>0.257245709794332</v>
+        <v>0.2572457097943321</v>
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
@@ -17861,41 +17906,73 @@
         <v>90</v>
       </c>
       <c r="D144" s="52">
-        <v>0</v>
+        <v>268228.26</v>
       </c>
       <c r="E144" s="52">
-        <v>0</v>
-      </c>
-      <c r="F144" s="52"/>
-      <c r="G144" s="53"/>
+        <v>9034.53</v>
+      </c>
+      <c r="F144" s="52">
+        <v>259193.73</v>
+      </c>
+      <c r="G144" s="53">
+        <v>0.9663177548853353</v>
+      </c>
       <c r="H144" s="52">
-        <v>0</v>
-      </c>
-      <c r="I144" s="52"/>
-      <c r="J144" s="52"/>
-      <c r="K144" s="52"/>
-      <c r="L144" s="52"/>
-      <c r="M144" s="53"/>
+        <v>238611.58</v>
+      </c>
+      <c r="I144" s="52">
+        <v>6362.08</v>
+      </c>
+      <c r="J144" s="52">
+        <v>214154.25</v>
+      </c>
+      <c r="K144" s="52">
+        <v>3465.35</v>
+      </c>
+      <c r="L144" s="52">
+        <v>210688.9</v>
+      </c>
+      <c r="M144" s="53">
+        <v>0.9838184392791645</v>
+      </c>
       <c r="N144" s="53"/>
       <c r="O144" s="52">
-        <v>0</v>
-      </c>
-      <c r="P144" s="52"/>
-      <c r="Q144" s="52"/>
-      <c r="R144" s="53"/>
+        <v>24457.33</v>
+      </c>
+      <c r="P144" s="52">
+        <v>2896.73</v>
+      </c>
+      <c r="Q144" s="52">
+        <v>21560.600000000002</v>
+      </c>
+      <c r="R144" s="53">
+        <v>0.8815598432044708</v>
+      </c>
       <c r="S144" s="54">
-        <v>0</v>
+        <v>497.55</v>
       </c>
       <c r="T144" s="54">
-        <v>0</v>
-      </c>
-      <c r="U144" s="54"/>
-      <c r="V144" s="53"/>
+        <v>58.25</v>
+      </c>
+      <c r="U144" s="54">
+        <v>439.3</v>
+      </c>
+      <c r="V144" s="53">
+        <v>0.8829263390614008</v>
+      </c>
       <c r="W144" s="53"/>
-      <c r="X144" s="55"/>
-      <c r="Y144" s="55"/>
-      <c r="Z144" s="53"/>
-      <c r="AA144" s="56"/>
+      <c r="X144" s="55">
+        <v>45.87896995708155</v>
+      </c>
+      <c r="Y144" s="55">
+        <v>59.52503266003418</v>
+      </c>
+      <c r="Z144" s="53">
+        <v>0.2958039875898359</v>
+      </c>
+      <c r="AA144" s="56">
+        <v>0.11041595691669484</v>
+      </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
         <v>91</v>
@@ -18227,8 +18304,12 @@
       <c r="E151" s="52">
         <v>32773.41</v>
       </c>
-      <c r="F151" s="52"/>
-      <c r="G151" s="53"/>
+      <c r="F151" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="G151" s="53" t="s">
+        <v>99</v>
+      </c>
       <c r="H151" s="52">
         <v>22750.99</v>
       </c>
@@ -18236,16 +18317,16 @@
         <v>22238.62</v>
       </c>
       <c r="J151" s="52">
-        <v>12243.41</v>
+        <v>12243.410000000002</v>
       </c>
       <c r="K151" s="52">
         <v>9324.41</v>
       </c>
       <c r="L151" s="52">
-        <v>2919</v>
+        <v>2919.000000000002</v>
       </c>
       <c r="M151" s="53">
-        <v>0.238413971271076</v>
+        <v>0.23841397127107575</v>
       </c>
       <c r="N151" s="53"/>
       <c r="O151" s="52">
@@ -18255,10 +18336,10 @@
         <v>12914.21</v>
       </c>
       <c r="Q151" s="52">
-        <v>-2406.63</v>
+        <v>-2406.629999999999</v>
       </c>
       <c r="R151" s="53">
-        <v>-0.229037513870939</v>
+        <v>-0.22903751387093882</v>
       </c>
       <c r="S151" s="54">
         <v>210.6</v>
@@ -18267,23 +18348,23 @@
         <v>260.75</v>
       </c>
       <c r="U151" s="54">
-        <v>-50.15</v>
+        <v>-50.150000000000006</v>
       </c>
       <c r="V151" s="53">
-        <v>-0.238129154795822</v>
+        <v>-0.2381291547958215</v>
       </c>
       <c r="W151" s="53"/>
       <c r="X151" s="55">
-        <v>40.4018791946309</v>
+        <v>40.40187919463089</v>
       </c>
       <c r="Y151" s="55">
-        <v>47.5898385565052</v>
+        <v>47.58983855650523</v>
       </c>
       <c r="Z151" s="53">
-        <v>0.321443206550676</v>
+        <v>0.3214432065506764</v>
       </c>
       <c r="AA151" s="56">
-        <v>0.30580949617388</v>
+        <v>0.30580949617388004</v>
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
@@ -18641,13 +18722,17 @@
         <v>7562.12</v>
       </c>
       <c r="J158" s="52">
-        <v>0</v>
+        <v>8410.93</v>
       </c>
       <c r="K158" s="52">
-        <v>0</v>
-      </c>
-      <c r="L158" s="52"/>
-      <c r="M158" s="53"/>
+        <v>5263.76</v>
+      </c>
+      <c r="L158" s="52">
+        <v>3147.17</v>
+      </c>
+      <c r="M158" s="53">
+        <v>0.37417622070329914</v>
+      </c>
       <c r="N158" s="53"/>
       <c r="O158" s="52">
         <v>5508.47</v>
@@ -18659,7 +18744,7 @@
         <v>3210.11</v>
       </c>
       <c r="R158" s="53">
-        <v>0.582758914907406</v>
+        <v>0.5827589149074063</v>
       </c>
       <c r="S158" s="54">
         <v>110.44</v>
@@ -18675,14 +18760,14 @@
       </c>
       <c r="W158" s="53"/>
       <c r="X158" s="55">
-        <v>-51.36</v>
+        <v>-168.98592178770951</v>
       </c>
       <c r="Y158" s="55">
-        <v>112.195400217313</v>
+        <v>36.03703368344804</v>
       </c>
       <c r="Z158" s="53"/>
       <c r="AA158" s="56">
-        <v>0.222350780727547</v>
+        <v>0.22235078072754688</v>
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
@@ -19027,30 +19112,62 @@
       <c r="C165" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="D165" s="52"/>
+      <c r="D165" s="52">
+        <v>10827.2</v>
+      </c>
       <c r="E165" s="52"/>
-      <c r="F165" s="52"/>
-      <c r="G165" s="53"/>
-      <c r="H165" s="52"/>
+      <c r="F165" s="52">
+        <v>10827.2</v>
+      </c>
+      <c r="G165" s="53">
+        <v>1</v>
+      </c>
+      <c r="H165" s="52">
+        <v>7619.53</v>
+      </c>
       <c r="I165" s="52"/>
-      <c r="J165" s="52"/>
-      <c r="K165" s="52"/>
-      <c r="L165" s="52"/>
-      <c r="M165" s="53"/>
+      <c r="J165" s="52">
+        <v>4388.87</v>
+      </c>
+      <c r="K165" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L165" s="52">
+        <v>4388.87</v>
+      </c>
+      <c r="M165" s="53">
+        <v>1</v>
+      </c>
       <c r="N165" s="53"/>
-      <c r="O165" s="52"/>
+      <c r="O165" s="52">
+        <v>3230.66</v>
+      </c>
       <c r="P165" s="52"/>
-      <c r="Q165" s="52"/>
-      <c r="R165" s="53"/>
-      <c r="S165" s="54"/>
+      <c r="Q165" s="52">
+        <v>3230.66</v>
+      </c>
+      <c r="R165" s="53">
+        <v>1</v>
+      </c>
+      <c r="S165" s="54">
+        <v>64.71</v>
+      </c>
       <c r="T165" s="54"/>
-      <c r="U165" s="54"/>
-      <c r="V165" s="53"/>
+      <c r="U165" s="54">
+        <v>64.71</v>
+      </c>
+      <c r="V165" s="53">
+        <v>1</v>
+      </c>
       <c r="W165" s="53"/>
       <c r="X165" s="55"/>
-      <c r="Y165" s="55"/>
+      <c r="Y165" s="55">
+        <v>49.569927368258405</v>
+      </c>
       <c r="Z165" s="53"/>
-      <c r="AA165" s="56"/>
+      <c r="AA165" s="56">
+        <v>0.29626034431801396</v>
+      </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
         <v>91</v>
@@ -19295,7 +19412,7 @@
         <v>94266.45</v>
       </c>
       <c r="F172" s="52">
-        <v>51970.66</v>
+        <v>51970.65999999999</v>
       </c>
       <c r="G172" s="53">
         <v>0.355386262761894</v>
@@ -19307,16 +19424,16 @@
         <v>75526.07</v>
       </c>
       <c r="J172" s="52">
-        <v>82888.08</v>
+        <v>82888.07999999999</v>
       </c>
       <c r="K172" s="52">
-        <v>0</v>
+        <v>60408.100000000006</v>
       </c>
       <c r="L172" s="52">
-        <v>82888.08</v>
+        <v>22479.97999999998</v>
       </c>
       <c r="M172" s="53">
-        <v>1</v>
+        <v>0.27120883967875703</v>
       </c>
       <c r="N172" s="53"/>
       <c r="O172" s="52">
@@ -19329,7 +19446,7 @@
         <v>16645.82</v>
       </c>
       <c r="R172" s="53">
-        <v>0.524050184187718</v>
+        <v>0.5240501841877181</v>
       </c>
       <c r="S172" s="54">
         <v>659.73</v>
@@ -19345,16 +19462,16 @@
       </c>
       <c r="W172" s="53"/>
       <c r="X172" s="55">
-        <v>259.716095159967</v>
+        <v>61.4942739950779</v>
       </c>
       <c r="Y172" s="55">
-        <v>47.8760098828309</v>
+        <v>47.87600988283085</v>
       </c>
       <c r="Z172" s="53">
-        <v>0.839625126436818</v>
+        <v>0.1988022249697532</v>
       </c>
       <c r="AA172" s="56">
-        <v>0.215986489339129</v>
+        <v>0.21598648933912873</v>
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
@@ -19756,16 +19873,16 @@
         <v>2946.15</v>
       </c>
       <c r="J179" s="52">
-        <v>2977.11</v>
+        <v>2977.1100000000006</v>
       </c>
       <c r="K179" s="52">
         <v>2298.71</v>
       </c>
       <c r="L179" s="52">
-        <v>678.400000000001</v>
+        <v>678.4000000000005</v>
       </c>
       <c r="M179" s="53">
-        <v>0.22787199666791</v>
+        <v>0.2278719966679096</v>
       </c>
       <c r="N179" s="53"/>
       <c r="O179" s="52">
@@ -19775,10 +19892,10 @@
         <v>647.44</v>
       </c>
       <c r="Q179" s="52">
-        <v>5601.72</v>
+        <v>5601.719999999999</v>
       </c>
       <c r="R179" s="53">
-        <v>0.896395675578798</v>
+        <v>0.8963956755787977</v>
       </c>
       <c r="S179" s="54">
         <v>125.17</v>
@@ -19790,18 +19907,18 @@
         <v>113.92</v>
       </c>
       <c r="V179" s="53">
-        <v>0.910122233762084</v>
+        <v>0.9101222337620836</v>
       </c>
       <c r="W179" s="53"/>
       <c r="X179" s="55">
         <v>-261.88</v>
       </c>
       <c r="Y179" s="55">
-        <v>61.2867300471359</v>
+        <v>61.28673004713588</v>
       </c>
       <c r="Z179" s="53"/>
       <c r="AA179" s="56">
-        <v>0.453987062014389</v>
+        <v>0.45398706201438904</v>
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
@@ -20162,13 +20279,13 @@
         <v>9784.33</v>
       </c>
       <c r="K186" s="52">
-        <v>0</v>
+        <v>3461.1499999999996</v>
       </c>
       <c r="L186" s="52">
-        <v>9784.33</v>
+        <v>6323.18</v>
       </c>
       <c r="M186" s="53">
-        <v>1</v>
+        <v>0.646255798813</v>
       </c>
       <c r="N186" s="53"/>
       <c r="O186" s="52">
@@ -20181,7 +20298,7 @@
         <v>5070.63</v>
       </c>
       <c r="R186" s="53">
-        <v>0.778329516359774</v>
+        <v>0.7783295163597738</v>
       </c>
       <c r="S186" s="54">
         <v>130.62</v>
@@ -20193,20 +20310,20 @@
         <v>98.37</v>
       </c>
       <c r="V186" s="53">
-        <v>0.753100597152044</v>
+        <v>0.7531005971520441</v>
       </c>
       <c r="W186" s="53"/>
       <c r="X186" s="55">
-        <v>-6.55968992248063</v>
+        <v>-113.88217054263565</v>
       </c>
       <c r="Y186" s="55">
-        <v>35.9288776603889</v>
+        <v>35.928877660388906</v>
       </c>
       <c r="Z186" s="53">
-        <v>-0.171631861623586</v>
+        <v>-2.979684888607636</v>
       </c>
       <c r="AA186" s="56">
-        <v>0.22356150784199</v>
+        <v>0.2235615078419902</v>
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
@@ -20546,47 +20663,71 @@
         <v>90</v>
       </c>
       <c r="D193" s="52">
-        <v>0</v>
+        <v>23770.95</v>
       </c>
       <c r="E193" s="52">
         <v>0</v>
       </c>
-      <c r="F193" s="52"/>
-      <c r="G193" s="53"/>
+      <c r="F193" s="52">
+        <v>23770.95</v>
+      </c>
+      <c r="G193" s="53">
+        <v>1</v>
+      </c>
       <c r="H193" s="52">
-        <v>0</v>
+        <v>14310.96</v>
       </c>
       <c r="I193" s="52">
-        <v>0</v>
-      </c>
-      <c r="J193" s="52"/>
-      <c r="K193" s="52">
-        <v>0</v>
-      </c>
-      <c r="L193" s="52"/>
-      <c r="M193" s="53"/>
+        <v>330.91</v>
+      </c>
+      <c r="J193" s="52">
+        <v>7389.339999999999</v>
+      </c>
+      <c r="K193" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L193" s="52">
+        <v>7389.339999999999</v>
+      </c>
+      <c r="M193" s="53">
+        <v>1</v>
+      </c>
       <c r="N193" s="53"/>
       <c r="O193" s="52">
-        <v>0</v>
+        <v>6921.62</v>
       </c>
       <c r="P193" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q193" s="52"/>
-      <c r="R193" s="53"/>
+        <v>330.91</v>
+      </c>
+      <c r="Q193" s="52">
+        <v>6590.71</v>
+      </c>
+      <c r="R193" s="53">
+        <v>0.9521918279246766</v>
+      </c>
       <c r="S193" s="54">
-        <v>0</v>
+        <v>140.15</v>
       </c>
       <c r="T193" s="54">
-        <v>0</v>
-      </c>
-      <c r="U193" s="54"/>
-      <c r="V193" s="53"/>
+        <v>5.75</v>
+      </c>
+      <c r="U193" s="54">
+        <v>134.4</v>
+      </c>
+      <c r="V193" s="53">
+        <v>0.9589725294327506</v>
+      </c>
       <c r="W193" s="53"/>
-      <c r="X193" s="55"/>
-      <c r="Y193" s="55"/>
+      <c r="X193" s="55">
+        <v>-57.54956521739131</v>
+      </c>
+      <c r="Y193" s="55">
+        <v>67.49903674634321</v>
+      </c>
       <c r="Z193" s="53"/>
-      <c r="AA193" s="56"/>
+      <c r="AA193" s="56">
+        <v>0.39796432199806914</v>
+      </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
         <v>91</v>
@@ -21517,11 +21658,13 @@
         <v>0</v>
       </c>
       <c r="J214" s="52">
-        <v>99479.62</v>
-      </c>
-      <c r="K214" s="52"/>
+        <v>99479.62000000001</v>
+      </c>
+      <c r="K214" s="52" t="s">
+        <v>99</v>
+      </c>
       <c r="L214" s="52">
-        <v>99479.62</v>
+        <v>99479.62000000001</v>
       </c>
       <c r="M214" s="53">
         <v>1</v>
@@ -21554,11 +21697,11 @@
       <c r="W214" s="53"/>
       <c r="X214" s="55"/>
       <c r="Y214" s="55">
-        <v>54.9378309089895</v>
+        <v>54.93783090898954</v>
       </c>
       <c r="Z214" s="53"/>
       <c r="AA214" s="56">
-        <v>0.143790046441692</v>
+        <v>0.14379004644169227</v>
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
@@ -21892,10 +22035,10 @@
         <v>271388.15</v>
       </c>
       <c r="F221" s="52">
-        <v>117930.2</v>
+        <v>117930.19999999995</v>
       </c>
       <c r="G221" s="53">
-        <v>0.302914568501587</v>
+        <v>0.3029145685015874</v>
       </c>
       <c r="H221" s="52">
         <v>289549.48</v>
@@ -21904,13 +22047,17 @@
         <v>224459.32</v>
       </c>
       <c r="J221" s="52">
-        <v>0</v>
+        <v>174279.97999999998</v>
       </c>
       <c r="K221" s="52">
-        <v>0</v>
-      </c>
-      <c r="L221" s="52"/>
-      <c r="M221" s="53"/>
+        <v>176149.13</v>
+      </c>
+      <c r="L221" s="52">
+        <v>-1869.1500000000233</v>
+      </c>
+      <c r="M221" s="53">
+        <v>-0.010724984017097221</v>
+      </c>
       <c r="N221" s="53"/>
       <c r="O221" s="52">
         <v>115269.5</v>
@@ -21922,7 +22069,7 @@
         <v>66959.31</v>
       </c>
       <c r="R221" s="53">
-        <v>0.580893558139838</v>
+        <v>0.5808935581398375</v>
       </c>
       <c r="S221" s="54">
         <v>2312.68</v>
@@ -21931,23 +22078,23 @@
         <v>1014.25</v>
       </c>
       <c r="U221" s="54">
-        <v>1298.43</v>
+        <v>1298.4299999999998</v>
       </c>
       <c r="V221" s="53">
         <v>0.561439542003217</v>
       </c>
       <c r="W221" s="53"/>
       <c r="X221" s="55">
-        <v>219.943761400049</v>
+        <v>46.26948977076659</v>
       </c>
       <c r="Y221" s="55">
-        <v>118.498387152568</v>
+        <v>43.139937215697806</v>
       </c>
       <c r="Z221" s="53">
-        <v>0.821988579825611</v>
+        <v>0.17292144111671792</v>
       </c>
       <c r="AA221" s="56">
-        <v>0.256265521519856</v>
+        <v>0.25626552151985643</v>
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
@@ -22817,7 +22964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22831,7 +22978,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -22853,55 +23000,55 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" s="81" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F2" s="82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H2" s="83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I2" s="81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J2" s="82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K2" s="82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L2" s="83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M2" s="83" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N2" s="81" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O2" s="84" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -22919,14 +23066,12 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
-        <f>'Main Sheet'!A4</f>
         <v>7658</v>
       </c>
-      <c r="B4" s="54" t="str">
-        <f>'Main Sheet'!B4</f>
-        <v>Charity Hospital</v>
+      <c r="B4" s="54" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="52">
         <v>0</v>
@@ -22968,7 +23113,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -22985,14 +23130,12 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
-        <f>'Main Sheet'!A6</f>
         <v>8142</v>
       </c>
-      <c r="B6" s="54" t="str">
-        <f>'Main Sheet'!B6</f>
-        <v>Fisher Developements</v>
+      <c r="B6" s="54" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="52">
         <v>3912</v>
@@ -23010,7 +23153,6 @@
         <v>-0.4803553169734155</v>
       </c>
       <c r="H6" s="53">
-        <f>'Deliverables Sheet'!AA11</f>
         <v>0.239214585617637</v>
       </c>
       <c r="I6" s="54">
@@ -23029,17 +23171,16 @@
         <v>-2791.7500000000014</v>
       </c>
       <c r="N6" s="54">
-        <f>'Deliverables Sheet'!AE11</f>
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
         <v>76.48630136986306</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23056,14 +23197,12 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
-        <f>'Main Sheet'!A8</f>
         <v>8824</v>
       </c>
-      <c r="B8" s="54" t="str">
-        <f>'Main Sheet'!B8</f>
-        <v>3 Innovation Road</v>
+      <c r="B8" s="54" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="52">
         <v>0</v>
@@ -23079,7 +23218,6 @@
         <v>0</v>
       </c>
       <c r="H8" s="53">
-        <f>'Deliverables Sheet'!AA18</f>
         <v>0.288523551725943</v>
       </c>
       <c r="I8" s="54">
@@ -23096,14 +23234,13 @@
         <v>-640</v>
       </c>
       <c r="N8" s="54">
-        <f>'Deliverables Sheet'!AE18</f>
         <v>-34.75</v>
       </c>
       <c r="O8" s="58">
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23120,14 +23257,12 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
-        <f>'Main Sheet'!A10</f>
         <v>8127</v>
       </c>
-      <c r="B10" s="54" t="str">
-        <f>'Main Sheet'!B10</f>
-        <v>Rolly Autowash</v>
+      <c r="B10" s="54" t="s">
+        <v>32</v>
       </c>
       <c r="C10" s="52">
         <v>0</v>
@@ -23145,7 +23280,6 @@
         <v>0</v>
       </c>
       <c r="H10" s="53">
-        <f>'Deliverables Sheet'!AA25</f>
         <v>0.32265253844825</v>
       </c>
       <c r="I10" s="54">
@@ -23164,14 +23298,13 @@
         <v>-13747.48999999999</v>
       </c>
       <c r="N10" s="54">
-        <f>'Deliverables Sheet'!AE25</f>
         <v>-388.25</v>
       </c>
       <c r="O10" s="58">
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23188,12 +23321,12 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="52">
         <v>0</v>
@@ -23209,7 +23342,6 @@
         <v>0</v>
       </c>
       <c r="H12" s="53">
-        <f>'Deliverables Sheet'!AA32</f>
         <v>0.176316261575212</v>
       </c>
       <c r="I12" s="54">
@@ -23234,10 +23366,10 @@
         <v>-54.9949275362318</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23254,14 +23386,12 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
-        <f>'Main Sheet'!A14</f>
         <v>8886</v>
       </c>
-      <c r="B14" s="54" t="str">
-        <f>'Main Sheet'!B14</f>
-        <v>Monkey Toe - Fisher fit out</v>
+      <c r="B14" s="54" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="52">
         <v>0</v>
@@ -23279,7 +23409,6 @@
         <v>0</v>
       </c>
       <c r="H14" s="53">
-        <f>'Deliverables Sheet'!AA39</f>
         <v>0.266338527271097</v>
       </c>
       <c r="I14" s="54">
@@ -23298,14 +23427,13 @@
         <v>-5138.1600000000035</v>
       </c>
       <c r="N14" s="54">
-        <f>'Deliverables Sheet'!AE39</f>
         <v>-112</v>
       </c>
       <c r="O14" s="58">
         <v>45.876428571428605</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23322,14 +23450,12 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
-        <f>'Main Sheet'!A16</f>
         <v>8887</v>
       </c>
-      <c r="B16" s="54" t="str">
-        <f>'Main Sheet'!B16</f>
-        <v>Tenancy 2 - Fisher Fit out</v>
+      <c r="B16" s="54" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="52">
         <v>0</v>
@@ -23345,7 +23471,6 @@
         <v>0</v>
       </c>
       <c r="H16" s="53">
-        <f>'Deliverables Sheet'!AA46</f>
         <v>0.226353821097855</v>
       </c>
       <c r="I16" s="54">
@@ -23364,14 +23489,13 @@
         <v>-8565.030000000002</v>
       </c>
       <c r="N16" s="54">
-        <f>'Deliverables Sheet'!AE46</f>
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
         <v>98.73233429394816</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23388,14 +23512,12 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
-        <f>'Main Sheet'!A18</f>
         <v>8670</v>
       </c>
-      <c r="B18" s="54" t="str">
-        <f>'Main Sheet'!B18</f>
-        <v>Studio DB - tautara fit out</v>
+      <c r="B18" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="52">
         <v>0</v>
@@ -23413,7 +23535,6 @@
         <v>0</v>
       </c>
       <c r="H18" s="53">
-        <f>'Deliverables Sheet'!AA53</f>
         <v>0.296537658865514</v>
       </c>
       <c r="I18" s="54">
@@ -23432,17 +23553,16 @@
         <v>-19182.64</v>
       </c>
       <c r="N18" s="54">
-        <f>'Deliverables Sheet'!AE53</f>
         <v>-269</v>
       </c>
       <c r="O18" s="58">
         <v>101.49544973544974</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23459,14 +23579,12 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
-        <f>'Main Sheet'!A20</f>
         <v>8907</v>
       </c>
-      <c r="B20" s="54" t="str">
-        <f>'Main Sheet'!B20</f>
-        <v>35 Mania</v>
+      <c r="B20" s="54" t="s">
+        <v>38</v>
       </c>
       <c r="C20" s="52">
         <v>0</v>
@@ -23482,7 +23600,6 @@
         <v>0</v>
       </c>
       <c r="H20" s="53">
-        <f>'Deliverables Sheet'!AA60</f>
         <v>0.223347449825078</v>
       </c>
       <c r="I20" s="54"/>
@@ -23501,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23518,14 +23635,12 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
-        <f>'Main Sheet'!A22</f>
         <v>9065</v>
       </c>
-      <c r="B22" s="54" t="str">
-        <f>'Main Sheet'!B22</f>
-        <v>Cooltranz stage 4</v>
+      <c r="B22" s="54" t="s">
+        <v>39</v>
       </c>
       <c r="C22" s="52">
         <v>0</v>
@@ -23543,7 +23658,6 @@
         <v>0</v>
       </c>
       <c r="H22" s="53">
-        <f>'Deliverables Sheet'!AA67</f>
         <v>0.252488256827238</v>
       </c>
       <c r="I22" s="54"/>
@@ -23557,15 +23671,12 @@
       <c r="M22" s="52">
         <v>-4584.16</v>
       </c>
-      <c r="N22" s="54">
-        <f>'Deliverables Sheet'!AE67</f>
-        <v>0</v>
-      </c>
+      <c r="N22" s="54"/>
       <c r="O22" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23582,14 +23693,12 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
-        <f>'Main Sheet'!A24</f>
         <v>9259</v>
       </c>
-      <c r="B24" s="54" t="str">
-        <f>'Main Sheet'!B24</f>
-        <v>Andrew Reeve Stage 2</v>
+      <c r="B24" s="54" t="s">
+        <v>40</v>
       </c>
       <c r="C24" s="52">
         <v>0</v>
@@ -23604,10 +23713,7 @@
       <c r="G24" s="53">
         <v>0</v>
       </c>
-      <c r="H24" s="53" t="e">
-        <f>'Deliverables Sheet'!AA74</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="H24" s="53"/>
       <c r="I24" s="54"/>
       <c r="J24" s="52"/>
       <c r="K24" s="52">
@@ -23619,15 +23725,12 @@
       <c r="M24" s="52">
         <v>-22353.17</v>
       </c>
-      <c r="N24" s="54">
-        <f>'Deliverables Sheet'!AE74</f>
-        <v>0</v>
-      </c>
+      <c r="N24" s="54"/>
       <c r="O24" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23644,14 +23747,12 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
-        <f>'Main Sheet'!A26</f>
         <v>8352</v>
       </c>
-      <c r="B26" s="54" t="str">
-        <f>'Main Sheet'!B26</f>
-        <v>5 Sanscrit Place</v>
+      <c r="B26" s="54" t="s">
+        <v>41</v>
       </c>
       <c r="C26" s="52">
         <v>0</v>
@@ -23669,7 +23770,6 @@
         <v>0</v>
       </c>
       <c r="H26" s="53">
-        <f>'Deliverables Sheet'!AA81</f>
         <v>0.347929388593615</v>
       </c>
       <c r="I26" s="54"/>
@@ -23686,14 +23786,13 @@
         <v>192.5</v>
       </c>
       <c r="N26" s="54">
-        <f>'Deliverables Sheet'!AE81</f>
         <v>-143.25</v>
       </c>
       <c r="O26" s="58">
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23710,14 +23809,12 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
-        <f>'Main Sheet'!A28</f>
         <v>8234</v>
       </c>
-      <c r="B28" s="54" t="str">
-        <f>'Main Sheet'!B28</f>
-        <v>Melhuish House</v>
+      <c r="B28" s="54" t="s">
+        <v>43</v>
       </c>
       <c r="C28" s="52">
         <v>0</v>
@@ -23735,7 +23832,6 @@
         <v>0</v>
       </c>
       <c r="H28" s="53">
-        <f>'Deliverables Sheet'!AA88</f>
         <v>0.271825144816915</v>
       </c>
       <c r="I28" s="54"/>
@@ -23750,14 +23846,13 @@
         <v>-4476.1500000000015</v>
       </c>
       <c r="N28" s="54">
-        <f>'Deliverables Sheet'!AE88</f>
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
         <v>30.14242424242425</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23774,14 +23869,12 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
-        <f>'Main Sheet'!A30</f>
         <v>8214</v>
       </c>
-      <c r="B30" s="54" t="str">
-        <f>'Main Sheet'!B30</f>
-        <v>6 Tiroroa Lane</v>
+      <c r="B30" s="54" t="s">
+        <v>44</v>
       </c>
       <c r="C30" s="52">
         <v>0</v>
@@ -23799,7 +23892,6 @@
         <v>0</v>
       </c>
       <c r="H30" s="53">
-        <f>'Deliverables Sheet'!AA95</f>
         <v>0.258043377145314</v>
       </c>
       <c r="I30" s="54"/>
@@ -23814,14 +23906,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="54">
-        <f>'Deliverables Sheet'!AE95</f>
         <v>-5</v>
       </c>
       <c r="O30" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23838,14 +23929,12 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
-        <f>'Main Sheet'!A32</f>
         <v>6792</v>
       </c>
-      <c r="B32" s="54" t="str">
-        <f>'Main Sheet'!B32</f>
-        <v>Major Hornbrook </v>
+      <c r="B32" s="54" t="s">
+        <v>45</v>
       </c>
       <c r="C32" s="52">
         <v>0</v>
@@ -23863,7 +23952,6 @@
         <v>0</v>
       </c>
       <c r="H32" s="53">
-        <f>'Deliverables Sheet'!AA102</f>
         <v>0.283172964220222</v>
       </c>
       <c r="I32" s="54">
@@ -23882,14 +23970,13 @@
         <v>-1388.1100000000006</v>
       </c>
       <c r="N32" s="54">
-        <f>'Deliverables Sheet'!AE102</f>
         <v>-317.25</v>
       </c>
       <c r="O32" s="58">
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23906,14 +23993,12 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
-        <f>'Main Sheet'!A34</f>
         <v>8840</v>
       </c>
-      <c r="B34" s="54" t="str">
-        <f>'Main Sheet'!B34</f>
-        <v>Inline Architecture</v>
+      <c r="B34" s="54" t="s">
+        <v>47</v>
       </c>
       <c r="C34" s="52">
         <v>-35454.43</v>
@@ -23931,7 +24016,6 @@
         <v>1.4607051925528065</v>
       </c>
       <c r="H34" s="53">
-        <f>'Deliverables Sheet'!AA109</f>
         <v>0.364182044343228</v>
       </c>
       <c r="I34" s="54"/>
@@ -23948,14 +24032,13 @@
         <v>-51788.47</v>
       </c>
       <c r="N34" s="54">
-        <f>'Deliverables Sheet'!AE109</f>
         <v>-204.75</v>
       </c>
       <c r="O34" s="58">
         <v>252.9351404151404</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -23972,14 +24055,12 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
-        <f>'Main Sheet'!A36</f>
         <v>8769</v>
       </c>
-      <c r="B36" s="54" t="str">
-        <f>'Main Sheet'!B36</f>
-        <v>Percival Bach</v>
+      <c r="B36" s="54" t="s">
+        <v>48</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -23996,10 +24077,7 @@
       <c r="G36" s="53">
         <v>0</v>
       </c>
-      <c r="H36" s="53" t="e">
-        <f>'Deliverables Sheet'!AA116</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="H36" s="53"/>
       <c r="I36" s="54">
         <v>80</v>
       </c>
@@ -24015,15 +24093,12 @@
       <c r="M36" s="52">
         <v>-3200</v>
       </c>
-      <c r="N36" s="54">
-        <f>'Deliverables Sheet'!AE116</f>
-        <v>0</v>
-      </c>
+      <c r="N36" s="54"/>
       <c r="O36" s="58">
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24040,14 +24115,12 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
-        <f>'Main Sheet'!A38</f>
         <v>7901</v>
       </c>
-      <c r="B38" s="54" t="str">
-        <f>'Main Sheet'!B38</f>
-        <v>St Albans Street</v>
+      <c r="B38" s="54" t="s">
+        <v>49</v>
       </c>
       <c r="C38" s="52">
         <v>0</v>
@@ -24065,7 +24138,6 @@
         <v>0</v>
       </c>
       <c r="H38" s="53">
-        <f>'Deliverables Sheet'!AA123</f>
         <v>0.1750921737769</v>
       </c>
       <c r="I38" s="54"/>
@@ -24079,15 +24151,12 @@
       <c r="M38" s="52">
         <v>-6365.780000000001</v>
       </c>
-      <c r="N38" s="54">
-        <f>'Deliverables Sheet'!AE123</f>
-        <v>0</v>
-      </c>
+      <c r="N38" s="54"/>
       <c r="O38" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24104,14 +24173,12 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
-        <f>'Main Sheet'!A40</f>
         <v>8923</v>
       </c>
-      <c r="B40" s="54" t="str">
-        <f>'Main Sheet'!B40</f>
-        <v>4 Perry St</v>
+      <c r="B40" s="54" t="s">
+        <v>50</v>
       </c>
       <c r="C40" s="52">
         <v>0</v>
@@ -24129,7 +24196,6 @@
         <v>0</v>
       </c>
       <c r="H40" s="53">
-        <f>'Deliverables Sheet'!AA130</f>
         <v>0.262692984588275</v>
       </c>
       <c r="I40" s="54"/>
@@ -24146,14 +24212,13 @@
         <v>0</v>
       </c>
       <c r="N40" s="54">
-        <f>'Deliverables Sheet'!AE130</f>
         <v>-2</v>
       </c>
       <c r="O40" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24170,14 +24235,12 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
-        <f>'Main Sheet'!A42</f>
         <v>7864</v>
       </c>
-      <c r="B42" s="54" t="str">
-        <f>'Main Sheet'!B42</f>
-        <v>Ryans House</v>
+      <c r="B42" s="54" t="s">
+        <v>51</v>
       </c>
       <c r="C42" s="52">
         <v>3554.300000000003</v>
@@ -24193,7 +24256,6 @@
         <v>0.8354415778071624</v>
       </c>
       <c r="H42" s="53">
-        <f>'Deliverables Sheet'!AA137</f>
         <v>0.257245709794332</v>
       </c>
       <c r="I42" s="54">
@@ -24210,14 +24272,13 @@
         <v>2969.41</v>
       </c>
       <c r="N42" s="54">
-        <f>'Deliverables Sheet'!AE137</f>
         <v>-266.75</v>
       </c>
       <c r="O42" s="58">
         <v>-11.131808809746953</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24234,52 +24295,44 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
-        <f>'Main Sheet'!A44</f>
         <v>7912</v>
       </c>
-      <c r="B44" s="54" t="str">
-        <f>'Main Sheet'!B44</f>
-        <v>71A Fendalton Road </v>
+      <c r="B44" s="54" t="s">
+        <v>52</v>
       </c>
       <c r="C44" s="52">
-        <v>9034.53</v>
+        <v>0</v>
       </c>
       <c r="D44" s="52">
-        <v>6362.08</v>
+        <v>0</v>
       </c>
       <c r="E44" s="52">
-        <v>2672.4500000000007</v>
+        <v>0</v>
       </c>
       <c r="F44" s="52"/>
       <c r="G44" s="53">
-        <v>0.29580398758983595</v>
-      </c>
-      <c r="H44" s="53" t="e">
-        <f>'Deliverables Sheet'!AA144</f>
-        <v>#DIV/0!</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H44" s="53"/>
       <c r="I44" s="54"/>
       <c r="J44" s="52"/>
       <c r="K44" s="52">
         <v>0</v>
       </c>
       <c r="L44" s="53">
-        <v>0.29580398758983595</v>
+        <v>0</v>
       </c>
       <c r="M44" s="52">
-        <v>2672.4500000000007</v>
-      </c>
-      <c r="N44" s="54">
-        <f>'Deliverables Sheet'!AE144</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N44" s="54"/>
       <c r="O44" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24296,14 +24349,12 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
-        <f>'Main Sheet'!A46</f>
         <v>8360</v>
       </c>
-      <c r="B46" s="98" t="str">
-        <f>'Main Sheet'!B46</f>
-        <v>Dixon House</v>
+      <c r="B46" s="98" t="s">
+        <v>53</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -24319,7 +24370,6 @@
         <v>0</v>
       </c>
       <c r="H46" s="100">
-        <f>'Deliverables Sheet'!AA151</f>
         <v>0.30580949617388</v>
       </c>
       <c r="I46" s="98"/>
@@ -24334,14 +24384,13 @@
         <v>-15.4900000000016</v>
       </c>
       <c r="N46" s="98">
-        <f>'Deliverables Sheet'!AE151</f>
         <v>-260.75</v>
       </c>
       <c r="O46" s="60">
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24358,14 +24407,12 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
-        <f>'Main Sheet'!A48</f>
         <v>8337</v>
       </c>
-      <c r="B48" s="98" t="str">
-        <f>'Main Sheet'!B48</f>
-        <v>Waimak Dairys </v>
+      <c r="B48" s="98" t="s">
+        <v>54</v>
       </c>
       <c r="C48" s="99">
         <v>13424.5</v>
@@ -24381,7 +24428,6 @@
         <v>0.7868069574285822</v>
       </c>
       <c r="H48" s="100">
-        <f>'Deliverables Sheet'!AA158</f>
         <v>0.222350780727547</v>
       </c>
       <c r="I48" s="98"/>
@@ -24398,14 +24444,13 @@
         <v>8032.490000000002</v>
       </c>
       <c r="N48" s="98">
-        <f>'Deliverables Sheet'!AE158</f>
         <v>-44.75</v>
       </c>
       <c r="O48" s="60">
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24422,14 +24467,12 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
-        <f>'Main Sheet'!A50</f>
         <v>9240</v>
       </c>
-      <c r="B50" s="98" t="str">
-        <f>'Main Sheet'!B50</f>
-        <v>Daves Twizel Shack</v>
+      <c r="B50" s="98" t="s">
+        <v>55</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -24444,10 +24487,7 @@
       <c r="G50" s="100">
         <v>0</v>
       </c>
-      <c r="H50" s="100" t="e">
-        <f>'Deliverables Sheet'!AA165</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="H50" s="100"/>
       <c r="I50" s="98">
         <v>0</v>
       </c>
@@ -24461,18 +24501,15 @@
       <c r="M50" s="99">
         <v>0</v>
       </c>
-      <c r="N50" s="98">
-        <f>'Deliverables Sheet'!AE165</f>
-        <v>0</v>
-      </c>
+      <c r="N50" s="98"/>
       <c r="O50" s="60">
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24489,14 +24526,12 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
-        <f>'Main Sheet'!A52</f>
         <v>7428</v>
       </c>
-      <c r="B52" s="98" t="str">
-        <f>'Main Sheet'!B52</f>
-        <v>FAB Pegasus Lakeside</v>
+      <c r="B52" s="98" t="s">
+        <v>56</v>
       </c>
       <c r="C52" s="99">
         <v>0</v>
@@ -24512,7 +24547,6 @@
         <v>0</v>
       </c>
       <c r="H52" s="100">
-        <f>'Deliverables Sheet'!AA172</f>
         <v>0.215986489339129</v>
       </c>
       <c r="I52" s="98">
@@ -24531,14 +24565,13 @@
         <v>-21630.28</v>
       </c>
       <c r="N52" s="98">
-        <f>'Deliverables Sheet'!AE172</f>
         <v>-304.75</v>
       </c>
       <c r="O52" s="60">
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24555,14 +24588,12 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
-        <f>'Main Sheet'!A54</f>
         <v>9351</v>
       </c>
-      <c r="B54" s="98" t="str">
-        <f>'Main Sheet'!B54</f>
-        <v>Harewood Golf Club</v>
+      <c r="B54" s="98" t="s">
+        <v>57</v>
       </c>
       <c r="C54" s="99">
         <v>5491.7</v>
@@ -24578,7 +24609,6 @@
         <v>0.8622229910592348</v>
       </c>
       <c r="H54" s="100">
-        <f>'Deliverables Sheet'!AA179</f>
         <v>0.453987062014389</v>
       </c>
       <c r="I54" s="98">
@@ -24597,14 +24627,13 @@
         <v>4095.0699999999997</v>
       </c>
       <c r="N54" s="98">
-        <f>'Deliverables Sheet'!AE179</f>
         <v>-11.25</v>
       </c>
       <c r="O54" s="60">
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24621,14 +24650,12 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
-        <f>'Main Sheet'!A56</f>
         <v>7429</v>
       </c>
-      <c r="B56" s="98" t="str">
-        <f>'Main Sheet'!B56</f>
-        <v>Taggart House</v>
+      <c r="B56" s="98" t="s">
+        <v>58</v>
       </c>
       <c r="C56" s="99">
         <v>12937.1</v>
@@ -24644,7 +24671,6 @@
         <v>0.6250944956752287</v>
       </c>
       <c r="H56" s="100">
-        <f>'Deliverables Sheet'!AA186</f>
         <v>0.22356150784199</v>
       </c>
       <c r="I56" s="98">
@@ -24663,14 +24689,13 @@
         <v>2686.9100000000008</v>
       </c>
       <c r="N56" s="98">
-        <f>'Deliverables Sheet'!AE186</f>
         <v>-32.25</v>
       </c>
       <c r="O56" s="60">
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24687,32 +24712,27 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
-        <f>'Main Sheet'!A58</f>
         <v>9508</v>
       </c>
-      <c r="B58" s="98" t="str">
-        <f>'Main Sheet'!B58</f>
-        <v>St Barnabas Church</v>
+      <c r="B58" s="98" t="s">
+        <v>59</v>
       </c>
       <c r="C58" s="99">
         <v>0</v>
       </c>
       <c r="D58" s="99">
-        <v>7180.07</v>
+        <v>6849.16</v>
       </c>
       <c r="E58" s="99">
-        <v>-7180.07</v>
+        <v>-6849.16</v>
       </c>
       <c r="F58" s="99"/>
       <c r="G58" s="100">
         <v>0</v>
       </c>
-      <c r="H58" s="100" t="e">
-        <f>'Deliverables Sheet'!AA193</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="H58" s="100"/>
       <c r="I58" s="98"/>
       <c r="J58" s="99"/>
       <c r="K58" s="99">
@@ -24722,17 +24742,14 @@
         <v>0</v>
       </c>
       <c r="M58" s="99">
-        <v>-7180.07</v>
-      </c>
-      <c r="N58" s="98">
-        <f>'Deliverables Sheet'!AE193</f>
-        <v>0</v>
-      </c>
+        <v>-6849.16</v>
+      </c>
+      <c r="N58" s="98"/>
       <c r="O58" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24749,54 +24766,24 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="59">
-        <f>'Main Sheet'!A60</f>
-        <v>0</v>
-      </c>
-      <c r="B60" s="98">
-        <f>'Main Sheet'!B60</f>
-        <v>0</v>
-      </c>
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="59"/>
+      <c r="B60" s="98"/>
       <c r="C60" s="99"/>
       <c r="D60" s="99"/>
-      <c r="E60" s="99">
-        <f>C60-D60</f>
-        <v>0</v>
-      </c>
+      <c r="E60" s="99"/>
       <c r="F60" s="99"/>
-      <c r="G60" s="100" t="e">
-        <f>(E60+F60)/C60</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H60" s="100" t="e">
-        <f>'Deliverables Sheet'!AA200</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="G60" s="100"/>
+      <c r="H60" s="100"/>
       <c r="I60" s="98"/>
       <c r="J60" s="99"/>
-      <c r="K60" s="99">
-        <f>(I60*40)+J60</f>
-        <v>0</v>
-      </c>
-      <c r="L60" s="100" t="e">
-        <f>((E60-K60)+F60)/C60</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M60" s="99">
-        <f>SUM(E60:F60)-K60</f>
-        <v>0</v>
-      </c>
-      <c r="N60" s="98">
-        <f>'Deliverables Sheet'!AE200</f>
-        <v>0</v>
-      </c>
-      <c r="O60" s="60" t="e">
-        <f>SUM(M60/(N60+I60))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="K60" s="99"/>
+      <c r="L60" s="100"/>
+      <c r="M60" s="99"/>
+      <c r="N60" s="98"/>
+      <c r="O60" s="60"/>
+    </row>
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24813,56 +24800,28 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="59">
-        <f>'Main Sheet'!A62</f>
-        <v>0</v>
-      </c>
-      <c r="B62" s="98" t="str">
-        <f>'Main Sheet'!B62</f>
-        <v>Contracting</v>
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="59"/>
+      <c r="B62" s="98" t="s">
+        <v>60</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
-      <c r="E62" s="99">
-        <f>C62-D62</f>
-        <v>0</v>
-      </c>
+      <c r="E62" s="99"/>
       <c r="F62" s="99"/>
-      <c r="G62" s="100" t="e">
-        <f>(E62+F62)/C62</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H62" s="100" t="e">
-        <f>'Deliverables Sheet'!AA207</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="G62" s="100"/>
+      <c r="H62" s="100"/>
       <c r="I62" s="98">
         <v>0</v>
       </c>
       <c r="J62" s="99"/>
-      <c r="K62" s="99">
-        <f>(I62*40)+J62</f>
-        <v>0</v>
-      </c>
-      <c r="L62" s="100" t="e">
-        <f>((E62-K62)+F62)/C62</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M62" s="99">
-        <f>SUM(E62:F62)-K62</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="98">
-        <f>'Deliverables Sheet'!AE207</f>
-        <v>0</v>
-      </c>
-      <c r="O62" s="60" t="e">
-        <f>SUM(M62/(N62+I62))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="K62" s="99"/>
+      <c r="L62" s="100"/>
+      <c r="M62" s="99"/>
+      <c r="N62" s="98"/>
+      <c r="O62" s="60"/>
+    </row>
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24879,14 +24838,12 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
-        <f>'Main Sheet'!A64</f>
         <v>8946</v>
       </c>
-      <c r="B64" s="98" t="str">
-        <f>'Main Sheet'!B64</f>
-        <v>Westcoast Vaults</v>
+      <c r="B64" s="98" t="s">
+        <v>61</v>
       </c>
       <c r="C64" s="99">
         <v>0</v>
@@ -24902,7 +24859,6 @@
         <v>0</v>
       </c>
       <c r="H64" s="100">
-        <f>'Deliverables Sheet'!AA214</f>
         <v>0.143790046441692</v>
       </c>
       <c r="I64" s="98"/>
@@ -24918,15 +24874,12 @@
       <c r="M64" s="99">
         <v>-3499.8</v>
       </c>
-      <c r="N64" s="98">
-        <f>'Deliverables Sheet'!AE214</f>
-        <v>0</v>
-      </c>
+      <c r="N64" s="98"/>
       <c r="O64" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24943,13 +24896,12 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
-      <c r="B66" s="98" t="str">
-        <f>'Main Sheet'!B66</f>
-        <v>Roydvale</v>
+      <c r="B66" s="98" t="s">
+        <v>62</v>
       </c>
       <c r="C66" s="99">
         <v>0</v>
@@ -24965,7 +24917,6 @@
         <v>0</v>
       </c>
       <c r="H66" s="100">
-        <f>'Deliverables Sheet'!AA221</f>
         <v>0.256265521519856</v>
       </c>
       <c r="I66" s="98">
@@ -24984,14 +24935,13 @@
         <v>-5784.239999999991</v>
       </c>
       <c r="N66" s="98">
-        <f>'Deliverables Sheet'!AE221</f>
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -25008,7 +24958,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -25025,12 +24975,12 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B69" s="103" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C69" s="104">
         <v>3912</v>
@@ -25042,13 +24992,13 @@
         <v>-110579.38</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G69" s="107">
         <v>-28.266712678936607</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I69" s="109">
         <v>-34.24897239263804</v>
@@ -25060,10 +25010,10 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -25075,13 +25025,13 @@
         <v>-55639.640000000014</v>
       </c>
       <c r="F70" s="111" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G70" s="112">
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -25445,7 +25395,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25456,7 +25406,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25477,55 +25427,55 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F2" s="117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" s="117" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H2" s="117" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I2" s="117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J2" s="117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K2" s="117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L2" s="117" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M2" s="117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N2" s="117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O2" s="117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P2" s="117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q2" s="118" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -25539,12 +25489,12 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -25597,14 +25547,12 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
-        <f>'Main Sheet'!A4</f>
         <v>7658</v>
       </c>
-      <c r="B4" s="20" t="str">
-        <f>'Main Sheet'!B4</f>
-        <v>Charity Hospital</v>
+      <c r="B4" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="54">
         <v>530.95</v>
@@ -25630,10 +25578,10 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25652,14 +25600,12 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
-        <f>'Main Sheet'!A6</f>
         <v>8142</v>
       </c>
-      <c r="B6" s="20" t="str">
-        <f>'Main Sheet'!B6</f>
-        <v>Fisher Developements</v>
+      <c r="B6" s="20" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="54">
         <v>356.07</v>
@@ -25685,10 +25631,10 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25707,14 +25653,12 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
-        <f>'Main Sheet'!A8</f>
         <v>8824</v>
       </c>
-      <c r="B8" s="20" t="str">
-        <f>'Main Sheet'!B8</f>
-        <v>3 Innovation Road</v>
+      <c r="B8" s="20" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="54">
         <v>125.39</v>
@@ -25740,10 +25684,10 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25762,14 +25706,12 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
-        <f>'Main Sheet'!A10</f>
         <v>8127</v>
       </c>
-      <c r="B10" s="20" t="str">
-        <f>'Main Sheet'!B10</f>
-        <v>Rolly Autowash</v>
+      <c r="B10" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="C10" s="54">
         <v>795.22</v>
@@ -25797,10 +25739,10 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25819,12 +25761,12 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -25854,10 +25796,10 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25876,14 +25818,12 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
-        <f>'Main Sheet'!A14</f>
         <v>8886</v>
       </c>
-      <c r="B14" s="20" t="str">
-        <f>'Main Sheet'!B14</f>
-        <v>Monkey Toe - Fisher fit out</v>
+      <c r="B14" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="54">
         <v>501.83</v>
@@ -25913,10 +25853,10 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25935,14 +25875,12 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
-        <f>'Main Sheet'!A16</f>
         <v>8887</v>
       </c>
-      <c r="B16" s="20" t="str">
-        <f>'Main Sheet'!B16</f>
-        <v>Tenancy 2 - Fisher Fit out</v>
+      <c r="B16" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="54">
         <v>223.22</v>
@@ -25970,7 +25908,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25989,14 +25927,12 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
-        <f>'Main Sheet'!A18</f>
         <v>8670</v>
       </c>
-      <c r="B18" s="20" t="str">
-        <f>'Main Sheet'!B18</f>
-        <v>Studio DB - tautara fit out</v>
+      <c r="B18" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="C18" s="54">
         <v>679.42</v>
@@ -26024,7 +25960,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -26043,14 +25979,12 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
-        <f>'Main Sheet'!A20</f>
         <v>8907</v>
       </c>
-      <c r="B20" s="20" t="str">
-        <f>'Main Sheet'!B20</f>
-        <v>35 Mania</v>
+      <c r="B20" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="C20" s="54">
         <v>63.5</v>
@@ -26076,7 +26010,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26095,14 +26029,12 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
-        <f>'Main Sheet'!A22</f>
         <v>9065</v>
       </c>
-      <c r="B22" s="20" t="str">
-        <f>'Main Sheet'!B22</f>
-        <v>Cooltranz stage 4</v>
+      <c r="B22" s="20" t="s">
+        <v>39</v>
       </c>
       <c r="C22" s="54">
         <v>160.82</v>
@@ -26132,7 +26064,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26151,14 +26083,12 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
-        <f>'Main Sheet'!A24</f>
         <v>9259</v>
       </c>
-      <c r="B24" s="20" t="str">
-        <f>'Main Sheet'!B24</f>
-        <v>Andrew Reeve Stage 2</v>
+      <c r="B24" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="C24" s="54">
         <v>470.62</v>
@@ -26186,7 +26116,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26205,14 +26135,12 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
-        <f>'Main Sheet'!A26</f>
         <v>8352</v>
       </c>
-      <c r="B26" s="20" t="str">
-        <f>'Main Sheet'!B26</f>
-        <v>5 Sanscrit Place</v>
+      <c r="B26" s="20" t="s">
+        <v>41</v>
       </c>
       <c r="C26" s="54">
         <v>139.07</v>
@@ -26238,7 +26166,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26257,14 +26185,12 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
-        <f>'Main Sheet'!A28</f>
         <v>8234</v>
       </c>
-      <c r="B28" s="20" t="str">
-        <f>'Main Sheet'!B28</f>
-        <v>Melhuish House</v>
+      <c r="B28" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="C28" s="54">
         <v>231.75</v>
@@ -26291,7 +26217,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26310,14 +26236,12 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
-        <f>'Main Sheet'!A30</f>
         <v>8214</v>
       </c>
-      <c r="B30" s="20" t="str">
-        <f>'Main Sheet'!B30</f>
-        <v>6 Tiroroa Lane</v>
+      <c r="B30" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="C30" s="54">
         <v>147.9</v>
@@ -26348,7 +26272,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26367,14 +26291,12 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
-        <f>'Main Sheet'!A32</f>
         <v>6792</v>
       </c>
-      <c r="B32" s="20" t="str">
-        <f>'Main Sheet'!B32</f>
-        <v>Major Hornbrook </v>
+      <c r="B32" s="20" t="s">
+        <v>45</v>
       </c>
       <c r="C32" s="54">
         <v>208.2</v>
@@ -26398,7 +26320,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26417,14 +26339,12 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
-        <f>'Main Sheet'!A34</f>
         <v>8840</v>
       </c>
-      <c r="B34" s="20" t="str">
-        <f>'Main Sheet'!B34</f>
-        <v>Inline Architecture</v>
+      <c r="B34" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -26450,7 +26370,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26469,14 +26389,12 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
-        <f>'Main Sheet'!A36</f>
         <v>8769</v>
       </c>
-      <c r="B36" s="20" t="str">
-        <f>'Main Sheet'!B36</f>
-        <v>Percival Bach</v>
+      <c r="B36" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -26504,7 +26422,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26523,14 +26441,12 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
-        <f>'Main Sheet'!A38</f>
         <v>7901</v>
       </c>
-      <c r="B38" s="20" t="str">
-        <f>'Main Sheet'!B38</f>
-        <v>St Albans Street</v>
+      <c r="B38" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -26561,7 +26477,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26580,14 +26496,12 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
-        <f>'Main Sheet'!A40</f>
         <v>8923</v>
       </c>
-      <c r="B40" s="20" t="str">
-        <f>'Main Sheet'!B40</f>
-        <v>4 Perry St</v>
+      <c r="B40" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -26617,7 +26531,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26636,14 +26550,12 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
-        <f>'Main Sheet'!A42</f>
         <v>7864</v>
       </c>
-      <c r="B42" s="20" t="str">
-        <f>'Main Sheet'!B42</f>
-        <v>Ryans House</v>
+      <c r="B42" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -26668,7 +26580,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26687,14 +26599,12 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
-        <f>'Main Sheet'!A44</f>
         <v>7912</v>
       </c>
-      <c r="B44" s="20" t="str">
-        <f>'Main Sheet'!B44</f>
-        <v>71A Fendalton Road </v>
+      <c r="B44" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -26729,7 +26639,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26748,14 +26658,12 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
-        <f>'Main Sheet'!A46</f>
         <v>8360</v>
       </c>
-      <c r="B46" s="75" t="str">
-        <f>'Main Sheet'!B46</f>
-        <v>Dixon House</v>
+      <c r="B46" s="75" t="s">
+        <v>53</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -26779,7 +26687,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26798,14 +26706,12 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
-        <f>'Main Sheet'!A48</f>
         <v>8337</v>
       </c>
-      <c r="B48" s="20" t="str">
-        <f>'Main Sheet'!B48</f>
-        <v>Waimak Dairys </v>
+      <c r="B48" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -26833,7 +26739,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26852,23 +26758,21 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
-        <f>'Main Sheet'!A50</f>
         <v>9240</v>
       </c>
-      <c r="B50" s="20" t="str">
-        <f>'Main Sheet'!B50</f>
-        <v>Daves Twizel Shack</v>
+      <c r="B50" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="C50" s="54">
-        <v>0</v>
+        <v>64.71</v>
       </c>
       <c r="D50" s="54">
         <v>0</v>
       </c>
       <c r="E50" s="54">
-        <v>0</v>
+        <v>64.71</v>
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="54"/>
@@ -26887,7 +26791,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26906,14 +26810,12 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
-        <f>'Main Sheet'!A52</f>
         <v>7428</v>
       </c>
-      <c r="B52" s="20" t="str">
-        <f>'Main Sheet'!B52</f>
-        <v>FAB Pegasus Lakeside</v>
+      <c r="B52" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -26944,7 +26846,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26963,14 +26865,12 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
-        <f>'Main Sheet'!A54</f>
         <v>9351</v>
       </c>
-      <c r="B54" s="20" t="str">
-        <f>'Main Sheet'!B54</f>
-        <v>Harewood Golf Club</v>
+      <c r="B54" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -27001,7 +26901,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -27020,14 +26920,12 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
-        <f>'Main Sheet'!A56</f>
         <v>7429</v>
       </c>
-      <c r="B56" s="20" t="str">
-        <f>'Main Sheet'!B56</f>
-        <v>Taggart House</v>
+      <c r="B56" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -27056,7 +26954,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -27075,14 +26973,12 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
-        <f>'Main Sheet'!A58</f>
         <v>9508</v>
       </c>
-      <c r="B58" s="20" t="str">
-        <f>'Main Sheet'!B58</f>
-        <v>St Barnabas Church</v>
+      <c r="B58" s="20" t="s">
+        <v>59</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -27112,7 +27008,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27131,27 +27027,12 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
-        <f>'Main Sheet'!A60</f>
-        <v>0</v>
-      </c>
-      <c r="B60" s="20">
-        <f>'Main Sheet'!B60</f>
-        <v>0</v>
-      </c>
-      <c r="C60" s="54" t="e">
-        <f t="array" ref="C60:C60">LOOKUP(2,1/('Deliverables Sheet'!S200:S205&lt;&gt;0),'Deliverables Sheet'!S200:S205)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D60" s="54" t="e">
-        <f t="array" ref="D60:D60">LOOKUP(2,1/('Deliverables Sheet'!T200:T205&lt;&gt;0),'Deliverables Sheet'!T200:T205)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E60" s="54" t="e">
-        <f t="array" ref="E60:E60">LOOKUP(2,1/('Deliverables Sheet'!U200:U205&lt;&gt;0),'Deliverables Sheet'!U200:U205)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="19"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
       <c r="F60" s="54"/>
       <c r="G60" s="54"/>
       <c r="H60" s="54"/>
@@ -27165,7 +27046,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27184,27 +27065,14 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
-        <f>'Main Sheet'!A62</f>
-        <v>0</v>
-      </c>
-      <c r="B62" s="20" t="str">
-        <f>'Main Sheet'!B62</f>
-        <v>Contracting</v>
-      </c>
-      <c r="C62" s="54" t="e">
-        <f t="array" ref="C62:C62">LOOKUP(2,1/('Deliverables Sheet'!S207:S212&lt;&gt;0),'Deliverables Sheet'!S207:S212)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D62" s="54" t="e">
-        <f t="array" ref="D62:D62">LOOKUP(2,1/('Deliverables Sheet'!T207:T212&lt;&gt;0),'Deliverables Sheet'!T207:T212)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E62" s="54" t="e">
-        <f t="array" ref="E62:E62">LOOKUP(2,1/('Deliverables Sheet'!U207:U212&lt;&gt;0),'Deliverables Sheet'!U207:U212)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="19"/>
+      <c r="B62" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
       <c r="F62" s="54"/>
       <c r="G62" s="54"/>
       <c r="H62" s="54"/>
@@ -27218,7 +27086,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27237,14 +27105,12 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
-        <f>'Main Sheet'!A64</f>
         <v>8946</v>
       </c>
-      <c r="B64" s="20" t="str">
-        <f>'Main Sheet'!B64</f>
-        <v>Westcoast Vaults</v>
+      <c r="B64" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -27272,7 +27138,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27291,14 +27157,12 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
-        <f>'Main Sheet'!A66</f>
         <v>8308</v>
       </c>
-      <c r="B66" s="20" t="str">
-        <f>'Main Sheet'!B66</f>
-        <v>Roydvale</v>
+      <c r="B66" s="20" t="s">
+        <v>62</v>
       </c>
       <c r="C66" s="54">
         <v>2312.68</v>
@@ -27332,7 +27196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27351,7 +27215,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27370,7 +27234,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27389,319 +27253,210 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>144</v>
-      </c>
-      <c r="C70" s="147" t="e">
-        <f>C3+C71+C72</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D70" s="147" t="e">
-        <f>D3+D71+D72</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E70" s="147" t="e">
-        <f>E3+E71+E72</f>
-        <v>#N/A</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C70" s="147"/>
+      <c r="D70" s="147"/>
+      <c r="E70" s="147"/>
       <c r="F70" s="147">
-        <f>F3+F71+F72</f>
         <v>640</v>
       </c>
       <c r="G70" s="147">
-        <f>G3+G71+G72</f>
         <v>715</v>
       </c>
       <c r="H70" s="147">
-        <f>H3+H71+H72</f>
         <v>790</v>
       </c>
       <c r="I70" s="147">
-        <f>I3+I71+I72</f>
         <v>700</v>
       </c>
       <c r="J70" s="147">
-        <f>J3+J71+J72</f>
         <v>700</v>
       </c>
       <c r="K70" s="147">
-        <f>K3+K71+K72</f>
         <v>700</v>
       </c>
       <c r="L70" s="147">
-        <f>L3+L71+L72</f>
         <v>716</v>
       </c>
       <c r="M70" s="147">
-        <f>M3+M71+M72</f>
         <v>2520</v>
       </c>
       <c r="N70" s="147">
-        <f>N3+N71+N72</f>
         <v>3060</v>
       </c>
       <c r="O70" s="147">
-        <f>O3+O71+O72</f>
         <v>1316</v>
       </c>
       <c r="P70" s="147">
-        <f>P3+P71+P72</f>
         <v>914</v>
       </c>
       <c r="Q70" s="147">
-        <f>Q3+Q71+Q72</f>
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="C71" s="20" t="e">
-        <f>SUM(C26:C46)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D71" s="20" t="e">
-        <f>SUM(D26:D46)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E71" s="20" t="e">
-        <f>SUM(E26:E46)</f>
-        <v>#N/A</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
       <c r="F71" s="20">
-        <f>SUM(F26:F46)</f>
         <v>140</v>
       </c>
       <c r="G71" s="20">
-        <f>SUM(G26:G46)</f>
         <v>15</v>
       </c>
       <c r="H71" s="20">
-        <f>SUM(H26:H46)</f>
         <v>90</v>
       </c>
-      <c r="I71" s="20">
-        <f>SUM(I26:I66)</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="20">
-        <f>SUM(J26:J66)</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="20">
-        <f>SUM(K26:K66)</f>
-        <v>0</v>
-      </c>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
       <c r="L71" s="20">
-        <f>SUM(L26:L66)</f>
         <v>16</v>
       </c>
       <c r="M71" s="20">
-        <f>SUM(M26:M66)</f>
         <v>800</v>
       </c>
       <c r="N71" s="20">
-        <f>SUM(N26:N66)</f>
         <v>858</v>
       </c>
       <c r="O71" s="20">
-        <f>SUM(O26:O46)</f>
         <v>476</v>
       </c>
       <c r="P71" s="20">
-        <f>SUM(P26:P46)</f>
         <v>214</v>
       </c>
       <c r="Q71" s="20">
-        <f>SUM(Q26:Q46)</f>
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C72" s="20">
-        <f>SUM(C4:C24)</f>
         <v>4490.26</v>
       </c>
-      <c r="D72" s="20" t="e">
-        <f>SUM(D4:D24)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E72" s="20" t="e">
-        <f>SUM(E4:E24)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F72" s="20">
-        <f>SUM(F4:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G72" s="20">
-        <f>SUM(G4:G24)</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="20">
-        <f>SUM(H4:H24)</f>
-        <v>0</v>
-      </c>
-      <c r="I72" s="20">
-        <f>SUM(I4:I24)</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="20">
-        <f>SUM(J4:J24)</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="20">
-        <f>SUM(K4:K24)</f>
-        <v>0</v>
-      </c>
-      <c r="L72" s="20">
-        <f>SUM(L4:L24)</f>
-        <v>0</v>
-      </c>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20"/>
       <c r="M72" s="20">
-        <f>SUM(M4:M24)</f>
         <v>1020</v>
       </c>
       <c r="N72" s="20">
-        <f>SUM(N4:N24)</f>
         <v>1502</v>
       </c>
       <c r="O72" s="20">
-        <f>SUM(O4:O24)</f>
         <v>140</v>
       </c>
-      <c r="P72" s="20">
-        <f>SUM(P4:P24)</f>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="20">
-        <f>SUM(Q4:Q24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+    </row>
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
       <c r="E73" s="149"/>
       <c r="F73" s="149">
-        <f>F77*F76*8*0.8</f>
         <v>1488</v>
       </c>
       <c r="G73" s="149">
-        <f>G77*G76*8*0.8</f>
         <v>2112</v>
       </c>
       <c r="H73" s="149">
-        <f>H77*H76*8*0.8</f>
         <v>1984</v>
       </c>
       <c r="I73" s="149">
-        <f>I77*I76*8*0.8</f>
         <v>1884.8</v>
       </c>
       <c r="J73" s="149">
-        <f>J77*J76*8*0.8</f>
         <v>1948.8</v>
       </c>
       <c r="K73" s="149">
-        <f>K77*K76*8*0.8</f>
         <v>2083.2</v>
       </c>
       <c r="L73" s="149">
-        <f>L77*L76*8*0.8</f>
         <v>2604.8</v>
       </c>
       <c r="M73" s="149">
-        <f>M77*M76*8*0.8</f>
         <v>2486.4</v>
       </c>
       <c r="N73" s="149">
-        <f>N77*N76*8*0.8</f>
         <v>2604.8</v>
       </c>
       <c r="O73" s="149">
-        <f>O77*O76*8*0.8</f>
         <v>2217.6</v>
       </c>
       <c r="P73" s="149">
-        <f>P77*P76*8*0.8</f>
         <v>2112</v>
       </c>
       <c r="Q73" s="150">
-        <f>Q77*Q76*8*0.8</f>
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
       <c r="E74" s="152"/>
       <c r="F74" s="153">
-        <f>F70-F73</f>
         <v>-848</v>
       </c>
       <c r="G74" s="153">
-        <f>G70-G73</f>
         <v>-1397</v>
       </c>
       <c r="H74" s="154">
-        <f>H70-H73</f>
         <v>-1194</v>
       </c>
       <c r="I74" s="153">
-        <f>I70-I73</f>
         <v>-1184.8</v>
       </c>
       <c r="J74" s="153">
-        <f>J70-J73</f>
         <v>-1248.8</v>
       </c>
       <c r="K74" s="153">
-        <f>K70-K73</f>
         <v>-1383.2</v>
       </c>
       <c r="L74" s="153">
-        <f>L70-L73</f>
         <v>-1888.8</v>
       </c>
       <c r="M74" s="153">
-        <f>M70-M73</f>
         <v>33.5999999999999</v>
       </c>
       <c r="N74" s="153">
-        <f>N70-N73</f>
         <v>455.2</v>
       </c>
       <c r="O74" s="153">
-        <f>O70-O73</f>
         <v>-901.6</v>
       </c>
       <c r="P74" s="153">
-        <f>P70-P73</f>
         <v>-1198</v>
       </c>
       <c r="Q74" s="155">
-        <f>Q70-Q73</f>
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27720,13 +27475,13 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C76" s="157" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -27767,10 +27522,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -27812,7 +27567,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27831,10 +27586,10 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -27846,7 +27601,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -27854,10 +27609,10 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -27877,10 +27632,10 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -27900,10 +27655,10 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -27923,10 +27678,10 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -27946,10 +27701,10 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -27969,10 +27724,10 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -27992,10 +27747,10 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -28015,10 +27770,10 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -28038,10 +27793,10 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -28061,10 +27816,10 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -28084,10 +27839,10 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -28107,7 +27862,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -28128,7 +27883,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -28149,7 +27904,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -28170,7 +27925,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -28191,7 +27946,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -28212,7 +27967,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -28233,7 +27988,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28254,10 +28009,10 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -28277,10 +28032,10 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -28300,10 +28055,10 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -28323,10 +28078,10 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -28346,10 +28101,10 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -28369,10 +28124,10 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -28392,10 +28147,10 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -28415,7 +28170,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28434,7 +28189,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28453,7 +28208,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28472,7 +28227,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28491,13 +28246,12 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C109" s="170">
-        <f>SUM(C80:C108)</f>
         <v>16.5</v>
       </c>
       <c r="D109" s="35"/>
@@ -28566,13 +28320,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -28602,9 +28355,9 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28635,9 +28388,9 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28668,9 +28421,9 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -28701,9 +28454,9 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28734,9 +28487,9 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -28767,9 +28520,9 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28800,9 +28553,9 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -28833,7 +28586,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28864,7 +28617,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28895,9 +28648,9 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -28928,9 +28681,9 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -28961,9 +28714,9 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -28994,9 +28747,9 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -29027,9 +28780,9 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -29060,9 +28813,9 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -29093,9 +28846,9 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -29126,9 +28879,9 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -29159,9 +28912,9 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -29192,9 +28945,9 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -29225,9 +28978,9 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -29258,9 +29011,9 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -29291,9 +29044,9 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -29324,9 +29077,9 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -29357,9 +29110,9 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -29390,9 +29143,9 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -29423,9 +29176,9 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29455,9 +29208,9 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -29487,9 +29240,9 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -29519,9 +29272,9 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -29551,9 +29304,9 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -29583,7 +29336,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29613,7 +29366,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29643,9 +29396,9 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -29675,9 +29428,9 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -29707,9 +29460,9 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -29739,9 +29492,9 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -29771,9 +29524,9 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -29803,7 +29556,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29833,9 +29586,9 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -29865,9 +29618,9 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -29897,9 +29650,9 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -29929,9 +29682,9 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -29961,7 +29714,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -29991,7 +29744,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -30021,7 +29774,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -30051,7 +29804,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -30081,9 +29834,9 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -30113,9 +29866,9 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -30145,7 +29898,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -30175,7 +29928,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -30205,7 +29958,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -30235,7 +29988,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30265,7 +30018,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30295,7 +30048,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30390,13 +30143,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -30426,7 +30178,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30457,7 +30209,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30488,7 +30240,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30519,7 +30271,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30550,7 +30302,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30581,7 +30333,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30612,7 +30364,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30643,7 +30395,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30674,7 +30426,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30705,7 +30457,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30736,7 +30488,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30767,7 +30519,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30798,7 +30550,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30829,7 +30581,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30860,7 +30612,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30891,7 +30643,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -30922,7 +30674,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -30953,7 +30705,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -30984,7 +30736,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -31015,7 +30767,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -31045,7 +30797,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -31075,7 +30827,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -31105,7 +30857,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -31135,7 +30887,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -31165,7 +30917,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -31195,7 +30947,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -31225,7 +30977,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31255,7 +31007,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31285,7 +31037,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31315,7 +31067,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31345,7 +31097,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31375,7 +31127,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31405,7 +31157,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31435,7 +31187,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31465,7 +31217,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31495,9 +31247,9 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -31527,9 +31279,9 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -31559,7 +31311,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31589,7 +31341,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31619,7 +31371,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31649,7 +31401,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31679,7 +31431,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31709,7 +31461,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -31900,13 +31652,13 @@
         <v>74</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R2" s="43" t="s">
         <v>75</v>
@@ -53452,35 +53204,35 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -53490,9 +53242,9 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -53501,9 +53253,9 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -53512,9 +53264,9 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>
@@ -53523,13 +53275,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -422,7 +422,7 @@
     <t>Totals</t>
   </si>
   <si>
-    <t>Commercial</t>
+    <t>Total</t>
   </si>
   <si>
     <t>GP%</t>
@@ -22964,7 +22964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22978,7 +22978,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -23000,7 +23000,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -23066,7 +23066,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -23113,7 +23113,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -23130,7 +23130,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23197,7 +23197,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23257,7 +23257,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23321,7 +23321,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23386,7 +23386,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -23433,7 +23433,7 @@
         <v>45.876428571428605</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23450,7 +23450,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>98.73233429394816</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23512,7 +23512,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23579,7 +23579,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -23618,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23635,7 +23635,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23693,7 +23693,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23747,7 +23747,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23809,7 +23809,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>30.14242424242425</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23869,7 +23869,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23929,7 +23929,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -23976,7 +23976,7 @@
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23993,7 +23993,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>252.9351404151404</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -24055,7 +24055,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24115,7 +24115,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24173,7 +24173,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24235,7 +24235,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>-11.131808809746953</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24295,7 +24295,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24349,7 +24349,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24407,7 +24407,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -24450,7 +24450,7 @@
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24467,7 +24467,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -24509,7 +24509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24526,7 +24526,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24588,7 +24588,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24650,7 +24650,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -24695,7 +24695,7 @@
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24712,7 +24712,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24766,7 +24766,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -24783,7 +24783,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24800,7 +24800,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -24821,7 +24821,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24838,7 +24838,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24941,7 +24941,7 @@
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -24958,7 +24958,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -24975,7 +24975,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -24983,25 +24983,25 @@
         <v>121</v>
       </c>
       <c r="C69" s="104">
-        <v>3912</v>
+        <v>3865.1700000000037</v>
       </c>
       <c r="D69" s="104">
-        <v>114491.38</v>
+        <v>180905.65</v>
       </c>
       <c r="E69" s="105">
-        <v>-110579.38</v>
+        <v>-177040.47999999995</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>122</v>
       </c>
       <c r="G69" s="107">
-        <v>-28.266712678936607</v>
+        <v>-45.80406036474457</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>123</v>
       </c>
       <c r="I69" s="109">
-        <v>-34.24897239263804</v>
+        <v>-57.17810083385718</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -25010,7 +25010,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -25024,9 +25024,7 @@
       <c r="E70" s="110">
         <v>-55639.640000000014</v>
       </c>
-      <c r="F70" s="111" t="s">
-        <v>122</v>
-      </c>
+      <c r="F70" s="111"/>
       <c r="G70" s="112">
         <v>2.433333916450914</v>
       </c>
@@ -25395,7 +25393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25406,7 +25404,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25427,7 +25425,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -25489,7 +25487,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -25547,7 +25545,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -25581,7 +25579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25600,7 +25598,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -25634,7 +25632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25653,7 +25651,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -25687,7 +25685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25706,7 +25704,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -25742,7 +25740,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25761,7 +25759,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25799,7 +25797,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25818,7 +25816,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -25856,7 +25854,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25875,7 +25873,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -25908,7 +25906,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25927,7 +25925,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -25960,7 +25958,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -25979,7 +25977,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -26010,7 +26008,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26029,7 +26027,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -26064,7 +26062,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26083,7 +26081,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -26116,7 +26114,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26135,7 +26133,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -26166,7 +26164,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26185,7 +26183,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -26217,7 +26215,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26236,7 +26234,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -26272,7 +26270,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26291,7 +26289,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -26320,7 +26318,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26339,7 +26337,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -26370,7 +26368,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26389,7 +26387,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -26422,7 +26420,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26441,7 +26439,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -26477,7 +26475,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26496,7 +26494,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -26531,7 +26529,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26550,7 +26548,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -26580,7 +26578,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26599,7 +26597,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -26639,7 +26637,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26658,7 +26656,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -26687,7 +26685,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26706,7 +26704,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -26739,7 +26737,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26758,7 +26756,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -26791,7 +26789,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26810,7 +26808,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -26846,7 +26844,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26865,7 +26863,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -26901,7 +26899,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -26920,7 +26918,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -26954,7 +26952,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -26973,7 +26971,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -27008,7 +27006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27027,7 +27025,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -27046,7 +27044,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27065,7 +27063,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -27086,7 +27084,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27105,7 +27103,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -27138,7 +27136,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27157,7 +27155,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -27196,7 +27194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27215,7 +27213,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27234,7 +27232,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27253,7 +27251,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -27298,7 +27296,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -27337,7 +27335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -27366,7 +27364,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -27411,7 +27409,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -27456,7 +27454,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27475,7 +27473,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -27522,7 +27520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -27567,7 +27565,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27586,7 +27584,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -27609,7 +27607,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -27632,7 +27630,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -27655,7 +27653,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -27678,7 +27676,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -27701,7 +27699,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -27724,7 +27722,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -27747,7 +27745,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -27770,7 +27768,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -27793,7 +27791,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -27816,7 +27814,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -27839,7 +27837,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -27862,7 +27860,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -27883,7 +27881,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -27904,7 +27902,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -27925,7 +27923,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -27946,7 +27944,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -27967,7 +27965,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -27988,7 +27986,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28009,7 +28007,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -28032,7 +28030,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -28055,7 +28053,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -28078,7 +28076,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -28101,7 +28099,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -28124,7 +28122,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -28147,7 +28145,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -28170,7 +28168,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28189,7 +28187,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28208,7 +28206,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28227,7 +28225,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28246,7 +28244,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -28320,10 +28318,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -28355,7 +28354,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -28388,7 +28387,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -28421,7 +28420,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -28454,7 +28453,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -28487,7 +28486,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -28520,7 +28519,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -28553,7 +28552,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -28586,7 +28585,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28617,7 +28616,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28648,7 +28647,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -28681,7 +28680,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -28714,7 +28713,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -28747,7 +28746,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -28780,7 +28779,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -28813,7 +28812,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -28846,7 +28845,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -28879,7 +28878,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -28912,7 +28911,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -28945,7 +28944,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -28978,7 +28977,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -29011,7 +29010,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -29044,7 +29043,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -29077,7 +29076,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -29110,7 +29109,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -29143,7 +29142,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -29176,7 +29175,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -29208,7 +29207,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -29240,7 +29239,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -29272,7 +29271,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -29304,7 +29303,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -29336,7 +29335,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29366,7 +29365,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29396,7 +29395,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -29428,7 +29427,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -29460,7 +29459,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -29492,7 +29491,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -29524,7 +29523,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -29556,7 +29555,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29586,7 +29585,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -29618,7 +29617,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -29650,7 +29649,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -29682,7 +29681,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -29714,7 +29713,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -29744,7 +29743,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -29774,7 +29773,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -29804,7 +29803,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -29834,7 +29833,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -29866,7 +29865,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -29898,7 +29897,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -29928,7 +29927,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -29958,7 +29957,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -29988,7 +29987,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30018,7 +30017,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30048,7 +30047,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30143,10 +30142,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -30178,7 +30178,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30209,7 +30209,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30240,7 +30240,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30271,7 +30271,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30302,7 +30302,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30333,7 +30333,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30364,7 +30364,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30395,7 +30395,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30426,7 +30426,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30457,7 +30457,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30488,7 +30488,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30519,7 +30519,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30550,7 +30550,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30581,7 +30581,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30612,7 +30612,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30643,7 +30643,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -30674,7 +30674,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -30705,7 +30705,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -30736,7 +30736,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -30767,7 +30767,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -30797,7 +30797,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -30827,7 +30827,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -30857,7 +30857,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -30887,7 +30887,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -30917,7 +30917,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -30947,7 +30947,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30977,7 +30977,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31007,7 +31007,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31037,7 +31037,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31067,7 +31067,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31097,7 +31097,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31127,7 +31127,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31157,7 +31157,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31187,7 +31187,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31217,7 +31217,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31247,7 +31247,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -31279,7 +31279,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -31311,7 +31311,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31341,7 +31341,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31371,7 +31371,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31401,7 +31401,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31431,7 +31431,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31461,7 +31461,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53204,19 +53204,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53230,7 +53230,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -53242,7 +53242,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -53253,7 +53253,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -53264,7 +53264,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -53275,13 +53275,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6719,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>
@@ -17252,7 +17252,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -22964,7 +22964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22978,7 +22978,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -23000,7 +23000,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -23066,7 +23066,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -23113,7 +23113,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -23130,7 +23130,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23197,7 +23197,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23257,7 +23257,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23321,7 +23321,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23386,7 +23386,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -23433,7 +23433,7 @@
         <v>45.876428571428605</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23450,7 +23450,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>98.73233429394816</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23512,7 +23512,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23579,7 +23579,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -23618,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23635,7 +23635,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23693,7 +23693,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23747,7 +23747,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23809,7 +23809,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>30.14242424242425</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23869,7 +23869,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23929,7 +23929,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -23976,7 +23976,7 @@
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23993,7 +23993,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>252.9351404151404</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -24055,7 +24055,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24115,7 +24115,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24173,7 +24173,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24235,7 +24235,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>-11.131808809746953</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24295,7 +24295,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24349,7 +24349,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24407,7 +24407,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -24450,7 +24450,7 @@
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24467,7 +24467,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -24509,7 +24509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24526,7 +24526,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24588,7 +24588,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24650,7 +24650,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -24695,7 +24695,7 @@
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24712,7 +24712,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24766,7 +24766,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -24783,7 +24783,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24800,7 +24800,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -24821,7 +24821,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24838,7 +24838,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24941,7 +24941,7 @@
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -24958,7 +24958,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -24975,7 +24975,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -25010,7 +25010,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -25393,7 +25393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25404,7 +25404,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25425,7 +25425,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -25487,7 +25487,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -25545,7 +25545,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25598,7 +25598,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -25632,7 +25632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25651,7 +25651,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25704,7 +25704,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25759,7 +25759,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25797,7 +25797,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25816,7 +25816,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -25854,7 +25854,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25873,7 +25873,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -25906,7 +25906,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25925,7 +25925,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -25958,7 +25958,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -25977,7 +25977,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -26008,7 +26008,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26027,7 +26027,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -26062,7 +26062,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26081,7 +26081,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -26114,7 +26114,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26133,7 +26133,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -26164,7 +26164,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26183,7 +26183,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -26215,7 +26215,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26234,7 +26234,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -26270,7 +26270,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26289,7 +26289,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -26318,7 +26318,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26337,7 +26337,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -26368,7 +26368,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26387,7 +26387,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -26420,7 +26420,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26439,7 +26439,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -26475,7 +26475,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26494,7 +26494,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -26529,7 +26529,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26548,7 +26548,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -26578,7 +26578,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26597,7 +26597,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26656,7 +26656,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -26685,7 +26685,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26704,7 +26704,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -26737,7 +26737,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26756,7 +26756,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -26789,7 +26789,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26808,7 +26808,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -26844,7 +26844,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26863,7 +26863,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -26899,7 +26899,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -26918,7 +26918,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -26952,7 +26952,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -26971,7 +26971,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -27006,7 +27006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27025,7 +27025,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -27044,7 +27044,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27063,7 +27063,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -27084,7 +27084,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27103,7 +27103,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27155,7 +27155,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -27194,7 +27194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27213,7 +27213,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27232,7 +27232,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27251,7 +27251,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -27296,7 +27296,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -27335,7 +27335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -27364,7 +27364,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -27409,7 +27409,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -27454,7 +27454,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27473,7 +27473,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -27520,7 +27520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -27565,7 +27565,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27584,7 +27584,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -27607,7 +27607,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -27630,7 +27630,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -27653,7 +27653,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -27676,7 +27676,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -27699,7 +27699,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -27722,7 +27722,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -27745,7 +27745,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -27768,7 +27768,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -27791,7 +27791,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -27814,7 +27814,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -27837,7 +27837,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -27860,7 +27860,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -27881,7 +27881,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -27902,7 +27902,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -27923,7 +27923,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -27944,7 +27944,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -27965,7 +27965,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -27986,7 +27986,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28007,7 +28007,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -28030,7 +28030,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -28053,7 +28053,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -28076,7 +28076,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -28099,7 +28099,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -28122,7 +28122,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -28145,7 +28145,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -28168,7 +28168,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28187,7 +28187,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28206,7 +28206,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28225,7 +28225,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28244,7 +28244,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -28318,11 +28318,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -28354,7 +28353,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -28387,7 +28386,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -28420,7 +28419,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -28453,7 +28452,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -28486,7 +28485,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -28519,7 +28518,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -28552,7 +28551,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -28585,7 +28584,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28616,7 +28615,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28647,7 +28646,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -28680,7 +28679,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -28713,7 +28712,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -28746,7 +28745,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -28779,7 +28778,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -28812,7 +28811,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -28845,7 +28844,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -28878,7 +28877,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -28911,7 +28910,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -28944,7 +28943,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -28977,7 +28976,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -29010,7 +29009,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -29043,7 +29042,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -29076,7 +29075,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -29109,7 +29108,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -29142,7 +29141,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -29175,7 +29174,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -29207,7 +29206,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -29239,7 +29238,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -29271,7 +29270,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -29303,7 +29302,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -29335,7 +29334,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29365,7 +29364,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29395,7 +29394,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -29427,7 +29426,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -29459,7 +29458,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -29491,7 +29490,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -29523,7 +29522,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -29555,7 +29554,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29585,7 +29584,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -29617,7 +29616,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -29649,7 +29648,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -29681,7 +29680,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -29713,7 +29712,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -29743,7 +29742,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -29773,7 +29772,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -29803,7 +29802,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -29833,7 +29832,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -29865,7 +29864,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -29897,7 +29896,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -29927,7 +29926,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -29957,7 +29956,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -29987,7 +29986,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30017,7 +30016,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30047,7 +30046,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30142,11 +30141,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -30178,7 +30176,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30209,7 +30207,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30240,7 +30238,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30271,7 +30269,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30302,7 +30300,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30333,7 +30331,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30364,7 +30362,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30395,7 +30393,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30426,7 +30424,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30457,7 +30455,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30488,7 +30486,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30519,7 +30517,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30550,7 +30548,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30581,7 +30579,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30612,7 +30610,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30643,7 +30641,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -30674,7 +30672,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -30705,7 +30703,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -30736,7 +30734,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -30767,7 +30765,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -30797,7 +30795,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -30827,7 +30825,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -30857,7 +30855,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -30887,7 +30885,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -30917,7 +30915,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -30947,7 +30945,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30977,7 +30975,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31007,7 +31005,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31037,7 +31035,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31067,7 +31065,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31097,7 +31095,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31127,7 +31125,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31157,7 +31155,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31187,7 +31185,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31217,7 +31215,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31247,7 +31245,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -31279,7 +31277,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -31311,7 +31309,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31341,7 +31339,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31371,7 +31369,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31401,7 +31399,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31431,7 +31429,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31461,7 +31459,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53204,19 +53202,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53230,7 +53228,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -53242,7 +53240,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -53253,7 +53251,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -53264,7 +53262,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -53275,13 +53273,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6719,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -11777,54 +11777,54 @@
         <v>94098.32</v>
       </c>
       <c r="I42" s="52">
-        <v>34659.62</v>
+        <v>34818.98</v>
       </c>
       <c r="J42" s="52">
         <v>69042.09000000001</v>
       </c>
       <c r="K42" s="52">
-        <v>28340.06</v>
+        <v>28340.060000000005</v>
       </c>
       <c r="L42" s="52">
-        <v>40702.03000000001</v>
+        <v>40702.030000000006</v>
       </c>
       <c r="M42" s="53">
-        <v>0.5895248825752524</v>
+        <v>0.5895248825752523</v>
       </c>
       <c r="N42" s="53"/>
       <c r="O42" s="52">
         <v>25056.23</v>
       </c>
       <c r="P42" s="52">
-        <v>6319.56</v>
+        <v>6478.92</v>
       </c>
       <c r="Q42" s="52">
-        <v>18736.67</v>
+        <v>18577.309999999998</v>
       </c>
       <c r="R42" s="53">
-        <v>0.7477848822428593</v>
+        <v>0.7414247873682512</v>
       </c>
       <c r="S42" s="54">
         <v>501.83</v>
       </c>
       <c r="T42" s="54">
-        <v>123.75</v>
+        <v>127.75</v>
       </c>
       <c r="U42" s="54">
-        <v>378.08</v>
+        <v>374.08</v>
       </c>
       <c r="V42" s="53">
-        <v>0.7534025466791543</v>
+        <v>0.7454317199051471</v>
       </c>
       <c r="W42" s="53"/>
       <c r="X42" s="55">
-        <v>14.050666666666666</v>
+        <v>12.363287671232877</v>
       </c>
       <c r="Y42" s="55">
         <v>68.07122423898531</v>
       </c>
       <c r="Z42" s="53">
-        <v>0.0478</v>
+        <v>0.0434</v>
       </c>
       <c r="AA42" s="56">
         <v>0.2663</v>
@@ -12230,54 +12230,54 @@
         <v>50582.37</v>
       </c>
       <c r="I49" s="52">
-        <v>25131.9</v>
+        <v>25211.58</v>
       </c>
       <c r="J49" s="52">
         <v>39438.990000000005</v>
       </c>
       <c r="K49" s="52">
-        <v>20456.64</v>
+        <v>20456.640000000003</v>
       </c>
       <c r="L49" s="52">
-        <v>18982.350000000006</v>
+        <v>18982.350000000002</v>
       </c>
       <c r="M49" s="53">
-        <v>0.4813092323104624</v>
+        <v>0.4813092323104623</v>
       </c>
       <c r="N49" s="53"/>
       <c r="O49" s="52">
         <v>11143.38</v>
       </c>
       <c r="P49" s="52">
-        <v>4675.26</v>
+        <v>4754.94</v>
       </c>
       <c r="Q49" s="52">
-        <v>6468.119999999999</v>
+        <v>6388.44</v>
       </c>
       <c r="R49" s="53">
-        <v>0.5804450714235716</v>
+        <v>0.5732946377131535</v>
       </c>
       <c r="S49" s="54">
         <v>223.22</v>
       </c>
       <c r="T49" s="54">
-        <v>102.25</v>
+        <v>104.25</v>
       </c>
       <c r="U49" s="54">
-        <v>120.97</v>
+        <v>118.97</v>
       </c>
       <c r="V49" s="53">
-        <v>0.5419317265478004</v>
+        <v>0.5329719559179285</v>
       </c>
       <c r="W49" s="53"/>
       <c r="X49" s="55">
-        <v>1.8598533007334963</v>
+        <v>1.0598561151079136</v>
       </c>
       <c r="Y49" s="55">
         <v>67.69550512136009</v>
       </c>
       <c r="Z49" s="53">
-        <v>0.0075</v>
+        <v>0.0044</v>
       </c>
       <c r="AA49" s="56">
         <v>0.23</v>
@@ -12681,54 +12681,54 @@
         <v>108880.28</v>
       </c>
       <c r="I56" s="52">
-        <v>90918.83</v>
+        <v>91257.87</v>
       </c>
       <c r="J56" s="52">
         <v>74953.01000000001</v>
       </c>
       <c r="K56" s="52">
-        <v>71302.07</v>
+        <v>71042.06999999999</v>
       </c>
       <c r="L56" s="52">
-        <v>3650.9400000000023</v>
+        <v>3910.940000000017</v>
       </c>
       <c r="M56" s="53">
-        <v>0.04870971826214854</v>
+        <v>0.052178558272710014</v>
       </c>
       <c r="N56" s="53"/>
       <c r="O56" s="52">
         <v>33927.27</v>
       </c>
       <c r="P56" s="52">
-        <v>19616.76</v>
+        <v>20215.8</v>
       </c>
       <c r="Q56" s="52">
-        <v>14310.509999999998</v>
+        <v>13711.469999999998</v>
       </c>
       <c r="R56" s="53">
-        <v>0.4217996319774624</v>
+        <v>0.4041430389182507</v>
       </c>
       <c r="S56" s="54">
         <v>679.42</v>
       </c>
       <c r="T56" s="54">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="U56" s="54">
-        <v>266.41999999999996</v>
+        <v>252.41999999999996</v>
       </c>
       <c r="V56" s="53">
-        <v>0.39212858025963315</v>
+        <v>0.3715227694209767</v>
       </c>
       <c r="W56" s="53"/>
       <c r="X56" s="55">
-        <v>18.50767554479419</v>
+        <v>17.10686182669789</v>
       </c>
       <c r="Y56" s="55">
         <v>67.18600078134293</v>
       </c>
       <c r="Z56" s="53">
-        <v>0.0776</v>
+        <v>0.0741</v>
       </c>
       <c r="AA56" s="56">
         <v>0.2954</v>
@@ -13132,54 +13132,54 @@
         <v>15859.68</v>
       </c>
       <c r="I63" s="52">
-        <v>13601.05</v>
+        <v>13642</v>
       </c>
       <c r="J63" s="52">
         <v>12689.1</v>
       </c>
       <c r="K63" s="52">
-        <v>11685.13</v>
+        <v>11685.130000000001</v>
       </c>
       <c r="L63" s="52">
-        <v>1003.9700000000012</v>
+        <v>1003.9699999999993</v>
       </c>
       <c r="M63" s="53">
-        <v>0.07912066261594605</v>
+        <v>0.07912066261594591</v>
       </c>
       <c r="N63" s="53"/>
       <c r="O63" s="52">
         <v>3170.58</v>
       </c>
       <c r="P63" s="52">
-        <v>1915.92</v>
+        <v>1956.87</v>
       </c>
       <c r="Q63" s="52">
-        <v>1254.6599999999999</v>
+        <v>1213.71</v>
       </c>
       <c r="R63" s="53">
-        <v>0.39571939518952365</v>
+        <v>0.38280377722687964</v>
       </c>
       <c r="S63" s="54">
         <v>63.5</v>
       </c>
       <c r="T63" s="54">
-        <v>47.5</v>
+        <v>48.25</v>
       </c>
       <c r="U63" s="54">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="V63" s="53">
-        <v>0.25196850393700787</v>
+        <v>0.24015748031496062</v>
       </c>
       <c r="W63" s="53"/>
       <c r="X63" s="55">
-        <v>58.04884210526316</v>
+        <v>56.29782383419689</v>
       </c>
       <c r="Y63" s="55">
         <v>71.82495570677168</v>
       </c>
       <c r="Z63" s="53">
-        <v>0.1686</v>
+        <v>0.1661</v>
       </c>
       <c r="AA63" s="56">
         <v>0.2233</v>
@@ -13946,19 +13946,19 @@
         <v>54302.66</v>
       </c>
       <c r="I77" s="52">
-        <v>22353.17</v>
+        <v>25724.04</v>
       </c>
       <c r="J77" s="52">
         <v>31383.390000000003</v>
       </c>
       <c r="K77" s="52">
-        <v>22353.17</v>
+        <v>25724.04</v>
       </c>
       <c r="L77" s="52">
-        <v>9030.220000000005</v>
+        <v>5659.350000000002</v>
       </c>
       <c r="M77" s="53">
-        <v>0.28773883254804544</v>
+        <v>0.18032946727552382</v>
       </c>
       <c r="N77" s="53"/>
       <c r="O77" s="52">
@@ -14800,54 +14800,54 @@
         <v>27002.93</v>
       </c>
       <c r="I91" s="52">
-        <v>25996.77</v>
+        <v>26156.33</v>
       </c>
       <c r="J91" s="52">
         <v>15440.32</v>
       </c>
       <c r="K91" s="52">
-        <v>15990.78</v>
+        <v>16043.360000000002</v>
       </c>
       <c r="L91" s="52">
-        <v>-550.460000000001</v>
+        <v>-603.0400000000027</v>
       </c>
       <c r="M91" s="53">
-        <v>-0.0356508155271394</v>
+        <v>-0.03905618536403408</v>
       </c>
       <c r="N91" s="53"/>
       <c r="O91" s="52">
         <v>11562.61</v>
       </c>
       <c r="P91" s="52">
-        <v>10005.99</v>
+        <v>10112.97</v>
       </c>
       <c r="Q91" s="52">
-        <v>1556.6200000000008</v>
+        <v>1449.6400000000012</v>
       </c>
       <c r="R91" s="53">
-        <v>0.13462531383485224</v>
+        <v>0.12537307753180305</v>
       </c>
       <c r="S91" s="68">
         <v>231.75</v>
       </c>
       <c r="T91" s="68">
-        <v>204.75</v>
+        <v>207.25</v>
       </c>
       <c r="U91" s="54">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="V91" s="53">
-        <v>0.11650485436893204</v>
+        <v>0.10571736785329018</v>
       </c>
       <c r="W91" s="53"/>
       <c r="X91" s="55">
-        <v>34.316483516483515</v>
+        <v>33.13264173703257</v>
       </c>
       <c r="Y91" s="55">
         <v>43.49557070636461</v>
       </c>
       <c r="Z91" s="53">
-        <v>0.21280000000000002</v>
+        <v>0.2079</v>
       </c>
       <c r="AA91" s="56">
         <v>0.2718</v>
@@ -16067,54 +16067,54 @@
         <v>37601.88</v>
       </c>
       <c r="I112" s="52">
-        <v>38195.76</v>
+        <v>39781.27</v>
       </c>
       <c r="J112" s="52">
         <v>21415.85</v>
       </c>
       <c r="K112" s="52">
-        <v>19158.27</v>
+        <v>20554.529999999995</v>
       </c>
       <c r="L112" s="52">
-        <v>2257.579999999998</v>
+        <v>861.3200000000033</v>
       </c>
       <c r="M112" s="53">
-        <v>0.10541631548596009</v>
+        <v>0.04021880990014421</v>
       </c>
       <c r="N112" s="53"/>
       <c r="O112" s="52">
         <v>16186.03</v>
       </c>
       <c r="P112" s="52">
-        <v>19037.49</v>
+        <v>19226.74</v>
       </c>
       <c r="Q112" s="52">
-        <v>-2851.460000000001</v>
+        <v>-3040.710000000001</v>
       </c>
       <c r="R112" s="53">
-        <v>-0.1761679670678975</v>
+        <v>-0.1878601485354964</v>
       </c>
       <c r="S112" s="54">
         <v>324.19</v>
       </c>
       <c r="T112" s="54">
-        <v>412.5</v>
+        <v>417</v>
       </c>
       <c r="U112" s="54">
-        <v>-88.31</v>
+        <v>-92.81</v>
       </c>
       <c r="V112" s="53">
-        <v>-0.2724019864894044</v>
+        <v>-0.28628273543292515</v>
       </c>
       <c r="W112" s="53"/>
       <c r="X112" s="55">
-        <v>-6.6456484848484845</v>
+        <v>-10.37611510791367</v>
       </c>
       <c r="Y112" s="55">
         <v>65.70431400737223</v>
       </c>
       <c r="Z112" s="53">
-        <v>-0.07730000000000001</v>
+        <v>-0.122</v>
       </c>
       <c r="AA112" s="56">
         <v>0.3616</v>
@@ -16894,34 +16894,34 @@
         <v>95</v>
       </c>
       <c r="D126" s="52">
-        <v>99768.39</v>
+        <v>100987.51</v>
       </c>
       <c r="E126" s="52">
         <v>15366.74</v>
       </c>
       <c r="F126" s="52">
-        <v>84401.65</v>
+        <v>85620.76999999999</v>
       </c>
       <c r="G126" s="53">
-        <v>0.8459758647002321</v>
+        <v>0.8478352421997531</v>
       </c>
       <c r="H126" s="52">
-        <v>81719.58</v>
+        <v>82694.87</v>
       </c>
       <c r="I126" s="52">
         <v>18551.86</v>
       </c>
       <c r="J126" s="52">
-        <v>67238.96</v>
+        <v>68214.25</v>
       </c>
       <c r="K126" s="52">
         <v>14369.1</v>
       </c>
       <c r="L126" s="52">
-        <v>52869.86000000001</v>
+        <v>53845.15</v>
       </c>
       <c r="M126" s="53">
-        <v>0.7862980034194461</v>
+        <v>0.7893533975672239</v>
       </c>
       <c r="N126" s="53"/>
       <c r="O126" s="52">
@@ -16953,13 +16953,13 @@
         <v>-34.715204359673024</v>
       </c>
       <c r="Y126" s="55">
-        <v>62.2051177714286</v>
+        <v>63.04545035767707</v>
       </c>
       <c r="Z126" s="53">
         <v>-0.2073</v>
       </c>
       <c r="AA126" s="56">
-        <v>0.1809</v>
+        <v>0.1811</v>
       </c>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
@@ -17252,7 +17252,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -17724,19 +17724,19 @@
         <v>22587.89</v>
       </c>
       <c r="I140" s="52">
-        <v>25550.31</v>
+        <v>25625.28</v>
       </c>
       <c r="J140" s="52">
         <v>12565.06</v>
       </c>
       <c r="K140" s="52">
-        <v>11750.840000000002</v>
+        <v>11825.81</v>
       </c>
       <c r="L140" s="52">
-        <v>814.2199999999975</v>
+        <v>739.25</v>
       </c>
       <c r="M140" s="53">
-        <v>0.06480032725669416</v>
+        <v>0.05883378193180136</v>
       </c>
       <c r="N140" s="53"/>
       <c r="O140" s="52">
@@ -17765,13 +17765,13 @@
       </c>
       <c r="W140" s="53"/>
       <c r="X140" s="55">
-        <v>18.68438454627134</v>
+        <v>18.414950584007187</v>
       </c>
       <c r="Y140" s="55">
         <v>40.64013272149188</v>
       </c>
       <c r="Z140" s="53">
-        <v>0.1691</v>
+        <v>0.1666</v>
       </c>
       <c r="AA140" s="56">
         <v>0.2654</v>
@@ -22964,7 +22964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22978,7 +22978,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -23000,7 +23000,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -23066,7 +23066,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -23113,7 +23113,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -23130,7 +23130,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23197,7 +23197,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23257,7 +23257,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23321,7 +23321,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23386,7 +23386,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -23397,10 +23397,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="52">
-        <v>2138.1600000000035</v>
+        <v>2297.520000000004</v>
       </c>
       <c r="E14" s="52">
-        <v>-2138.1600000000035</v>
+        <v>-2297.520000000004</v>
       </c>
       <c r="F14" s="52">
         <v>0</v>
@@ -23424,16 +23424,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="52">
-        <v>-5138.1600000000035</v>
+        <v>-5297.520000000004</v>
       </c>
       <c r="N14" s="54">
         <v>-112</v>
       </c>
       <c r="O14" s="58">
-        <v>45.876428571428605</v>
-      </c>
-    </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>47.29928571428575</v>
+      </c>
+    </row>
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23450,7 +23450,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -23461,10 +23461,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="52">
-        <v>5565.0300000000025</v>
+        <v>5644.710000000003</v>
       </c>
       <c r="E16" s="52">
-        <v>-5565.0300000000025</v>
+        <v>-5644.710000000003</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="53">
@@ -23486,16 +23486,16 @@
         <v>0</v>
       </c>
       <c r="M16" s="52">
-        <v>-8565.030000000002</v>
+        <v>-8644.710000000003</v>
       </c>
       <c r="N16" s="54">
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
-        <v>98.73233429394816</v>
-      </c>
-    </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>99.65083573487036</v>
+      </c>
+    </row>
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23512,7 +23512,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -23523,10 +23523,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="52">
-        <v>10982.64</v>
+        <v>11321.679999999993</v>
       </c>
       <c r="E18" s="52">
-        <v>-10982.64</v>
+        <v>-11321.679999999993</v>
       </c>
       <c r="F18" s="52">
         <v>0</v>
@@ -23550,19 +23550,19 @@
         <v>0</v>
       </c>
       <c r="M18" s="52">
-        <v>-19182.64</v>
+        <v>-19521.679999999993</v>
       </c>
       <c r="N18" s="54">
         <v>-269</v>
       </c>
       <c r="O18" s="58">
-        <v>101.49544973544974</v>
+        <v>103.28931216931213</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23579,7 +23579,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -23590,10 +23590,10 @@
         <v>0</v>
       </c>
       <c r="D20" s="52">
-        <v>1407.8799999999992</v>
+        <v>1448.83</v>
       </c>
       <c r="E20" s="52">
-        <v>-1407.8799999999992</v>
+        <v>-1448.83</v>
       </c>
       <c r="F20" s="52"/>
       <c r="G20" s="53">
@@ -23611,14 +23611,14 @@
         <v>0</v>
       </c>
       <c r="M20" s="52">
-        <v>-1407.8799999999992</v>
+        <v>-1448.83</v>
       </c>
       <c r="N20" s="54"/>
       <c r="O20" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23635,7 +23635,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23693,7 +23693,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -23704,10 +23704,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="52">
-        <v>22353.17</v>
+        <v>25724.04</v>
       </c>
       <c r="E24" s="52">
-        <v>-22353.17</v>
+        <v>-25724.04</v>
       </c>
       <c r="F24" s="52"/>
       <c r="G24" s="53">
@@ -23723,14 +23723,14 @@
         <v>0</v>
       </c>
       <c r="M24" s="52">
-        <v>-22353.17</v>
+        <v>-25724.04</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23747,7 +23747,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23809,7 +23809,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="52">
-        <v>4476.1500000000015</v>
+        <v>4635.710000000003</v>
       </c>
       <c r="E28" s="52">
-        <v>-4476.1500000000015</v>
+        <v>-4635.710000000003</v>
       </c>
       <c r="F28" s="52">
         <v>0</v>
@@ -23843,16 +23843,16 @@
         <v>0</v>
       </c>
       <c r="M28" s="52">
-        <v>-4476.1500000000015</v>
+        <v>-4635.710000000003</v>
       </c>
       <c r="N28" s="54">
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
-        <v>30.14242424242425</v>
-      </c>
-    </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31.216902356902377</v>
+      </c>
+    </row>
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23869,7 +23869,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23929,7 +23929,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -23976,7 +23976,7 @@
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23993,7 +23993,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24004,16 +24004,16 @@
         <v>-35454.43</v>
       </c>
       <c r="D34" s="52">
-        <v>16334.04</v>
+        <v>17919.549999999996</v>
       </c>
       <c r="E34" s="52">
-        <v>-51788.47</v>
+        <v>-53373.979999999996</v>
       </c>
       <c r="F34" s="52">
         <v>0</v>
       </c>
       <c r="G34" s="53">
-        <v>1.4607051925528065</v>
+        <v>1.5054248509988737</v>
       </c>
       <c r="H34" s="53">
         <v>0.364182044343228</v>
@@ -24026,19 +24026,19 @@
         <v>0</v>
       </c>
       <c r="L34" s="53">
-        <v>1.4607051925528065</v>
+        <v>1.5054248509988737</v>
       </c>
       <c r="M34" s="52">
-        <v>-51788.47</v>
+        <v>-53373.979999999996</v>
       </c>
       <c r="N34" s="54">
         <v>-204.75</v>
       </c>
       <c r="O34" s="58">
-        <v>252.9351404151404</v>
-      </c>
-    </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>260.67877899877897</v>
+      </c>
+    </row>
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -24055,7 +24055,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24115,7 +24115,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24173,7 +24173,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24235,7 +24235,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24246,14 +24246,14 @@
         <v>3554.300000000003</v>
       </c>
       <c r="D42" s="52">
-        <v>584.890000000003</v>
+        <v>659.8600000000006</v>
       </c>
       <c r="E42" s="52">
-        <v>2969.41</v>
+        <v>2894.4400000000023</v>
       </c>
       <c r="F42" s="52"/>
       <c r="G42" s="53">
-        <v>0.8354415778071624</v>
+        <v>0.8143488169259769</v>
       </c>
       <c r="H42" s="53">
         <v>0.257245709794332</v>
@@ -24266,19 +24266,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="53">
-        <v>0.8354415778071624</v>
+        <v>0.8143488169259769</v>
       </c>
       <c r="M42" s="52">
-        <v>2969.41</v>
+        <v>2894.4400000000023</v>
       </c>
       <c r="N42" s="54">
         <v>-266.75</v>
       </c>
       <c r="O42" s="58">
-        <v>-11.131808809746953</v>
-      </c>
-    </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-10.850759137769456</v>
+      </c>
+    </row>
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24295,7 +24295,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24349,7 +24349,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24407,7 +24407,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -24450,7 +24450,7 @@
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24467,7 +24467,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -24509,7 +24509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24526,7 +24526,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24588,7 +24588,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24650,7 +24650,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -24695,7 +24695,7 @@
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24712,7 +24712,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24766,7 +24766,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -24783,7 +24783,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24800,7 +24800,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -24821,7 +24821,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24838,7 +24838,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24941,7 +24941,7 @@
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -24958,7 +24958,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -24975,7 +24975,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -24986,22 +24986,22 @@
         <v>3865.1700000000037</v>
       </c>
       <c r="D69" s="104">
-        <v>180905.65</v>
+        <v>186715.58999999997</v>
       </c>
       <c r="E69" s="105">
-        <v>-177040.47999999995</v>
+        <v>-182850.41999999998</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>122</v>
       </c>
       <c r="G69" s="107">
-        <v>-45.80406036474457</v>
+        <v>-47.30721287808811</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>123</v>
       </c>
       <c r="I69" s="109">
-        <v>-57.17810083385718</v>
+        <v>-58.68125334720071</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -25010,7 +25010,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -25393,7 +25393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25404,7 +25404,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25425,7 +25425,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -25487,7 +25487,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -25545,7 +25545,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25598,7 +25598,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -25632,7 +25632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25651,7 +25651,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25704,7 +25704,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25759,7 +25759,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25797,7 +25797,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25816,7 +25816,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -25827,10 +25827,10 @@
         <v>501.83</v>
       </c>
       <c r="D14" s="54">
-        <v>123.75</v>
+        <v>127.75</v>
       </c>
       <c r="E14" s="54">
-        <v>378.08</v>
+        <v>374.08</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -25854,7 +25854,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25873,7 +25873,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -25884,10 +25884,10 @@
         <v>223.22</v>
       </c>
       <c r="D16" s="54">
-        <v>102.25</v>
+        <v>104.25</v>
       </c>
       <c r="E16" s="54">
-        <v>120.97</v>
+        <v>118.97</v>
       </c>
       <c r="F16" s="54"/>
       <c r="G16" s="54"/>
@@ -25906,7 +25906,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25925,7 +25925,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -25936,10 +25936,10 @@
         <v>679.42</v>
       </c>
       <c r="D18" s="54">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E18" s="54">
-        <v>266.41999999999996</v>
+        <v>252.41999999999996</v>
       </c>
       <c r="F18" s="54"/>
       <c r="G18" s="54"/>
@@ -25958,7 +25958,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -25977,7 +25977,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -25988,10 +25988,10 @@
         <v>63.5</v>
       </c>
       <c r="D20" s="54">
-        <v>47.5</v>
+        <v>48.25</v>
       </c>
       <c r="E20" s="54">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="F20" s="54"/>
       <c r="G20" s="54"/>
@@ -26008,7 +26008,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26027,7 +26027,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -26062,7 +26062,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26081,7 +26081,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -26114,7 +26114,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26133,7 +26133,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -26164,7 +26164,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26183,7 +26183,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -26194,10 +26194,10 @@
         <v>231.75</v>
       </c>
       <c r="D28" s="54">
-        <v>204.75</v>
+        <v>207.25</v>
       </c>
       <c r="E28" s="54">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="F28" s="54"/>
       <c r="G28" s="54"/>
@@ -26215,7 +26215,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26234,7 +26234,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -26270,7 +26270,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26289,7 +26289,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -26318,7 +26318,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26337,7 +26337,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -26348,10 +26348,10 @@
         <v>324.19</v>
       </c>
       <c r="D34" s="54">
-        <v>412.5</v>
+        <v>417</v>
       </c>
       <c r="E34" s="54">
-        <v>-88.31</v>
+        <v>-92.81</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
@@ -26368,7 +26368,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26387,7 +26387,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -26420,7 +26420,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26439,7 +26439,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -26475,7 +26475,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26494,7 +26494,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -26529,7 +26529,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26548,7 +26548,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -26578,7 +26578,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26597,7 +26597,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26656,7 +26656,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -26685,7 +26685,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26704,7 +26704,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -26737,7 +26737,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26756,7 +26756,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -26789,7 +26789,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26808,7 +26808,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -26844,7 +26844,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26863,7 +26863,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -26899,7 +26899,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -26918,7 +26918,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -26952,7 +26952,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -26971,7 +26971,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -27006,7 +27006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27025,7 +27025,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -27044,7 +27044,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27063,7 +27063,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -27084,7 +27084,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27103,7 +27103,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27155,7 +27155,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -27194,7 +27194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27213,7 +27213,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27232,7 +27232,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27251,7 +27251,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -27296,7 +27296,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -27335,7 +27335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -27364,7 +27364,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -27409,7 +27409,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -27454,7 +27454,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27473,7 +27473,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -27520,7 +27520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -27565,7 +27565,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27584,7 +27584,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -27607,7 +27607,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -27630,7 +27630,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -27653,7 +27653,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -27676,7 +27676,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -27699,7 +27699,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -27722,7 +27722,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -27745,7 +27745,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -27768,7 +27768,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -27791,7 +27791,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -27814,7 +27814,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -27837,7 +27837,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -27860,7 +27860,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -27881,7 +27881,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -27902,7 +27902,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -27923,7 +27923,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -27944,7 +27944,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -27965,7 +27965,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -27986,7 +27986,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28007,7 +28007,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -28030,7 +28030,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -28053,7 +28053,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -28076,7 +28076,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -28099,7 +28099,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -28122,7 +28122,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -28145,7 +28145,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -28168,7 +28168,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28187,7 +28187,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28206,7 +28206,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28225,7 +28225,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28244,7 +28244,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -28318,10 +28318,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -28353,7 +28354,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -28386,7 +28387,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -28419,7 +28420,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -28452,7 +28453,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -28485,7 +28486,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -28518,7 +28519,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -28551,7 +28552,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -28584,7 +28585,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28615,7 +28616,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28646,7 +28647,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -28679,7 +28680,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -28712,7 +28713,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -28745,7 +28746,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -28778,7 +28779,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -28811,7 +28812,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -28844,7 +28845,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -28877,7 +28878,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -28910,7 +28911,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -28943,7 +28944,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -28976,7 +28977,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -29009,7 +29010,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -29042,7 +29043,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -29075,7 +29076,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -29108,7 +29109,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -29141,7 +29142,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -29174,7 +29175,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -29206,7 +29207,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -29238,7 +29239,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -29270,7 +29271,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -29302,7 +29303,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -29334,7 +29335,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29364,7 +29365,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29394,7 +29395,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -29426,7 +29427,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -29458,7 +29459,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -29490,7 +29491,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -29522,7 +29523,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -29554,7 +29555,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29584,7 +29585,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -29616,7 +29617,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -29648,7 +29649,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -29680,7 +29681,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -29712,7 +29713,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -29742,7 +29743,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -29772,7 +29773,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -29802,7 +29803,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -29832,7 +29833,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -29864,7 +29865,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -29896,7 +29897,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -29926,7 +29927,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -29956,7 +29957,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -29986,7 +29987,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30016,7 +30017,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30046,7 +30047,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30141,10 +30142,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -30176,7 +30178,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30207,7 +30209,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30238,7 +30240,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30269,7 +30271,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30300,7 +30302,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30331,7 +30333,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30362,7 +30364,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30393,7 +30395,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30424,7 +30426,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30455,7 +30457,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30486,7 +30488,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30517,7 +30519,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30548,7 +30550,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30579,7 +30581,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30610,7 +30612,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30641,7 +30643,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -30672,7 +30674,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -30703,7 +30705,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -30734,7 +30736,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -30765,7 +30767,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -30795,7 +30797,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -30825,7 +30827,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -30855,7 +30857,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -30885,7 +30887,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -30915,7 +30917,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -30945,7 +30947,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30975,7 +30977,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31005,7 +31007,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31035,7 +31037,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31065,7 +31067,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31095,7 +31097,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31125,7 +31127,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31155,7 +31157,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31185,7 +31187,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31215,7 +31217,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31245,7 +31247,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -31277,7 +31279,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -31309,7 +31311,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31339,7 +31341,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31369,7 +31371,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31399,7 +31401,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31429,7 +31431,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31459,7 +31461,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53202,19 +53204,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53228,7 +53230,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -53240,7 +53242,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -53251,7 +53253,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -53262,7 +53264,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -53273,13 +53275,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -17252,7 +17252,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -22964,7 +22964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22978,7 +22978,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -23000,7 +23000,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -23066,7 +23066,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -23092,10 +23092,10 @@
         <v>0.2149</v>
       </c>
       <c r="I4" s="86">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J4" s="87">
-        <v>90</v>
+        <v>5000</v>
       </c>
       <c r="K4" s="52">
         <v>90</v>
@@ -23113,7 +23113,7 @@
         <v>-2588.8525</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -23130,7 +23130,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -23197,7 +23197,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>34.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -23257,7 +23257,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>40.40408523144744</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23321,7 +23321,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23386,7 +23386,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -23433,7 +23433,7 @@
         <v>47.29928571428575</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23450,7 +23450,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>99.65083573487036</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23512,7 +23512,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23579,7 +23579,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -23618,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23635,7 +23635,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23693,7 +23693,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23747,7 +23747,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>-1.343804537521815</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23809,7 +23809,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>31.216902356902377</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23869,7 +23869,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23929,7 +23929,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -23976,7 +23976,7 @@
         <v>5.481184600197436</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23993,7 +23993,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>260.67877899877897</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -24055,7 +24055,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -24115,7 +24115,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24156,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -24173,7 +24173,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -24235,7 +24235,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>-10.850759137769456</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24295,7 +24295,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24349,7 +24349,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24407,7 +24407,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -24450,7 +24450,7 @@
         <v>-179.4969832402235</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24467,7 +24467,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -24509,7 +24509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24526,7 +24526,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>79.30441796516956</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24588,7 +24588,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24650,7 +24650,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -24695,7 +24695,7 @@
         <v>-120.76000000000003</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24712,7 +24712,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24766,7 +24766,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -24783,7 +24783,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24800,7 +24800,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -24821,7 +24821,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24838,7 +24838,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24941,7 +24941,7 @@
         <v>6.191319240032102</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -24958,7 +24958,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -24975,7 +24975,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -25010,7 +25010,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -25393,7 +25393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25404,7 +25404,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25425,7 +25425,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -25487,7 +25487,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -25545,7 +25545,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25598,7 +25598,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -25632,7 +25632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25651,7 +25651,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25704,7 +25704,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25759,7 +25759,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25797,7 +25797,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25816,7 +25816,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -25854,7 +25854,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25873,7 +25873,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -25906,7 +25906,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25925,7 +25925,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -25958,7 +25958,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -25977,7 +25977,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -26008,7 +26008,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -26027,7 +26027,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -26062,7 +26062,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -26081,7 +26081,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -26114,7 +26114,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -26133,7 +26133,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -26164,7 +26164,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -26183,7 +26183,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -26215,7 +26215,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -26234,7 +26234,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -26270,7 +26270,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26289,7 +26289,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -26318,7 +26318,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26337,7 +26337,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -26368,7 +26368,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26387,7 +26387,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -26420,7 +26420,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26439,7 +26439,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -26475,7 +26475,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26494,7 +26494,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -26529,7 +26529,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26548,7 +26548,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -26578,7 +26578,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26597,7 +26597,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26656,7 +26656,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -26685,7 +26685,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26704,7 +26704,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -26737,7 +26737,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26756,7 +26756,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -26789,7 +26789,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26808,7 +26808,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -26844,7 +26844,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26863,7 +26863,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -26899,7 +26899,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -26918,7 +26918,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -26952,7 +26952,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -26971,7 +26971,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -27006,7 +27006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -27025,7 +27025,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -27044,7 +27044,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -27063,7 +27063,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -27084,7 +27084,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -27103,7 +27103,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -27155,7 +27155,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -27194,7 +27194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -27213,7 +27213,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27232,7 +27232,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -27251,7 +27251,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -27296,7 +27296,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -27335,7 +27335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -27364,7 +27364,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -27409,7 +27409,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -27454,7 +27454,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -27473,7 +27473,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -27520,7 +27520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -27565,7 +27565,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -27584,7 +27584,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -27607,7 +27607,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -27630,7 +27630,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -27653,7 +27653,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -27676,7 +27676,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -27699,7 +27699,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -27722,7 +27722,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -27745,7 +27745,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -27768,7 +27768,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -27791,7 +27791,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -27814,7 +27814,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -27837,7 +27837,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -27860,7 +27860,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -27881,7 +27881,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -27902,7 +27902,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -27923,7 +27923,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -27944,7 +27944,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -27965,7 +27965,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -27986,7 +27986,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -28007,7 +28007,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -28030,7 +28030,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -28053,7 +28053,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -28076,7 +28076,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -28099,7 +28099,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -28122,7 +28122,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -28145,7 +28145,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -28168,7 +28168,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -28187,7 +28187,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -28206,7 +28206,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -28225,7 +28225,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -28244,7 +28244,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -28318,11 +28318,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -28354,7 +28353,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -28387,7 +28386,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -28420,7 +28419,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -28453,7 +28452,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -28486,7 +28485,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -28519,7 +28518,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -28552,7 +28551,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -28585,7 +28584,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -28616,7 +28615,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -28647,7 +28646,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -28680,7 +28679,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -28713,7 +28712,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -28746,7 +28745,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -28779,7 +28778,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -28812,7 +28811,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -28845,7 +28844,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -28878,7 +28877,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -28911,7 +28910,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -28944,7 +28943,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -28977,7 +28976,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -29010,7 +29009,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -29043,7 +29042,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -29076,7 +29075,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -29109,7 +29108,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -29142,7 +29141,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -29175,7 +29174,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -29207,7 +29206,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -29239,7 +29238,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -29271,7 +29270,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -29303,7 +29302,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -29335,7 +29334,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -29365,7 +29364,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -29395,7 +29394,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -29427,7 +29426,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -29459,7 +29458,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -29491,7 +29490,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -29523,7 +29522,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -29555,7 +29554,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -29585,7 +29584,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -29617,7 +29616,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -29649,7 +29648,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -29681,7 +29680,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -29713,7 +29712,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -29743,7 +29742,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -29773,7 +29772,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -29803,7 +29802,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -29833,7 +29832,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -29865,7 +29864,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -29897,7 +29896,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -29927,7 +29926,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -29957,7 +29956,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -29987,7 +29986,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -30017,7 +30016,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -30047,7 +30046,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -30142,11 +30141,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -30178,7 +30176,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -30209,7 +30207,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -30240,7 +30238,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -30271,7 +30269,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -30302,7 +30300,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -30333,7 +30331,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -30364,7 +30362,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -30395,7 +30393,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -30426,7 +30424,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -30457,7 +30455,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -30488,7 +30486,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -30519,7 +30517,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -30550,7 +30548,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -30581,7 +30579,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -30612,7 +30610,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -30643,7 +30641,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -30674,7 +30672,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -30705,7 +30703,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -30736,7 +30734,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -30767,7 +30765,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -30797,7 +30795,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -30827,7 +30825,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -30857,7 +30855,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -30887,7 +30885,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -30917,7 +30915,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -30947,7 +30945,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30977,7 +30975,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -31007,7 +31005,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -31037,7 +31035,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -31067,7 +31065,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -31097,7 +31095,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -31127,7 +31125,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -31157,7 +31155,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -31187,7 +31185,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -31217,7 +31215,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -31247,7 +31245,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -31279,7 +31277,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -31311,7 +31309,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -31341,7 +31339,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -31371,7 +31369,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -31401,7 +31399,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -31431,7 +31429,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -31461,7 +31459,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -53204,19 +53202,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -53230,7 +53228,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -53242,7 +53240,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -53253,7 +53251,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -53264,7 +53262,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -53275,13 +53273,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -23156,7 +23156,7 @@
         <v>0.239214585617637</v>
       </c>
       <c r="I6" s="54">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J6" s="52">
         <v>272.6</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -23147,7 +23147,7 @@
         <v>-1879.1500000000015</v>
       </c>
       <c r="F6" s="52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="53">
         <v>-0.4803553169734155</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6724,8 +6724,8 @@
       <c r="F32" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="14">
-        <v>45979</v>
+      <c r="G32" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>27</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -23946,7 +23946,7 @@
         <v>1171.8899999999994</v>
       </c>
       <c r="F32" s="52">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G32" s="53">
         <v>0</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6725,7 +6725,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>27</v>
@@ -23946,7 +23946,7 @@
         <v>1171.8899999999994</v>
       </c>
       <c r="F32" s="52">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G32" s="53">
         <v>0</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6725,7 +6725,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>27</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6719,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -21193,30 +21193,74 @@
       <c r="C183" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D183" s="52"/>
-      <c r="E183" s="52"/>
-      <c r="F183" s="52"/>
-      <c r="G183" s="53"/>
-      <c r="H183" s="52"/>
-      <c r="I183" s="52"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="52"/>
-      <c r="L183" s="52"/>
-      <c r="M183" s="53"/>
+      <c r="D183" s="52">
+        <v>16897.53</v>
+      </c>
+      <c r="E183" s="52">
+        <v>5491.7</v>
+      </c>
+      <c r="F183" s="52">
+        <v>11405.829999999998</v>
+      </c>
+      <c r="G183" s="53">
+        <v>0.6749998372543206</v>
+      </c>
+      <c r="H183" s="52">
+        <v>9226.27</v>
+      </c>
+      <c r="I183" s="52">
+        <v>3702.78</v>
+      </c>
+      <c r="J183" s="52">
+        <v>2977.1100000000006</v>
+      </c>
+      <c r="K183" s="52">
+        <v>2335.9700000000003</v>
+      </c>
+      <c r="L183" s="52">
+        <v>641.1400000000003</v>
+      </c>
+      <c r="M183" s="53">
+        <v>0.2153565034546927</v>
+      </c>
       <c r="N183" s="53"/>
-      <c r="O183" s="52"/>
-      <c r="P183" s="52"/>
-      <c r="Q183" s="52"/>
-      <c r="R183" s="53"/>
-      <c r="S183" s="54"/>
-      <c r="T183" s="54"/>
-      <c r="U183" s="54"/>
-      <c r="V183" s="53"/>
+      <c r="O183" s="52">
+        <v>6249.16</v>
+      </c>
+      <c r="P183" s="52">
+        <v>1366.81</v>
+      </c>
+      <c r="Q183" s="52">
+        <v>4882.35</v>
+      </c>
+      <c r="R183" s="53">
+        <v>0.7812810041669601</v>
+      </c>
+      <c r="S183" s="54">
+        <v>125.17</v>
+      </c>
+      <c r="T183" s="54">
+        <v>23.75</v>
+      </c>
+      <c r="U183" s="54">
+        <v>101.42</v>
+      </c>
+      <c r="V183" s="53">
+        <v>0.8102580490532876</v>
+      </c>
       <c r="W183" s="53"/>
-      <c r="X183" s="55"/>
-      <c r="Y183" s="55"/>
-      <c r="Z183" s="53"/>
-      <c r="AA183" s="56"/>
+      <c r="X183" s="55">
+        <v>75.32294736842105</v>
+      </c>
+      <c r="Y183" s="55">
+        <v>61.286703843093385</v>
+      </c>
+      <c r="Z183" s="53">
+        <v>0.3257</v>
+      </c>
+      <c r="AA183" s="56">
+        <v>0.454</v>
+      </c>
       <c r="AB183" s="57"/>
       <c r="AD183" s="35"/>
       <c r="AE183" s="35"/>
@@ -21596,32 +21640,74 @@
       <c r="C190" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D190" s="52"/>
-      <c r="E190" s="52"/>
-      <c r="F190" s="52"/>
-      <c r="G190" s="53"/>
-      <c r="H190" s="52"/>
-      <c r="I190" s="52"/>
-      <c r="J190" s="52"/>
+      <c r="D190" s="52">
+        <v>20992.12</v>
+      </c>
+      <c r="E190" s="52">
+        <v>14169.68</v>
+      </c>
+      <c r="F190" s="52">
+        <v>6822.439999999999</v>
+      </c>
+      <c r="G190" s="53">
+        <v>0.32500004763692275</v>
+      </c>
+      <c r="H190" s="52">
+        <v>16299.09</v>
+      </c>
+      <c r="I190" s="52">
+        <v>9699.51</v>
+      </c>
+      <c r="J190" s="52">
+        <v>9784.33</v>
+      </c>
       <c r="K190" s="52">
-        <v>0</v>
-      </c>
-      <c r="L190" s="52"/>
-      <c r="M190" s="53"/>
+        <v>8137.88</v>
+      </c>
+      <c r="L190" s="52">
+        <v>1646.4499999999998</v>
+      </c>
+      <c r="M190" s="53">
+        <v>0.16827416900288522</v>
+      </c>
       <c r="N190" s="53"/>
-      <c r="O190" s="52"/>
-      <c r="P190" s="52"/>
-      <c r="Q190" s="52"/>
-      <c r="R190" s="53"/>
-      <c r="S190" s="54"/>
-      <c r="T190" s="54"/>
-      <c r="U190" s="54"/>
-      <c r="V190" s="53"/>
+      <c r="O190" s="52">
+        <v>6514.76</v>
+      </c>
+      <c r="P190" s="52">
+        <v>1561.63</v>
+      </c>
+      <c r="Q190" s="52">
+        <v>4953.13</v>
+      </c>
+      <c r="R190" s="53">
+        <v>0.7602935488030257</v>
+      </c>
+      <c r="S190" s="54">
+        <v>130.62</v>
+      </c>
+      <c r="T190" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U190" s="54">
+        <v>95.87</v>
+      </c>
+      <c r="V190" s="53">
+        <v>0.7339611085591793</v>
+      </c>
       <c r="W190" s="53"/>
-      <c r="X190" s="55"/>
-      <c r="Y190" s="55"/>
-      <c r="Z190" s="53"/>
-      <c r="AA190" s="56"/>
+      <c r="X190" s="55">
+        <v>128.6379856115108</v>
+      </c>
+      <c r="Y190" s="55">
+        <v>35.92887828502527</v>
+      </c>
+      <c r="Z190" s="53">
+        <v>0.3155</v>
+      </c>
+      <c r="AA190" s="56">
+        <v>0.2236</v>
+      </c>
       <c r="AB190" s="57"/>
       <c r="AD190" s="35"/>
       <c r="AE190" s="35"/>
@@ -21995,32 +22081,74 @@
       <c r="C197" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D197" s="52"/>
-      <c r="E197" s="52"/>
-      <c r="F197" s="52"/>
-      <c r="G197" s="53"/>
-      <c r="H197" s="52"/>
-      <c r="I197" s="52"/>
-      <c r="J197" s="52"/>
+      <c r="D197" s="52">
+        <v>23770.95</v>
+      </c>
+      <c r="E197" s="52">
+        <v>10204.54</v>
+      </c>
+      <c r="F197" s="52">
+        <v>13566.41</v>
+      </c>
+      <c r="G197" s="53">
+        <v>0.5707138334816235</v>
+      </c>
+      <c r="H197" s="52">
+        <v>14310.96</v>
+      </c>
+      <c r="I197" s="52">
+        <v>6935.96</v>
+      </c>
+      <c r="J197" s="52">
+        <v>7389.339999999999</v>
+      </c>
       <c r="K197" s="52">
-        <v>0</v>
-      </c>
-      <c r="L197" s="52"/>
-      <c r="M197" s="53"/>
+        <v>6605.05</v>
+      </c>
+      <c r="L197" s="52">
+        <v>784.289999999999</v>
+      </c>
+      <c r="M197" s="53">
+        <v>0.1061380312720756</v>
+      </c>
       <c r="N197" s="53"/>
-      <c r="O197" s="52"/>
-      <c r="P197" s="52"/>
-      <c r="Q197" s="52"/>
-      <c r="R197" s="53"/>
-      <c r="S197" s="54"/>
-      <c r="T197" s="54"/>
-      <c r="U197" s="54"/>
-      <c r="V197" s="53"/>
+      <c r="O197" s="52">
+        <v>6921.62</v>
+      </c>
+      <c r="P197" s="52">
+        <v>330.91</v>
+      </c>
+      <c r="Q197" s="52">
+        <v>6590.71</v>
+      </c>
+      <c r="R197" s="53">
+        <v>0.9521918279246766</v>
+      </c>
+      <c r="S197" s="54">
+        <v>140.15</v>
+      </c>
+      <c r="T197" s="54">
+        <v>5.75</v>
+      </c>
+      <c r="U197" s="54">
+        <v>134.4</v>
+      </c>
+      <c r="V197" s="53">
+        <v>0.9589725294327506</v>
+      </c>
       <c r="W197" s="53"/>
-      <c r="X197" s="55"/>
-      <c r="Y197" s="55"/>
-      <c r="Z197" s="53"/>
-      <c r="AA197" s="56"/>
+      <c r="X197" s="55">
+        <v>568.4486956521739</v>
+      </c>
+      <c r="Y197" s="55">
+        <v>67.49902570438813</v>
+      </c>
+      <c r="Z197" s="53">
+        <v>0.32030000000000003</v>
+      </c>
+      <c r="AA197" s="56">
+        <v>0.398</v>
+      </c>
       <c r="AB197" s="57"/>
       <c r="AD197" s="35"/>
       <c r="AE197" s="35"/>
@@ -22968,30 +23096,74 @@
       <c r="C218" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D218" s="52"/>
-      <c r="E218" s="52"/>
-      <c r="F218" s="52"/>
-      <c r="G218" s="53"/>
-      <c r="H218" s="52"/>
-      <c r="I218" s="52"/>
-      <c r="J218" s="52"/>
-      <c r="K218" s="52"/>
-      <c r="L218" s="52"/>
-      <c r="M218" s="53"/>
+      <c r="D218" s="52">
+        <v>137109.56</v>
+      </c>
+      <c r="E218" s="52">
+        <v>30174.75</v>
+      </c>
+      <c r="F218" s="52">
+        <v>106934.81</v>
+      </c>
+      <c r="G218" s="53">
+        <v>0.7799223482301307</v>
+      </c>
+      <c r="H218" s="52">
+        <v>117394.57</v>
+      </c>
+      <c r="I218" s="52">
+        <v>26124</v>
+      </c>
+      <c r="J218" s="52">
+        <v>99479.62000000001</v>
+      </c>
+      <c r="K218" s="52">
+        <v>26124</v>
+      </c>
+      <c r="L218" s="52">
+        <v>73355.62000000001</v>
+      </c>
+      <c r="M218" s="53">
+        <v>0.7373934480248316</v>
+      </c>
       <c r="N218" s="53"/>
-      <c r="O218" s="52"/>
-      <c r="P218" s="52"/>
-      <c r="Q218" s="52"/>
-      <c r="R218" s="53"/>
-      <c r="S218" s="54"/>
-      <c r="T218" s="54"/>
-      <c r="U218" s="54"/>
-      <c r="V218" s="53"/>
+      <c r="O218" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="P218" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q218" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="R218" s="53">
+        <v>1</v>
+      </c>
+      <c r="S218" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="T218" s="54">
+        <v>0</v>
+      </c>
+      <c r="U218" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="V218" s="53">
+        <v>1</v>
+      </c>
       <c r="W218" s="53"/>
-      <c r="X218" s="55"/>
-      <c r="Y218" s="55"/>
-      <c r="Z218" s="53"/>
-      <c r="AA218" s="56"/>
+      <c r="X218" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y218" s="55">
+        <v>54.93783457863793</v>
+      </c>
+      <c r="Z218" s="53">
+        <v>0.13419999999999999</v>
+      </c>
+      <c r="AA218" s="56">
+        <v>0.1438</v>
+      </c>
       <c r="AB218" s="57"/>
       <c r="AD218" s="35"/>
       <c r="AE218" s="35"/>
@@ -23369,34 +23541,74 @@
       <c r="C225" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D225" s="52"/>
-      <c r="E225" s="52"/>
-      <c r="F225" s="52"/>
-      <c r="G225" s="53"/>
-      <c r="H225" s="52"/>
-      <c r="I225" s="52"/>
+      <c r="D225" s="52">
+        <v>396453.46</v>
+      </c>
+      <c r="E225" s="52">
+        <v>271388.15</v>
+      </c>
+      <c r="F225" s="52">
+        <v>125065.31</v>
+      </c>
+      <c r="G225" s="53">
+        <v>0.3154602560411504</v>
+      </c>
+      <c r="H225" s="52">
+        <v>295569.99</v>
+      </c>
+      <c r="I225" s="52">
+        <v>234322.81</v>
+      </c>
       <c r="J225" s="52">
-        <v>0</v>
+        <v>178700.37</v>
       </c>
       <c r="K225" s="52">
-        <v>0</v>
-      </c>
-      <c r="L225" s="52"/>
-      <c r="M225" s="53"/>
+        <v>177071.47999999998</v>
+      </c>
+      <c r="L225" s="52">
+        <v>1628.890000000014</v>
+      </c>
+      <c r="M225" s="53">
+        <v>0.009115202167740415</v>
+      </c>
       <c r="N225" s="53"/>
-      <c r="O225" s="52"/>
-      <c r="P225" s="52"/>
-      <c r="Q225" s="52"/>
-      <c r="R225" s="53"/>
-      <c r="S225" s="54"/>
-      <c r="T225" s="54"/>
-      <c r="U225" s="54"/>
-      <c r="V225" s="53"/>
+      <c r="O225" s="52">
+        <v>116869.62</v>
+      </c>
+      <c r="P225" s="52">
+        <v>57251.33</v>
+      </c>
+      <c r="Q225" s="52">
+        <v>59618.28999999999</v>
+      </c>
+      <c r="R225" s="53">
+        <v>0.5101264982293944</v>
+      </c>
+      <c r="S225" s="54">
+        <v>2344.68</v>
+      </c>
+      <c r="T225" s="54">
+        <v>1212</v>
+      </c>
+      <c r="U225" s="54">
+        <v>1132.6799999999998</v>
+      </c>
+      <c r="V225" s="53">
+        <v>0.48308511182762676</v>
+      </c>
       <c r="W225" s="53"/>
-      <c r="X225" s="55"/>
-      <c r="Y225" s="55"/>
-      <c r="Z225" s="53"/>
-      <c r="AA225" s="56"/>
+      <c r="X225" s="55">
+        <v>30.581963696369634</v>
+      </c>
+      <c r="Y225" s="55">
+        <v>43.0265399367206</v>
+      </c>
+      <c r="Z225" s="53">
+        <v>0.1366</v>
+      </c>
+      <c r="AA225" s="56">
+        <v>0.2545</v>
+      </c>
       <c r="AB225" s="57"/>
       <c r="AD225" s="35"/>
       <c r="AE225" s="35"/>
@@ -24013,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24027,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24049,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24097,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24115,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24162,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24179,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24199,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="53">
-        <v>0.2556317756411565</v>
+        <v>0.25548771651006935</v>
       </c>
       <c r="H6" s="53">
         <v>0.239214585617637</v>
@@ -24214,22 +24426,22 @@
         <v>1872.6</v>
       </c>
       <c r="L6" s="53">
-        <v>0.2016787498663849</v>
+        <v>0.20153469073529773</v>
       </c>
       <c r="M6" s="52">
-        <v>6999.8599999999915</v>
+        <v>6994.8599999999915</v>
       </c>
       <c r="N6" s="54">
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <v>-559.9887999999993</v>
+        <v>-559.5887999999993</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24246,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24289,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24306,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24353,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24370,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24418,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24435,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24482,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24499,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24544,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24561,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24611,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24628,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24667,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24684,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24725,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24742,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24779,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -24796,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24841,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -24858,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24901,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -24918,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24961,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -24978,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25025,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25042,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25087,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25104,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25147,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25164,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25205,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25222,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25267,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25284,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25327,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25344,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25381,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25398,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25439,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25456,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25499,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25516,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25558,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25575,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25620,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25637,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25682,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25699,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25710,14 +25922,14 @@
         <v>12937.1</v>
       </c>
       <c r="D56" s="99">
-        <v>4850.19</v>
+        <v>4794.2300000000005</v>
       </c>
       <c r="E56" s="99">
-        <v>8086.910000000001</v>
+        <v>8142.87</v>
       </c>
       <c r="F56" s="99"/>
       <c r="G56" s="100">
-        <v>0.6250944956752287</v>
+        <v>0.6294200400398853</v>
       </c>
       <c r="H56" s="100">
         <v>0.22356150784199</v>
@@ -25732,19 +25944,19 @@
         <v>5400</v>
       </c>
       <c r="L56" s="100">
-        <v>0.20769028607647777</v>
+        <v>0.2120158304411344</v>
       </c>
       <c r="M56" s="99">
-        <v>2686.9100000000008</v>
+        <v>2742.87</v>
       </c>
       <c r="N56" s="98">
         <v>-32.25</v>
       </c>
       <c r="O56" s="60">
-        <v>-120.76000000000003</v>
-      </c>
-    </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-123.27505617977528</v>
+      </c>
+    </row>
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25761,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -25769,17 +25981,17 @@
         <v>60</v>
       </c>
       <c r="C58" s="99">
-        <v>0</v>
+        <v>10204.54</v>
       </c>
       <c r="D58" s="99">
-        <v>6849.16</v>
+        <v>6605.05</v>
       </c>
       <c r="E58" s="99">
-        <v>-6849.16</v>
+        <v>3599.4900000000007</v>
       </c>
       <c r="F58" s="99"/>
       <c r="G58" s="100">
-        <v>0</v>
+        <v>0.35273417518085093</v>
       </c>
       <c r="H58" s="100"/>
       <c r="I58" s="98"/>
@@ -25788,17 +26000,17 @@
         <v>0</v>
       </c>
       <c r="L58" s="100">
-        <v>0</v>
+        <v>0.35273417518085093</v>
       </c>
       <c r="M58" s="99">
-        <v>-6849.16</v>
+        <v>3599.4900000000007</v>
       </c>
       <c r="N58" s="98"/>
       <c r="O58" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -25815,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -25832,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -25849,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -25870,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -25887,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -25895,17 +26107,17 @@
         <v>62</v>
       </c>
       <c r="C64" s="99">
-        <v>0</v>
+        <v>30174.75</v>
       </c>
       <c r="D64" s="99">
-        <v>1749.8</v>
+        <v>26124</v>
       </c>
       <c r="E64" s="99">
-        <v>-1749.8</v>
+        <v>4050.75</v>
       </c>
       <c r="F64" s="99"/>
       <c r="G64" s="100">
-        <v>0</v>
+        <v>0.13424303432505655</v>
       </c>
       <c r="H64" s="100">
         <v>0.143790046441692</v>
@@ -25918,17 +26130,17 @@
         <v>1750</v>
       </c>
       <c r="L64" s="100">
-        <v>0</v>
+        <v>0.07624752483450567</v>
       </c>
       <c r="M64" s="99">
-        <v>-3499.8</v>
+        <v>2300.75</v>
       </c>
       <c r="N64" s="98"/>
       <c r="O64" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -25945,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -25956,10 +26168,10 @@
         <v>0</v>
       </c>
       <c r="D66" s="99">
-        <v>2584.2399999999907</v>
+        <v>9863.48999999999</v>
       </c>
       <c r="E66" s="99">
-        <v>-2584.2399999999907</v>
+        <v>-9863.48999999999</v>
       </c>
       <c r="F66" s="99"/>
       <c r="G66" s="100">
@@ -25981,16 +26193,16 @@
         <v>0</v>
       </c>
       <c r="M66" s="99">
-        <v>-5784.239999999991</v>
+        <v>-13063.48999999999</v>
       </c>
       <c r="N66" s="98">
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
-        <v>6.191319240032102</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>13.982863259298894</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26007,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26024,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26032,25 +26244,25 @@
         <v>122</v>
       </c>
       <c r="C69" s="104">
-        <v>308475.47</v>
+        <v>348854.75999999995</v>
       </c>
       <c r="D69" s="104">
-        <v>345627.75999999995</v>
+        <v>376981.13999999996</v>
       </c>
       <c r="E69" s="105">
-        <v>-37152.289999999986</v>
+        <v>-28126.379999999983</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>123</v>
       </c>
       <c r="G69" s="107">
-        <v>-0.12043839336722621</v>
+        <v>-0.08062489960005129</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>124</v>
       </c>
       <c r="I69" s="109">
-        <v>-0.2884666647886135</v>
+        <v>-0.2292042109444056</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -26059,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26442,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26453,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26474,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26536,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26594,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26628,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26647,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26681,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26700,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26734,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26753,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -26789,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -26808,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -26846,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -26865,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -26903,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -26922,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -26955,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -26974,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27007,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27026,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27057,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27076,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27111,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27130,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27163,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27182,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27213,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27232,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27264,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27283,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27319,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27338,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27367,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27386,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27417,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27436,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27469,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27488,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27524,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27543,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27578,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27597,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27627,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27646,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27686,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27705,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27734,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27753,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27786,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -27805,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -27838,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -27857,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -27893,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -27912,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -27948,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -27967,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28001,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28020,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28055,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28074,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28093,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28112,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28133,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28152,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28185,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28204,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28212,13 +28424,13 @@
         <v>63</v>
       </c>
       <c r="C66" s="54">
-        <v>2312.68</v>
+        <v>2344.68</v>
       </c>
       <c r="D66" s="54">
-        <v>1120.5</v>
+        <v>1212</v>
       </c>
       <c r="E66" s="54">
-        <v>1192.1799999999998</v>
+        <v>1132.6799999999998</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>
@@ -28243,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28262,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28281,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28300,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28345,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28384,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28413,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28458,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28503,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28522,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28569,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28614,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28633,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28656,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28679,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28702,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28725,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28748,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28771,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -28794,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -28817,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -28840,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -28863,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -28886,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -28909,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -28930,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -28951,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -28972,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -28993,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29014,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29035,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29056,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29079,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29102,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29125,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29148,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29171,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29194,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29217,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29236,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29255,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29274,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29293,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29367,10 +29579,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29402,7 +29615,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29435,7 +29648,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29468,7 +29681,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29501,7 +29714,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29534,7 +29747,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29567,7 +29780,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29600,7 +29813,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29633,7 +29846,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29664,7 +29877,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29695,7 +29908,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29728,7 +29941,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29761,7 +29974,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -29794,7 +30007,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -29827,7 +30040,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -29860,7 +30073,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -29893,7 +30106,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -29926,7 +30139,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -29959,7 +30172,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -29992,7 +30205,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30025,7 +30238,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30058,7 +30271,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30091,7 +30304,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30124,7 +30337,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30157,7 +30370,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30190,7 +30403,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30223,7 +30436,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30255,7 +30468,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30287,7 +30500,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30319,7 +30532,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30351,7 +30564,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30383,7 +30596,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30413,7 +30626,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30443,7 +30656,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30475,7 +30688,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30507,7 +30720,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30539,7 +30752,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30571,7 +30784,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30603,7 +30816,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30633,7 +30846,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30665,7 +30878,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30697,7 +30910,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30729,7 +30942,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30761,7 +30974,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -30791,7 +31004,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -30821,7 +31034,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -30851,7 +31064,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -30881,7 +31094,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -30913,7 +31126,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -30945,7 +31158,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -30975,7 +31188,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31005,7 +31218,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31035,7 +31248,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31065,7 +31278,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31095,7 +31308,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31190,10 +31403,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31225,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31256,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31287,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31318,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31349,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31380,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31411,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31442,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31473,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31504,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31535,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31566,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31597,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31628,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31659,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31690,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31721,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31752,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31783,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -31814,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -31844,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -31874,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -31904,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -31934,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -31964,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -31994,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32024,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32054,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32084,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32114,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32144,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32174,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32204,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32234,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32264,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32294,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32326,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32358,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32388,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32418,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32448,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32478,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32508,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54251,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54277,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54289,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54300,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54311,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54322,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -27001,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,11 +29579,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29615,7 +29614,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29648,7 +29647,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29681,7 +29680,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29714,7 +29713,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29747,7 +29746,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29780,7 +29779,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29813,7 +29812,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29846,7 +29845,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29877,7 +29876,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29908,7 +29907,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29941,7 +29940,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29974,7 +29973,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30007,7 +30006,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30040,7 +30039,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30073,7 +30072,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30106,7 +30105,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30139,7 +30138,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30172,7 +30171,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30205,7 +30204,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30238,7 +30237,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30271,7 +30270,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30304,7 +30303,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30337,7 +30336,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30370,7 +30369,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30403,7 +30402,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30436,7 +30435,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30468,7 +30467,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30500,7 +30499,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30532,7 +30531,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30564,7 +30563,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30596,7 +30595,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30626,7 +30625,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30656,7 +30655,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30688,7 +30687,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30720,7 +30719,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30752,7 +30751,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30784,7 +30783,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30816,7 +30815,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30846,7 +30845,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30878,7 +30877,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30910,7 +30909,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30942,7 +30941,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30974,7 +30973,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31004,7 +31003,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31034,7 +31033,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31064,7 +31063,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31094,7 +31093,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31126,7 +31125,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31158,7 +31157,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31188,7 +31187,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31218,7 +31217,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31248,7 +31247,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31278,7 +31277,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31308,7 +31307,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31403,11 +31402,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31439,7 +31437,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31470,7 +31468,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31501,7 +31499,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31532,7 +31530,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31563,7 +31561,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31594,7 +31592,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31625,7 +31623,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31656,7 +31654,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31687,7 +31685,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31718,7 +31716,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31749,7 +31747,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31780,7 +31778,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31811,7 +31809,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31842,7 +31840,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31873,7 +31871,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31904,7 +31902,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31935,7 +31933,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31966,7 +31964,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31997,7 +31995,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32028,7 +32026,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32058,7 +32056,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32088,7 +32086,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32118,7 +32116,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32148,7 +32146,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32178,7 +32176,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32208,7 +32206,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32238,7 +32236,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32268,7 +32266,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32298,7 +32296,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32328,7 +32326,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32358,7 +32356,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32388,7 +32386,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32418,7 +32416,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32448,7 +32446,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32478,7 +32476,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32508,7 +32506,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32540,7 +32538,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32572,7 +32570,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32602,7 +32600,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32632,7 +32630,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32662,7 +32660,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32692,7 +32690,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32722,7 +32720,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54465,19 +54463,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54491,7 +54489,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54503,7 +54501,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54514,7 +54512,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54525,7 +54523,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54536,13 +54534,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -27001,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,10 +29579,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29614,7 +29615,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29647,7 +29648,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29680,7 +29681,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29713,7 +29714,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29746,7 +29747,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29779,7 +29780,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29812,7 +29813,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29845,7 +29846,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29876,7 +29877,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29907,7 +29908,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29940,7 +29941,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29973,7 +29974,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30006,7 +30007,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30039,7 +30040,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30072,7 +30073,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30105,7 +30106,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30138,7 +30139,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30171,7 +30172,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30204,7 +30205,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30237,7 +30238,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30270,7 +30271,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30303,7 +30304,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30336,7 +30337,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30369,7 +30370,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30402,7 +30403,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30435,7 +30436,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30467,7 +30468,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30499,7 +30500,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30531,7 +30532,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30563,7 +30564,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30595,7 +30596,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30625,7 +30626,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30655,7 +30656,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30687,7 +30688,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30719,7 +30720,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30751,7 +30752,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30783,7 +30784,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30815,7 +30816,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30845,7 +30846,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30877,7 +30878,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30909,7 +30910,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30941,7 +30942,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30973,7 +30974,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31003,7 +31004,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31033,7 +31034,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31063,7 +31064,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31093,7 +31094,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31125,7 +31126,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31157,7 +31158,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31187,7 +31188,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31217,7 +31218,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31247,7 +31248,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31277,7 +31278,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31307,7 +31308,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31402,10 +31403,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31437,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31468,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31499,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31530,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31561,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31592,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31623,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31654,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31685,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31716,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31747,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31778,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31809,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31840,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31871,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31902,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31933,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31964,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31995,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32026,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32056,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32086,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32116,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32146,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32176,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32206,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32236,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32266,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32296,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32326,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32356,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32386,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32416,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32446,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32476,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32506,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32538,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32570,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32600,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32630,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32660,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32690,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32720,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54463,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54489,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54501,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54512,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54523,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54534,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -26994,14 +26994,16 @@
       <c r="N10" s="54">
         <v>80</v>
       </c>
-      <c r="O10" s="54"/>
+      <c r="O10" s="54">
+        <v>0</v>
+      </c>
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27022,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27060,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27079,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27117,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27136,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27169,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27188,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27221,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27240,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27271,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27290,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27325,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27344,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27377,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27396,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27427,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27446,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27478,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27497,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27533,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27552,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27581,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27600,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27631,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27650,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27683,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27702,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27738,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27757,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27792,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27811,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27841,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27860,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27900,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27919,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27948,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27967,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +28000,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28019,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28052,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28071,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28107,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28126,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28162,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28181,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28215,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28234,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28269,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28288,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28307,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28326,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28347,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28366,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28399,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28418,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28457,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28476,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28495,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28514,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28559,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28598,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28627,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28672,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28717,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28736,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28828,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28847,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28870,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28893,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28916,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28939,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28962,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28985,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29008,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29031,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29054,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29077,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29100,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29123,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29144,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29165,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29186,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29207,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29228,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29249,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29270,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29293,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29316,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29339,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29362,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29385,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29408,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29431,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29450,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29469,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29488,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29507,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,11 +29581,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29615,7 +29616,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29648,7 +29649,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29681,7 +29682,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29714,7 +29715,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29747,7 +29748,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29780,7 +29781,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29813,7 +29814,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29846,7 +29847,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29877,7 +29878,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29908,7 +29909,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29941,7 +29942,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29974,7 +29975,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30007,7 +30008,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30040,7 +30041,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30073,7 +30074,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30106,7 +30107,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30139,7 +30140,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30172,7 +30173,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30205,7 +30206,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30238,7 +30239,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30271,7 +30272,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30304,7 +30305,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30337,7 +30338,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30370,7 +30371,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30403,7 +30404,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30436,7 +30437,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30468,7 +30469,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30500,7 +30501,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30532,7 +30533,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30564,7 +30565,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30596,7 +30597,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30626,7 +30627,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30656,7 +30657,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30688,7 +30689,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30720,7 +30721,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30752,7 +30753,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30784,7 +30785,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30816,7 +30817,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30846,7 +30847,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30878,7 +30879,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30910,7 +30911,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30942,7 +30943,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30974,7 +30975,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31004,7 +31005,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31034,7 +31035,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31064,7 +31065,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31094,7 +31095,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31126,7 +31127,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31158,7 +31159,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31188,7 +31189,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31218,7 +31219,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31248,7 +31249,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31278,7 +31279,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31308,7 +31309,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31403,11 +31404,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31439,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31470,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31501,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31532,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31563,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31594,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31625,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31656,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31687,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31718,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31749,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31780,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31811,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31842,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31873,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31904,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31935,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31966,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31997,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32028,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32058,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32088,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32118,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32148,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32178,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32208,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32238,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32268,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32298,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32328,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32358,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32388,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32418,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32448,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32478,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32508,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32540,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32572,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32602,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32632,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32662,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32692,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32722,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54465,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54491,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54503,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54514,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54525,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54536,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -6722,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>
@@ -6752,7 +6749,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6805,7 +6802,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6875,7 +6872,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6943,7 +6940,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7011,7 +7008,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7079,7 +7076,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7147,7 +7144,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7229,7 +7226,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7321,7 +7318,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7389,7 +7386,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7457,7 +7454,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7545,7 +7542,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7615,7 +7612,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7705,7 +7702,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7863,7 +7860,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7931,7 +7928,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -8001,7 +7998,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9391,79 +9388,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="E2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="I2" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="43" t="s">
+      <c r="P2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="43" t="s">
+      <c r="Q2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="R2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="S2" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="T2" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="U2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="45" t="s">
+      <c r="V2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="W2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="X2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="Y2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Z2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="AA2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AA2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9501,10 +9498,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AI3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9515,7 +9512,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>215046.91</v>
@@ -9589,7 +9586,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9605,7 +9602,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52">
         <v>233882.27</v>
@@ -9677,7 +9674,7 @@
       </c>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9689,7 +9686,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9725,7 +9722,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52">
         <v>233882.27</v>
@@ -9797,7 +9794,7 @@
       </c>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9809,7 +9806,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52">
         <v>245679.5</v>
@@ -9889,7 +9886,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9966,7 +9963,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="52">
         <v>95023.47</v>
@@ -10040,7 +10037,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -10056,7 +10053,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -10128,7 +10125,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10140,7 +10137,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10176,7 +10173,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="52">
         <v>129074.86</v>
@@ -10248,7 +10245,7 @@
       </c>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10260,7 +10257,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="52">
         <v>129074.86</v>
@@ -10340,7 +10337,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10417,7 +10414,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10491,7 +10488,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10507,7 +10504,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -10535,7 +10532,7 @@
       <c r="AA19" s="56"/>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10547,7 +10544,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10583,7 +10580,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52">
         <v>27500.32</v>
@@ -10655,7 +10652,7 @@
       </c>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10667,7 +10664,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52">
         <v>27500.32</v>
@@ -10747,7 +10744,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10824,7 +10821,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10900,7 +10897,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10916,7 +10913,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10988,7 +10985,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -11000,7 +10997,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -11036,7 +11033,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="55">
         <v>150850.82</v>
@@ -11108,7 +11105,7 @@
       </c>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -11120,7 +11117,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="55">
         <v>150850.82</v>
@@ -11200,7 +11197,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -11277,7 +11274,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>389022.03</v>
@@ -11351,7 +11348,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11367,7 +11364,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11439,7 +11436,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11451,7 +11448,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11487,7 +11484,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52">
         <v>396422.03</v>
@@ -11559,7 +11556,7 @@
       </c>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11571,7 +11568,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52">
         <v>396422.03</v>
@@ -11651,7 +11648,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11728,7 +11725,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11802,7 +11799,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11818,7 +11815,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11890,7 +11887,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11902,7 +11899,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52">
         <v>128258.5</v>
@@ -11982,7 +11979,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52">
         <v>128258.5</v>
@@ -12054,7 +12051,7 @@
       </c>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -12066,7 +12063,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52">
         <v>128258.5</v>
@@ -12146,7 +12143,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -12223,7 +12220,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>64305.21</v>
@@ -12299,7 +12296,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -12315,7 +12312,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -12387,7 +12384,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -12399,7 +12396,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52">
         <v>65693.36</v>
@@ -12479,7 +12476,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52">
         <v>65693.36</v>
@@ -12551,7 +12548,7 @@
       </c>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -12563,7 +12560,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52">
         <v>65693.36</v>
@@ -12643,7 +12640,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12720,7 +12717,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>150152.16</v>
@@ -12794,7 +12791,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12810,7 +12807,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>154527.79</v>
@@ -12882,7 +12879,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12894,7 +12891,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52">
         <v>154527.79</v>
@@ -12974,7 +12971,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52">
         <v>154527.79</v>
@@ -13046,7 +13043,7 @@
       </c>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -13058,7 +13055,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52">
         <v>155296.79</v>
@@ -13138,7 +13135,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -13215,7 +13212,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -13289,7 +13286,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -13305,7 +13302,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -13377,7 +13374,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -13389,7 +13386,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52">
         <v>20420.56</v>
@@ -13469,7 +13466,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52">
         <v>20420.56</v>
@@ -13541,7 +13538,7 @@
       </c>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -13553,7 +13550,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52">
         <v>20420.56</v>
@@ -13633,7 +13630,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -13710,7 +13707,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>46303.5</v>
@@ -13780,7 +13777,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -13792,7 +13789,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>46303.5</v>
@@ -13864,7 +13861,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -13876,7 +13873,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -13912,7 +13909,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52">
         <v>46303.5</v>
@@ -13984,7 +13981,7 @@
       </c>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -13996,7 +13993,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52">
         <v>47801.68</v>
@@ -14076,7 +14073,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -14151,31 +14148,31 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52"/>
       <c r="E74" s="52"/>
       <c r="F74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G74" s="53"/>
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
       <c r="J74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M74" s="53"/>
       <c r="N74" s="53"/>
       <c r="O74" s="52"/>
       <c r="P74" s="52"/>
       <c r="Q74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R74" s="53"/>
       <c r="S74" s="54">
@@ -14193,13 +14190,13 @@
       </c>
       <c r="X74" s="55"/>
       <c r="Y74" s="55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z74" s="53"/>
       <c r="AA74" s="56"/>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -14209,7 +14206,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -14281,7 +14278,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -14291,7 +14288,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52">
         <v>77166.16</v>
@@ -14371,7 +14368,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52">
         <v>77166.16</v>
@@ -14443,7 +14440,7 @@
       </c>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -14455,7 +14452,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52">
         <v>77166.16</v>
@@ -14535,7 +14532,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -14608,7 +14605,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -14682,7 +14679,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -14698,7 +14695,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -14770,7 +14767,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -14782,7 +14779,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -14818,7 +14815,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52">
         <v>25467.84</v>
@@ -14890,7 +14887,7 @@
       </c>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -14902,7 +14899,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52">
         <v>25467.84</v>
@@ -14982,7 +14979,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -15059,7 +15056,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -15133,7 +15130,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -15149,7 +15146,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -15221,7 +15218,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -15233,7 +15230,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67">
         <v>37083.03</v>
@@ -15313,7 +15310,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67">
         <v>37083.03</v>
@@ -15385,7 +15382,7 @@
       </c>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -15397,7 +15394,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67">
         <v>37083.03</v>
@@ -15477,7 +15474,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -15554,7 +15551,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -15628,7 +15625,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -15644,7 +15641,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52"/>
       <c r="E96" s="52"/>
@@ -15672,7 +15669,7 @@
       <c r="AA96" s="56"/>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -15684,7 +15681,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -15720,7 +15717,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52">
         <v>26186.14</v>
@@ -15792,7 +15789,7 @@
       </c>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -15804,7 +15801,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52">
         <v>26186.14</v>
@@ -15884,7 +15881,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -15961,7 +15958,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>33188.02</v>
@@ -16035,7 +16032,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -16051,7 +16048,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -16123,7 +16120,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -16135,7 +16132,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52">
         <v>32473.02</v>
@@ -16215,7 +16212,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52">
         <v>32473.02</v>
@@ -16287,7 +16284,7 @@
       </c>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -16299,7 +16296,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52">
         <v>32473.02</v>
@@ -16379,7 +16376,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -16453,10 +16450,10 @@
         <v>8840</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>56556.55</v>
@@ -16532,7 +16529,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -16548,7 +16545,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -16620,7 +16617,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -16632,7 +16629,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52">
         <v>58902.56</v>
@@ -16712,7 +16709,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52">
         <v>58902.56</v>
@@ -16784,7 +16781,7 @@
       </c>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -16796,7 +16793,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52">
         <v>58902.56</v>
@@ -16876,7 +16873,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -16950,10 +16947,10 @@
         <v>8769</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -16977,7 +16974,7 @@
         <v>13229.5</v>
       </c>
       <c r="K116" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L116" s="52">
         <v>13229.5</v>
@@ -17025,7 +17022,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -17035,7 +17032,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -17107,7 +17104,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -17117,7 +17114,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -17155,7 +17152,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52">
         <v>21404.82</v>
@@ -17227,7 +17224,7 @@
       </c>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -17239,7 +17236,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52">
         <v>21404.82</v>
@@ -17319,7 +17316,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -17391,10 +17388,10 @@
         <v>7901</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>96573.02</v>
@@ -17464,7 +17461,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -17476,7 +17473,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>99768.39</v>
@@ -17548,7 +17545,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -17560,7 +17557,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52">
         <v>99768.39</v>
@@ -17640,7 +17637,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52">
         <v>100987.51</v>
@@ -17712,7 +17709,7 @@
       </c>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -17724,7 +17721,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52">
         <v>100987.51</v>
@@ -17804,7 +17801,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -17878,10 +17875,10 @@
         <v>8923</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -17955,7 +17952,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -17971,7 +17968,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52"/>
       <c r="E131" s="52"/>
@@ -17999,7 +17996,7 @@
       <c r="AA131" s="56"/>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -18011,7 +18008,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -18046,7 +18043,7 @@
     <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52">
         <v>31802.41</v>
@@ -18118,7 +18115,7 @@
       </c>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -18130,7 +18127,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52">
         <v>31802.41</v>
@@ -18210,7 +18207,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -18284,10 +18281,10 @@
         <v>7864</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>28626.25</v>
@@ -18361,7 +18358,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -18377,7 +18374,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>28626.25</v>
@@ -18449,7 +18446,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -18461,7 +18458,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52">
         <v>30749.24</v>
@@ -18541,7 +18538,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52">
         <v>30749.24</v>
@@ -18613,7 +18610,7 @@
       </c>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -18625,7 +18622,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52">
         <v>30749.24</v>
@@ -18705,7 +18702,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -18779,10 +18776,10 @@
         <v>7912</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -18854,7 +18851,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -18864,7 +18861,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -18936,7 +18933,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -18946,7 +18943,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -18982,7 +18979,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52">
         <v>268228.26</v>
@@ -19054,7 +19051,7 @@
       </c>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -19066,7 +19063,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52">
         <v>268228.26</v>
@@ -19146,7 +19143,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -19216,10 +19213,10 @@
         <v>8360</v>
       </c>
       <c r="B151" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -19228,10 +19225,10 @@
         <v>32773.41</v>
       </c>
       <c r="F151" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G151" s="53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H151" s="52">
         <v>22750.99</v>
@@ -19291,7 +19288,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -19307,7 +19304,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -19379,7 +19376,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -19391,7 +19388,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -19427,7 +19424,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52">
         <v>32773.41</v>
@@ -19499,7 +19496,7 @@
       </c>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -19511,7 +19508,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52">
         <v>32773.41</v>
@@ -19591,7 +19588,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -19665,10 +19662,10 @@
         <v>8337</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -19738,7 +19735,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -19752,7 +19749,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -19824,7 +19821,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -19834,7 +19831,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -19874,7 +19871,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52">
         <v>17899.33</v>
@@ -19946,7 +19943,7 @@
       </c>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -19958,7 +19955,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52">
         <v>17899.33</v>
@@ -20038,7 +20035,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -20114,10 +20111,10 @@
         <v>9240</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -20137,7 +20134,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -20177,7 +20174,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -20187,7 +20184,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52"/>
       <c r="E166" s="52"/>
@@ -20215,7 +20212,7 @@
       <c r="AA166" s="56"/>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -20225,7 +20222,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -20261,7 +20258,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -20289,7 +20286,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -20301,7 +20298,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -20337,7 +20334,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -20407,10 +20404,10 @@
         <v>7428</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -20482,7 +20479,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -20496,7 +20493,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -20568,7 +20565,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -20578,7 +20575,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52">
         <v>146237.11</v>
@@ -20658,7 +20655,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52">
         <v>146237.11</v>
@@ -20730,7 +20727,7 @@
       </c>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -20742,7 +20739,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52">
         <v>146237.11</v>
@@ -20822,7 +20819,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -20898,10 +20895,10 @@
         <v>9351</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -20971,7 +20968,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -20987,7 +20984,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52">
         <v>16897.53</v>
@@ -21059,7 +21056,7 @@
       </c>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -21071,7 +21068,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -21107,7 +21104,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52">
         <v>16897.53</v>
@@ -21179,7 +21176,7 @@
       </c>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -21191,7 +21188,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52">
         <v>16897.53</v>
@@ -21271,7 +21268,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -21345,10 +21342,10 @@
         <v>7429</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -21420,7 +21417,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -21434,7 +21431,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -21506,7 +21503,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -21516,7 +21513,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -21554,7 +21551,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52">
         <v>20992.12</v>
@@ -21626,7 +21623,7 @@
       </c>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -21638,7 +21635,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52">
         <v>20992.12</v>
@@ -21718,7 +21715,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -21792,10 +21789,10 @@
         <v>9508</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -21819,7 +21816,7 @@
         <v>7389.339999999999</v>
       </c>
       <c r="K193" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L193" s="52">
         <v>7389.339999999999</v>
@@ -21865,7 +21862,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -21875,7 +21872,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -21947,7 +21944,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -21957,7 +21954,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -21995,7 +21992,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52">
         <v>23770.95</v>
@@ -22067,7 +22064,7 @@
       </c>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -22079,7 +22076,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52">
         <v>23770.95</v>
@@ -22159,7 +22156,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -22230,7 +22227,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -22278,7 +22275,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -22288,7 +22285,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -22320,7 +22317,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -22330,7 +22327,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -22370,7 +22367,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -22402,7 +22399,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -22414,7 +22411,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -22454,7 +22451,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -22526,10 +22523,10 @@
     <row r="207" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="19"/>
       <c r="B207" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -22561,7 +22558,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -22571,7 +22568,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -22603,7 +22600,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -22613,7 +22610,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -22653,7 +22650,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -22685,7 +22682,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -22697,7 +22694,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -22737,7 +22734,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -22811,10 +22808,10 @@
         <v>8946</v>
       </c>
       <c r="B214" s="77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -22838,7 +22835,7 @@
         <v>99479.62000000001</v>
       </c>
       <c r="K214" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L214" s="52">
         <v>99479.62000000001</v>
@@ -22882,7 +22879,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -22892,7 +22889,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -22964,7 +22961,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -22974,7 +22971,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -23010,7 +23007,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52">
         <v>137109.56</v>
@@ -23082,7 +23079,7 @@
       </c>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -23094,7 +23091,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52">
         <v>137109.56</v>
@@ -23174,7 +23171,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -23244,10 +23241,10 @@
         <v>8308</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>389318.35</v>
@@ -23319,7 +23316,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -23333,7 +23330,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>389318.35</v>
@@ -23405,7 +23402,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -23415,7 +23412,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -23455,7 +23452,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52">
         <v>389318.35</v>
@@ -23527,7 +23524,7 @@
       </c>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -23539,7 +23536,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52">
         <v>396453.46</v>
@@ -23619,7 +23616,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -24263,49 +24260,49 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="C2" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="D2" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="E2" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="F2" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="H2" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="I2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="J2" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="82" t="s">
+      <c r="K2" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="L2" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="83" t="s">
+      <c r="M2" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="N2" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="81" t="s">
+      <c r="O2" s="84" t="s">
         <v>114</v>
-      </c>
-      <c r="O2" s="84" t="s">
-        <v>115</v>
       </c>
       <c r="P2" s="35"/>
     </row>
@@ -24438,7 +24435,7 @@
         <v>-559.5887999999993</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -24587,7 +24584,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="52">
         <v>83186.06</v>
@@ -24627,7 +24624,7 @@
         <v>190.44884057971015</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -24820,7 +24817,7 @@
         <v>-29.987619047619066</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -25259,7 +25256,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="52">
         <v>-35454.43</v>
@@ -25321,7 +25318,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -25381,7 +25378,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="52">
         <v>0</v>
@@ -25439,7 +25436,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="52">
         <v>0</v>
@@ -25501,7 +25498,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="52">
         <v>3554.300000000003</v>
@@ -25561,7 +25558,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="52">
         <v>0</v>
@@ -25615,7 +25612,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -25673,7 +25670,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="99">
         <v>13424.5</v>
@@ -25733,7 +25730,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -25767,7 +25764,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -25792,7 +25789,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="99">
         <v>31119.76000000001</v>
@@ -25854,7 +25851,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="99">
         <v>5491.7</v>
@@ -25916,7 +25913,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="99">
         <v>12937.1</v>
@@ -25978,7 +25975,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="99">
         <v>10204.54</v>
@@ -26064,7 +26061,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
@@ -26104,7 +26101,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="99">
         <v>30174.75</v>
@@ -26162,7 +26159,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="99">
         <v>0</v>
@@ -26238,10 +26235,10 @@
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="103" t="s">
         <v>121</v>
-      </c>
-      <c r="B69" s="103" t="s">
-        <v>122</v>
       </c>
       <c r="C69" s="104">
         <v>348854.75999999995</v>
@@ -26253,13 +26250,13 @@
         <v>-28126.379999999983</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G69" s="107">
         <v>-0.08062489960005129</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I69" s="109">
         <v>-0.2292042109444056</v>
@@ -26274,7 +26271,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -26290,7 +26287,7 @@
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -26689,52 +26686,52 @@
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="D2" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="117" t="s">
+      <c r="E2" s="117" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="F2" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="G2" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="H2" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="I2" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="J2" s="117" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="K2" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="K2" s="117" t="s">
+      <c r="L2" s="117" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="117" t="s">
+      <c r="M2" s="117" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="117" t="s">
+      <c r="N2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="O2" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="117" t="s">
+      <c r="P2" s="117" t="s">
         <v>139</v>
       </c>
-      <c r="P2" s="117" t="s">
+      <c r="Q2" s="118" t="s">
         <v>140</v>
-      </c>
-      <c r="Q2" s="118" t="s">
-        <v>141</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -26750,10 +26747,10 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="123" t="s">
         <v>142</v>
-      </c>
-      <c r="B3" s="123" t="s">
-        <v>143</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -26837,7 +26834,7 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -26890,7 +26887,7 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -26943,7 +26940,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27000,7 +26997,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27027,7 +27024,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -27057,7 +27054,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27114,7 +27111,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27605,7 +27602,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -27655,7 +27652,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -27707,7 +27704,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -27762,7 +27759,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -27816,7 +27813,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -27865,7 +27862,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -27924,7 +27921,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -27972,7 +27969,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -28024,7 +28021,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="54">
         <v>64.71</v>
@@ -28076,7 +28073,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -28131,7 +28128,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -28186,7 +28183,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -28239,7 +28236,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -28329,7 +28326,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -28371,7 +28368,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -28423,7 +28420,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="54">
         <v>2344.68</v>
@@ -28517,7 +28514,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C70" s="147"/>
       <c r="D70" s="147"/>
@@ -28562,7 +28559,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
@@ -28601,7 +28598,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C72" s="20">
         <v>4490.26</v>
@@ -28630,7 +28627,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -28675,7 +28672,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
@@ -28739,10 +28736,10 @@
     <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="157" t="s">
         <v>151</v>
-      </c>
-      <c r="C76" s="157" t="s">
-        <v>152</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -28786,7 +28783,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -28850,7 +28847,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -28862,7 +28859,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -28873,7 +28870,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -28896,7 +28893,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -28919,7 +28916,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -28942,7 +28939,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -28965,7 +28962,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -28988,7 +28985,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -29011,7 +29008,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -29034,7 +29031,7 @@
     <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -29057,7 +29054,7 @@
     <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -29080,7 +29077,7 @@
     <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -29103,7 +29100,7 @@
     <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -29273,7 +29270,7 @@
     <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -29296,7 +29293,7 @@
     <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -29319,7 +29316,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -29342,7 +29339,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -29365,7 +29362,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -29388,7 +29385,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -29411,7 +29408,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -29510,7 +29507,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C109" s="170">
         <v>16.5</v>
@@ -29586,7 +29583,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -29618,7 +29615,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -29651,7 +29648,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -29684,7 +29681,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -29717,7 +29714,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -29750,7 +29747,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -29783,7 +29780,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -29816,7 +29813,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -29911,7 +29908,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -29944,7 +29941,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -29977,7 +29974,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -30010,7 +30007,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -30043,7 +30040,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -30076,7 +30073,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -30109,7 +30106,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -30142,7 +30139,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -30175,7 +30172,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -30208,7 +30205,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -30241,7 +30238,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -30274,7 +30271,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -30307,7 +30304,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -30340,7 +30337,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -30373,7 +30370,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -30406,7 +30403,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -30439,7 +30436,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30471,7 +30468,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -30503,7 +30500,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -30535,7 +30532,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -30567,7 +30564,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -30659,7 +30656,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -30691,7 +30688,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -30723,7 +30720,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -30755,7 +30752,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -30787,7 +30784,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -30849,7 +30846,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -30881,7 +30878,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -30913,7 +30910,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -30945,7 +30942,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -31097,7 +31094,7 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -31129,7 +31126,7 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -31409,7 +31406,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -32510,7 +32507,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -32542,7 +32539,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -32877,88 +32874,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q2" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q2" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="R2" s="43" t="s">
+      <c r="S2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="43" t="s">
+      <c r="T2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="U2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="V2" s="214" t="s">
         <v>79</v>
       </c>
-      <c r="V2" s="214" t="s">
+      <c r="W2" s="214" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="214" t="s">
+      <c r="X2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="X2" s="45" t="s">
+      <c r="Y2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Z2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AA2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="AB2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="47" t="s">
+      <c r="AC2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="46" t="s">
+      <c r="AD2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AD2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -32999,10 +32996,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AL3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -33015,7 +33012,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -33111,7 +33108,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -33130,7 +33127,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -33219,7 +33216,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -33238,7 +33235,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -33345,7 +33342,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -33418,7 +33415,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -33436,7 +33433,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -33523,7 +33520,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -33652,7 +33649,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -33741,7 +33738,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -33760,7 +33757,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -33849,7 +33846,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -33868,7 +33865,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -33971,7 +33968,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -34052,7 +34049,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -34070,7 +34067,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -34159,7 +34156,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -34293,7 +34290,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -34386,7 +34383,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -34405,7 +34402,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -34496,7 +34493,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -34515,7 +34512,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -34620,7 +34617,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -34695,7 +34692,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -34713,7 +34710,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -34802,7 +34799,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -34935,7 +34932,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -35028,7 +35025,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -35047,7 +35044,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -35140,7 +35137,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -35159,7 +35156,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -35266,7 +35263,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -35349,7 +35346,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -35367,7 +35364,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -35464,7 +35461,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -35603,7 +35600,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -35694,7 +35691,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -35713,7 +35710,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -35802,7 +35799,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -35821,7 +35818,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -35924,7 +35921,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -35997,7 +35994,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -36015,7 +36012,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -36102,7 +36099,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -36231,7 +36228,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -36318,7 +36315,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -36337,7 +36334,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -36422,7 +36419,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -36441,7 +36438,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -36544,7 +36541,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -36621,7 +36618,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -36639,7 +36636,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -36730,7 +36727,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -36863,7 +36860,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -36956,7 +36953,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -36975,7 +36972,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -37068,7 +37065,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -37087,7 +37084,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -37194,7 +37191,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -37275,7 +37272,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -37293,7 +37290,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -37388,7 +37385,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -37525,7 +37522,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -37618,7 +37615,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -37637,7 +37634,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -37726,7 +37723,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -37745,7 +37742,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -37848,7 +37845,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -37921,7 +37918,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -37939,7 +37936,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -38026,7 +38023,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -38159,7 +38156,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -38250,7 +38247,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -38269,7 +38266,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -38360,7 +38357,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -38379,7 +38376,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -38484,7 +38481,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -38561,7 +38558,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -38579,7 +38576,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -38670,7 +38667,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -38803,7 +38800,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -38892,7 +38889,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -38911,7 +38908,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -39002,7 +38999,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -39021,7 +39018,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -39110,7 +39107,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -39185,7 +39182,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -39203,7 +39200,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -39292,7 +39289,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -39421,7 +39418,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -39514,7 +39511,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -39533,7 +39530,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -39624,7 +39621,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -39643,7 +39640,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -39748,7 +39745,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -39827,7 +39824,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -39845,7 +39842,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -39940,7 +39937,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -40077,7 +40074,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -40170,7 +40167,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -40189,7 +40186,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -40282,7 +40279,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -40301,7 +40298,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -40406,7 +40403,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -40497,7 +40494,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -40515,7 +40512,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -40618,7 +40615,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -40763,7 +40760,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -40856,7 +40853,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -40875,7 +40872,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -40964,7 +40961,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -40983,7 +40980,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -41086,7 +41083,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -41175,7 +41172,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -41193,7 +41190,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -41296,7 +41293,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -41441,7 +41438,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -41534,7 +41531,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -41553,7 +41550,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -41646,7 +41643,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -41665,7 +41662,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -41772,7 +41769,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -41865,7 +41862,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -41883,7 +41880,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -41988,7 +41985,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -42135,7 +42132,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -42226,7 +42223,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -42245,7 +42242,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -42336,7 +42333,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -42355,7 +42352,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -42460,7 +42457,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -42551,7 +42548,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -42569,7 +42566,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -42674,7 +42671,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -42821,7 +42818,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -42913,7 +42910,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -42932,7 +42929,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -43025,7 +43022,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -43044,7 +43041,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -43151,7 +43148,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -43244,7 +43241,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -43262,7 +43259,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -43369,7 +43366,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -43518,7 +43515,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -43611,7 +43608,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -43630,7 +43627,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -43723,7 +43720,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -43742,7 +43739,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -43849,7 +43846,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -43942,7 +43939,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -43960,7 +43957,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -44067,7 +44064,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -44216,7 +44213,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -44308,7 +44305,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -44327,7 +44324,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -44416,7 +44413,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -44435,7 +44432,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -44538,7 +44535,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -44627,7 +44624,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -44645,7 +44642,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -44748,7 +44745,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -44893,7 +44890,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -44986,7 +44983,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -45005,7 +45002,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -45098,7 +45095,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -45117,7 +45114,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -45222,7 +45219,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -45313,7 +45310,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -45331,7 +45328,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -45436,7 +45433,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -45583,7 +45580,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -45676,7 +45673,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -45695,7 +45692,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -45782,7 +45779,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -45801,7 +45798,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -45902,7 +45899,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -45987,7 +45984,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -46005,7 +46002,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -46104,7 +46101,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -46245,7 +46242,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -46334,7 +46331,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -46353,7 +46350,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -46442,7 +46439,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -46461,7 +46458,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -46564,7 +46561,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -46653,7 +46650,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -46671,7 +46668,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -46774,7 +46771,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -46919,7 +46916,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -47008,7 +47005,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -47027,7 +47024,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -47116,7 +47113,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -47135,7 +47132,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -47238,7 +47235,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -47327,7 +47324,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -47345,7 +47342,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -47432,7 +47429,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -47561,7 +47558,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -47648,7 +47645,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -47667,7 +47664,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -47753,7 +47750,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -47772,7 +47769,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -47859,7 +47856,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -47932,7 +47929,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -47950,7 +47947,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -48037,7 +48034,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -48166,7 +48163,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -48255,7 +48252,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -48274,7 +48271,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -48363,7 +48360,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -48382,7 +48379,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -48485,7 +48482,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -48574,7 +48571,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -48592,7 +48589,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -48695,7 +48692,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -48840,7 +48837,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -48927,7 +48924,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -48946,7 +48943,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -49032,7 +49029,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -49051,7 +49048,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -49154,7 +49151,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -49243,7 +49240,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -49261,7 +49258,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -49364,7 +49361,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -49509,7 +49506,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -49596,7 +49593,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -49615,7 +49612,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -49701,7 +49698,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -49720,7 +49717,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -49823,7 +49820,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -49912,7 +49909,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -49930,7 +49927,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -50033,7 +50030,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -50178,7 +50175,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -50265,7 +50262,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -50284,7 +50281,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -50370,7 +50367,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -50389,7 +50386,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -50492,7 +50489,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -50581,7 +50578,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -50599,7 +50596,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -50702,7 +50699,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -50847,7 +50844,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -50938,7 +50935,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -50957,7 +50954,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -51043,7 +51040,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -51062,7 +51059,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -51165,7 +51162,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -51254,7 +51251,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -51272,7 +51269,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -51375,7 +51372,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -51520,7 +51517,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -51607,7 +51604,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -51626,7 +51623,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -51712,7 +51709,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -51731,7 +51728,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -51818,7 +51815,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -51891,7 +51888,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -51909,7 +51906,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -51996,7 +51993,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -52125,7 +52122,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -52212,7 +52209,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -52231,7 +52228,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -52317,7 +52314,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -52336,7 +52333,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -52423,7 +52420,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -52496,7 +52493,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -52514,7 +52511,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -52601,7 +52598,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -52730,7 +52727,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -52817,7 +52814,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -52836,7 +52833,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -52922,7 +52919,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -52941,7 +52938,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -53028,7 +53025,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -53101,7 +53098,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -53119,7 +53116,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -53206,7 +53203,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -53335,7 +53332,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -53422,7 +53419,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -53441,7 +53438,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -53527,7 +53524,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -53546,7 +53543,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -53633,7 +53630,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -53706,7 +53703,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -53724,7 +53721,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -53811,7 +53808,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -54482,18 +54479,18 @@
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>220</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -54505,7 +54502,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -54516,7 +54513,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -54527,7 +54524,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9939,54 +9939,54 @@
         <v>101420.72</v>
       </c>
       <c r="I12" s="52">
-        <v>75109.37</v>
+        <v>76488.35</v>
       </c>
       <c r="J12" s="52">
         <v>83645.65</v>
       </c>
       <c r="K12" s="52">
-        <v>70211.29</v>
+        <v>70758.46</v>
       </c>
       <c r="L12" s="52">
-        <v>13434.36</v>
+        <v>12887.189999999988</v>
       </c>
       <c r="M12" s="53">
-        <v>0.16061038440134068</v>
+        <v>0.1540688607237793</v>
       </c>
       <c r="N12" s="53"/>
       <c r="O12" s="52">
         <v>17775.07</v>
       </c>
       <c r="P12" s="52">
-        <v>4898.08</v>
+        <v>5729.89</v>
       </c>
       <c r="Q12" s="52">
-        <v>12876.99</v>
+        <v>12045.18</v>
       </c>
       <c r="R12" s="53">
-        <v>0.724441028924218</v>
+        <v>0.6776445887414227</v>
       </c>
       <c r="S12" s="54">
         <v>356.07</v>
       </c>
       <c r="T12" s="54">
-        <v>100.75</v>
+        <v>117.75</v>
       </c>
       <c r="U12" s="54">
-        <v>255.32</v>
+        <v>238.32</v>
       </c>
       <c r="V12" s="53">
-        <v>0.7170500182548375</v>
+        <v>0.6693065970174403</v>
       </c>
       <c r="W12" s="53"/>
       <c r="X12" s="55">
-        <v>106.74650124069478</v>
+        <v>79.624033970276</v>
       </c>
       <c r="Y12" s="55">
         <v>77.66490997775718</v>
       </c>
       <c r="Z12" s="53">
-        <v>0.1253</v>
+        <v>0.1092</v>
       </c>
       <c r="AA12" s="56">
         <v>0.2142</v>
@@ -10302,19 +10302,19 @@
         <v>19565.83</v>
       </c>
       <c r="I19" s="52">
-        <v>7621.92</v>
+        <v>7921.92</v>
       </c>
       <c r="J19" s="52">
         <v>13767.340000000002</v>
       </c>
       <c r="K19" s="52">
-        <v>5911.24</v>
+        <v>6211.24</v>
       </c>
       <c r="L19" s="52">
-        <v>7856.100000000002</v>
+        <v>7556.100000000002</v>
       </c>
       <c r="M19" s="53">
-        <v>0.5706331070490016</v>
+        <v>0.5488424052867149</v>
       </c>
       <c r="N19" s="53"/>
       <c r="O19" s="52">
@@ -10343,13 +10343,13 @@
       </c>
       <c r="W19" s="53"/>
       <c r="X19" s="55">
-        <v>125.96143884892086</v>
+        <v>117.328345323741</v>
       </c>
       <c r="Y19" s="55">
         <v>63.27846478985563</v>
       </c>
       <c r="Z19" s="53">
-        <v>0.36479999999999996</v>
+        <v>0.3398</v>
       </c>
       <c r="AA19" s="56">
         <v>0.2885</v>
@@ -10667,19 +10667,19 @@
         <v>102178.42</v>
       </c>
       <c r="I26" s="52">
-        <v>87230.67</v>
+        <v>87101.11</v>
       </c>
       <c r="J26" s="52">
         <v>62464.86</v>
       </c>
       <c r="K26" s="52">
-        <v>58028.31</v>
+        <v>57898.75</v>
       </c>
       <c r="L26" s="52">
-        <v>4436.550000000003</v>
+        <v>4566.110000000001</v>
       </c>
       <c r="M26" s="53">
-        <v>0.07102473294585152</v>
+        <v>0.07309885910254182</v>
       </c>
       <c r="N26" s="53"/>
       <c r="O26" s="52">
@@ -10708,13 +10708,13 @@
       </c>
       <c r="W26" s="53"/>
       <c r="X26" s="55">
-        <v>96.11460050462573</v>
+        <v>96.3325315391085</v>
       </c>
       <c r="Y26" s="55">
         <v>61.20621468124544</v>
       </c>
       <c r="Z26" s="53">
-        <v>0.3958</v>
+        <v>0.3967</v>
       </c>
       <c r="AA26" s="56">
         <v>0.3227</v>
@@ -11030,54 +11030,54 @@
         <v>327431.12</v>
       </c>
       <c r="I33" s="65">
-        <v>219182.25</v>
+        <v>220187.84</v>
       </c>
       <c r="J33" s="52">
         <v>271519.78</v>
       </c>
       <c r="K33" s="52">
-        <v>196853</v>
+        <v>196879.33</v>
       </c>
       <c r="L33" s="52">
-        <v>74666.78000000003</v>
+        <v>74640.45000000004</v>
       </c>
       <c r="M33" s="53">
-        <v>0.2749957295928865</v>
+        <v>0.27489875691561044</v>
       </c>
       <c r="N33" s="53"/>
       <c r="O33" s="52">
         <v>55911.34</v>
       </c>
       <c r="P33" s="52">
-        <v>22329.25</v>
+        <v>23308.51</v>
       </c>
       <c r="Q33" s="52">
-        <v>33582.09</v>
+        <v>32602.829999999998</v>
       </c>
       <c r="R33" s="53">
-        <v>0.6006311063193978</v>
+        <v>0.5831165913748445</v>
       </c>
       <c r="S33" s="54">
         <v>1120.27</v>
       </c>
       <c r="T33" s="54">
-        <v>522.25</v>
+        <v>543.5</v>
       </c>
       <c r="U33" s="54">
-        <v>598.02</v>
+        <v>576.77</v>
       </c>
       <c r="V33" s="53">
-        <v>0.5338177403661617</v>
+        <v>0.514849098877949</v>
       </c>
       <c r="W33" s="53"/>
       <c r="X33" s="55">
-        <v>76.90849210148396</v>
+        <v>72.05127874885005</v>
       </c>
       <c r="Y33" s="55">
         <v>61.5841822414239</v>
       </c>
       <c r="Z33" s="53">
-        <v>0.1549</v>
+        <v>0.151</v>
       </c>
       <c r="AA33" s="56">
         <v>0.174</v>
@@ -11393,54 +11393,54 @@
         <v>94098.32</v>
       </c>
       <c r="I40" s="52">
-        <v>45499.87</v>
+        <v>46289.42</v>
       </c>
       <c r="J40" s="52">
         <v>69042.09000000001</v>
       </c>
       <c r="K40" s="52">
-        <v>35731.93</v>
+        <v>35507.08</v>
       </c>
       <c r="L40" s="52">
-        <v>33310.16000000001</v>
+        <v>33535.01000000001</v>
       </c>
       <c r="M40" s="53">
-        <v>0.4824616404283243</v>
+        <v>0.4857183494879718</v>
       </c>
       <c r="N40" s="53"/>
       <c r="O40" s="52">
         <v>25056.23</v>
       </c>
       <c r="P40" s="52">
-        <v>9767.94</v>
+        <v>10782.34</v>
       </c>
       <c r="Q40" s="52">
-        <v>15288.289999999999</v>
+        <v>14273.89</v>
       </c>
       <c r="R40" s="53">
-        <v>0.6101592298601984</v>
+        <v>0.5696742885901032</v>
       </c>
       <c r="S40" s="54">
         <v>501.83</v>
       </c>
       <c r="T40" s="54">
-        <v>205.75</v>
+        <v>232.25</v>
       </c>
       <c r="U40" s="54">
-        <v>296.08</v>
+        <v>269.58</v>
       </c>
       <c r="V40" s="53">
-        <v>0.5900005978120081</v>
+        <v>0.5371938704342107</v>
       </c>
       <c r="W40" s="53"/>
       <c r="X40" s="55">
-        <v>41.0447630619684</v>
+        <v>32.96193756727664</v>
       </c>
       <c r="Y40" s="55">
         <v>68.07122423898531</v>
       </c>
       <c r="Z40" s="53">
-        <v>0.1565</v>
+        <v>0.1419</v>
       </c>
       <c r="AA40" s="56">
         <v>0.2663</v>
@@ -11758,19 +11758,19 @@
         <v>50582.37</v>
       </c>
       <c r="I47" s="52">
-        <v>25337.26</v>
+        <v>25187.36</v>
       </c>
       <c r="J47" s="52">
         <v>39438.990000000005</v>
       </c>
       <c r="K47" s="52">
-        <v>20582.32</v>
+        <v>20432.420000000002</v>
       </c>
       <c r="L47" s="52">
-        <v>18856.670000000006</v>
+        <v>19006.570000000003</v>
       </c>
       <c r="M47" s="53">
-        <v>0.4781225381278781</v>
+        <v>0.48192334540007237</v>
       </c>
       <c r="N47" s="53"/>
       <c r="O47" s="52">
@@ -11799,13 +11799,13 @@
       </c>
       <c r="W47" s="53"/>
       <c r="X47" s="55">
-        <v>76.63529976019184</v>
+        <v>78.07318944844125</v>
       </c>
       <c r="Y47" s="55">
         <v>67.69550512136009</v>
       </c>
       <c r="Z47" s="53">
-        <v>0.2397</v>
+        <v>0.24420000000000003</v>
       </c>
       <c r="AA47" s="56">
         <v>0.23</v>
@@ -12121,19 +12121,19 @@
         <v>109364.97</v>
       </c>
       <c r="I54" s="52">
-        <v>95642.03</v>
+        <v>95597.19</v>
       </c>
       <c r="J54" s="52">
         <v>75135.01000000001</v>
       </c>
       <c r="K54" s="52">
-        <v>71188.63</v>
+        <v>71143.79000000001</v>
       </c>
       <c r="L54" s="52">
-        <v>3946.3800000000047</v>
+        <v>3991.220000000001</v>
       </c>
       <c r="M54" s="53">
-        <v>0.05252385006669999</v>
+        <v>0.05312064242754477</v>
       </c>
       <c r="N54" s="53"/>
       <c r="O54" s="52">
@@ -12162,13 +12162,13 @@
       </c>
       <c r="W54" s="53"/>
       <c r="X54" s="55">
-        <v>62.138966682761954</v>
+        <v>62.22557218734911</v>
       </c>
       <c r="Y54" s="55">
         <v>67.00679527854935</v>
       </c>
       <c r="Z54" s="53">
-        <v>0.25170000000000003</v>
+        <v>0.2521</v>
       </c>
       <c r="AA54" s="56">
         <v>0.2958</v>
@@ -12841,19 +12841,19 @@
         <v>35572.59</v>
       </c>
       <c r="I68" s="52">
-        <v>9981.43</v>
+        <v>10547.08</v>
       </c>
       <c r="J68" s="52">
         <v>27136.549999999996</v>
       </c>
       <c r="K68" s="52">
-        <v>9832.65</v>
+        <v>10398.3</v>
       </c>
       <c r="L68" s="52">
-        <v>17303.899999999994</v>
+        <v>16738.249999999996</v>
       </c>
       <c r="M68" s="53">
-        <v>0.6376602773749794</v>
+        <v>0.6168156969106242</v>
       </c>
       <c r="N68" s="53"/>
       <c r="O68" s="52">
@@ -12882,13 +12882,13 @@
       </c>
       <c r="W68" s="53"/>
       <c r="X68" s="55">
-        <v>243.27272727272728</v>
+        <v>37.58181818181818</v>
       </c>
       <c r="Y68" s="55">
         <v>72.22475431425701</v>
       </c>
       <c r="Z68" s="53">
-        <v>0.06280000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="AA68" s="56">
         <v>0.2558</v>
@@ -13916,19 +13916,19 @@
         <v>27002.93</v>
       </c>
       <c r="I89" s="52">
-        <v>26005.99</v>
+        <v>24950.27</v>
       </c>
       <c r="J89" s="52">
         <v>15440.32</v>
       </c>
       <c r="K89" s="52">
-        <v>14988.440000000002</v>
+        <v>13932.720000000001</v>
       </c>
       <c r="L89" s="52">
-        <v>451.8799999999974</v>
+        <v>1507.5999999999985</v>
       </c>
       <c r="M89" s="53">
-        <v>0.029266232824190004</v>
+        <v>0.09764046341008467</v>
       </c>
       <c r="N89" s="53"/>
       <c r="O89" s="52">
@@ -13957,13 +13957,13 @@
       </c>
       <c r="W89" s="53"/>
       <c r="X89" s="55">
-        <v>46.26684503901895</v>
+        <v>50.9746265328874</v>
       </c>
       <c r="Y89" s="55">
         <v>43.49557070636461</v>
       </c>
       <c r="Z89" s="53">
-        <v>0.2852</v>
+        <v>0.31420000000000003</v>
       </c>
       <c r="AA89" s="56">
         <v>0.2718</v>
@@ -14626,30 +14626,74 @@
       <c r="C103" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D103" s="52"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="52"/>
-      <c r="I103" s="52"/>
-      <c r="J103" s="52"/>
-      <c r="K103" s="52"/>
-      <c r="L103" s="52"/>
-      <c r="M103" s="53"/>
+      <c r="D103" s="52">
+        <v>32473.02</v>
+      </c>
+      <c r="E103" s="69">
+        <v>33188.03</v>
+      </c>
+      <c r="F103" s="52">
+        <v>-715.0099999999984</v>
+      </c>
+      <c r="G103" s="53">
+        <v>-0.022018586506582952</v>
+      </c>
+      <c r="H103" s="52">
+        <v>23075.07</v>
+      </c>
+      <c r="I103" s="52">
+        <v>30925.21</v>
+      </c>
+      <c r="J103" s="52">
+        <v>12691.21</v>
+      </c>
+      <c r="K103" s="52">
+        <v>15184.269999999999</v>
+      </c>
+      <c r="L103" s="52">
+        <v>-2493.0599999999995</v>
+      </c>
+      <c r="M103" s="53">
+        <v>-0.1964398981657383</v>
+      </c>
       <c r="N103" s="53"/>
-      <c r="O103" s="52"/>
-      <c r="P103" s="52"/>
-      <c r="Q103" s="52"/>
-      <c r="R103" s="53"/>
-      <c r="S103" s="54"/>
-      <c r="T103" s="54"/>
-      <c r="U103" s="54"/>
-      <c r="V103" s="53"/>
+      <c r="O103" s="52">
+        <v>10383.86</v>
+      </c>
+      <c r="P103" s="52">
+        <v>15740.94</v>
+      </c>
+      <c r="Q103" s="52">
+        <v>-5357.08</v>
+      </c>
+      <c r="R103" s="53">
+        <v>-0.5159044902377343</v>
+      </c>
+      <c r="S103" s="54">
+        <v>208.2</v>
+      </c>
+      <c r="T103" s="54">
+        <v>317.25</v>
+      </c>
+      <c r="U103" s="54">
+        <v>-109.05000000000001</v>
+      </c>
+      <c r="V103" s="53">
+        <v>-0.5237752161383286</v>
+      </c>
       <c r="W103" s="53"/>
-      <c r="X103" s="55"/>
-      <c r="Y103" s="55"/>
-      <c r="Z103" s="53"/>
-      <c r="AA103" s="56"/>
+      <c r="X103" s="55">
+        <v>7.132608353033885</v>
+      </c>
+      <c r="Y103" s="55">
+        <v>45.139084580403456</v>
+      </c>
+      <c r="Z103" s="53">
+        <v>0.0682</v>
+      </c>
+      <c r="AA103" s="56">
+        <v>0.2894</v>
+      </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
         <v>93</v>
@@ -14963,19 +15007,19 @@
         <v>37601.88</v>
       </c>
       <c r="I110" s="52">
-        <v>45837.23</v>
+        <v>45817.77</v>
       </c>
       <c r="J110" s="52">
         <v>21415.85</v>
       </c>
       <c r="K110" s="52">
-        <v>23958.850000000002</v>
+        <v>23939.389999999996</v>
       </c>
       <c r="L110" s="52">
-        <v>-2543.0000000000036</v>
+        <v>-2523.5399999999972</v>
       </c>
       <c r="M110" s="53">
-        <v>-0.11874382758564352</v>
+        <v>-0.11783515480356826</v>
       </c>
       <c r="N110" s="53"/>
       <c r="O110" s="52">
@@ -15004,13 +15048,13 @@
       </c>
       <c r="W110" s="53"/>
       <c r="X110" s="55">
-        <v>48.93201480698043</v>
+        <v>48.973178212585935</v>
       </c>
       <c r="Y110" s="55">
         <v>65.70431400737223</v>
       </c>
       <c r="Z110" s="53">
-        <v>0.3354</v>
+        <v>0.3357</v>
       </c>
       <c r="AA110" s="56">
         <v>0.3616</v>
@@ -15673,19 +15717,19 @@
         <v>82694.87</v>
       </c>
       <c r="I124" s="52">
-        <v>56983.56</v>
+        <v>56763.31</v>
       </c>
       <c r="J124" s="52">
         <v>68214.25</v>
       </c>
       <c r="K124" s="52">
-        <v>52178.049999999996</v>
+        <v>51957.799999999996</v>
       </c>
       <c r="L124" s="52">
-        <v>16036.200000000004</v>
+        <v>16256.450000000004</v>
       </c>
       <c r="M124" s="53">
-        <v>0.23508577753182075</v>
+        <v>0.23831457503380898</v>
       </c>
       <c r="N124" s="53"/>
       <c r="O124" s="52">
@@ -15714,13 +15758,13 @@
       </c>
       <c r="W124" s="53"/>
       <c r="X124" s="55">
-        <v>99.27371428571428</v>
+        <v>101.37133333333333</v>
       </c>
       <c r="Y124" s="55">
         <v>63.04545035767707</v>
       </c>
       <c r="Z124" s="53">
-        <v>0.15460000000000002</v>
+        <v>0.15789999999999998</v>
       </c>
       <c r="AA124" s="56">
         <v>0.1811</v>
@@ -18141,30 +18185,74 @@
       <c r="C173" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D173" s="52"/>
-      <c r="E173" s="52"/>
-      <c r="F173" s="52"/>
-      <c r="G173" s="53"/>
-      <c r="H173" s="52"/>
-      <c r="I173" s="52"/>
-      <c r="J173" s="52"/>
-      <c r="K173" s="52"/>
-      <c r="L173" s="52"/>
-      <c r="M173" s="53"/>
+      <c r="D173" s="52">
+        <v>146237.11</v>
+      </c>
+      <c r="E173" s="52">
+        <v>125386.21</v>
+      </c>
+      <c r="F173" s="52">
+        <v>20850.89999999998</v>
+      </c>
+      <c r="G173" s="53">
+        <v>0.14258282319720336</v>
+      </c>
+      <c r="H173" s="52">
+        <v>114651.87</v>
+      </c>
+      <c r="I173" s="52">
+        <v>105511.63</v>
+      </c>
+      <c r="J173" s="52">
+        <v>82888.07999999999</v>
+      </c>
+      <c r="K173" s="52">
+        <v>78161.06</v>
+      </c>
+      <c r="L173" s="52">
+        <v>4727.0199999999895</v>
+      </c>
+      <c r="M173" s="53">
+        <v>0.05702894795005495</v>
+      </c>
       <c r="N173" s="53"/>
-      <c r="O173" s="52"/>
-      <c r="P173" s="52"/>
-      <c r="Q173" s="52"/>
-      <c r="R173" s="53"/>
-      <c r="S173" s="54"/>
-      <c r="T173" s="54"/>
-      <c r="U173" s="54"/>
-      <c r="V173" s="53"/>
+      <c r="O173" s="52">
+        <v>31763.79</v>
+      </c>
+      <c r="P173" s="52">
+        <v>27350.57</v>
+      </c>
+      <c r="Q173" s="52">
+        <v>4413.220000000001</v>
+      </c>
+      <c r="R173" s="53">
+        <v>0.13893870976983544</v>
+      </c>
+      <c r="S173" s="54">
+        <v>659.73</v>
+      </c>
+      <c r="T173" s="54">
+        <v>548.75</v>
+      </c>
+      <c r="U173" s="54">
+        <v>110.98000000000002</v>
+      </c>
+      <c r="V173" s="53">
+        <v>0.16822033256028984</v>
+      </c>
       <c r="W173" s="53"/>
-      <c r="X173" s="55"/>
-      <c r="Y173" s="55"/>
-      <c r="Z173" s="53"/>
-      <c r="AA173" s="56"/>
+      <c r="X173" s="55">
+        <v>36.21791343963554</v>
+      </c>
+      <c r="Y173" s="55">
+        <v>47.87601261940491</v>
+      </c>
+      <c r="Z173" s="53">
+        <v>0.1585</v>
+      </c>
+      <c r="AA173" s="56">
+        <v>0.216</v>
+      </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
         <v>93</v>
@@ -18771,30 +18859,74 @@
       <c r="C187" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D187" s="52"/>
-      <c r="E187" s="52"/>
-      <c r="F187" s="52"/>
-      <c r="G187" s="53"/>
-      <c r="H187" s="52"/>
-      <c r="I187" s="52"/>
-      <c r="J187" s="52"/>
-      <c r="K187" s="52"/>
-      <c r="L187" s="52"/>
-      <c r="M187" s="53"/>
+      <c r="D187" s="52">
+        <v>20992.12</v>
+      </c>
+      <c r="E187" s="52">
+        <v>14169.68</v>
+      </c>
+      <c r="F187" s="52">
+        <v>6822.439999999999</v>
+      </c>
+      <c r="G187" s="53">
+        <v>0.32500004763692275</v>
+      </c>
+      <c r="H187" s="52">
+        <v>16299.09</v>
+      </c>
+      <c r="I187" s="52">
+        <v>9699.51</v>
+      </c>
+      <c r="J187" s="52">
+        <v>9784.33</v>
+      </c>
+      <c r="K187" s="52">
+        <v>8137.88</v>
+      </c>
+      <c r="L187" s="52">
+        <v>1646.4499999999998</v>
+      </c>
+      <c r="M187" s="53">
+        <v>0.16827416900288522</v>
+      </c>
       <c r="N187" s="53"/>
-      <c r="O187" s="52"/>
-      <c r="P187" s="52"/>
-      <c r="Q187" s="52"/>
-      <c r="R187" s="53"/>
-      <c r="S187" s="54"/>
-      <c r="T187" s="54"/>
-      <c r="U187" s="54"/>
-      <c r="V187" s="53"/>
+      <c r="O187" s="52">
+        <v>6514.76</v>
+      </c>
+      <c r="P187" s="52">
+        <v>1561.63</v>
+      </c>
+      <c r="Q187" s="52">
+        <v>4953.13</v>
+      </c>
+      <c r="R187" s="53">
+        <v>0.7602935488030257</v>
+      </c>
+      <c r="S187" s="54">
+        <v>130.62</v>
+      </c>
+      <c r="T187" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U187" s="54">
+        <v>95.87</v>
+      </c>
+      <c r="V187" s="53">
+        <v>0.7339611085591793</v>
+      </c>
       <c r="W187" s="53"/>
-      <c r="X187" s="55"/>
-      <c r="Y187" s="55"/>
-      <c r="Z187" s="53"/>
-      <c r="AA187" s="56"/>
+      <c r="X187" s="55">
+        <v>128.6379856115108</v>
+      </c>
+      <c r="Y187" s="55">
+        <v>35.92887828502527</v>
+      </c>
+      <c r="Z187" s="53">
+        <v>0.3155</v>
+      </c>
+      <c r="AA187" s="56">
+        <v>0.2236</v>
+      </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
         <v>93</v>
@@ -20023,19 +20155,19 @@
         <v>117394.57</v>
       </c>
       <c r="I215" s="52">
-        <v>26124</v>
+        <v>30594.96</v>
       </c>
       <c r="J215" s="52">
         <v>99479.62000000001</v>
       </c>
       <c r="K215" s="52">
-        <v>26124</v>
+        <v>30594.96</v>
       </c>
       <c r="L215" s="52">
-        <v>73355.62000000001</v>
+        <v>68884.66</v>
       </c>
       <c r="M215" s="53">
-        <v>0.7373934480248316</v>
+        <v>0.692449971159922</v>
       </c>
       <c r="N215" s="53"/>
       <c r="O215" s="52">
@@ -20070,7 +20202,7 @@
         <v>54.93783457863793</v>
       </c>
       <c r="Z215" s="53">
-        <v>0.13419999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="AA215" s="56">
         <v>0.1438</v>
@@ -20376,54 +20508,54 @@
         <v>295569.99</v>
       </c>
       <c r="I222" s="52">
-        <v>240067.38</v>
+        <v>241753.24</v>
       </c>
       <c r="J222" s="52">
         <v>178700.37</v>
       </c>
       <c r="K222" s="52">
-        <v>178119.89</v>
+        <v>178956.15</v>
       </c>
       <c r="L222" s="52">
-        <v>580.4799999999814</v>
+        <v>-255.77999999999884</v>
       </c>
       <c r="M222" s="53">
-        <v>0.003248342462861053</v>
+        <v>-0.0014313344734540776</v>
       </c>
       <c r="N222" s="53"/>
       <c r="O222" s="52">
         <v>116869.62</v>
       </c>
       <c r="P222" s="52">
-        <v>61947.49</v>
+        <v>62797.09</v>
       </c>
       <c r="Q222" s="52">
-        <v>54922.13</v>
+        <v>54072.53</v>
       </c>
       <c r="R222" s="53">
-        <v>0.4699436003984611</v>
+        <v>0.4626739609489618</v>
       </c>
       <c r="S222" s="54">
         <v>2344.68</v>
       </c>
       <c r="T222" s="54">
-        <v>1315</v>
+        <v>1335</v>
       </c>
       <c r="U222" s="54">
-        <v>1029.6799999999998</v>
+        <v>1009.6799999999998</v>
       </c>
       <c r="V222" s="53">
-        <v>0.4391558762816247</v>
+        <v>0.4306259276319156</v>
       </c>
       <c r="W222" s="53"/>
       <c r="X222" s="55">
-        <v>50.16819011406844</v>
+        <v>48.153790262172286</v>
       </c>
       <c r="Y222" s="55">
         <v>43.0265399367206</v>
       </c>
       <c r="Z222" s="53">
-        <v>0.21559999999999999</v>
+        <v>0.2101</v>
       </c>
       <c r="AA222" s="56">
         <v>0.2545</v>
@@ -21331,10 +21463,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="52">
-        <v>972.0499999999884</v>
+        <v>2351.029999999999</v>
       </c>
       <c r="E6" s="52">
-        <v>-972.0499999999884</v>
+        <v>-2351.029999999999</v>
       </c>
       <c r="F6" s="52">
         <v>0</v>
@@ -21358,13 +21490,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="52">
-        <v>-2844.6499999999883</v>
+        <v>-4223.629999999999</v>
       </c>
       <c r="N6" s="54">
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <v>227.57199999999906</v>
+        <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>115</v>
@@ -21398,10 +21530,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="52">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E8" s="52">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F8" s="52"/>
       <c r="G8" s="53">
@@ -21421,13 +21553,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="52">
-        <v>-640</v>
+        <v>-940</v>
       </c>
       <c r="N8" s="54">
         <v>-34.75</v>
       </c>
       <c r="O8" s="58">
-        <v>34.13333333333333</v>
+        <v>50.13333333333333</v>
       </c>
     </row>
     <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21458,10 +21590,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="52">
-        <v>1382.2599999999948</v>
+        <v>1252.699999999997</v>
       </c>
       <c r="E10" s="52">
-        <v>-1382.2599999999948</v>
+        <v>-1252.699999999997</v>
       </c>
       <c r="F10" s="52">
         <v>0</v>
@@ -21485,13 +21617,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="52">
-        <v>-6302.259999999995</v>
+        <v>-6172.699999999997</v>
       </c>
       <c r="N10" s="54">
         <v>-388.25</v>
       </c>
       <c r="O10" s="58">
-        <v>18.522439382806745</v>
+        <v>18.141660543717848</v>
       </c>
     </row>
     <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21522,10 +21654,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="52">
-        <v>2837.649999999994</v>
+        <v>3843.2399999999907</v>
       </c>
       <c r="E12" s="52">
-        <v>-2837.649999999994</v>
+        <v>-3843.2399999999907</v>
       </c>
       <c r="F12" s="52"/>
       <c r="G12" s="53">
@@ -21547,13 +21679,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="52">
-        <v>-5477.649999999994</v>
+        <v>-6483.239999999991</v>
       </c>
       <c r="N12" s="54">
         <v>53</v>
       </c>
       <c r="O12" s="58">
-        <v>-79.38623188405789</v>
+        <v>-93.95999999999987</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>117</v>
@@ -21587,10 +21719,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="52">
-        <v>3226.1800000000003</v>
+        <v>4015.729999999996</v>
       </c>
       <c r="E14" s="52">
-        <v>-3226.1800000000003</v>
+        <v>-4015.729999999996</v>
       </c>
       <c r="F14" s="52">
         <v>0</v>
@@ -21614,13 +21746,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="52">
-        <v>-6226.18</v>
+        <v>-7015.729999999996</v>
       </c>
       <c r="N14" s="54">
         <v>-112</v>
       </c>
       <c r="O14" s="58">
-        <v>55.59089285714286</v>
+        <v>62.640446428571394</v>
       </c>
     </row>
     <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21651,10 +21783,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="52">
-        <v>125.67999999999665</v>
+        <v>-24.220000000001164</v>
       </c>
       <c r="E16" s="52">
-        <v>-125.67999999999665</v>
+        <v>24.220000000001164</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="53">
@@ -21676,13 +21808,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="52">
-        <v>-3125.6799999999967</v>
+        <v>-2975.779999999999</v>
       </c>
       <c r="N16" s="54">
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
-        <v>36.030893371757884</v>
+        <v>34.302939481268</v>
       </c>
     </row>
     <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21713,10 +21845,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="52">
-        <v>321.5200000000041</v>
+        <v>276.68000000000757</v>
       </c>
       <c r="E18" s="52">
-        <v>-321.5200000000041</v>
+        <v>-276.68000000000757</v>
       </c>
       <c r="F18" s="52">
         <v>0</v>
@@ -21740,13 +21872,13 @@
         <v>0</v>
       </c>
       <c r="M18" s="52">
-        <v>-8521.520000000004</v>
+        <v>-8476.680000000008</v>
       </c>
       <c r="N18" s="54">
         <v>-269</v>
       </c>
       <c r="O18" s="58">
-        <v>45.087407407407426</v>
+        <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>118</v>
@@ -21836,10 +21968,10 @@
         <v>0</v>
       </c>
       <c r="D22" s="52">
-        <v>0</v>
+        <v>565.6499999999996</v>
       </c>
       <c r="E22" s="52">
-        <v>0</v>
+        <v>-565.6499999999996</v>
       </c>
       <c r="F22" s="52">
         <v>0</v>
@@ -21859,7 +21991,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="52">
-        <v>0</v>
+        <v>-565.6499999999996</v>
       </c>
       <c r="N22" s="54"/>
       <c r="O22" s="58">
@@ -22010,10 +22142,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="52">
-        <v>0</v>
+        <v>-1055.7200000000012</v>
       </c>
       <c r="E28" s="52">
-        <v>0</v>
+        <v>1055.7200000000012</v>
       </c>
       <c r="F28" s="52">
         <v>0</v>
@@ -22033,13 +22165,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="52">
-        <v>0</v>
+        <v>1055.7200000000012</v>
       </c>
       <c r="N28" s="54">
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
-        <v>0</v>
+        <v>-7.109225589225597</v>
       </c>
     </row>
     <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22194,10 +22326,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="52">
-        <v>943.3400000000038</v>
+        <v>923.8799999999974</v>
       </c>
       <c r="E34" s="52">
-        <v>-943.3400000000038</v>
+        <v>-923.8799999999974</v>
       </c>
       <c r="F34" s="52">
         <v>0</v>
@@ -22219,13 +22351,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="52">
-        <v>-943.3400000000038</v>
+        <v>-923.8799999999974</v>
       </c>
       <c r="N34" s="54">
         <v>-204.75</v>
       </c>
       <c r="O34" s="58">
-        <v>4.607277167277186</v>
+        <v>4.512234432234419</v>
       </c>
     </row>
     <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22316,16 +22448,16 @@
         <v>52040.560000000005</v>
       </c>
       <c r="D38" s="52">
-        <v>746.3099999999977</v>
+        <v>526.0599999999977</v>
       </c>
       <c r="E38" s="52">
-        <v>51294.25000000001</v>
+        <v>51514.50000000001</v>
       </c>
       <c r="F38" s="52">
         <v>0</v>
       </c>
       <c r="G38" s="53">
-        <v>0.9856590705403632</v>
+        <v>0.9898913462883566</v>
       </c>
       <c r="H38" s="53">
         <v>0.1750921737769</v>
@@ -22336,10 +22468,10 @@
         <v>0</v>
       </c>
       <c r="L38" s="53">
-        <v>0.9856590705403632</v>
+        <v>0.9898913462883566</v>
       </c>
       <c r="M38" s="52">
-        <v>51294.25000000001</v>
+        <v>51514.50000000001</v>
       </c>
       <c r="N38" s="54"/>
       <c r="O38" s="58">
@@ -22727,10 +22859,10 @@
         <v>0</v>
       </c>
       <c r="D52" s="99">
-        <v>0</v>
+        <v>2629.5100000000093</v>
       </c>
       <c r="E52" s="99">
-        <v>0</v>
+        <v>-2629.5100000000093</v>
       </c>
       <c r="F52" s="99"/>
       <c r="G52" s="100">
@@ -22752,13 +22884,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="99">
-        <v>-1280</v>
+        <v>-3909.5100000000093</v>
       </c>
       <c r="N52" s="98">
         <v>-304.75</v>
       </c>
       <c r="O52" s="60">
-        <v>4.692942254812099</v>
+        <v>14.333675527039448</v>
       </c>
     </row>
     <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -23039,10 +23171,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="99">
-        <v>0</v>
+        <v>4470.959999999999</v>
       </c>
       <c r="E64" s="99">
-        <v>0</v>
+        <v>-4470.959999999999</v>
       </c>
       <c r="F64" s="99"/>
       <c r="G64" s="100">
@@ -23062,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="99">
-        <v>-1750</v>
+        <v>-6220.959999999999</v>
       </c>
       <c r="N64" s="98"/>
       <c r="O64" s="60">
@@ -23097,14 +23229,14 @@
         <v>34650.399999999965</v>
       </c>
       <c r="D66" s="99">
-        <v>5744.570000000007</v>
+        <v>7430.429999999993</v>
       </c>
       <c r="E66" s="99">
-        <v>28905.829999999958</v>
+        <v>27219.969999999972</v>
       </c>
       <c r="F66" s="99"/>
       <c r="G66" s="100">
-        <v>0.8342134578533</v>
+        <v>0.7855600512548195</v>
       </c>
       <c r="H66" s="100">
         <v>0.256265521519856</v>
@@ -23119,16 +23251,16 @@
         <v>3200</v>
       </c>
       <c r="L66" s="100">
-        <v>0.7418624316025207</v>
+        <v>0.6932090250040402</v>
       </c>
       <c r="M66" s="99">
-        <v>25705.829999999958</v>
+        <v>24019.969999999972</v>
       </c>
       <c r="N66" s="98">
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
-        <v>-27.51493711533311</v>
+        <v>-25.71043082686644</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -23176,22 +23308,22 @@
         <v>88818.76999999996</v>
       </c>
       <c r="D69" s="104">
-        <v>18681.369999999988</v>
+        <v>29887.739999999983</v>
       </c>
       <c r="E69" s="105">
-        <v>70137.39999999998</v>
+        <v>58931.02999999998</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>122</v>
       </c>
       <c r="G69" s="107">
-        <v>0.7896686702596761</v>
+        <v>0.6634974791927427</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>123</v>
       </c>
       <c r="I69" s="109">
-        <v>0.20609157276102777</v>
+        <v>0.0799203816940944</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -23799,10 +23931,10 @@
         <v>356.07</v>
       </c>
       <c r="D6" s="54">
-        <v>100.75</v>
+        <v>117.75</v>
       </c>
       <c r="E6" s="54">
-        <v>255.32</v>
+        <v>238.32</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -23962,10 +24094,10 @@
         <v>1120.27</v>
       </c>
       <c r="D12" s="54">
-        <v>522.25</v>
+        <v>543.5</v>
       </c>
       <c r="E12" s="54">
-        <v>598.02</v>
+        <v>576.77</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="54"/>
@@ -24019,10 +24151,10 @@
         <v>501.83</v>
       </c>
       <c r="D14" s="54">
-        <v>205.75</v>
+        <v>232.25</v>
       </c>
       <c r="E14" s="54">
-        <v>296.08</v>
+        <v>269.58</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -25011,10 +25143,10 @@
         <v>659.73</v>
       </c>
       <c r="D52" s="54">
-        <v>505.25</v>
+        <v>548.75</v>
       </c>
       <c r="E52" s="54">
-        <v>154.48000000000002</v>
+        <v>110.98000000000002</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="54"/>
@@ -25358,10 +25490,10 @@
         <v>2344.68</v>
       </c>
       <c r="D66" s="54">
-        <v>1315</v>
+        <v>1335</v>
       </c>
       <c r="E66" s="54">
-        <v>1029.6799999999998</v>
+        <v>1009.6799999999998</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16176,7 +16176,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21286,7 +21286,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21300,7 +21300,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21322,7 +21322,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21370,7 +21370,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21388,7 +21388,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21452,7 +21452,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21502,7 +21502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21519,7 +21519,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21562,7 +21562,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21579,7 +21579,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21643,7 +21643,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21659,7 +21659,9 @@
       <c r="E12" s="52">
         <v>-3843.2399999999907</v>
       </c>
-      <c r="F12" s="52"/>
+      <c r="F12" s="52">
+        <v>3</v>
+      </c>
       <c r="G12" s="53">
         <v>0</v>
       </c>
@@ -21691,7 +21693,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21708,7 +21710,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21755,7 +21757,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21772,7 +21774,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21817,7 +21819,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21834,7 +21836,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -21884,7 +21886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -21901,7 +21903,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -21940,7 +21942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -21957,7 +21959,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -21998,7 +22000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22015,7 +22017,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22052,7 +22054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22069,7 +22071,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22114,7 +22116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22131,7 +22133,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22174,7 +22176,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22191,7 +22193,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22234,7 +22236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22251,7 +22253,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22298,7 +22300,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22315,7 +22317,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22360,7 +22362,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22377,7 +22379,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22420,7 +22422,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22437,7 +22439,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22478,7 +22480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22495,7 +22497,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22540,7 +22542,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22557,7 +22559,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22600,7 +22602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22617,7 +22619,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22654,7 +22656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22671,7 +22673,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22712,7 +22714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22729,7 +22731,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22772,7 +22774,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22789,7 +22791,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22831,7 +22833,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22848,7 +22850,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -22893,7 +22895,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -22910,7 +22912,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -22955,7 +22957,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -22972,7 +22974,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23017,7 +23019,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23034,7 +23036,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23071,7 +23073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23088,7 +23090,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23105,7 +23107,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23122,7 +23124,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23143,7 +23145,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23160,7 +23162,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23201,7 +23203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23218,7 +23220,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23263,7 +23265,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23280,7 +23282,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23297,7 +23299,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23332,7 +23334,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23715,7 +23717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23726,7 +23728,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23747,7 +23749,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23809,7 +23811,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -23867,7 +23869,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -23901,7 +23903,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -23920,7 +23922,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -23954,7 +23956,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -23973,7 +23975,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24007,7 +24009,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24026,7 +24028,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24064,7 +24066,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24083,7 +24085,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24121,7 +24123,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24140,7 +24142,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24178,7 +24180,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24197,7 +24199,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24230,7 +24232,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24249,7 +24251,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24282,7 +24284,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24301,7 +24303,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24332,7 +24334,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24351,7 +24353,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24386,7 +24388,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24405,7 +24407,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24438,7 +24440,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24457,7 +24459,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24488,7 +24490,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24507,7 +24509,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24539,7 +24541,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24558,7 +24560,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24594,7 +24596,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24613,7 +24615,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24642,7 +24644,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24661,7 +24663,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24692,7 +24694,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24711,7 +24713,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24744,7 +24746,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24763,7 +24765,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24799,7 +24801,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24818,7 +24820,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24853,7 +24855,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -24872,7 +24874,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24902,7 +24904,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -24921,7 +24923,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24961,7 +24963,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -24980,7 +24982,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25009,7 +25011,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25028,7 +25030,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25061,7 +25063,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25080,7 +25082,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25113,7 +25115,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25132,7 +25134,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25168,7 +25170,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25187,7 +25189,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25223,7 +25225,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25242,7 +25244,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25276,7 +25278,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25295,7 +25297,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25330,7 +25332,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25349,7 +25351,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25368,7 +25370,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25387,7 +25389,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25408,7 +25410,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25427,7 +25429,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25460,7 +25462,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25479,7 +25481,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25518,7 +25520,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25537,7 +25539,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25556,7 +25558,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25575,7 +25577,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25620,7 +25622,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25659,7 +25661,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25688,7 +25690,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25733,7 +25735,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25778,7 +25780,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25797,7 +25799,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25844,7 +25846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -25889,7 +25891,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -25908,7 +25910,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -25931,7 +25933,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -25954,7 +25956,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -25977,7 +25979,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26000,7 +26002,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26023,7 +26025,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26046,7 +26048,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26069,7 +26071,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26092,7 +26094,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26115,7 +26117,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26138,7 +26140,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26161,7 +26163,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26184,7 +26186,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26205,7 +26207,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26226,7 +26228,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26247,7 +26249,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26268,7 +26270,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26289,7 +26291,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26310,7 +26312,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26331,7 +26333,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26354,7 +26356,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26377,7 +26379,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26400,7 +26402,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26423,7 +26425,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26446,7 +26448,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26469,7 +26471,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26492,7 +26494,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26511,7 +26513,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26530,7 +26532,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26549,7 +26551,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26568,7 +26570,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26642,11 +26644,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26678,7 +26679,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26711,7 +26712,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26744,7 +26745,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26777,7 +26778,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26810,7 +26811,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26843,7 +26844,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -26876,7 +26877,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -26909,7 +26910,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -26940,7 +26941,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -26971,7 +26972,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27004,7 +27005,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27037,7 +27038,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27070,7 +27071,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27103,7 +27104,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27136,7 +27137,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27169,7 +27170,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27202,7 +27203,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27235,7 +27236,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27268,7 +27269,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27301,7 +27302,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27334,7 +27335,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27367,7 +27368,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27400,7 +27401,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27433,7 +27434,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27466,7 +27467,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27499,7 +27500,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27531,7 +27532,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27563,7 +27564,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27595,7 +27596,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27627,7 +27628,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27659,7 +27660,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27689,7 +27690,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27719,7 +27720,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27751,7 +27752,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27783,7 +27784,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27815,7 +27816,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27847,7 +27848,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -27879,7 +27880,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -27909,7 +27910,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -27941,7 +27942,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -27973,7 +27974,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28005,7 +28006,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28037,7 +28038,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28067,7 +28068,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28097,7 +28098,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28127,7 +28128,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28157,7 +28158,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28189,7 +28190,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28221,7 +28222,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28251,7 +28252,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28281,7 +28282,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28311,7 +28312,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28341,7 +28342,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28371,7 +28372,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28466,11 +28467,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28502,7 +28502,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28533,7 +28533,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28564,7 +28564,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28595,7 +28595,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28626,7 +28626,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28657,7 +28657,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28688,7 +28688,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28719,7 +28719,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28750,7 +28750,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28781,7 +28781,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28812,7 +28812,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28843,7 +28843,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -28874,7 +28874,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -28905,7 +28905,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -28936,7 +28936,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -28967,7 +28967,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -28998,7 +28998,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29029,7 +29029,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29060,7 +29060,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29091,7 +29091,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29121,7 +29121,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29151,7 +29151,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29181,7 +29181,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29211,7 +29211,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29241,7 +29241,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29271,7 +29271,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29301,7 +29301,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29331,7 +29331,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29361,7 +29361,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29391,7 +29391,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29421,7 +29421,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29451,7 +29451,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29481,7 +29481,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29511,7 +29511,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29541,7 +29541,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29571,7 +29571,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29603,7 +29603,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29635,7 +29635,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29665,7 +29665,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29695,7 +29695,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29725,7 +29725,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29755,7 +29755,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29785,7 +29785,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51528,19 +51528,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51554,7 +51554,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51566,7 +51566,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51577,7 +51577,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51588,7 +51588,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51599,13 +51599,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -6734,7 +6737,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>28</v>
@@ -6749,7 +6752,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6802,7 +6805,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6872,7 +6875,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6940,7 +6943,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7008,7 +7011,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7076,7 +7079,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7144,7 +7147,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7226,7 +7229,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7318,7 +7321,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7386,7 +7389,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7454,7 +7457,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7542,7 +7545,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7612,7 +7615,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7702,7 +7705,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7860,7 +7863,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7928,7 +7931,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -7998,7 +8001,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9388,79 +9391,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" s="43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R2" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T2" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W2" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X2" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" s="47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z2" s="46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA2" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9498,10 +9501,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9512,7 +9515,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="52">
         <v>245679.5</v>
@@ -9586,7 +9589,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9602,7 +9605,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
@@ -9630,7 +9633,7 @@
       <c r="AA5" s="56"/>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9642,7 +9645,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9678,7 +9681,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -9706,7 +9709,7 @@
       <c r="AA7" s="56"/>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9718,7 +9721,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -9754,7 +9757,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9831,7 +9834,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="52">
         <v>129074.86</v>
@@ -9905,7 +9908,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -9921,7 +9924,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -9993,7 +9996,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10005,7 +10008,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10041,7 +10044,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="52"/>
       <c r="E14" s="62"/>
@@ -10069,7 +10072,7 @@
       <c r="AA14" s="56"/>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10081,7 +10084,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="62"/>
@@ -10117,7 +10120,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10194,7 +10197,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10268,7 +10271,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10284,7 +10287,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="52">
         <v>27500.32</v>
@@ -10356,7 +10359,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10368,7 +10371,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10404,7 +10407,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -10432,7 +10435,7 @@
       <c r="AA21" s="56"/>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10444,7 +10447,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -10480,7 +10483,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10557,7 +10560,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10633,7 +10636,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10649,7 +10652,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10721,7 +10724,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -10733,7 +10736,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -10769,7 +10772,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
@@ -10797,7 +10800,7 @@
       <c r="AA28" s="56"/>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -10809,7 +10812,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="55"/>
@@ -10845,7 +10848,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -10922,7 +10925,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="52">
         <v>396422.03</v>
@@ -10996,7 +10999,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11012,7 +11015,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11084,7 +11087,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11096,7 +11099,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11132,7 +11135,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -11160,7 +11163,7 @@
       <c r="AA35" s="56"/>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11172,7 +11175,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -11208,7 +11211,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11285,7 +11288,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11359,7 +11362,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11375,7 +11378,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11447,7 +11450,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11459,7 +11462,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="52"/>
       <c r="E41" s="52"/>
@@ -11495,7 +11498,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -11523,7 +11526,7 @@
       <c r="AA42" s="56"/>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -11535,7 +11538,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -11571,7 +11574,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -11648,7 +11651,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="52">
         <v>65693.36</v>
@@ -11724,7 +11727,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -11740,7 +11743,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -11812,7 +11815,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -11824,7 +11827,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
@@ -11860,7 +11863,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52"/>
@@ -11888,7 +11891,7 @@
       <c r="AA49" s="56"/>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -11900,7 +11903,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
@@ -11936,7 +11939,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12013,7 +12016,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D53" s="52">
         <v>155296.79</v>
@@ -12087,7 +12090,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12103,7 +12106,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D54" s="52">
         <v>155296.79</v>
@@ -12175,7 +12178,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12187,7 +12190,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D55" s="52"/>
       <c r="E55" s="52"/>
@@ -12223,7 +12226,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -12251,7 +12254,7 @@
       <c r="AA56" s="56"/>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -12263,7 +12266,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -12299,7 +12302,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -12376,7 +12379,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -12450,7 +12453,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -12466,7 +12469,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -12538,7 +12541,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -12550,7 +12553,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62" s="52"/>
       <c r="E62" s="52"/>
@@ -12586,7 +12589,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -12614,7 +12617,7 @@
       <c r="AA63" s="56"/>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -12626,7 +12629,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -12662,7 +12665,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -12739,7 +12742,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D67" s="52">
         <v>47801.68</v>
@@ -12811,7 +12814,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -12823,7 +12826,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D68" s="52">
         <v>47801.68</v>
@@ -12895,7 +12898,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -12907,7 +12910,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -12943,7 +12946,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -12971,7 +12974,7 @@
       <c r="AA70" s="56"/>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -12983,7 +12986,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -13019,7 +13022,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -13094,7 +13097,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D74" s="52">
         <v>77166.16</v>
@@ -13168,7 +13171,7 @@
       </c>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -13178,7 +13181,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -13250,7 +13253,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -13260,7 +13263,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D76" s="52"/>
       <c r="E76" s="52"/>
@@ -13296,7 +13299,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -13324,7 +13327,7 @@
       <c r="AA77" s="56"/>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -13336,7 +13339,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -13372,7 +13375,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -13445,7 +13448,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -13519,7 +13522,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -13535,7 +13538,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -13607,7 +13610,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -13619,7 +13622,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -13655,7 +13658,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" s="52"/>
       <c r="E84" s="52"/>
@@ -13683,7 +13686,7 @@
       <c r="AA84" s="56"/>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -13695,7 +13698,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="52"/>
       <c r="E85" s="52"/>
@@ -13731,7 +13734,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -13808,7 +13811,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -13882,7 +13885,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -13898,7 +13901,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -13970,7 +13973,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -13982,7 +13985,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" s="67"/>
       <c r="E90" s="67"/>
@@ -14018,7 +14021,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D91" s="67"/>
       <c r="E91" s="67"/>
@@ -14046,7 +14049,7 @@
       <c r="AA91" s="56"/>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -14058,7 +14061,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="67"/>
       <c r="E92" s="67"/>
@@ -14094,7 +14097,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -14171,7 +14174,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -14245,7 +14248,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -14261,7 +14264,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="52">
         <v>26186.14</v>
@@ -14333,7 +14336,7 @@
       </c>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -14345,7 +14348,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -14381,7 +14384,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D98" s="52"/>
       <c r="E98" s="52"/>
@@ -14409,7 +14412,7 @@
       <c r="AA98" s="56"/>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -14421,7 +14424,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D99" s="52"/>
       <c r="E99" s="52"/>
@@ -14457,7 +14460,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -14534,7 +14537,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" s="52">
         <v>32473.02</v>
@@ -14608,7 +14611,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -14624,7 +14627,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -14696,7 +14699,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -14708,7 +14711,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" s="52"/>
       <c r="E104" s="69"/>
@@ -14744,7 +14747,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D105" s="52"/>
       <c r="E105" s="69"/>
@@ -14772,7 +14775,7 @@
       <c r="AA105" s="56"/>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -14784,7 +14787,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D106" s="52"/>
       <c r="E106" s="69"/>
@@ -14820,7 +14823,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -14894,10 +14897,10 @@
         <v>8840</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D109" s="52">
         <v>58902.56</v>
@@ -14973,7 +14976,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -14989,7 +14992,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -15061,7 +15064,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -15073,7 +15076,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D111" s="52"/>
       <c r="E111" s="52"/>
@@ -15109,7 +15112,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D112" s="52"/>
       <c r="E112" s="52"/>
@@ -15137,7 +15140,7 @@
       <c r="AA112" s="56"/>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -15149,7 +15152,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D113" s="52"/>
       <c r="E113" s="52"/>
@@ -15185,7 +15188,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -15259,10 +15262,10 @@
         <v>8769</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -15338,7 +15341,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -15348,7 +15351,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -15420,7 +15423,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -15430,7 +15433,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -15466,7 +15469,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D119" s="52"/>
       <c r="E119" s="52"/>
@@ -15494,7 +15497,7 @@
       <c r="AA119" s="56"/>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -15506,7 +15509,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D120" s="52"/>
       <c r="E120" s="52"/>
@@ -15542,7 +15545,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -15612,10 +15615,10 @@
         <v>7901</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D123" s="52">
         <v>100987.51</v>
@@ -15687,7 +15690,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -15699,7 +15702,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D124" s="52">
         <v>100987.51</v>
@@ -15771,7 +15774,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -15783,7 +15786,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D125" s="52"/>
       <c r="E125" s="52"/>
@@ -15819,7 +15822,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D126" s="52"/>
       <c r="E126" s="52"/>
@@ -15847,7 +15850,7 @@
       <c r="AA126" s="56"/>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -15859,7 +15862,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D127" s="52"/>
       <c r="E127" s="52"/>
@@ -15895,7 +15898,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -15967,10 +15970,10 @@
         <v>8923</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -16044,7 +16047,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -16060,7 +16063,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D131" s="52">
         <v>31802.41</v>
@@ -16132,7 +16135,7 @@
       </c>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -16144,7 +16147,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -16179,7 +16182,7 @@
     <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D133" s="52"/>
       <c r="E133" s="52"/>
@@ -16207,7 +16210,7 @@
       <c r="AA133" s="56"/>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -16219,7 +16222,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D134" s="52"/>
       <c r="E134" s="52"/>
@@ -16255,7 +16258,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -16329,10 +16332,10 @@
         <v>7864</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D137" s="52">
         <v>30749.24</v>
@@ -16406,7 +16409,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -16422,7 +16425,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D138" s="52">
         <v>30749.24</v>
@@ -16494,7 +16497,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -16506,7 +16509,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D139" s="52"/>
       <c r="E139" s="52"/>
@@ -16542,7 +16545,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D140" s="52"/>
       <c r="E140" s="52"/>
@@ -16570,7 +16573,7 @@
       <c r="AA140" s="56"/>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -16582,7 +16585,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D141" s="52"/>
       <c r="E141" s="52"/>
@@ -16618,7 +16621,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -16692,10 +16695,10 @@
         <v>7912</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -16767,7 +16770,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -16777,7 +16780,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -16849,7 +16852,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -16859,7 +16862,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -16895,7 +16898,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D147" s="52"/>
       <c r="E147" s="52"/>
@@ -16923,7 +16926,7 @@
       <c r="AA147" s="56"/>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -16935,7 +16938,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D148" s="52"/>
       <c r="E148" s="52"/>
@@ -16971,7 +16974,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -17041,10 +17044,10 @@
         <v>8360</v>
       </c>
       <c r="B151" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -17116,7 +17119,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -17132,7 +17135,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -17204,7 +17207,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -17216,7 +17219,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -17252,7 +17255,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D154" s="52"/>
       <c r="E154" s="52"/>
@@ -17280,7 +17283,7 @@
       <c r="AA154" s="56"/>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -17292,7 +17295,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -17328,7 +17331,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -17402,10 +17405,10 @@
         <v>8337</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -17477,7 +17480,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -17491,7 +17494,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -17563,7 +17566,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -17573,7 +17576,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -17609,7 +17612,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -17637,7 +17640,7 @@
       <c r="AA161" s="56"/>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -17649,7 +17652,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -17685,7 +17688,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -17757,10 +17760,10 @@
         <v>9240</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -17780,7 +17783,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -17820,7 +17823,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -17830,7 +17833,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D166" s="52">
         <v>10827.2</v>
@@ -17902,7 +17905,7 @@
       </c>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -17912,7 +17915,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -17948,7 +17951,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -17976,7 +17979,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -17988,7 +17991,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -18024,7 +18027,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -18094,10 +18097,10 @@
         <v>7428</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -18169,7 +18172,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -18183,7 +18186,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -18255,7 +18258,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -18265,7 +18268,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D174" s="52"/>
       <c r="E174" s="52"/>
@@ -18301,7 +18304,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D175" s="52"/>
       <c r="E175" s="52"/>
@@ -18329,7 +18332,7 @@
       <c r="AA175" s="56"/>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -18341,7 +18344,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D176" s="52"/>
       <c r="E176" s="52"/>
@@ -18377,7 +18380,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -18451,10 +18454,10 @@
         <v>9351</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -18526,7 +18529,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -18542,7 +18545,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D180" s="52"/>
       <c r="E180" s="52"/>
@@ -18570,7 +18573,7 @@
       <c r="AA180" s="56"/>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -18582,7 +18585,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -18618,7 +18621,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
@@ -18646,7 +18649,7 @@
       <c r="AA182" s="56"/>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -18658,7 +18661,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
@@ -18694,7 +18697,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -18768,10 +18771,10 @@
         <v>7429</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -18843,7 +18846,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -18857,7 +18860,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -18929,7 +18932,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -18939,7 +18942,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -18975,7 +18978,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D189" s="52"/>
       <c r="E189" s="52"/>
@@ -19003,7 +19006,7 @@
       <c r="AA189" s="56"/>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -19015,7 +19018,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D190" s="52"/>
       <c r="E190" s="52"/>
@@ -19051,7 +19054,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -19123,10 +19126,10 @@
         <v>9508</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -19198,7 +19201,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -19208,7 +19211,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -19280,7 +19283,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -19290,7 +19293,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -19326,7 +19329,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D196" s="52"/>
       <c r="E196" s="52"/>
@@ -19354,7 +19357,7 @@
       <c r="AA196" s="56"/>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -19366,7 +19369,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D197" s="52"/>
       <c r="E197" s="52"/>
@@ -19402,7 +19405,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -19471,7 +19474,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -19519,7 +19522,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -19529,7 +19532,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -19561,7 +19564,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -19571,7 +19574,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -19611,7 +19614,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -19643,7 +19646,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -19655,7 +19658,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -19695,7 +19698,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -19767,10 +19770,10 @@
     <row r="207" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="19"/>
       <c r="B207" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -19802,7 +19805,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -19812,7 +19815,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -19844,7 +19847,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -19854,7 +19857,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -19894,7 +19897,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -19926,7 +19929,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -19938,7 +19941,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -19978,7 +19981,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -20052,10 +20055,10 @@
         <v>8946</v>
       </c>
       <c r="B214" s="77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -20127,7 +20130,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -20137,7 +20140,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -20209,7 +20212,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -20219,7 +20222,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -20255,7 +20258,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -20283,7 +20286,7 @@
       <c r="AA217" s="56"/>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -20295,7 +20298,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -20331,7 +20334,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -20401,10 +20404,10 @@
         <v>8308</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D221" s="52">
         <v>396453.46</v>
@@ -20476,7 +20479,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -20490,7 +20493,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D222" s="52">
         <v>396453.46</v>
@@ -20562,7 +20565,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -20572,7 +20575,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -20608,7 +20611,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -20636,7 +20639,7 @@
       <c r="AA224" s="56"/>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -20648,7 +20651,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -20684,7 +20687,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -21324,49 +21327,49 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F2" s="82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2" s="83" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I2" s="81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" s="82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K2" s="82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L2" s="83" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M2" s="83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N2" s="81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O2" s="84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P2" s="35"/>
     </row>
@@ -21499,7 +21502,7 @@
         <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21648,7 +21651,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="52">
         <v>0</v>
@@ -21690,7 +21693,7 @@
         <v>-93.95999999999987</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21883,7 +21886,7 @@
         <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22322,7 +22325,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="52">
         <v>0</v>
@@ -22384,7 +22387,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -22444,7 +22447,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="52">
         <v>52040.560000000005</v>
@@ -22502,7 +22505,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="52">
         <v>2127.8099999999995</v>
@@ -22564,7 +22567,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="52">
         <v>0</v>
@@ -22624,7 +22627,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="52">
         <v>0</v>
@@ -22678,7 +22681,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -22736,7 +22739,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="99">
         <v>0</v>
@@ -22796,7 +22799,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -22830,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22855,7 +22858,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="99">
         <v>0</v>
@@ -22917,7 +22920,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="99">
         <v>0</v>
@@ -22979,7 +22982,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="99">
         <v>0</v>
@@ -23041,7 +23044,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="99">
         <v>0</v>
@@ -23127,7 +23130,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
@@ -23167,7 +23170,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="99">
         <v>0</v>
@@ -23225,7 +23228,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="98" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="99">
         <v>34650.399999999965</v>
@@ -23301,10 +23304,10 @@
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B69" s="103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C69" s="104">
         <v>88818.76999999996</v>
@@ -23316,13 +23319,13 @@
         <v>58931.02999999998</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G69" s="107">
         <v>0.6634974791927427</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I69" s="109">
         <v>0.0799203816940944</v>
@@ -23337,7 +23340,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -23353,7 +23356,7 @@
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -23752,52 +23755,52 @@
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="117" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" s="117" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H2" s="117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I2" s="117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J2" s="117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K2" s="117" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L2" s="117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M2" s="117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N2" s="117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O2" s="117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P2" s="117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q2" s="118" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -23813,10 +23816,10 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -23900,7 +23903,7 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -23953,7 +23956,7 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24006,7 +24009,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24063,7 +24066,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24090,7 +24093,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -24120,7 +24123,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24177,7 +24180,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24668,7 +24671,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -24718,7 +24721,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -24770,7 +24773,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -24825,7 +24828,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -24879,7 +24882,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -24928,7 +24931,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -24987,7 +24990,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -25035,7 +25038,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -25087,7 +25090,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="54">
         <v>65.13</v>
@@ -25139,7 +25142,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -25194,7 +25197,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -25249,7 +25252,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -25302,7 +25305,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -25392,7 +25395,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -25434,7 +25437,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -25486,7 +25489,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="54">
         <v>2344.68</v>
@@ -25580,7 +25583,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C70" s="147"/>
       <c r="D70" s="147"/>
@@ -25625,7 +25628,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
@@ -25664,7 +25667,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C72" s="20">
         <v>4490.26</v>
@@ -25693,7 +25696,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -25738,7 +25741,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
@@ -25802,10 +25805,10 @@
     <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C76" s="157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -25849,7 +25852,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -25913,7 +25916,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -25925,7 +25928,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -25936,7 +25939,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -25959,7 +25962,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -25982,7 +25985,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -26005,7 +26008,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -26028,7 +26031,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -26051,7 +26054,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -26074,7 +26077,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -26097,7 +26100,7 @@
     <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -26120,7 +26123,7 @@
     <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -26143,7 +26146,7 @@
     <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -26166,7 +26169,7 @@
     <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -26336,7 +26339,7 @@
     <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -26359,7 +26362,7 @@
     <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -26382,7 +26385,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -26405,7 +26408,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -26428,7 +26431,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -26451,7 +26454,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -26474,7 +26477,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -26573,7 +26576,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C109" s="170">
         <v>16.5</v>
@@ -26649,7 +26652,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -26681,7 +26684,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -26714,7 +26717,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -26747,7 +26750,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -26780,7 +26783,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -26813,7 +26816,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -26846,7 +26849,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -26879,7 +26882,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -26974,7 +26977,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -27007,7 +27010,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -27040,7 +27043,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -27073,7 +27076,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -27106,7 +27109,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -27139,7 +27142,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -27172,7 +27175,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -27205,7 +27208,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -27238,7 +27241,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -27271,7 +27274,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -27304,7 +27307,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -27337,7 +27340,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -27370,7 +27373,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -27403,7 +27406,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -27436,7 +27439,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -27469,7 +27472,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -27502,7 +27505,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -27534,7 +27537,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -27566,7 +27569,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -27598,7 +27601,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -27630,7 +27633,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -27722,7 +27725,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -27754,7 +27757,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -27786,7 +27789,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -27818,7 +27821,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -27850,7 +27853,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -27912,7 +27915,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -27944,7 +27947,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -27976,7 +27979,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -28008,7 +28011,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -28160,7 +28163,7 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -28192,7 +28195,7 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -28472,7 +28475,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -29573,7 +29576,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -29605,7 +29608,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -29940,88 +29943,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R2" s="43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" s="43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U2" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V2" s="214" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W2" s="214" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X2" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y2" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA2" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AC2" s="46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD2" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -30062,10 +30065,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AL3" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -30078,7 +30081,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -30174,7 +30177,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -30193,7 +30196,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -30282,7 +30285,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -30301,7 +30304,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -30408,7 +30411,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -30481,7 +30484,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -30499,7 +30502,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -30586,7 +30589,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -30715,7 +30718,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -30804,7 +30807,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -30823,7 +30826,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -30912,7 +30915,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -30931,7 +30934,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -31034,7 +31037,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -31115,7 +31118,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -31133,7 +31136,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -31222,7 +31225,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -31356,7 +31359,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -31449,7 +31452,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -31468,7 +31471,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -31559,7 +31562,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -31578,7 +31581,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -31683,7 +31686,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -31758,7 +31761,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -31776,7 +31779,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -31865,7 +31868,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -31998,7 +32001,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -32091,7 +32094,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -32110,7 +32113,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -32203,7 +32206,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -32222,7 +32225,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -32329,7 +32332,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -32412,7 +32415,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -32430,7 +32433,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -32527,7 +32530,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -32666,7 +32669,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -32757,7 +32760,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -32776,7 +32779,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -32865,7 +32868,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -32884,7 +32887,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -32987,7 +32990,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -33060,7 +33063,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -33078,7 +33081,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -33165,7 +33168,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -33294,7 +33297,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -33381,7 +33384,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -33400,7 +33403,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -33485,7 +33488,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -33504,7 +33507,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -33607,7 +33610,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -33684,7 +33687,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -33702,7 +33705,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -33793,7 +33796,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -33926,7 +33929,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -34019,7 +34022,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -34038,7 +34041,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -34131,7 +34134,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -34150,7 +34153,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -34257,7 +34260,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -34338,7 +34341,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -34356,7 +34359,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -34451,7 +34454,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -34588,7 +34591,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -34681,7 +34684,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -34700,7 +34703,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -34789,7 +34792,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -34808,7 +34811,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -34911,7 +34914,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -34984,7 +34987,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -35002,7 +35005,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -35089,7 +35092,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -35222,7 +35225,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -35313,7 +35316,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -35332,7 +35335,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -35423,7 +35426,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -35442,7 +35445,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -35547,7 +35550,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -35624,7 +35627,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -35642,7 +35645,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -35733,7 +35736,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -35866,7 +35869,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -35955,7 +35958,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -35974,7 +35977,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -36065,7 +36068,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -36084,7 +36087,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -36173,7 +36176,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -36248,7 +36251,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -36266,7 +36269,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -36355,7 +36358,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -36484,7 +36487,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -36577,7 +36580,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -36596,7 +36599,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -36687,7 +36690,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -36706,7 +36709,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -36811,7 +36814,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -36890,7 +36893,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -36908,7 +36911,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -37003,7 +37006,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -37140,7 +37143,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -37233,7 +37236,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -37252,7 +37255,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -37345,7 +37348,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -37364,7 +37367,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -37469,7 +37472,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -37560,7 +37563,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -37578,7 +37581,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -37681,7 +37684,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -37826,7 +37829,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -37919,7 +37922,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -37938,7 +37941,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -38027,7 +38030,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -38046,7 +38049,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -38149,7 +38152,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -38238,7 +38241,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -38256,7 +38259,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -38359,7 +38362,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -38504,7 +38507,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -38597,7 +38600,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -38616,7 +38619,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -38709,7 +38712,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -38728,7 +38731,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -38835,7 +38838,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -38928,7 +38931,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -38946,7 +38949,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -39051,7 +39054,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -39198,7 +39201,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -39289,7 +39292,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -39308,7 +39311,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -39399,7 +39402,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -39418,7 +39421,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -39523,7 +39526,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -39614,7 +39617,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -39632,7 +39635,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -39737,7 +39740,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -39884,7 +39887,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -39976,7 +39979,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -39995,7 +39998,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -40088,7 +40091,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -40107,7 +40110,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -40214,7 +40217,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -40307,7 +40310,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -40325,7 +40328,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -40432,7 +40435,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -40581,7 +40584,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -40674,7 +40677,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -40693,7 +40696,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -40786,7 +40789,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -40805,7 +40808,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -40912,7 +40915,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -41005,7 +41008,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -41023,7 +41026,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -41130,7 +41133,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -41279,7 +41282,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -41371,7 +41374,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -41390,7 +41393,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -41479,7 +41482,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -41498,7 +41501,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -41601,7 +41604,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -41690,7 +41693,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -41708,7 +41711,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -41811,7 +41814,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -41956,7 +41959,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -42049,7 +42052,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -42068,7 +42071,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -42161,7 +42164,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -42180,7 +42183,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -42285,7 +42288,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -42376,7 +42379,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -42394,7 +42397,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -42499,7 +42502,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -42646,7 +42649,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -42739,7 +42742,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -42758,7 +42761,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -42845,7 +42848,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -42864,7 +42867,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -42965,7 +42968,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -43050,7 +43053,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -43068,7 +43071,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -43167,7 +43170,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -43308,7 +43311,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -43397,7 +43400,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -43416,7 +43419,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -43505,7 +43508,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -43524,7 +43527,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -43627,7 +43630,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -43716,7 +43719,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -43734,7 +43737,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -43837,7 +43840,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -43982,7 +43985,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -44071,7 +44074,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -44090,7 +44093,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -44179,7 +44182,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -44198,7 +44201,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -44301,7 +44304,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -44390,7 +44393,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -44408,7 +44411,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -44495,7 +44498,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -44624,7 +44627,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -44711,7 +44714,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -44730,7 +44733,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -44816,7 +44819,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -44835,7 +44838,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -44922,7 +44925,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -44995,7 +44998,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -45013,7 +45016,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -45100,7 +45103,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -45229,7 +45232,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -45318,7 +45321,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -45337,7 +45340,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -45426,7 +45429,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -45445,7 +45448,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -45548,7 +45551,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -45637,7 +45640,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -45655,7 +45658,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -45758,7 +45761,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -45903,7 +45906,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -45990,7 +45993,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -46009,7 +46012,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -46095,7 +46098,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -46114,7 +46117,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -46217,7 +46220,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -46306,7 +46309,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -46324,7 +46327,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -46427,7 +46430,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -46572,7 +46575,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -46659,7 +46662,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -46678,7 +46681,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -46764,7 +46767,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -46783,7 +46786,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -46886,7 +46889,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -46975,7 +46978,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -46993,7 +46996,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -47096,7 +47099,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -47241,7 +47244,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -47328,7 +47331,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -47347,7 +47350,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -47433,7 +47436,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -47452,7 +47455,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -47555,7 +47558,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -47644,7 +47647,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -47662,7 +47665,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -47765,7 +47768,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -47910,7 +47913,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -48001,7 +48004,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -48020,7 +48023,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -48106,7 +48109,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -48125,7 +48128,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -48228,7 +48231,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -48317,7 +48320,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -48335,7 +48338,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -48438,7 +48441,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -48583,7 +48586,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -48670,7 +48673,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -48689,7 +48692,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -48775,7 +48778,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -48794,7 +48797,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -48881,7 +48884,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -48954,7 +48957,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -48972,7 +48975,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -49059,7 +49062,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -49188,7 +49191,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -49275,7 +49278,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -49294,7 +49297,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -49380,7 +49383,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -49399,7 +49402,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -49486,7 +49489,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -49559,7 +49562,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -49577,7 +49580,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -49664,7 +49667,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -49793,7 +49796,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -49880,7 +49883,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -49899,7 +49902,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -49985,7 +49988,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -50004,7 +50007,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -50091,7 +50094,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -50164,7 +50167,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -50182,7 +50185,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -50269,7 +50272,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -50398,7 +50401,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -50485,7 +50488,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -50504,7 +50507,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -50590,7 +50593,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -50609,7 +50612,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -50696,7 +50699,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -50769,7 +50772,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -50787,7 +50790,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -50874,7 +50877,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -51545,18 +51548,18 @@
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -51568,7 +51571,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -51579,7 +51582,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -51590,7 +51593,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6757,7 +6757,9 @@
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
       <c r="T32" s="16"/>
-      <c r="U32" s="1"/>
+      <c r="U32" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5974,18 +5974,30 @@
       <c r="K12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="13"/>
+      <c r="L12" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="M12" s="13" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="14"/>
       <c r="O12" s="18"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="T12" s="16"/>
-      <c r="U12" s="1"/>
+      <c r="U12" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5798,8 +5798,12 @@
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>

--- a/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -5804,7 +5801,9 @@
       <c r="G8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -6747,13 +6746,13 @@
         <v>27</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I32" s="13" t="s">
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>28</v>
@@ -6768,7 +6767,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6823,7 +6822,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6893,7 +6892,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6961,7 +6960,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7029,7 +7028,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7097,7 +7096,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7165,7 +7164,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7247,7 +7246,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7339,7 +7338,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7407,7 +7406,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7475,7 +7474,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7563,7 +7562,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7633,7 +7632,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7723,7 +7722,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7881,7 +7880,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7949,7 +7948,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -8019,7 +8018,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9409,79 +9408,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="E2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="I2" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="43" t="s">
+      <c r="P2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="43" t="s">
+      <c r="Q2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="R2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="S2" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="T2" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="U2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="45" t="s">
+      <c r="V2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="W2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="X2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="Y2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Z2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="AA2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AA2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9519,10 +9518,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AI3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9533,7 +9532,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>245679.5</v>
@@ -9607,7 +9606,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9623,7 +9622,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
@@ -9651,7 +9650,7 @@
       <c r="AA5" s="56"/>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9663,7 +9662,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9699,7 +9698,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -9727,7 +9726,7 @@
       <c r="AA7" s="56"/>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9739,7 +9738,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -9775,7 +9774,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9852,7 +9851,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="52">
         <v>129074.86</v>
@@ -9926,7 +9925,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -9942,7 +9941,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -10014,7 +10013,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10026,7 +10025,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10062,7 +10061,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="52"/>
       <c r="E14" s="62"/>
@@ -10090,7 +10089,7 @@
       <c r="AA14" s="56"/>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10102,7 +10101,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="62"/>
@@ -10138,7 +10137,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10215,7 +10214,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10305,7 +10304,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52">
         <v>27500.32</v>
@@ -10377,7 +10376,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
     